--- a/Investment_Research_Dashboard.xlsx
+++ b/Investment_Research_Dashboard.xlsx
@@ -188,7 +188,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DashboardTable" displayName="DashboardTable" ref="A1:R25" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DashboardTable" displayName="DashboardTable" ref="A1:R26" headerRowCount="1">
   <autoFilter ref="A1:R2"/>
   <tableColumns count="18">
     <tableColumn id="1" name="Ticker"/>
@@ -215,7 +215,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WatchlistTable" displayName="WatchlistTable" ref="A1:I25" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WatchlistTable" displayName="WatchlistTable" ref="A1:I26" headerRowCount="1">
   <autoFilter ref="A1:I2"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Ticker"/>
@@ -233,7 +233,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ValuationTable" displayName="ValuationTable" ref="A1:R25" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ValuationTable" displayName="ValuationTable" ref="A1:R26" headerRowCount="1">
   <autoFilter ref="A1:R2"/>
   <tableColumns count="18">
     <tableColumn id="1" name="Ticker"/>
@@ -260,7 +260,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="RatiosTable" displayName="RatiosTable" ref="A1:Q149" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="RatiosTable" displayName="RatiosTable" ref="A1:Q156" headerRowCount="1">
   <autoFilter ref="A1:Q7"/>
   <tableColumns count="17">
     <tableColumn id="1" name="Ticker"/>
@@ -286,7 +286,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FinancialsTable" displayName="FinancialsTable" ref="A1:Y149" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FinancialsTable" displayName="FinancialsTable" ref="A1:Y156" headerRowCount="1">
   <autoFilter ref="A1:Y7"/>
   <tableColumns count="25">
     <tableColumn id="1" name="Ticker"/>
@@ -320,7 +320,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="NewsTable" displayName="NewsTable" ref="A1:I229" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="NewsTable" displayName="NewsTable" ref="A1:I238" headerRowCount="1">
   <autoFilter ref="A1:I11"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Date"/>
@@ -338,7 +338,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="NarrativeTable" displayName="NarrativeTable" ref="A1:P24" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="NarrativeTable" displayName="NarrativeTable" ref="A1:P25" headerRowCount="1">
   <autoFilter ref="A1:P2"/>
   <tableColumns count="16">
     <tableColumn id="1" name="Ticker"/>
@@ -651,8 +651,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:R26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -664,14 +664,14 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="21" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -2423,6 +2423,74 @@
         </is>
       </c>
       <c r="R25" s="10" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GameStop Corp.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Specialty Retail</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>GameStop Corp., a specialty retailer, provides games, collectibles, and entertainment products through its stores and e-commerce platforms in United States, Australia and Europe. The company sells new and pre-owned gaming platforms; accessories, such as controllers, gaming headsets, and other peripheral devices; new and pre-owned gaming software; and in-game digital currency, digital downloadable content, and full-game downloads. It also sells collectibles comprising apparel, toys, trading cards, gadgets, and other retail products for pop culture and technology enthusiasts. The company operates stores and e-commerce sites under the GameStop, EB Games, and Micromania brands; and pop culture themed stores that sell collectibles, apparel, gadgets, electronics, toys, and other retail products under the Zing Pop Culture brand. The company was formerly known as GSC Holdings Corp. GameStop Corp. was founded in 1996 and is based in Grapevine, Texas.</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>21.995</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>9868964864</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>16.414179</v>
+      </c>
+      <c r="I26" s="9" t="n">
+        <v>18.177687</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n">
+        <v>0.1404969961769525</v>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>0.466419250568658</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>0.1306379555296897</v>
+      </c>
+      <c r="O26" s="9" t="n">
+        <v>0.7427294979545027</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Fairly Valued</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>GameStop is best understood as a hybrid of a declining specialty retailer and a cash-rich capital-allocation vehicle. The operating business has stabilized and become profitable, with genuinely improv...</t>
+        </is>
+      </c>
+      <c r="R26" s="10" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -2709,6 +2777,17 @@
       <formula>"Fairly Valued"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P26">
+    <cfRule type="cellIs" priority="79" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="80" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="81" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2722,8 +2801,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -3215,6 +3294,24 @@
       </c>
       <c r="G25" s="8" t="n"/>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GameStop Corp.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -3229,11 +3326,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:R26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -3245,7 +3342,7 @@
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
@@ -4730,6 +4827,62 @@
       </c>
       <c r="R25" s="7" t="n">
         <v>2279755</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>21.995</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>9868964864</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>6183213056</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>448691257</v>
+      </c>
+      <c r="G26" s="9" t="n">
+        <v>16.414179</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>18.177687</v>
+      </c>
+      <c r="I26" s="9" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>2.6438503</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>1.6893241</v>
+      </c>
+      <c r="L26" s="9" t="n">
+        <v>1.656</v>
+      </c>
+      <c r="M26" s="9" t="n">
+        <v>14.997</v>
+      </c>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="P26" s="8" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="Q26" s="8" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="R26" s="7" t="n">
+        <v>7510416</v>
       </c>
     </row>
   </sheetData>
@@ -4746,8 +4899,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q149"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:Q156"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
@@ -4755,17 +4908,17 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
     <col width="21" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -11427,6 +11580,303 @@
         <v>7.828327922077922</v>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Q4 2024</t>
+        </is>
+      </c>
+      <c r="C150" s="10" t="n">
+        <v>45596</v>
+      </c>
+      <c r="D150" s="5" t="n"/>
+      <c r="E150" s="5" t="n"/>
+      <c r="F150" s="5" t="n"/>
+      <c r="G150" s="5" t="n"/>
+      <c r="H150" s="5" t="n"/>
+      <c r="I150" s="5" t="n"/>
+      <c r="J150" s="5" t="n"/>
+      <c r="K150" s="9" t="n"/>
+      <c r="L150" s="9" t="n"/>
+      <c r="M150" s="9" t="n"/>
+      <c r="N150" s="5" t="n"/>
+      <c r="O150" s="5" t="n"/>
+      <c r="P150" s="5" t="n"/>
+      <c r="Q150" s="9" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
+      <c r="C151" s="10" t="n">
+        <v>45688</v>
+      </c>
+      <c r="D151" s="5" t="n"/>
+      <c r="E151" s="5" t="n"/>
+      <c r="F151" s="5" t="n"/>
+      <c r="G151" s="5" t="n"/>
+      <c r="H151" s="5" t="n"/>
+      <c r="I151" s="5" t="n"/>
+      <c r="J151" s="5" t="n"/>
+      <c r="K151" s="9" t="n"/>
+      <c r="L151" s="9" t="n"/>
+      <c r="M151" s="9" t="n"/>
+      <c r="N151" s="5" t="n"/>
+      <c r="O151" s="5" t="n"/>
+      <c r="P151" s="5" t="n"/>
+      <c r="Q151" s="9" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Q2 2025</t>
+        </is>
+      </c>
+      <c r="C152" s="10" t="n">
+        <v>45777</v>
+      </c>
+      <c r="D152" s="5" t="n">
+        <v>0.3451665756417258</v>
+      </c>
+      <c r="E152" s="5" t="n">
+        <v>0.03372474057891862</v>
+      </c>
+      <c r="F152" s="5" t="n">
+        <v>0.06116876024030585</v>
+      </c>
+      <c r="G152" s="5" t="n">
+        <v>0.2588749317312944</v>
+      </c>
+      <c r="H152" s="5" t="n"/>
+      <c r="I152" s="5" t="n"/>
+      <c r="J152" s="5" t="n"/>
+      <c r="K152" s="9" t="n">
+        <v>0.3532501904800096</v>
+      </c>
+      <c r="L152" s="9" t="n">
+        <v>8.387466068688775</v>
+      </c>
+      <c r="M152" s="9" t="n">
+        <v>7.890239584562728</v>
+      </c>
+      <c r="N152" s="5" t="n"/>
+      <c r="O152" s="5" t="n"/>
+      <c r="P152" s="5" t="n"/>
+      <c r="Q152" s="9" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Q3 2025</t>
+        </is>
+      </c>
+      <c r="C153" s="10" t="n">
+        <v>45869</v>
+      </c>
+      <c r="D153" s="5" t="n">
+        <v>0.2911952273194816</v>
+      </c>
+      <c r="E153" s="5" t="n">
+        <v>0.06613865459781938</v>
+      </c>
+      <c r="F153" s="5" t="n">
+        <v>0.1734211067681547</v>
+      </c>
+      <c r="G153" s="5" t="n">
+        <v>0.1165398066241514</v>
+      </c>
+      <c r="H153" s="5" t="n">
+        <v>0.3274167121791371</v>
+      </c>
+      <c r="I153" s="5" t="n"/>
+      <c r="J153" s="5" t="n"/>
+      <c r="K153" s="9" t="n">
+        <v>0.853469592767174</v>
+      </c>
+      <c r="L153" s="9" t="n">
+        <v>11.3729364983733</v>
+      </c>
+      <c r="M153" s="9" t="n">
+        <v>10.78864923484757</v>
+      </c>
+      <c r="N153" s="5" t="n"/>
+      <c r="O153" s="5" t="n"/>
+      <c r="P153" s="5" t="n"/>
+      <c r="Q153" s="9" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
+      <c r="C154" s="10" t="n">
+        <v>45961</v>
+      </c>
+      <c r="D154" s="5" t="n">
+        <v>0.3330085261875761</v>
+      </c>
+      <c r="E154" s="5" t="n">
+        <v>0.06333739342265529</v>
+      </c>
+      <c r="F154" s="5" t="n">
+        <v>0.09390986601705238</v>
+      </c>
+      <c r="G154" s="5" t="n">
+        <v>0.1303288672350792</v>
+      </c>
+      <c r="H154" s="5" t="n">
+        <v>-0.1555235548241103</v>
+      </c>
+      <c r="I154" s="5" t="n"/>
+      <c r="J154" s="5" t="n"/>
+      <c r="K154" s="9" t="n">
+        <v>0.8281161606637752</v>
+      </c>
+      <c r="L154" s="9" t="n">
+        <v>10.39071214071214</v>
+      </c>
+      <c r="M154" s="9" t="n">
+        <v>9.773487773487773</v>
+      </c>
+      <c r="N154" s="5" t="n"/>
+      <c r="O154" s="5" t="n"/>
+      <c r="P154" s="5" t="n"/>
+      <c r="Q154" s="9" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Q1 2026</t>
+        </is>
+      </c>
+      <c r="C155" s="10" t="n">
+        <v>46053</v>
+      </c>
+      <c r="D155" s="5" t="n">
+        <v>0.3502671375532011</v>
+      </c>
+      <c r="E155" s="5" t="n">
+        <v>0.1312143439282804</v>
+      </c>
+      <c r="F155" s="5" t="n">
+        <v>0.1158199764556733</v>
+      </c>
+      <c r="G155" s="5" t="n">
+        <v>0.1697002626097981</v>
+      </c>
+      <c r="H155" s="5" t="n">
+        <v>0.3450669914738124</v>
+      </c>
+      <c r="I155" s="5" t="n"/>
+      <c r="J155" s="5" t="n"/>
+      <c r="K155" s="9" t="n">
+        <v>0.8011718463007861</v>
+      </c>
+      <c r="L155" s="9" t="n">
+        <v>15.29656226126814</v>
+      </c>
+      <c r="M155" s="9" t="n">
+        <v>14.6803666921314</v>
+      </c>
+      <c r="N155" s="5" t="n">
+        <v>0.07684960693556682</v>
+      </c>
+      <c r="O155" s="5" t="n">
+        <v>0.04027569211813176</v>
+      </c>
+      <c r="P155" s="5" t="n">
+        <v>0.06450222755311857</v>
+      </c>
+      <c r="Q155" s="9" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="C156" s="10" t="n">
+        <v>46142</v>
+      </c>
+      <c r="D156" s="5" t="n">
+        <v>0.4073985394469053</v>
+      </c>
+      <c r="E156" s="5" t="n">
+        <v>0.1660481264216449</v>
+      </c>
+      <c r="F156" s="5" t="n">
+        <v>0.466419250568658</v>
+      </c>
+      <c r="G156" s="5" t="n">
+        <v>0.3985394469053035</v>
+      </c>
+      <c r="H156" s="5" t="n">
+        <v>-0.2435932264783121</v>
+      </c>
+      <c r="I156" s="5" t="n">
+        <v>0.1404969961769525</v>
+      </c>
+      <c r="J156" s="5" t="n">
+        <v>6.333333333333334</v>
+      </c>
+      <c r="K156" s="9" t="n">
+        <v>0.7427294979545027</v>
+      </c>
+      <c r="L156" s="9" t="n">
+        <v>12.40090666046728</v>
+      </c>
+      <c r="M156" s="9" t="n">
+        <v>11.90886899918633</v>
+      </c>
+      <c r="N156" s="5" t="n">
+        <v>0.1306379555296897</v>
+      </c>
+      <c r="O156" s="5" t="n">
+        <v>0.0695442989530084</v>
+      </c>
+      <c r="P156" s="5" t="n">
+        <v>0.1134936772524788</v>
+      </c>
+      <c r="Q156" s="9" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -11441,32 +11891,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y149"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:Y156"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
-    <col width="17" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
     <col width="21" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
     <col width="21" customWidth="1" min="21" max="21"/>
     <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="17" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
     <col width="21" customWidth="1" min="24" max="24"/>
     <col width="21" customWidth="1" min="25" max="25"/>
   </cols>
@@ -22172,6 +22622,475 @@
         <v>47600000</v>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Q4 2024</t>
+        </is>
+      </c>
+      <c r="C150" s="10" t="n">
+        <v>45596</v>
+      </c>
+      <c r="D150" s="3" t="n"/>
+      <c r="E150" s="3" t="n"/>
+      <c r="F150" s="3" t="n"/>
+      <c r="G150" s="3" t="n"/>
+      <c r="H150" s="3" t="n"/>
+      <c r="I150" s="3" t="n"/>
+      <c r="J150" s="8" t="n"/>
+      <c r="K150" s="8" t="n"/>
+      <c r="L150" s="3" t="n"/>
+      <c r="M150" s="3" t="n"/>
+      <c r="N150" s="3" t="n"/>
+      <c r="O150" s="3" t="n"/>
+      <c r="P150" s="3" t="n"/>
+      <c r="Q150" s="3" t="n"/>
+      <c r="R150" s="3" t="n"/>
+      <c r="S150" s="3" t="n"/>
+      <c r="T150" s="3" t="n"/>
+      <c r="U150" s="3" t="n"/>
+      <c r="V150" s="3" t="n"/>
+      <c r="W150" s="3" t="n"/>
+      <c r="X150" s="3" t="n"/>
+      <c r="Y150" s="3" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
+      <c r="C151" s="10" t="n">
+        <v>45688</v>
+      </c>
+      <c r="D151" s="3" t="n"/>
+      <c r="E151" s="3" t="n"/>
+      <c r="F151" s="3" t="n"/>
+      <c r="G151" s="3" t="n"/>
+      <c r="H151" s="3" t="n"/>
+      <c r="I151" s="3" t="n"/>
+      <c r="J151" s="8" t="n"/>
+      <c r="K151" s="8" t="n"/>
+      <c r="L151" s="3" t="n"/>
+      <c r="M151" s="3" t="n"/>
+      <c r="N151" s="3" t="n"/>
+      <c r="O151" s="3" t="n"/>
+      <c r="P151" s="3" t="n"/>
+      <c r="Q151" s="3" t="n"/>
+      <c r="R151" s="3" t="n"/>
+      <c r="S151" s="3" t="n"/>
+      <c r="T151" s="3" t="n"/>
+      <c r="U151" s="3" t="n"/>
+      <c r="V151" s="3" t="n"/>
+      <c r="W151" s="3" t="n"/>
+      <c r="X151" s="3" t="n"/>
+      <c r="Y151" s="3" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Q2 2025</t>
+        </is>
+      </c>
+      <c r="C152" s="10" t="n">
+        <v>45777</v>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>732400000</v>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>252800000</v>
+      </c>
+      <c r="F152" s="3" t="n">
+        <v>24700000</v>
+      </c>
+      <c r="G152" s="3" t="n">
+        <v>24700000</v>
+      </c>
+      <c r="H152" s="3" t="n">
+        <v>30300000</v>
+      </c>
+      <c r="I152" s="3" t="n">
+        <v>44800000</v>
+      </c>
+      <c r="J152" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K152" s="8" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L152" s="3" t="n"/>
+      <c r="M152" s="3" t="n">
+        <v>6385800000</v>
+      </c>
+      <c r="N152" s="3" t="n">
+        <v>7502600000</v>
+      </c>
+      <c r="O152" s="3" t="n">
+        <v>7106700000</v>
+      </c>
+      <c r="P152" s="3" t="n">
+        <v>1761800000</v>
+      </c>
+      <c r="Q152" s="3" t="n">
+        <v>1480700000</v>
+      </c>
+      <c r="R152" s="3" t="n">
+        <v>4987400000</v>
+      </c>
+      <c r="S152" s="3" t="n">
+        <v>847300000</v>
+      </c>
+      <c r="T152" s="3" t="n">
+        <v>421300000</v>
+      </c>
+      <c r="U152" s="3" t="n">
+        <v>192500000</v>
+      </c>
+      <c r="V152" s="3" t="n">
+        <v>-2900000</v>
+      </c>
+      <c r="W152" s="3" t="n">
+        <v>189600000</v>
+      </c>
+      <c r="X152" s="3" t="n">
+        <v>7300000</v>
+      </c>
+      <c r="Y152" s="3" t="n">
+        <v>1478000000</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Q3 2025</t>
+        </is>
+      </c>
+      <c r="C153" s="10" t="n">
+        <v>45869</v>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>972200000</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>283100000</v>
+      </c>
+      <c r="F153" s="3" t="n">
+        <v>64300000</v>
+      </c>
+      <c r="G153" s="3" t="n">
+        <v>64300000</v>
+      </c>
+      <c r="H153" s="3" t="n">
+        <v>69000000</v>
+      </c>
+      <c r="I153" s="3" t="n">
+        <v>168600000</v>
+      </c>
+      <c r="J153" s="8" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K153" s="8" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="L153" s="3" t="n"/>
+      <c r="M153" s="3" t="n">
+        <v>8694400000</v>
+      </c>
+      <c r="N153" s="3" t="n">
+        <v>10341100000</v>
+      </c>
+      <c r="O153" s="3" t="n">
+        <v>9438400000</v>
+      </c>
+      <c r="P153" s="3" t="n">
+        <v>4417900000</v>
+      </c>
+      <c r="Q153" s="3" t="n">
+        <v>4160900000</v>
+      </c>
+      <c r="R153" s="3" t="n">
+        <v>5176400000</v>
+      </c>
+      <c r="S153" s="3" t="n">
+        <v>829900000</v>
+      </c>
+      <c r="T153" s="3" t="n">
+        <v>484900000</v>
+      </c>
+      <c r="U153" s="3" t="n">
+        <v>117400000</v>
+      </c>
+      <c r="V153" s="3" t="n">
+        <v>-4100000</v>
+      </c>
+      <c r="W153" s="3" t="n">
+        <v>113300000</v>
+      </c>
+      <c r="X153" s="3" t="n">
+        <v>-523300000</v>
+      </c>
+      <c r="Y153" s="3" t="n">
+        <v>2675300000</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
+      <c r="C154" s="10" t="n">
+        <v>45961</v>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>821000000</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>273400000</v>
+      </c>
+      <c r="F154" s="3" t="n">
+        <v>52000000</v>
+      </c>
+      <c r="G154" s="3" t="n">
+        <v>52000000</v>
+      </c>
+      <c r="H154" s="3" t="n">
+        <v>56600000</v>
+      </c>
+      <c r="I154" s="3" t="n">
+        <v>77100000</v>
+      </c>
+      <c r="J154" s="8" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K154" s="8" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L154" s="3" t="n"/>
+      <c r="M154" s="3" t="n">
+        <v>7842700000</v>
+      </c>
+      <c r="N154" s="3" t="n">
+        <v>10550700000</v>
+      </c>
+      <c r="O154" s="3" t="n">
+        <v>9688300000</v>
+      </c>
+      <c r="P154" s="3" t="n">
+        <v>4391500000</v>
+      </c>
+      <c r="Q154" s="3" t="n">
+        <v>4162600000</v>
+      </c>
+      <c r="R154" s="3" t="n">
+        <v>5303000000</v>
+      </c>
+      <c r="S154" s="3" t="n">
+        <v>932400000</v>
+      </c>
+      <c r="T154" s="3" t="n">
+        <v>575500000</v>
+      </c>
+      <c r="U154" s="3" t="n">
+        <v>111300000</v>
+      </c>
+      <c r="V154" s="3" t="n">
+        <v>-4300000</v>
+      </c>
+      <c r="W154" s="3" t="n">
+        <v>107000000</v>
+      </c>
+      <c r="X154" s="3" t="n">
+        <v>-979900000</v>
+      </c>
+      <c r="Y154" s="3" t="n">
+        <v>-3300000</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Q1 2026</t>
+        </is>
+      </c>
+      <c r="C155" s="10" t="n">
+        <v>46053</v>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>1104300000</v>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>386800000</v>
+      </c>
+      <c r="F155" s="3" t="n">
+        <v>144900000</v>
+      </c>
+      <c r="G155" s="3" t="n">
+        <v>144900000</v>
+      </c>
+      <c r="H155" s="3" t="n">
+        <v>144900000</v>
+      </c>
+      <c r="I155" s="3" t="n">
+        <v>127900000</v>
+      </c>
+      <c r="J155" s="8" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K155" s="8" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L155" s="3" t="n"/>
+      <c r="M155" s="3" t="n">
+        <v>6304700000</v>
+      </c>
+      <c r="N155" s="3" t="n">
+        <v>10388400000</v>
+      </c>
+      <c r="O155" s="3" t="n">
+        <v>10011600000</v>
+      </c>
+      <c r="P155" s="3" t="n">
+        <v>4361900000</v>
+      </c>
+      <c r="Q155" s="3" t="n">
+        <v>4164300000</v>
+      </c>
+      <c r="R155" s="3" t="n">
+        <v>5444400000</v>
+      </c>
+      <c r="S155" s="3" t="n">
+        <v>654500000</v>
+      </c>
+      <c r="T155" s="3" t="n">
+        <v>403300000</v>
+      </c>
+      <c r="U155" s="3" t="n">
+        <v>193600000</v>
+      </c>
+      <c r="V155" s="3" t="n">
+        <v>-6200000</v>
+      </c>
+      <c r="W155" s="3" t="n">
+        <v>187400000</v>
+      </c>
+      <c r="X155" s="3" t="n">
+        <v>-1713900000</v>
+      </c>
+      <c r="Y155" s="3" t="n">
+        <v>-3800000</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="C156" s="10" t="n">
+        <v>46142</v>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>835300000</v>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>340300000</v>
+      </c>
+      <c r="F156" s="3" t="n">
+        <v>138700000</v>
+      </c>
+      <c r="G156" s="3" t="n">
+        <v>138700000</v>
+      </c>
+      <c r="H156" s="3" t="n">
+        <v>143200000</v>
+      </c>
+      <c r="I156" s="3" t="n">
+        <v>389600000</v>
+      </c>
+      <c r="J156" s="8" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K156" s="8" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L156" s="3" t="n"/>
+      <c r="M156" s="3" t="n">
+        <v>7397600000</v>
+      </c>
+      <c r="N156" s="3" t="n">
+        <v>10974300000</v>
+      </c>
+      <c r="O156" s="3" t="n">
+        <v>10668500000</v>
+      </c>
+      <c r="P156" s="3" t="n">
+        <v>4339100000</v>
+      </c>
+      <c r="Q156" s="3" t="n">
+        <v>4166100000</v>
+      </c>
+      <c r="R156" s="3" t="n">
+        <v>5842100000</v>
+      </c>
+      <c r="S156" s="3" t="n">
+        <v>860300000</v>
+      </c>
+      <c r="T156" s="3" t="n">
+        <v>423300000</v>
+      </c>
+      <c r="U156" s="3" t="n">
+        <v>337400000</v>
+      </c>
+      <c r="V156" s="3" t="n">
+        <v>-4500000</v>
+      </c>
+      <c r="W156" s="3" t="n">
+        <v>332900000</v>
+      </c>
+      <c r="X156" s="3" t="n">
+        <v>742900000</v>
+      </c>
+      <c r="Y156" s="3" t="n">
+        <v>1500000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -22186,8 +23105,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I229"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:I238"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
@@ -32507,6 +33426,411 @@
         </is>
       </c>
     </row>
+    <row r="230">
+      <c r="A230" s="10" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Trading Cards Are the New Lottery Tickets. ‘Brother, It’s Gambling!’</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Barrons.com</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>https://www.barrons.com/articles/pokemon-baseball-cards-gambling-8ebdf1be?siteid=yhoof2&amp;yptr=yahoo</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>GameStop Corp.</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>GameStop's pivot into trading cards taps a lucrative, gambling-like consumer trend, but regulatory scrutiny of that dynamic poses potential long-term risk.</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="10" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>GameStop (GME) Keeps Chasing EBay As Ryan Cohen Drops Award And Targets Rise</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Simply Wall St.</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/gamestop-gme-keeps-chasing-ebay-050724446.html</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>GameStop Corp.</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>A major diversification via eBay acquisition and Cohen's award withdrawal signal strategic transformation and improved governance alignment for long-term shareholders.</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="10" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>GameStop (GME) Stock Looks Undervalued On Earnings But Mixed On Fair Value</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Simply Wall St.</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/gamestop-gme-stock-looks-undervalued-191548294.html</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>GameStop Corp.</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Conflicting valuation signals mean investors should weigh earnings strength against long-term price decline before assuming a durable recovery.</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Earnings</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="10" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Is the Clock Ticking on GameStop Stock?</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Motley Fool</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/investing/2026/07/02/is-the-clock-ticking-on-gamestop-stock/</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>GameStop Corp.</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>The industry shift toward digital game distribution threatens GameStop's core physical retail business, raising concerns about long-term revenue viability.</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="10" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Sony to cease physical PlayStation disc production in 2028</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Yahoo Finance Video</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/video/sony-cease-physical-playstation-disc-201500457.html</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>GameStop Corp.</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>The decline of physical game discs threatens GameStop's core retail model, reducing foot traffic and pre-owned game sales that drive margins.</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="10" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Is The Jack In The Box Short Squeeze Back On?</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Investor's Business Daily</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>https://www.investors.com/news/jack-in-the-box-short-squeeze-wendys-reddit-retail-investors/?src=A00220&amp;yptr=yahoo</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>GameStop Corp.</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>This headline concerns Jack in the Box, not GameStop, so it holds no direct relevance for a long-term GME investor.</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="10" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Musk Meme Traders Rush Back Into Tesla When the Stock Hits $420</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/musk-meme-traders-rush-back-194156049.html</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>GameStop Corp.</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>This headline concerns Tesla retail trading behavior and has no direct relevance to GME's business or long-term fundamentals.</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="10" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Sony to end PlayStation disc production in January 2028</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Investing.com</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/media-advertising/articles/sony-end-playstation-disc-production-141328232.html</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>GameStop Corp.</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>The accelerating shift to digital game distribution threatens GameStop's core physical software and used-game resale business, eroding a key long-term revenue stream.</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="10" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Global M&amp;A Tops $2.5 Trillion After First-Half Deals Surge</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/global-m-tops-2-5-040001637.html</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>GameStop Corp.</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>This macro report on global M&amp;A activity has no direct connection to GME's fundamentals or business outlook.</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -32521,11 +33845,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:P25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
@@ -34326,6 +35650,80 @@
         <v>68</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>GameStop is a specialty retailer of physical games, hardware, and collectibles that has been transforming into a cash-rich holding entity under Ryan Cohen. The operating business remains modest in scale (roughly $3.5B trailing revenue) but has swung to consistent profitability across the last several quarters, aided by aggressive cost cutting and a shift toward higher-margin collectibles and trading cards. The dominant feature of the balance sheet is an enormous cash and investment position (over $7.3B against a market cap of ~$9.9B and enterprise value of only ~$6.2B), largely funded by equity issuance and convertible debt. Recent quarters show real operating income (Q2 2026 operating margin of ~16.6%), though headline net income is heavily distorted by non-operating items such as investment gains and possibly one-time items (Q2 2026 net margin of 46.6% far exceeds operating margin). The core retail thesis faces a genuine structural headwind: Sony's announced end of physical PlayStation disc production by 2028 accelerates the decline of the pre-owned and physical software business that historically drove margins. Management is diversifying into trading cards and reportedly pursuing an eBay-adjacent marketplace strategy. The stock trades near the low end of its 52-week range. This remains a business in transition where the investment case depends more on capital allocation of the cash hoard than on the durability of the legacy retail operation.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>No previous analysis exists, so the most material items are: (1) Sony's confirmed decision to cease physical PlayStation disc production in January 2028, a direct structural threat to GameStop's core physical software and lucrative pre-owned game resale margins. (2) A strategic push into trading cards, which taps a fast-growing, high-margin collectibles trend but carries potential regulatory risk given the gambling-like dynamics being scrutinized. (3) Reported strategic moves suggesting a marketplace/e-commerce diversification (framed as chasing eBay) alongside governance signals from Ryan Cohen. (4) The financial data itself shows the business has stabilized into profitability with expanding operating margins over the trailing quarters, funded and buttressed by a massive cash and investments position that now dwarfs the operating business. The combination of improving operating economics and an existential threat to the legacy revenue base is the central tension.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>The strongest bull argument is optionality on the balance sheet: with roughly $7.3B in cash and investments against a ~$6.2B enterprise value, the market is effectively assigning near-zero or negative value to the operating business. If Cohen deploys that capital into accretive acquisitions or high-return investments, per-share value could compound meaningfully. Operating fundamentals have genuinely improved — the company is now consistently profitable, gross margins have expanded (Q2 2026 gross margin ~40.7% vs ~29-35% in prior quarters) as the mix shifts toward collectibles and trading cards, and operating margin reached ~16.6% in the most recent quarter. The trading card business is a legitimate secular growth vector with attractive economics and existing store infrastructure to leverage. Free cash flow has been positive and substantial ($333M in Q2 2026). The balance sheet is fortress-like (current ratio above 12x, minimal operating leverage risk). A leaner store base and reduced cash burn mean the company is no longer fighting for survival, giving management time to execute a transformation.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>The core retail business is in structural decline. Sony ending physical disc production by 2028 removes a pillar of the pre-owned/physical software model that generated GameStop's best margins and drove store traffic. The broader industry shift to digital distribution is secular and irreversible, and there is no evidence GameStop has a defensible position in digital or a differentiated moat in collectibles or trading cards, which are competitive, fragmented, and potentially subject to fad dynamics and regulatory scrutiny. The dramatic Q2 2026 net income ($389.6M, 46.6% net margin) far exceeds operating income ($138.7M), indicating earnings are inflated by non-operating gains that are not repeatable — the headline P/E of ~16x is therefore misleading. The company's value is increasingly that of a closed-end investment vehicle rather than an operating retailer, and that cash was substantially raised via equity dilution (financing inflows and rising share counts). Returns on capital remain modest (ROIC ~11%, ROE ~13%, and much of that is cash-driven). If capital is deployed poorly or sits idle, shareholders earn low returns while paying a premium to book. Beta of 1.76 and meme-driven trading history add volatility unrelated to fundamentals.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>The balance sheet is exceptionally strong on a liquidity basis: over $7.3B in cash/investments, current ratio above 12x, and inventory kept lean (~$423M). Total debt of ~$4.3B is largely long-term (likely low-coupon convertibles) and is more than covered by cash. Revenue quality is mixed — top line is roughly flat-to-modestly-growing (Q2 2026 revenue +14% YoY but down QoQ, with meaningful seasonality), while margin improvement is real at the operating level (gross margin expanding to ~40%, operating margin to ~16.6%). However, net income is distorted by non-operating investment gains, so reported net margins (46.6% in Q2 2026) overstate the durable earnings power; operating margin is the more honest gauge. Free cash flow is genuinely positive and healthy across recent quarters. Capital allocation is the key uncertainty: the cash was accumulated partly through equity issuance (dilution), and the return on that capital depends entirely on future deployment. No dividend. Returns on capital are modest (ROIC ~6-11%, ROE ~8-13%), reflecting a large low-yielding cash base. Debt is sustainable given the cash cushion.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Fairly Valued</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>The headline P/E of ~16x and forward P/E of ~18x are misleading because trailing net income is inflated by non-operating investment gains that are not part of the recurring operating engine. A cleaner lens is enterprise value: EV of ~$6.2B against a business generating roughly $200-550M in annualized operating income implies an EV/EBIT in the mid-teens to low-20s for a business with structural revenue headwinds — not cheap on operating fundamentals alone. However, the P/B of ~1.69x is the more relevant frame given the company is effectively part operating-retailer, part cash-holding vehicle. Trading only modestly above book value, with the majority of assets being cash and investments, limits downside if capital is preserved. The stock sits near its 52-week low ($19.93) versus the high of $28.10. On balance, the market appears to be appropriately discounting the declining core business while assigning limited premium for capital-deployment optionality. That balance justifies a Fairly Valued rating rather than clearly cheap or clearly expensive — the outcome hinges on management execution that is not yet demonstrated in the data.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>GameStop's economic moat is weak and eroding. Its historical advantage was scale in physical game retail and a lucrative pre-owned/trade-in model, both of which are being structurally undermined by digital distribution and now Sony's move to end physical disc production. There are minimal switching costs and limited pricing power in a business where digital storefronts (Sony, Microsoft, Steam), Amazon, and mass retailers compete directly. The pivot into collectibles and trading cards leverages physical store presence and brand recognition among enthusiasts, but that market is fragmented, competitive (eBay, dedicated card shops, online marketplaces), and lacks durable barriers to entry. The company's most distinctive asset is its cash pile and the capital-allocation latitude it affords, which is a financial rather than an operating moat. Brand recognition and a loyal retail-investor community provide intangible support but do not constitute a defensible competitive advantage in the traditional sense.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Over five years, the legacy physical software and pre-owned business is likely to shrink materially, with Sony's 2028 disc discontinuation a concrete catalyst and the broader digital shift a persistent headwind. The bull path depends on two things: (1) successful reinvention around collectibles, trading cards, and possibly a marketplace platform, and (2) intelligent deployment of the ~$7B cash hoard into value-creating acquisitions or investments. Neither is proven, and management's track record on large-scale capital deployment is still developing. Industry tailwinds exist in collectibles/trading cards, but these are cyclical and carry fad and regulatory risks. The most probable outcome is a smaller but profitable operating business plus a large investment portfolio whose returns determine shareholder outcomes. Expected challenges include continued store rationalization, defending margins as physical volumes fall, and demonstrating that the diversified strategy can scale. The range of outcomes is unusually wide, skewing on the downside toward slow value erosion and on the upside toward transformative capital allocation.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>GameStop is best understood as a hybrid of a declining specialty retailer and a cash-rich capital-allocation vehicle. The operating business has stabilized and become profitable, with genuinely improving gross and operating margins driven by a mix shift toward collectibles, but its historical revenue engine faces an accelerating structural decline confirmed by Sony's exit from physical discs. Reported earnings and the resulting P/E overstate durable profitability due to non-operating gains, so valuation should rest on EV and book value, where the stock looks fairly — not attractively — priced. The central variable is what Cohen does with over $7B in cash: this is the source of both the optionality and the risk. Absent evidence of value-accretive deployment, an investor is paying roughly book value for a shrinking retailer wrapped around a low-yielding cash pile. The risk/reward is roughly balanced with a wide distribution of outcomes. This is a watch-and-wait situation where I would want to see concrete, disciplined capital deployment and durable collectibles/trading-card economics before underwriting a long-term position.</t>
+        </is>
+      </c>
+      <c r="M25" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Confidence is limited by several factors: two quarters of income statement data are missing (NaN), obscuring longer trend analysis; recent net income is distorted by non-operating items that make earnings quality hard to assess; and the entire thesis hinges on future capital allocation for which there is little concrete evidence in the data. The strong, well-documented cash position and improving operating margins increase confidence in the near-term financial stability, but the structural decline of the core business (well-corroborated by multiple independent news items on Sony and digital distribution) and the unproven diversification strategy widen the range of long-term outcomes. The meme-driven trading history and high beta add noise unrelated to fundamentals.</t>
+        </is>
+      </c>
+      <c r="O25" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="P25" s="11" t="n">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/Investment_Research_Dashboard.xlsx
+++ b/Investment_Research_Dashboard.xlsx
@@ -188,7 +188,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DashboardTable" displayName="DashboardTable" ref="A1:R26" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DashboardTable" displayName="DashboardTable" ref="A1:R27" headerRowCount="1">
   <autoFilter ref="A1:R2"/>
   <tableColumns count="18">
     <tableColumn id="1" name="Ticker"/>
@@ -215,7 +215,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WatchlistTable" displayName="WatchlistTable" ref="A1:I26" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WatchlistTable" displayName="WatchlistTable" ref="A1:I27" headerRowCount="1">
   <autoFilter ref="A1:I2"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Ticker"/>
@@ -233,7 +233,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ValuationTable" displayName="ValuationTable" ref="A1:R26" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ValuationTable" displayName="ValuationTable" ref="A1:R27" headerRowCount="1">
   <autoFilter ref="A1:R2"/>
   <tableColumns count="18">
     <tableColumn id="1" name="Ticker"/>
@@ -260,7 +260,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="RatiosTable" displayName="RatiosTable" ref="A1:Q156" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="RatiosTable" displayName="RatiosTable" ref="A1:Q162" headerRowCount="1">
   <autoFilter ref="A1:Q7"/>
   <tableColumns count="17">
     <tableColumn id="1" name="Ticker"/>
@@ -286,7 +286,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FinancialsTable" displayName="FinancialsTable" ref="A1:Y156" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FinancialsTable" displayName="FinancialsTable" ref="A1:Y162" headerRowCount="1">
   <autoFilter ref="A1:Y7"/>
   <tableColumns count="25">
     <tableColumn id="1" name="Ticker"/>
@@ -320,7 +320,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="NewsTable" displayName="NewsTable" ref="A1:I238" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="NewsTable" displayName="NewsTable" ref="A1:I239" headerRowCount="1">
   <autoFilter ref="A1:I11"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Date"/>
@@ -338,7 +338,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="NarrativeTable" displayName="NarrativeTable" ref="A1:P25" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="NarrativeTable" displayName="NarrativeTable" ref="A1:P26" headerRowCount="1">
   <autoFilter ref="A1:P2"/>
   <tableColumns count="16">
     <tableColumn id="1" name="Ticker"/>
@@ -651,8 +651,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:R27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -2491,6 +2491,72 @@
         </is>
       </c>
       <c r="R26" s="10" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MANU</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Manchester United plc</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Manchester United plc, together with its subsidiaries, operates a professional sports team in the United Kingdom. The company is involved in marketing and sponsorship relationships with international and regional companies to commercialize its brand. It also markets and sells sports apparel, training and leisure wear, and other clothing; and other licensed products, such as coffee mugs and home accessories featuring the Manchester United brand and trademarks through Manchester United branded retail centers and e-commerce platforms, and through partners' wholesale distribution channels. In addition, the company distributes live football content directly, as well as through commercial partners; television rights relating to the Premier League, Union of European Football Associations club competitions, and other competitions, as well as delivers Manchester United programming through the MUTV television channel to territories worldwide. Further, it operates Old Trafford, a sports venue, as well as owns or leases, and invests in properties. The company was formerly known as Manchester United Ltd. changed its name to Manchester United plc in August 2012. Manchester United plc was founded in 1878 and is headquartered in Manchester, the United Kingdom.</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>22.465</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>3873737728</v>
+      </c>
+      <c r="H27" s="9" t="n"/>
+      <c r="I27" s="9" t="n">
+        <v>152.95403</v>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n">
+        <v>0.1801960588924043</v>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>-0.0621487411410207</v>
+      </c>
+      <c r="N27" s="5" t="n">
+        <v>-0.1010618433154037</v>
+      </c>
+      <c r="O27" s="9" t="n">
+        <v>4.213606086786879</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Overvalued</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>MANU is a world-class brand attached to a financially weak, highly leveraged operating entity trading at a rich valuation. The bull thesis rests almost entirely on scarcity/trophy-asset dynamics and o...</t>
+        </is>
+      </c>
+      <c r="R27" s="10" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -2788,6 +2854,17 @@
       <formula>"Fairly Valued"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P27">
+    <cfRule type="cellIs" priority="82" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="83" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="84" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2801,8 +2878,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -3312,6 +3389,24 @@
       </c>
       <c r="G26" s="8" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MANU</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Manchester United plc</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -3326,8 +3421,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:R27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
@@ -4885,6 +4980,58 @@
         <v>7510416</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MANU</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>22.465</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>3873737728</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>4533395968</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>56086184</v>
+      </c>
+      <c r="G27" s="9" t="n"/>
+      <c r="H27" s="9" t="n">
+        <v>152.95403</v>
+      </c>
+      <c r="I27" s="9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J27" s="9" t="n"/>
+      <c r="K27" s="9" t="n">
+        <v>16.328491</v>
+      </c>
+      <c r="L27" s="9" t="n">
+        <v>6.625</v>
+      </c>
+      <c r="M27" s="9" t="n">
+        <v>21.057</v>
+      </c>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P27" s="8" t="n">
+        <v>24.22</v>
+      </c>
+      <c r="Q27" s="8" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="R27" s="7" t="n">
+        <v>365627</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -4899,26 +5046,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q156"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:Q162"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="21" customWidth="1" min="16" max="16"/>
-    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -11877,6 +12024,268 @@
       </c>
       <c r="Q156" s="9" t="n"/>
     </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>MANU</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Q4 2024</t>
+        </is>
+      </c>
+      <c r="C157" s="10" t="n">
+        <v>45657</v>
+      </c>
+      <c r="D157" s="5" t="n"/>
+      <c r="E157" s="5" t="n"/>
+      <c r="F157" s="5" t="n"/>
+      <c r="G157" s="5" t="n"/>
+      <c r="H157" s="5" t="n"/>
+      <c r="I157" s="5" t="n"/>
+      <c r="J157" s="5" t="n"/>
+      <c r="K157" s="9" t="n"/>
+      <c r="L157" s="9" t="n"/>
+      <c r="M157" s="9" t="n"/>
+      <c r="N157" s="5" t="n"/>
+      <c r="O157" s="5" t="n"/>
+      <c r="P157" s="5" t="n"/>
+      <c r="Q157" s="9" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>MANU</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
+      <c r="C158" s="10" t="n">
+        <v>45747</v>
+      </c>
+      <c r="D158" s="5" t="n"/>
+      <c r="E158" s="5" t="n">
+        <v>-0.009740664158840088</v>
+      </c>
+      <c r="F158" s="5" t="n">
+        <v>-0.01687800503226128</v>
+      </c>
+      <c r="G158" s="5" t="n">
+        <v>-0.1905906678956678</v>
+      </c>
+      <c r="H158" s="5" t="n"/>
+      <c r="I158" s="5" t="n"/>
+      <c r="J158" s="5" t="n"/>
+      <c r="K158" s="9" t="n">
+        <v>3.656201403135527</v>
+      </c>
+      <c r="L158" s="9" t="n">
+        <v>0.3887269961802266</v>
+      </c>
+      <c r="M158" s="9" t="n">
+        <v>0.3714711662456817</v>
+      </c>
+      <c r="N158" s="5" t="n"/>
+      <c r="O158" s="5" t="n"/>
+      <c r="P158" s="5" t="n"/>
+      <c r="Q158" s="9" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>MANU</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Q2 2025</t>
+        </is>
+      </c>
+      <c r="C159" s="10" t="n">
+        <v>45838</v>
+      </c>
+      <c r="D159" s="5" t="n"/>
+      <c r="E159" s="5" t="n">
+        <v>-0.06643725066236258</v>
+      </c>
+      <c r="F159" s="5" t="n">
+        <v>-0.02373542040990346</v>
+      </c>
+      <c r="G159" s="5" t="n">
+        <v>0.3084447422115297</v>
+      </c>
+      <c r="H159" s="5" t="n">
+        <v>0.02255175506340151</v>
+      </c>
+      <c r="I159" s="5" t="n"/>
+      <c r="J159" s="5" t="n"/>
+      <c r="K159" s="9" t="n">
+        <v>3.331621355164066</v>
+      </c>
+      <c r="L159" s="9" t="n">
+        <v>0.3785024247940691</v>
+      </c>
+      <c r="M159" s="9" t="n">
+        <v>0.3611070760808291</v>
+      </c>
+      <c r="N159" s="5" t="n"/>
+      <c r="O159" s="5" t="n"/>
+      <c r="P159" s="5" t="n"/>
+      <c r="Q159" s="9" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>MANU</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Q3 2025</t>
+        </is>
+      </c>
+      <c r="C160" s="10" t="n">
+        <v>45930</v>
+      </c>
+      <c r="D160" s="5" t="n"/>
+      <c r="E160" s="5" t="n">
+        <v>-0.2283088104314368</v>
+      </c>
+      <c r="F160" s="5" t="n">
+        <v>-0.0473119811892123</v>
+      </c>
+      <c r="G160" s="5" t="n">
+        <v>-1.288638711746054</v>
+      </c>
+      <c r="H160" s="5" t="n">
+        <v>-0.1452020586533484</v>
+      </c>
+      <c r="I160" s="5" t="n"/>
+      <c r="J160" s="5" t="n"/>
+      <c r="K160" s="9" t="n">
+        <v>4.06612142385652</v>
+      </c>
+      <c r="L160" s="9" t="n">
+        <v>0.3090137346404756</v>
+      </c>
+      <c r="M160" s="9" t="n">
+        <v>0.2870768971047523</v>
+      </c>
+      <c r="N160" s="5" t="n"/>
+      <c r="O160" s="5" t="n"/>
+      <c r="P160" s="5" t="n"/>
+      <c r="Q160" s="9" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>MANU</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
+      <c r="C161" s="10" t="n">
+        <v>46022</v>
+      </c>
+      <c r="D161" s="5" t="n"/>
+      <c r="E161" s="5" t="n">
+        <v>0.08605043429826544</v>
+      </c>
+      <c r="F161" s="5" t="n">
+        <v>0.02198027397836128</v>
+      </c>
+      <c r="G161" s="5" t="n">
+        <v>-0.351038059556401</v>
+      </c>
+      <c r="H161" s="5" t="n">
+        <v>0.3559941572553351</v>
+      </c>
+      <c r="I161" s="5" t="n"/>
+      <c r="J161" s="5" t="n"/>
+      <c r="K161" s="9" t="n">
+        <v>4.091407151095733</v>
+      </c>
+      <c r="L161" s="9" t="n">
+        <v>0.321948744478491</v>
+      </c>
+      <c r="M161" s="9" t="n">
+        <v>0.298611663814716</v>
+      </c>
+      <c r="N161" s="5" t="n">
+        <v>-0.047520184544406</v>
+      </c>
+      <c r="O161" s="5" t="n">
+        <v>-0.005427174432404015</v>
+      </c>
+      <c r="P161" s="5" t="n">
+        <v>0.03953030497588831</v>
+      </c>
+      <c r="Q161" s="9" t="n">
+        <v>0.828456068889127</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>MANU</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Q1 2026</t>
+        </is>
+      </c>
+      <c r="C162" s="10" t="n">
+        <v>46112</v>
+      </c>
+      <c r="D162" s="5" t="n"/>
+      <c r="E162" s="5" t="n">
+        <v>0.05439136239623846</v>
+      </c>
+      <c r="F162" s="5" t="n">
+        <v>-0.0621487411410207</v>
+      </c>
+      <c r="G162" s="5" t="n">
+        <v>-0.07974268721932273</v>
+      </c>
+      <c r="H162" s="5" t="n">
+        <v>-0.004256280641279617</v>
+      </c>
+      <c r="I162" s="5" t="n">
+        <v>0.1801960588924043</v>
+      </c>
+      <c r="J162" s="5" t="n">
+        <v>-3.35031847133758</v>
+      </c>
+      <c r="K162" s="9" t="n">
+        <v>4.213606086786879</v>
+      </c>
+      <c r="L162" s="9" t="n">
+        <v>0.3714644371994635</v>
+      </c>
+      <c r="M162" s="9" t="n">
+        <v>0.3528093685599328</v>
+      </c>
+      <c r="N162" s="5" t="n">
+        <v>-0.1010618433154037</v>
+      </c>
+      <c r="O162" s="5" t="n">
+        <v>-0.01139986092056502</v>
+      </c>
+      <c r="P162" s="5" t="n">
+        <v>0.04263538240554796</v>
+      </c>
+      <c r="Q162" s="9" t="n">
+        <v>0.6844334218045222</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -11891,8 +12300,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y156"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:Y162"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
@@ -23091,6 +23500,438 @@
         <v>1500000</v>
       </c>
     </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>MANU</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Q4 2024</t>
+        </is>
+      </c>
+      <c r="C157" s="10" t="n">
+        <v>45657</v>
+      </c>
+      <c r="D157" s="3" t="n"/>
+      <c r="E157" s="3" t="n"/>
+      <c r="F157" s="3" t="n"/>
+      <c r="G157" s="3" t="n"/>
+      <c r="H157" s="3" t="n"/>
+      <c r="I157" s="3" t="n"/>
+      <c r="J157" s="8" t="n"/>
+      <c r="K157" s="8" t="n"/>
+      <c r="L157" s="3" t="n"/>
+      <c r="M157" s="3" t="n"/>
+      <c r="N157" s="3" t="n"/>
+      <c r="O157" s="3" t="n"/>
+      <c r="P157" s="3" t="n"/>
+      <c r="Q157" s="3" t="n"/>
+      <c r="R157" s="3" t="n"/>
+      <c r="S157" s="3" t="n"/>
+      <c r="T157" s="3" t="n"/>
+      <c r="U157" s="3" t="n"/>
+      <c r="V157" s="3" t="n"/>
+      <c r="W157" s="3" t="n"/>
+      <c r="X157" s="3" t="n"/>
+      <c r="Y157" s="3" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>MANU</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
+      <c r="C158" s="10" t="n">
+        <v>45747</v>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>160564000</v>
+      </c>
+      <c r="E158" s="3" t="n"/>
+      <c r="F158" s="3" t="n">
+        <v>-1564000</v>
+      </c>
+      <c r="G158" s="3" t="n">
+        <v>10726000</v>
+      </c>
+      <c r="H158" s="3" t="n">
+        <v>60847000</v>
+      </c>
+      <c r="I158" s="3" t="n">
+        <v>-2710000</v>
+      </c>
+      <c r="J158" s="8" t="n">
+        <v>-0.0157</v>
+      </c>
+      <c r="K158" s="8" t="n">
+        <v>-0.0157</v>
+      </c>
+      <c r="L158" s="3" t="n">
+        <v>13783000</v>
+      </c>
+      <c r="M158" s="3" t="n">
+        <v>73211000</v>
+      </c>
+      <c r="N158" s="3" t="n">
+        <v>1593013000</v>
+      </c>
+      <c r="O158" s="3" t="n">
+        <v>270395000</v>
+      </c>
+      <c r="P158" s="3" t="n">
+        <v>721789000</v>
+      </c>
+      <c r="Q158" s="3" t="n">
+        <v>500883000</v>
+      </c>
+      <c r="R158" s="3" t="n">
+        <v>197415000</v>
+      </c>
+      <c r="S158" s="3" t="n">
+        <v>695591000</v>
+      </c>
+      <c r="T158" s="3" t="n">
+        <v>12003000</v>
+      </c>
+      <c r="U158" s="3" t="n">
+        <v>22317000</v>
+      </c>
+      <c r="V158" s="3" t="n">
+        <v>-52919000</v>
+      </c>
+      <c r="W158" s="3" t="n">
+        <v>-30602000</v>
+      </c>
+      <c r="X158" s="3" t="n">
+        <v>-48116000</v>
+      </c>
+      <c r="Y158" s="3" t="n">
+        <v>-102000</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>MANU</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Q2 2025</t>
+        </is>
+      </c>
+      <c r="C159" s="10" t="n">
+        <v>45838</v>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>164185000</v>
+      </c>
+      <c r="E159" s="3" t="n"/>
+      <c r="F159" s="3" t="n">
+        <v>-10908000</v>
+      </c>
+      <c r="G159" s="3" t="n">
+        <v>9459000</v>
+      </c>
+      <c r="H159" s="3" t="n">
+        <v>61471000</v>
+      </c>
+      <c r="I159" s="3" t="n">
+        <v>-3897000</v>
+      </c>
+      <c r="J159" s="8" t="n">
+        <v>-0.0226</v>
+      </c>
+      <c r="K159" s="8" t="n">
+        <v>-0.0226</v>
+      </c>
+      <c r="L159" s="3" t="n">
+        <v>13177000</v>
+      </c>
+      <c r="M159" s="3" t="n">
+        <v>86105000</v>
+      </c>
+      <c r="N159" s="3" t="n">
+        <v>1637733000</v>
+      </c>
+      <c r="O159" s="3" t="n">
+        <v>284018000</v>
+      </c>
+      <c r="P159" s="3" t="n">
+        <v>645445000</v>
+      </c>
+      <c r="Q159" s="3" t="n">
+        <v>471855000</v>
+      </c>
+      <c r="R159" s="3" t="n">
+        <v>193733000</v>
+      </c>
+      <c r="S159" s="3" t="n">
+        <v>750373000</v>
+      </c>
+      <c r="T159" s="3" t="n">
+        <v>13053000</v>
+      </c>
+      <c r="U159" s="3" t="n">
+        <v>100298000</v>
+      </c>
+      <c r="V159" s="3" t="n">
+        <v>-49656000</v>
+      </c>
+      <c r="W159" s="3" t="n">
+        <v>50642000</v>
+      </c>
+      <c r="X159" s="3" t="n">
+        <v>-45005000</v>
+      </c>
+      <c r="Y159" s="3" t="n">
+        <v>-50110000</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>MANU</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Q3 2025</t>
+        </is>
+      </c>
+      <c r="C160" s="10" t="n">
+        <v>45930</v>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>140345000</v>
+      </c>
+      <c r="E160" s="3" t="n"/>
+      <c r="F160" s="3" t="n">
+        <v>-32042000</v>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>6375000</v>
+      </c>
+      <c r="H160" s="3" t="n">
+        <v>65356000</v>
+      </c>
+      <c r="I160" s="3" t="n">
+        <v>-6640000</v>
+      </c>
+      <c r="J160" s="8" t="n">
+        <v>-0.0385</v>
+      </c>
+      <c r="K160" s="8" t="n">
+        <v>-0.0385</v>
+      </c>
+      <c r="L160" s="3" t="n">
+        <v>14830000</v>
+      </c>
+      <c r="M160" s="3" t="n">
+        <v>80458000</v>
+      </c>
+      <c r="N160" s="3" t="n">
+        <v>1727597000</v>
+      </c>
+      <c r="O160" s="3" t="n">
+        <v>256262000</v>
+      </c>
+      <c r="P160" s="3" t="n">
+        <v>757677000</v>
+      </c>
+      <c r="Q160" s="3" t="n">
+        <v>481218000</v>
+      </c>
+      <c r="R160" s="3" t="n">
+        <v>186339000</v>
+      </c>
+      <c r="S160" s="3" t="n">
+        <v>829290000</v>
+      </c>
+      <c r="T160" s="3" t="n">
+        <v>18192000</v>
+      </c>
+      <c r="U160" s="3" t="n">
+        <v>-1303000</v>
+      </c>
+      <c r="V160" s="3" t="n">
+        <v>-179551000</v>
+      </c>
+      <c r="W160" s="3" t="n">
+        <v>-180854000</v>
+      </c>
+      <c r="X160" s="3" t="n">
+        <v>-116690000</v>
+      </c>
+      <c r="Y160" s="3" t="n">
+        <v>102694000</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>MANU</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
+      <c r="C161" s="10" t="n">
+        <v>46022</v>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>190307000</v>
+      </c>
+      <c r="E161" s="3" t="n"/>
+      <c r="F161" s="3" t="n">
+        <v>16376000</v>
+      </c>
+      <c r="G161" s="3" t="n">
+        <v>19812000</v>
+      </c>
+      <c r="H161" s="3" t="n">
+        <v>79389000</v>
+      </c>
+      <c r="I161" s="3" t="n">
+        <v>4183000</v>
+      </c>
+      <c r="J161" s="8" t="n">
+        <v>0.0243</v>
+      </c>
+      <c r="K161" s="8" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="L161" s="3" t="n">
+        <v>14184000</v>
+      </c>
+      <c r="M161" s="3" t="n">
+        <v>44406000</v>
+      </c>
+      <c r="N161" s="3" t="n">
+        <v>1670114000</v>
+      </c>
+      <c r="O161" s="3" t="n">
+        <v>258888000</v>
+      </c>
+      <c r="P161" s="3" t="n">
+        <v>780395000</v>
+      </c>
+      <c r="Q161" s="3" t="n">
+        <v>481265000</v>
+      </c>
+      <c r="R161" s="3" t="n">
+        <v>190740000</v>
+      </c>
+      <c r="S161" s="3" t="n">
+        <v>804128000</v>
+      </c>
+      <c r="T161" s="3" t="n">
+        <v>18766000</v>
+      </c>
+      <c r="U161" s="3" t="n">
+        <v>-11428000</v>
+      </c>
+      <c r="V161" s="3" t="n">
+        <v>-55377000</v>
+      </c>
+      <c r="W161" s="3" t="n">
+        <v>-66805000</v>
+      </c>
+      <c r="X161" s="3" t="n">
+        <v>-37772000</v>
+      </c>
+      <c r="Y161" s="3" t="n">
+        <v>23676000</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>MANU</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Q1 2026</t>
+        </is>
+      </c>
+      <c r="C162" s="10" t="n">
+        <v>46112</v>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>189497000</v>
+      </c>
+      <c r="E162" s="3" t="n"/>
+      <c r="F162" s="3" t="n">
+        <v>10307000</v>
+      </c>
+      <c r="G162" s="3" t="n">
+        <v>11545000</v>
+      </c>
+      <c r="H162" s="3" t="n">
+        <v>69206000</v>
+      </c>
+      <c r="I162" s="3" t="n">
+        <v>-11777000</v>
+      </c>
+      <c r="J162" s="8" t="n">
+        <v>-0.0683</v>
+      </c>
+      <c r="K162" s="8" t="n">
+        <v>-0.0683</v>
+      </c>
+      <c r="L162" s="3" t="n">
+        <v>26758000</v>
+      </c>
+      <c r="M162" s="3" t="n">
+        <v>60935000</v>
+      </c>
+      <c r="N162" s="3" t="n">
+        <v>1590458000</v>
+      </c>
+      <c r="O162" s="3" t="n">
+        <v>272539000</v>
+      </c>
+      <c r="P162" s="3" t="n">
+        <v>755942000</v>
+      </c>
+      <c r="Q162" s="3" t="n">
+        <v>490140000</v>
+      </c>
+      <c r="R162" s="3" t="n">
+        <v>179405000</v>
+      </c>
+      <c r="S162" s="3" t="n">
+        <v>733688000</v>
+      </c>
+      <c r="T162" s="3" t="n">
+        <v>13687000</v>
+      </c>
+      <c r="U162" s="3" t="n">
+        <v>27369000</v>
+      </c>
+      <c r="V162" s="3" t="n">
+        <v>-42480000</v>
+      </c>
+      <c r="W162" s="3" t="n">
+        <v>-15111000</v>
+      </c>
+      <c r="X162" s="3" t="n">
+        <v>20696000</v>
+      </c>
+      <c r="Y162" s="3" t="n">
+        <v>-30434000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -23105,8 +23946,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I238"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I239"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
@@ -33831,6 +34672,51 @@
         </is>
       </c>
     </row>
+    <row r="239">
+      <c r="A239" s="10" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>MarketBeat Week in Review – 06/29 - 07/03</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>MarketBeat</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>https://www.marketbeat.com/articles/marketbeat-week-in-review-06-29-07-03/?utm_source=yahoofinance&amp;utm_medium=yahoofinance</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Manchester United plc</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>MANU</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>This generic market roundup doesn't mention MANU, offering no relevant insight for a long-term investor in the company.</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -33845,8 +34731,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:P26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
@@ -35724,6 +36610,80 @@
         <v>40</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MANU</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Manchester United is one of the most globally recognized sports franchises, monetizing its brand through matchday, broadcasting, and commercial/sponsorship revenue. The financial data show a business with strong top-line seasonality (fiscal quarters swing meaningfully with the football calendar and competition participation) and revenue in the roughly $140-190M per quarter range, but persistently weak profitability at the net level and a heavily leveraged balance sheet. Debt-to-equity sits above 4x, shareholder equity is thin (~$179M) relative to $756M total debt, and interest expense is large enough that interest coverage is well below 1x in recent quarters. Free cash flow is negative in most quarters, driven partly by heavy capital expenditures (notably a ~$180M capex quarter in Q3 2025, likely stadium/infrastructure related). The club swung to a small net profit in Q4 2025 but fell back to a ~$12M net loss in Q1 2026, with a spike in interest expense to ~$27M that quarter. The stock trades near its 52-week high at a rich forward P/E (~153x) and elevated EV/EBITDA (~21x). This is a trophy asset with a durable brand but chronically poor financial economics, where equity value is driven more by scarcity and control-premium dynamics than by fundamental cash generation.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>This is the first writeup, so there is no prior baseline to compare against. The most material recent facts in the data: (1) revenue grew ~18% year-over-year in Q1 2026 to ~$189M, indicating healthy top-line recovery, likely tied to competition participation and commercial activity; (2) despite that revenue strength, the club posted a ~$12M net loss in Q1 2026, driven by a sharp jump in interest expense to ~$27M (roughly double the ~$13-15M run rate of prior quarters), which is a red flag worth monitoring; (3) very heavy capital expenditure through fiscal 2025 (a ~$180M capex quarter in Q3 2025) points to significant infrastructure/stadium investment that is currently depressing free cash flow; (4) leverage continues to climb, with debt-to-equity moving from ~3.3x to ~4.2x over the trailing quarters. The recent news item is a generic market roundup with no MANU-specific content, so it carries no analytical weight.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Manchester United owns a globally scarce, multi-decade brand asset with a worldwide fanbase that generates resilient commercial and broadcasting revenue largely independent of on-pitch results in the short term. Top-line growth of ~18% YoY in the latest quarter shows revenue durability and pricing power in sponsorships, media rights, and matchday. Sports franchises of this caliber are scarce trophy assets that command persistent control/scarcity premiums; equity can appreciate on ownership-change, minority-stake sales, or strategic investment even when underlying profitability is weak. Heavy current capex (stadium/infrastructure) is a discretionary investment that, once complete, could expand high-margin matchday and hospitality revenue and improve future cash generation. Structural tailwinds in global sports media rights valuations and streaming demand for premium live content support long-run revenue. The low beta (0.6) reflects that the asset value is somewhat decoupled from broader market cycles.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>The fundamental economics are poor: net losses recur, interest coverage is below 1x, and free cash flow is negative in most quarters, meaning the business is not self-funding its investment and debt service from operations. Leverage is high and rising (debt-to-equity above 4x), equity is thin, and the Q1 2026 doubling of interest expense to ~$27M signals rising financing cost pressure that directly eats into any operating profit. Valuation is extreme on any earnings or cash-flow basis (forward P/E ~153x, EV/EBITDA ~21x) for a business with negative returns on equity and marginal ROIC (~4%). Player wages, transfer spending, and stadium capex are structurally high and difficult to control, keeping margins compressed. On-pitch underperformance can reduce lucrative competition revenue (e.g., Champions League) and sponsorship value. If a control-premium/M&amp;A catalyst does not materialize, the stock is left resting on weak fundamentals at a rich price. Current ratio near 0.37 signals persistent working-capital/liquidity strain.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Balance sheet strength is weak. Total debt of ~$756M dwarfs shareholder equity of ~$179M (D/E ~4.2x), and current ratio (~0.37) and quick ratio (~0.35) indicate current liabilities substantially exceed current assets every quarter. Interest coverage is below 1x in the two most recent quarters where computed, meaning EBIT does not cover interest expense -- a structural concern. EBITDA is positive and sizable (~$60-79M per quarter), but this is flattered by large depreciation/amortization (player registrations, stadium assets); net income is frequently negative and ROE is negative (~-10% in Q1 2026). Free cash flow is negative in four of the last five quarters, driven by elevated capex; the strong FCF in Q2 2025 appears seasonal/working-capital driven rather than a durable trend. Revenue quality is decent and diversified (broadcast, commercial, matchday) with ~18% YoY growth in the latest quarter. Capital allocation is dominated by debt service and heavy infrastructure/player investment; no dividend is paid. There is no evidence of buybacks and share count is small and stable, so dilution is not an acute concern. Net: revenue resilient, but leverage and cash generation are the clear weaknesses.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Overvalued</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>On conventional metrics the stock is expensive: forward P/E of ~153x and EV/EBITDA of ~21x against a business generating negative net income, negative ROE, and roughly 4% ROIC. EV/revenue of ~6.6x is high for an entity with mid-single-digit or negative operating margins. The PEG of 0.35 looks optically cheap but is unreliable here because it leans on distorted/near-zero earnings and volatile growth. The price sits near the 52-week high (~$22.5 vs $24.22 high, $14.59 low), so the market is already capitalizing an optimistic scenario. The honest read is that MANU trades as a scarce trophy asset where price reflects control/scarcity premium and potential ownership-change optionality rather than fundamental cash flows; on a pure fundamentals basis the valuation is stretched. Because sports franchises persistently trade above what earnings justify, I rate it Overvalued on fundamentals while acknowledging that the scarcity premium can persist and even expand on M&amp;A catalysts.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>The moat is the brand, not the financials. Manchester United possesses one of the strongest and most durable brands in global sports, with a worldwide fanbase, embedded fan loyalty (extremely high emotional switching costs -- fans do not switch clubs), and privileged access to Premier League and UEFA broadcast revenue pools. This supports genuine pricing power in sponsorship and matchday. However, the competitive field is intense: sporting success drives a meaningful share of revenue, and rivals with deeper financial backing can outspend on players. The listed sector peers (GOOGL, META) are not true comparables -- MANU competes within elite football, not digital advertising -- so peer financials offer no direct read. Overall the brand moat is wide and durable, but it does not translate into strong financial returns because the cost structure (wages, transfers) captures much of the economic value.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Over five years, revenue is likely to grow modestly, supported by global sports media-rights inflation, streaming demand for premium live content, sponsorship monetization, and potential upside from stadium/infrastructure investment (higher-margin matchday and hospitality). The key risks are financial rather than commercial: high and rising leverage, interest costs consuming operating profit, and dependence on on-pitch performance to unlock top competition revenue. Player-wage and transfer inflation will continue to pressure margins, and the club must fund large capex while servicing significant debt. The most powerful potential value catalyst is corporate/ownership action (further stake sales, strategic investment, or a control transaction) given the scarcity of assets of this caliber. Absent balance-sheet deleveraging or a step-change in operating margins, sustained profitability improvement is uncertain.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>MANU is a world-class brand attached to a financially weak, highly leveraged operating entity trading at a rich valuation. The bull thesis rests almost entirely on scarcity/trophy-asset dynamics and ownership-change optionality rather than on cash generation, while the fundamentals -- negative net income, sub-1x interest coverage, D/E above 4x, and recurring negative free cash flow amid heavy capex -- argue for caution. Revenue is resilient and growing, and the brand moat is durable, but the equity is priced well above what earnings or free cash flow justify. For a long-term fundamentals-driven investor, the risk/reward is unattractive at current levels near the 52-week high: you are paying a premium multiple for a business that does not currently cover its interest costs, with a rising financing burden. The setup is a hold/avoid on fundamentals, where the main upside case is an M&amp;A/control catalyst that is inherently hard to underwrite. I would want either meaningful deleveraging, a durable turn to positive free cash flow, or a materially lower entry price before turning constructive.</t>
+        </is>
+      </c>
+      <c r="M26" s="11" t="n">
+        <v>62</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Confidence is supported by six quarters of consistent financial data showing clear, repeated signals: negative FCF, sub-1x interest coverage, rising leverage, and stretched multiples. These are structural, not one-off, which raises conviction on the fundamentals-based bear/valuation view. Confidence is reduced by missing gross-margin data, NaN fields in the oldest quarter, absence of prior-period baselines, no meaningful company-specific news, and the inherent difficulty of valuing a scarce sports asset where equity value is driven by control-premium and M&amp;A optionality that fundamentals cannot capture. The unexplained doubling of interest expense in Q1 2026 also introduces uncertainty about the trajectory of financing costs.</t>
+        </is>
+      </c>
+      <c r="O26" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="P26" s="11" t="n">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/Investment_Research_Dashboard.xlsx
+++ b/Investment_Research_Dashboard.xlsx
@@ -188,7 +188,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DashboardTable" displayName="DashboardTable" ref="A1:R27" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DashboardTable" displayName="DashboardTable" ref="A1:R28" headerRowCount="1">
   <autoFilter ref="A1:R2"/>
   <tableColumns count="18">
     <tableColumn id="1" name="Ticker"/>
@@ -215,7 +215,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WatchlistTable" displayName="WatchlistTable" ref="A1:I27" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WatchlistTable" displayName="WatchlistTable" ref="A1:I28" headerRowCount="1">
   <autoFilter ref="A1:I2"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Ticker"/>
@@ -233,7 +233,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ValuationTable" displayName="ValuationTable" ref="A1:R27" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ValuationTable" displayName="ValuationTable" ref="A1:R28" headerRowCount="1">
   <autoFilter ref="A1:R2"/>
   <tableColumns count="18">
     <tableColumn id="1" name="Ticker"/>
@@ -260,7 +260,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="RatiosTable" displayName="RatiosTable" ref="A1:Q162" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="RatiosTable" displayName="RatiosTable" ref="A1:Q168" headerRowCount="1">
   <autoFilter ref="A1:Q7"/>
   <tableColumns count="17">
     <tableColumn id="1" name="Ticker"/>
@@ -286,7 +286,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FinancialsTable" displayName="FinancialsTable" ref="A1:Y162" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FinancialsTable" displayName="FinancialsTable" ref="A1:Y168" headerRowCount="1">
   <autoFilter ref="A1:Y7"/>
   <tableColumns count="25">
     <tableColumn id="1" name="Ticker"/>
@@ -320,7 +320,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="NewsTable" displayName="NewsTable" ref="A1:I239" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="NewsTable" displayName="NewsTable" ref="A1:I249" headerRowCount="1">
   <autoFilter ref="A1:I11"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Date"/>
@@ -651,8 +651,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:R28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -2557,6 +2557,66 @@
         </is>
       </c>
       <c r="R27" s="10" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company operates as an entertainment company in Americas, Europe, and the Asia Pacific. It operates in three segments: Entertainment, Sports, and Experiences. The company produces and distributes film and television content under the ABC Television Network, Disney, Freeform, FX, Fox, National Geographic, and Star brand television channels, as well as ABC television stations and A+E television networks; and produces original content under the Disney Branded Television, FX Productions, Lucasfilm, Marvel, National Geographic Studios, Pixar, Searchlight Pictures, Twentieth Century Studios, 20th Television, and Walt Disney Pictures banners. It also provides direct-to-consumer streaming services through Disney+, Disney+ Hotstar, and Hulu; sports-related video streaming content through ESPN, ESPN on ABC, ESPN+ DTC, and Star; sale/licensing of film and episodic content to television and video-on-demand services; theatrical, home entertainment, and music distribution services; DVD and Blu-ray discs, electronic home video licenses, and VOD rental services; staging and licensing of live entertainment events; and post-production services. In addition, the company operates theme parks and resorts, such as Walt Disney World Resort, Disneyland Resort, Disneyland Paris, Hong Kong Disneyland Resort, Shanghai Disney Resort, Disney Cruise Line, Disney Vacation Club, National Geographic Expeditions, and Adventures by Disney, as well as Aulani, a Disney resort and spa in Hawaii. Further, it licenses its intellectual property (IP) to a third party that owns and operates Tokyo Disney Resort; licenses trade names, characters, visual, literary, and other IP for use on merchandise, published materials, and games; operates a direct-to-home satellite distribution platform; sells branded merchandise through retail, online, and wholesale businesses; and develops and publishes books, comic books, and magazines. The company was founded in 1923 and is based in Burbank, California.</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>97.56</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>169414049792</v>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>15.6096</v>
+      </c>
+      <c r="I28" s="9" t="n">
+        <v>13.028934</v>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>2.2618</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>0.0154</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>0.0654925701706109</v>
+      </c>
+      <c r="M28" s="5" t="n">
+        <v>0.08928003814367451</v>
+      </c>
+      <c r="N28" s="5" t="n">
+        <v>0.1032490709055451</v>
+      </c>
+      <c r="O28" s="9" t="n">
+        <v>0.4356441108290098</v>
+      </c>
+      <c r="R28" s="10" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -2865,6 +2925,17 @@
       <formula>"Fairly Valued"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P28">
+    <cfRule type="cellIs" priority="85" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="86" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="87" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2878,8 +2949,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -3407,6 +3478,24 @@
       </c>
       <c r="G27" s="8" t="n"/>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -3421,8 +3510,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:R28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
@@ -5032,6 +5121,64 @@
         <v>365627</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>97.56</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>169414049792</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>217433571328</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>1736511424</v>
+      </c>
+      <c r="G28" s="9" t="n">
+        <v>15.6096</v>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>13.028934</v>
+      </c>
+      <c r="I28" s="9" t="n">
+        <v>2.2618</v>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>1.7418139</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>1.5660465</v>
+      </c>
+      <c r="L28" s="9" t="n">
+        <v>2.236</v>
+      </c>
+      <c r="M28" s="9" t="n">
+        <v>11.026</v>
+      </c>
+      <c r="N28" s="5" t="n">
+        <v>0.0154</v>
+      </c>
+      <c r="O28" s="9" t="n">
+        <v>1.398</v>
+      </c>
+      <c r="P28" s="8" t="n">
+        <v>123.71</v>
+      </c>
+      <c r="Q28" s="8" t="n">
+        <v>92.19</v>
+      </c>
+      <c r="R28" s="7" t="n">
+        <v>9560960</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -5046,8 +5193,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q162"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:Q168"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
@@ -5056,15 +5203,15 @@
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="23" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
@@ -12286,6 +12433,278 @@
         <v>0.6844334218045222</v>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Q4 2024</t>
+        </is>
+      </c>
+      <c r="C163" s="10" t="n">
+        <v>45657</v>
+      </c>
+      <c r="D163" s="5" t="n"/>
+      <c r="E163" s="5" t="n"/>
+      <c r="F163" s="5" t="n"/>
+      <c r="G163" s="5" t="n"/>
+      <c r="H163" s="5" t="n"/>
+      <c r="I163" s="5" t="n"/>
+      <c r="J163" s="5" t="n"/>
+      <c r="K163" s="9" t="n"/>
+      <c r="L163" s="9" t="n"/>
+      <c r="M163" s="9" t="n"/>
+      <c r="N163" s="5" t="n"/>
+      <c r="O163" s="5" t="n"/>
+      <c r="P163" s="5" t="n"/>
+      <c r="Q163" s="9" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
+      <c r="C164" s="10" t="n">
+        <v>45747</v>
+      </c>
+      <c r="D164" s="5" t="n">
+        <v>0.3730155370221413</v>
+      </c>
+      <c r="E164" s="5" t="n">
+        <v>0.1484272469412811</v>
+      </c>
+      <c r="F164" s="5" t="n">
+        <v>0.1386478133863935</v>
+      </c>
+      <c r="G164" s="5" t="n">
+        <v>0.2070615130604123</v>
+      </c>
+      <c r="H164" s="5" t="n"/>
+      <c r="I164" s="5" t="n"/>
+      <c r="J164" s="5" t="n"/>
+      <c r="K164" s="9" t="n">
+        <v>0.4110543516805796</v>
+      </c>
+      <c r="L164" s="9" t="n">
+        <v>0.6681066149460754</v>
+      </c>
+      <c r="M164" s="9" t="n">
+        <v>0.6093626024861147</v>
+      </c>
+      <c r="N164" s="5" t="n"/>
+      <c r="O164" s="5" t="n"/>
+      <c r="P164" s="5" t="n"/>
+      <c r="Q164" s="9" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Q2 2025</t>
+        </is>
+      </c>
+      <c r="C165" s="10" t="n">
+        <v>45838</v>
+      </c>
+      <c r="D165" s="5" t="n">
+        <v>0.38553911205074</v>
+      </c>
+      <c r="E165" s="5" t="n">
+        <v>0.154122621564482</v>
+      </c>
+      <c r="F165" s="5" t="n">
+        <v>0.2224947145877378</v>
+      </c>
+      <c r="G165" s="5" t="n">
+        <v>0.07987315010570825</v>
+      </c>
+      <c r="H165" s="5" t="n">
+        <v>0.00122772109563524</v>
+      </c>
+      <c r="I165" s="5" t="n"/>
+      <c r="J165" s="5" t="n"/>
+      <c r="K165" s="9" t="n">
+        <v>0.3872188373264923</v>
+      </c>
+      <c r="L165" s="9" t="n">
+        <v>0.7224311537061749</v>
+      </c>
+      <c r="M165" s="9" t="n">
+        <v>0.6593473250030328</v>
+      </c>
+      <c r="N165" s="5" t="n"/>
+      <c r="O165" s="5" t="n"/>
+      <c r="P165" s="5" t="n"/>
+      <c r="Q165" s="9" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Q3 2025</t>
+        </is>
+      </c>
+      <c r="C166" s="10" t="n">
+        <v>45930</v>
+      </c>
+      <c r="D166" s="5" t="n">
+        <v>0.3759793447293447</v>
+      </c>
+      <c r="E166" s="5" t="n">
+        <v>0.1158742877492877</v>
+      </c>
+      <c r="F166" s="5" t="n">
+        <v>0.05844907407407408</v>
+      </c>
+      <c r="G166" s="5" t="n">
+        <v>0.1138710826210826</v>
+      </c>
+      <c r="H166" s="5" t="n">
+        <v>-0.05014799154334038</v>
+      </c>
+      <c r="I166" s="5" t="n"/>
+      <c r="J166" s="5" t="n"/>
+      <c r="K166" s="9" t="n">
+        <v>0.4084591650055976</v>
+      </c>
+      <c r="L166" s="9" t="n">
+        <v>0.7103506820443768</v>
+      </c>
+      <c r="M166" s="9" t="n">
+        <v>0.6478836133715825</v>
+      </c>
+      <c r="N166" s="5" t="n"/>
+      <c r="O166" s="5" t="n"/>
+      <c r="P166" s="5" t="n"/>
+      <c r="Q166" s="9" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
+      <c r="C167" s="10" t="n">
+        <v>46022</v>
+      </c>
+      <c r="D167" s="5" t="n">
+        <v>0.358415765366999</v>
+      </c>
+      <c r="E167" s="5" t="n">
+        <v>0.1491474539086255</v>
+      </c>
+      <c r="F167" s="5" t="n">
+        <v>0.09245217659058542</v>
+      </c>
+      <c r="G167" s="5" t="n">
+        <v>-0.08767945806550941</v>
+      </c>
+      <c r="H167" s="5" t="n">
+        <v>0.1565616096866097</v>
+      </c>
+      <c r="I167" s="5" t="n"/>
+      <c r="J167" s="5" t="n"/>
+      <c r="K167" s="9" t="n">
+        <v>0.4299568568162543</v>
+      </c>
+      <c r="L167" s="9" t="n">
+        <v>0.6693476318141197</v>
+      </c>
+      <c r="M167" s="9" t="n">
+        <v>0.6126531041370972</v>
+      </c>
+      <c r="N167" s="5" t="n">
+        <v>0.1129466425753162</v>
+      </c>
+      <c r="O167" s="5" t="n">
+        <v>0.06062675355907546</v>
+      </c>
+      <c r="P167" s="5" t="n">
+        <v>0.07297447770981946</v>
+      </c>
+      <c r="Q167" s="9" t="n">
+        <v>7.807692307692307</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Q1 2026</t>
+        </is>
+      </c>
+      <c r="C168" s="10" t="n">
+        <v>46112</v>
+      </c>
+      <c r="D168" s="5" t="n">
+        <v>0.3682056579783852</v>
+      </c>
+      <c r="E168" s="5" t="n">
+        <v>0.1505483153210426</v>
+      </c>
+      <c r="F168" s="5" t="n">
+        <v>0.08928003814367451</v>
+      </c>
+      <c r="G168" s="5" t="n">
+        <v>0.1963207247298156</v>
+      </c>
+      <c r="H168" s="5" t="n">
+        <v>-0.03129209807166776</v>
+      </c>
+      <c r="I168" s="5" t="n">
+        <v>0.0654925701706109</v>
+      </c>
+      <c r="J168" s="5" t="n">
+        <v>-0.2983425414364641</v>
+      </c>
+      <c r="K168" s="9" t="n">
+        <v>0.4356441108290098</v>
+      </c>
+      <c r="L168" s="9" t="n">
+        <v>0.6790989150539712</v>
+      </c>
+      <c r="M168" s="9" t="n">
+        <v>0.6216768351599812</v>
+      </c>
+      <c r="N168" s="5" t="n">
+        <v>0.1032490709055451</v>
+      </c>
+      <c r="O168" s="5" t="n">
+        <v>0.05469332462710205</v>
+      </c>
+      <c r="P168" s="5" t="n">
+        <v>0.07399683476965635</v>
+      </c>
+      <c r="Q168" s="9" t="n">
+        <v>7.95819209039548</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -12300,8 +12719,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y162"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:Y168"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
@@ -12316,7 +12735,7 @@
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
@@ -23932,6 +24351,448 @@
         <v>-30434000</v>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Q4 2024</t>
+        </is>
+      </c>
+      <c r="C163" s="10" t="n">
+        <v>45657</v>
+      </c>
+      <c r="D163" s="3" t="n"/>
+      <c r="E163" s="3" t="n"/>
+      <c r="F163" s="3" t="n"/>
+      <c r="G163" s="3" t="n"/>
+      <c r="H163" s="3" t="n"/>
+      <c r="I163" s="3" t="n"/>
+      <c r="J163" s="8" t="n"/>
+      <c r="K163" s="8" t="n"/>
+      <c r="L163" s="3" t="n"/>
+      <c r="M163" s="3" t="n"/>
+      <c r="N163" s="3" t="n"/>
+      <c r="O163" s="3" t="n"/>
+      <c r="P163" s="3" t="n"/>
+      <c r="Q163" s="3" t="n"/>
+      <c r="R163" s="3" t="n"/>
+      <c r="S163" s="3" t="n"/>
+      <c r="T163" s="3" t="n"/>
+      <c r="U163" s="3" t="n"/>
+      <c r="V163" s="3" t="n"/>
+      <c r="W163" s="3" t="n"/>
+      <c r="X163" s="3" t="n"/>
+      <c r="Y163" s="3" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
+      <c r="C164" s="10" t="n">
+        <v>45747</v>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>23621000000</v>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>8811000000</v>
+      </c>
+      <c r="F164" s="3" t="n">
+        <v>3506000000</v>
+      </c>
+      <c r="G164" s="3" t="n">
+        <v>3558000000</v>
+      </c>
+      <c r="H164" s="3" t="n">
+        <v>4882000000</v>
+      </c>
+      <c r="I164" s="3" t="n">
+        <v>3275000000</v>
+      </c>
+      <c r="J164" s="8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="K164" s="8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="L164" s="3" t="n">
+        <v>471000000</v>
+      </c>
+      <c r="M164" s="3" t="n">
+        <v>5852000000</v>
+      </c>
+      <c r="N164" s="3" t="n">
+        <v>195833000000</v>
+      </c>
+      <c r="O164" s="3" t="n">
+        <v>22735000000</v>
+      </c>
+      <c r="P164" s="3" t="n">
+        <v>42889000000</v>
+      </c>
+      <c r="Q164" s="3" t="n">
+        <v>36443000000</v>
+      </c>
+      <c r="R164" s="3" t="n">
+        <v>104339000000</v>
+      </c>
+      <c r="S164" s="3" t="n">
+        <v>34029000000</v>
+      </c>
+      <c r="T164" s="3" t="n">
+        <v>1999000000</v>
+      </c>
+      <c r="U164" s="3" t="n">
+        <v>6753000000</v>
+      </c>
+      <c r="V164" s="3" t="n">
+        <v>-1862000000</v>
+      </c>
+      <c r="W164" s="3" t="n">
+        <v>4891000000</v>
+      </c>
+      <c r="X164" s="3" t="n">
+        <v>-1898000000</v>
+      </c>
+      <c r="Y164" s="3" t="n">
+        <v>-4556000000</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Q2 2025</t>
+        </is>
+      </c>
+      <c r="C165" s="10" t="n">
+        <v>45838</v>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>23650000000</v>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>9118000000</v>
+      </c>
+      <c r="F165" s="3" t="n">
+        <v>3645000000</v>
+      </c>
+      <c r="G165" s="3" t="n">
+        <v>3649000000</v>
+      </c>
+      <c r="H165" s="3" t="n">
+        <v>4981000000</v>
+      </c>
+      <c r="I165" s="3" t="n">
+        <v>5262000000</v>
+      </c>
+      <c r="J165" s="8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K165" s="8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="L165" s="3" t="n">
+        <v>438000000</v>
+      </c>
+      <c r="M165" s="3" t="n">
+        <v>5367000000</v>
+      </c>
+      <c r="N165" s="3" t="n">
+        <v>196612000000</v>
+      </c>
+      <c r="O165" s="3" t="n">
+        <v>23820000000</v>
+      </c>
+      <c r="P165" s="3" t="n">
+        <v>42263000000</v>
+      </c>
+      <c r="Q165" s="3" t="n">
+        <v>36531000000</v>
+      </c>
+      <c r="R165" s="3" t="n">
+        <v>109145000000</v>
+      </c>
+      <c r="S165" s="3" t="n">
+        <v>32972000000</v>
+      </c>
+      <c r="T165" s="3" t="n">
+        <v>2080000000</v>
+      </c>
+      <c r="U165" s="3" t="n">
+        <v>3669000000</v>
+      </c>
+      <c r="V165" s="3" t="n">
+        <v>-1780000000</v>
+      </c>
+      <c r="W165" s="3" t="n">
+        <v>1889000000</v>
+      </c>
+      <c r="X165" s="3" t="n">
+        <v>-1720000000</v>
+      </c>
+      <c r="Y165" s="3" t="n">
+        <v>-2537000000</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Q3 2025</t>
+        </is>
+      </c>
+      <c r="C166" s="10" t="n">
+        <v>45930</v>
+      </c>
+      <c r="D166" s="3" t="n">
+        <v>22464000000</v>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>8446000000</v>
+      </c>
+      <c r="F166" s="3" t="n">
+        <v>2603000000</v>
+      </c>
+      <c r="G166" s="3" t="n">
+        <v>2461000000</v>
+      </c>
+      <c r="H166" s="3" t="n">
+        <v>3855000000</v>
+      </c>
+      <c r="I166" s="3" t="n">
+        <v>1313000000</v>
+      </c>
+      <c r="J166" s="8" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K166" s="8" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L166" s="3" t="n">
+        <v>416000000</v>
+      </c>
+      <c r="M166" s="3" t="n">
+        <v>5695000000</v>
+      </c>
+      <c r="N166" s="3" t="n">
+        <v>197514000000</v>
+      </c>
+      <c r="O166" s="3" t="n">
+        <v>24267000000</v>
+      </c>
+      <c r="P166" s="3" t="n">
+        <v>44877000000</v>
+      </c>
+      <c r="Q166" s="3" t="n">
+        <v>35315000000</v>
+      </c>
+      <c r="R166" s="3" t="n">
+        <v>109869000000</v>
+      </c>
+      <c r="S166" s="3" t="n">
+        <v>34162000000</v>
+      </c>
+      <c r="T166" s="3" t="n">
+        <v>2134000000</v>
+      </c>
+      <c r="U166" s="3" t="n">
+        <v>4474000000</v>
+      </c>
+      <c r="V166" s="3" t="n">
+        <v>-1916000000</v>
+      </c>
+      <c r="W166" s="3" t="n">
+        <v>2558000000</v>
+      </c>
+      <c r="X166" s="3" t="n">
+        <v>-1850000000</v>
+      </c>
+      <c r="Y166" s="3" t="n">
+        <v>-2276000000</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
+      <c r="C167" s="10" t="n">
+        <v>46022</v>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>25981000000</v>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>9312000000</v>
+      </c>
+      <c r="F167" s="3" t="n">
+        <v>3875000000</v>
+      </c>
+      <c r="G167" s="3" t="n">
+        <v>4136000000</v>
+      </c>
+      <c r="H167" s="3" t="n">
+        <v>5452000000</v>
+      </c>
+      <c r="I167" s="3" t="n">
+        <v>2402000000</v>
+      </c>
+      <c r="J167" s="8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="K167" s="8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="L167" s="3" t="n">
+        <v>443000000</v>
+      </c>
+      <c r="M167" s="3" t="n">
+        <v>5678000000</v>
+      </c>
+      <c r="N167" s="3" t="n">
+        <v>202089000000</v>
+      </c>
+      <c r="O167" s="3" t="n">
+        <v>25466000000</v>
+      </c>
+      <c r="P167" s="3" t="n">
+        <v>46640000000</v>
+      </c>
+      <c r="Q167" s="3" t="n">
+        <v>35821000000</v>
+      </c>
+      <c r="R167" s="3" t="n">
+        <v>108476000000</v>
+      </c>
+      <c r="S167" s="3" t="n">
+        <v>38046000000</v>
+      </c>
+      <c r="T167" s="3" t="n">
+        <v>2157000000</v>
+      </c>
+      <c r="U167" s="3" t="n">
+        <v>735000000</v>
+      </c>
+      <c r="V167" s="3" t="n">
+        <v>-3013000000</v>
+      </c>
+      <c r="W167" s="3" t="n">
+        <v>-2278000000</v>
+      </c>
+      <c r="X167" s="3" t="n">
+        <v>-2737000000</v>
+      </c>
+      <c r="Y167" s="3" t="n">
+        <v>1984000000</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Q1 2026</t>
+        </is>
+      </c>
+      <c r="C168" s="10" t="n">
+        <v>46112</v>
+      </c>
+      <c r="D168" s="3" t="n">
+        <v>25168000000</v>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>9267000000</v>
+      </c>
+      <c r="F168" s="3" t="n">
+        <v>3789000000</v>
+      </c>
+      <c r="G168" s="3" t="n">
+        <v>3840000000</v>
+      </c>
+      <c r="H168" s="3" t="n">
+        <v>5245000000</v>
+      </c>
+      <c r="I168" s="3" t="n">
+        <v>2247000000</v>
+      </c>
+      <c r="J168" s="8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="K168" s="8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L168" s="3" t="n">
+        <v>473000000</v>
+      </c>
+      <c r="M168" s="3" t="n">
+        <v>5682000000</v>
+      </c>
+      <c r="N168" s="3" t="n">
+        <v>205217000000</v>
+      </c>
+      <c r="O168" s="3" t="n">
+        <v>24599000000</v>
+      </c>
+      <c r="P168" s="3" t="n">
+        <v>47358000000</v>
+      </c>
+      <c r="Q168" s="3" t="n">
+        <v>38471000000</v>
+      </c>
+      <c r="R168" s="3" t="n">
+        <v>108708000000</v>
+      </c>
+      <c r="S168" s="3" t="n">
+        <v>36223000000</v>
+      </c>
+      <c r="T168" s="3" t="n">
+        <v>2080000000</v>
+      </c>
+      <c r="U168" s="3" t="n">
+        <v>6914000000</v>
+      </c>
+      <c r="V168" s="3" t="n">
+        <v>-1973000000</v>
+      </c>
+      <c r="W168" s="3" t="n">
+        <v>4941000000</v>
+      </c>
+      <c r="X168" s="3" t="n">
+        <v>-2732000000</v>
+      </c>
+      <c r="Y168" s="3" t="n">
+        <v>-4146000000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -23946,8 +24807,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I239"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:I249"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
@@ -34714,6 +35575,456 @@
       <c r="I239" t="inlineStr">
         <is>
           <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Netflix desperately needs M&amp;A, but there's also a second 'emerging' threat to deal with</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Yahoo Finance Video</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/video/netflix-desperately-needs-ma-but-theres-also-a-second-emerging-threat-to-deal-with-161048162.html</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Streaming competitive dynamics and consolidation pressures affecting Netflix could reshape the industry landscape Disney competes in.</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Walt Disney vs. Netflix: What Their Revenue Trends Tell Investors</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Motley Fool</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/coverage/charts/2026/07/07/walt-disney-vs-netflix-what-their-revenue-trends-tell-investors/</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Disney's shrinking revenue lead over Netflix signals intensifying streaming competition that could pressure DIS's long-term market position and growth.</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Walt Disney (DIS) On FCC Scrutiny Is The Bull Case Still Intact</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Simply Wall St.</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/walt-disney-dis-fcc-scrutiny-161546103.html</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Regulatory scrutiny of ABC broadcast licenses introduces compliance risks and potential headwinds that could pressure Disney's media segment and long-term valuation.</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Disney's ABC spars with the FCC (again) in defense of 'The View'</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>LA Times</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/politics/articles/disneys-abc-blasts-fcc-again-155136918.html</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Regulatory scrutiny of ABC's programming could pressure Disney's broadcast licenses and content flexibility, though financial impact appears limited near-term.</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>The Retirement Portfolio Sweet Spot Explained With Real Examples</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/07/the-retirement-portfolio-sweet-spot-explained-with-real-examples/</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>This generic listicle offers no DIS-specific insight, making it largely irrelevant for assessing Disney's long-term investment thesis.</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>What The Selloff In CMCSA Ignores About Its Cash</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Trefis</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>https://www.trefis.com/articles/605914/what-the-selloff-in-cmcsa-ignores-about-its-cash/2026-07-07</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Comcast's undervaluation on strong cash flow signals sector-wide pessimism that could similarly mispricing Disney's own cash-generating media assets.</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="10" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>$50M Disney settlement: What to know to claim your share</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>USA TODAY</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>https://www.usatoday.com/story/money/2026/07/06/disney-streaming-settlement-claim-50-million-espn/90826973007/</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>A $50M settlement is immaterial to Disney's finances but signals ongoing streaming compliance risks that could invite future litigation.</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="10" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Disney World closing one of Epcot's most iconic restaurants</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>TheStreet</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>https://www.thestreet.com/restaurants/disney-world-epcot-coral-reef-restaurant-closing</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>A single restaurant closure is immaterial to DIS financials and likely reflects routine park refurbishment rather than any strategic shift.</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="10" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Walt Disney (DIS) Stock Drops Despite Market Gains: Important Facts to Note</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/walt-disney-dis-stock-drops-214505753.html</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Short-term daily price movements diverging from the broader market carry little significance for long-term fundamentals or investment thesis in Disney.</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="10" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>How Wide Is The Range Of Possibilities For Netflix Stock?</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Trefis</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>https://www.trefis.com/articles/605497/how-wide-is-the-range-of-possibilities-for-netflix-stock/2026-07-06</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Elevated volatility expectations for Netflix signal broader streaming sector uncertainty that could similarly affect Disney's direct-to-consumer valuation.</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Competition</t>
         </is>
       </c>
     </row>
@@ -34732,7 +36043,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:P26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>

--- a/Investment_Research_Dashboard.xlsx
+++ b/Investment_Research_Dashboard.xlsx
@@ -188,7 +188,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DashboardTable" displayName="DashboardTable" ref="A1:R28" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DashboardTable" displayName="DashboardTable" ref="A1:R29" headerRowCount="1">
   <autoFilter ref="A1:R2"/>
   <tableColumns count="18">
     <tableColumn id="1" name="Ticker"/>
@@ -215,7 +215,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WatchlistTable" displayName="WatchlistTable" ref="A1:I28" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WatchlistTable" displayName="WatchlistTable" ref="A1:I29" headerRowCount="1">
   <autoFilter ref="A1:I2"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Ticker"/>
@@ -233,7 +233,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ValuationTable" displayName="ValuationTable" ref="A1:R28" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ValuationTable" displayName="ValuationTable" ref="A1:R29" headerRowCount="1">
   <autoFilter ref="A1:R2"/>
   <tableColumns count="18">
     <tableColumn id="1" name="Ticker"/>
@@ -260,7 +260,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="RatiosTable" displayName="RatiosTable" ref="A1:Q168" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="RatiosTable" displayName="RatiosTable" ref="A1:Q174" headerRowCount="1">
   <autoFilter ref="A1:Q7"/>
   <tableColumns count="17">
     <tableColumn id="1" name="Ticker"/>
@@ -286,7 +286,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FinancialsTable" displayName="FinancialsTable" ref="A1:Y168" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FinancialsTable" displayName="FinancialsTable" ref="A1:Y174" headerRowCount="1">
   <autoFilter ref="A1:Y7"/>
   <tableColumns count="25">
     <tableColumn id="1" name="Ticker"/>
@@ -320,7 +320,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="NewsTable" displayName="NewsTable" ref="A1:I249" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="NewsTable" displayName="NewsTable" ref="A1:I259" headerRowCount="1">
   <autoFilter ref="A1:I11"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Date"/>
@@ -338,7 +338,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="NarrativeTable" displayName="NarrativeTable" ref="A1:P26" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="NarrativeTable" displayName="NarrativeTable" ref="A1:P27" headerRowCount="1">
   <autoFilter ref="A1:P2"/>
   <tableColumns count="16">
     <tableColumn id="1" name="Ticker"/>
@@ -651,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -668,7 +668,7 @@
     <col width="21" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="21" customWidth="1" min="18" max="18"/>
@@ -2617,6 +2617,74 @@
         <v>0.4356441108290098</v>
       </c>
       <c r="R28" s="10" t="n">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Software - Infrastructure</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc. builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States, the United Kingdom, and internationally. It provides Palantir Gotham integrates with other platforms for defense offerings which enables users to see, understand, and act in the modern battlespace; operations centers to the tactical edge; integrating data from domains and sensors in near real-time; and situational awareness and accelerating operational decision-making, as well as facilitates the hand-off between analysts and operational users, helping operators plan and execute real-world responses to threats that have been identified within the platform. The company also offers Palantir Foundry, a platform that helps organizations operate by creating a central operating system for their data; and allows individual users to integrate and analyze the data they need in one place. In addition, it provides Palantir Apollo, a software that delivers software and updates across the business, as well as enables customers to deploy their software virtually in any environment; and Palantir Artificial Intelligence Platform that provides unified access to open-source, self-hosted, and commercial large language models (LLMs) that can transform structured and unstructured data into LLM-understandable objects and can turn organizations' actions and processes into tools for humans and LLM-driven agents. The company also has a strategic partnership with Ondas Inc. to develop and deploy AI-enabled operational capabilities to scale stratospheric, aerial, and land-based ISR missions. The company was incorporated in 2003 and is headquartered in Aventura, Florida.</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>134.37</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>322126807040</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>150.97752</v>
+      </c>
+      <c r="I29" s="9" t="n">
+        <v>64.15434</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>1.8605</v>
+      </c>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n">
+        <v>0.8471163256416494</v>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>0.5332206693319728</v>
+      </c>
+      <c r="N29" s="5" t="n">
+        <v>0.2700142005663421</v>
+      </c>
+      <c r="O29" s="9" t="n">
+        <v>0.0250870360155192</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Overvalued</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Palantir is one of the highest-quality growth-software franchises available: accelerating revenue, rapidly expanding margins, prodigious free cash flow, a debt-free fortress balance sheet, and rising ...</t>
+        </is>
+      </c>
+      <c r="R29" s="10" t="n">
         <v>46210</v>
       </c>
     </row>
@@ -2936,6 +3004,17 @@
       <formula>"Fairly Valued"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P29">
+    <cfRule type="cellIs" priority="88" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="89" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="90" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2949,7 +3028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3496,6 +3575,24 @@
       </c>
       <c r="G28" s="8" t="n"/>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -3510,7 +3607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5179,6 +5276,62 @@
         <v>9560960</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>134.37</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>322126807040</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>310031908864</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>2296071334</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>150.97752</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>64.15434</v>
+      </c>
+      <c r="I29" s="9" t="n">
+        <v>1.8605</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>61.66081</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>38.11915</v>
+      </c>
+      <c r="L29" s="9" t="n">
+        <v>59.346</v>
+      </c>
+      <c r="M29" s="9" t="n">
+        <v>153.614</v>
+      </c>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="9" t="n">
+        <v>1.562</v>
+      </c>
+      <c r="P29" s="8" t="n">
+        <v>207.52</v>
+      </c>
+      <c r="Q29" s="8" t="n">
+        <v>106.37</v>
+      </c>
+      <c r="R29" s="7" t="n">
+        <v>46368559</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -5193,20 +5346,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q168"/>
+  <dimension ref="A1:Q174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
@@ -12705,6 +12858,274 @@
         <v>7.95819209039548</v>
       </c>
     </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Q4 2024</t>
+        </is>
+      </c>
+      <c r="C169" s="10" t="n">
+        <v>45657</v>
+      </c>
+      <c r="D169" s="5" t="n"/>
+      <c r="E169" s="5" t="n"/>
+      <c r="F169" s="5" t="n"/>
+      <c r="G169" s="5" t="n"/>
+      <c r="H169" s="5" t="n"/>
+      <c r="I169" s="5" t="n"/>
+      <c r="J169" s="5" t="n"/>
+      <c r="K169" s="9" t="n"/>
+      <c r="L169" s="9" t="n"/>
+      <c r="M169" s="9" t="n"/>
+      <c r="N169" s="5" t="n"/>
+      <c r="O169" s="5" t="n"/>
+      <c r="P169" s="5" t="n"/>
+      <c r="Q169" s="9" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
+      <c r="C170" s="10" t="n">
+        <v>45747</v>
+      </c>
+      <c r="D170" s="5" t="n">
+        <v>0.804300479150992</v>
+      </c>
+      <c r="E170" s="5" t="n">
+        <v>0.1991819925213977</v>
+      </c>
+      <c r="F170" s="5" t="n">
+        <v>0.2421562360341911</v>
+      </c>
+      <c r="G170" s="5" t="n">
+        <v>0.344037200672056</v>
+      </c>
+      <c r="H170" s="5" t="n"/>
+      <c r="I170" s="5" t="n"/>
+      <c r="J170" s="5" t="n"/>
+      <c r="K170" s="9" t="n">
+        <v>0.04509384411028077</v>
+      </c>
+      <c r="L170" s="9" t="n">
+        <v>6.494024970980202</v>
+      </c>
+      <c r="M170" s="9" t="n">
+        <v>6.494024970980202</v>
+      </c>
+      <c r="N170" s="5" t="n"/>
+      <c r="O170" s="5" t="n"/>
+      <c r="P170" s="5" t="n"/>
+      <c r="Q170" s="9" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Q2 2025</t>
+        </is>
+      </c>
+      <c r="C171" s="10" t="n">
+        <v>45838</v>
+      </c>
+      <c r="D171" s="5" t="n">
+        <v>0.8077766497259631</v>
+      </c>
+      <c r="E171" s="5" t="n">
+        <v>0.2683250024658836</v>
+      </c>
+      <c r="F171" s="5" t="n">
+        <v>0.3255235394745625</v>
+      </c>
+      <c r="G171" s="5" t="n">
+        <v>0.5296588512270137</v>
+      </c>
+      <c r="H171" s="5" t="n">
+        <v>0.1355901137630041</v>
+      </c>
+      <c r="I171" s="5" t="n"/>
+      <c r="J171" s="5" t="n"/>
+      <c r="K171" s="9" t="n">
+        <v>0.04011063770503168</v>
+      </c>
+      <c r="L171" s="9" t="n">
+        <v>6.323549979809846</v>
+      </c>
+      <c r="M171" s="9" t="n">
+        <v>6.323549979809846</v>
+      </c>
+      <c r="N171" s="5" t="n"/>
+      <c r="O171" s="5" t="n"/>
+      <c r="P171" s="5" t="n"/>
+      <c r="Q171" s="9" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Q3 2025</t>
+        </is>
+      </c>
+      <c r="C172" s="10" t="n">
+        <v>45930</v>
+      </c>
+      <c r="D172" s="5" t="n">
+        <v>0.8244785334249999</v>
+      </c>
+      <c r="E172" s="5" t="n">
+        <v>0.3329596678328191</v>
+      </c>
+      <c r="F172" s="5" t="n">
+        <v>0.4026773528226421</v>
+      </c>
+      <c r="G172" s="5" t="n">
+        <v>0.4240753472210463</v>
+      </c>
+      <c r="H172" s="5" t="n">
+        <v>0.1767415863552447</v>
+      </c>
+      <c r="I172" s="5" t="n"/>
+      <c r="J172" s="5" t="n"/>
+      <c r="K172" s="9" t="n">
+        <v>0.03572377454249379</v>
+      </c>
+      <c r="L172" s="9" t="n">
+        <v>6.426750863899872</v>
+      </c>
+      <c r="M172" s="9" t="n">
+        <v>6.426750863899872</v>
+      </c>
+      <c r="N172" s="5" t="n"/>
+      <c r="O172" s="5" t="n"/>
+      <c r="P172" s="5" t="n"/>
+      <c r="Q172" s="9" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
+      <c r="C173" s="10" t="n">
+        <v>46022</v>
+      </c>
+      <c r="D173" s="5" t="n">
+        <v>0.8464844377531451</v>
+      </c>
+      <c r="E173" s="5" t="n">
+        <v>0.4090085171900523</v>
+      </c>
+      <c r="F173" s="5" t="n">
+        <v>0.4326664306704142</v>
+      </c>
+      <c r="G173" s="5" t="n">
+        <v>0.5430920627067632</v>
+      </c>
+      <c r="H173" s="5" t="n">
+        <v>0.1911028099419859</v>
+      </c>
+      <c r="I173" s="5" t="n"/>
+      <c r="J173" s="5" t="n"/>
+      <c r="K173" s="9" t="n">
+        <v>0.03104503586440887</v>
+      </c>
+      <c r="L173" s="9" t="n">
+        <v>7.109823993412619</v>
+      </c>
+      <c r="M173" s="9" t="n">
+        <v>7.109823993412619</v>
+      </c>
+      <c r="N173" s="5" t="n">
+        <v>0.2199775343198595</v>
+      </c>
+      <c r="O173" s="5" t="n">
+        <v>0.1825799358050746</v>
+      </c>
+      <c r="P173" s="5" t="n">
+        <v>0.1803820640387805</v>
+      </c>
+      <c r="Q173" s="9" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Q1 2026</t>
+        </is>
+      </c>
+      <c r="C174" s="10" t="n">
+        <v>46112</v>
+      </c>
+      <c r="D174" s="5" t="n">
+        <v>0.8678180527421883</v>
+      </c>
+      <c r="E174" s="5" t="n">
+        <v>0.4618435938632217</v>
+      </c>
+      <c r="F174" s="5" t="n">
+        <v>0.5332206693319728</v>
+      </c>
+      <c r="G174" s="5" t="n">
+        <v>0.5462288900472442</v>
+      </c>
+      <c r="H174" s="5" t="n">
+        <v>0.1604923791692079</v>
+      </c>
+      <c r="I174" s="5" t="n">
+        <v>0.8471163256416494</v>
+      </c>
+      <c r="J174" s="5" t="n">
+        <v>3.243793452076339</v>
+      </c>
+      <c r="K174" s="9" t="n">
+        <v>0.0250870360155192</v>
+      </c>
+      <c r="L174" s="9" t="n">
+        <v>6.906765180783962</v>
+      </c>
+      <c r="M174" s="9" t="n">
+        <v>6.906765180783962</v>
+      </c>
+      <c r="N174" s="5" t="n">
+        <v>0.2700142005663421</v>
+      </c>
+      <c r="O174" s="5" t="n">
+        <v>0.2236972314351061</v>
+      </c>
+      <c r="P174" s="5" t="n">
+        <v>0.2470408362060399</v>
+      </c>
+      <c r="Q174" s="9" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -12719,7 +13140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y168"/>
+  <dimension ref="A1:Y174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12735,7 +13156,7 @@
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
@@ -24793,6 +25214,428 @@
         <v>-4146000000</v>
       </c>
     </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Q4 2024</t>
+        </is>
+      </c>
+      <c r="C169" s="10" t="n">
+        <v>45657</v>
+      </c>
+      <c r="D169" s="3" t="n"/>
+      <c r="E169" s="3" t="n"/>
+      <c r="F169" s="3" t="n"/>
+      <c r="G169" s="3" t="n"/>
+      <c r="H169" s="3" t="n"/>
+      <c r="I169" s="3" t="n"/>
+      <c r="J169" s="8" t="n"/>
+      <c r="K169" s="8" t="n"/>
+      <c r="L169" s="3" t="n"/>
+      <c r="M169" s="3" t="n"/>
+      <c r="N169" s="3" t="n"/>
+      <c r="O169" s="3" t="n"/>
+      <c r="P169" s="3" t="n"/>
+      <c r="Q169" s="3" t="n"/>
+      <c r="R169" s="3" t="n"/>
+      <c r="S169" s="3" t="n"/>
+      <c r="T169" s="3" t="n"/>
+      <c r="U169" s="3" t="n"/>
+      <c r="V169" s="3" t="n"/>
+      <c r="W169" s="3" t="n"/>
+      <c r="X169" s="3" t="n"/>
+      <c r="Y169" s="3" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
+      <c r="C170" s="10" t="n">
+        <v>45747</v>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>883855000</v>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>710885000</v>
+      </c>
+      <c r="F170" s="3" t="n">
+        <v>176048000</v>
+      </c>
+      <c r="G170" s="3" t="n">
+        <v>176048000</v>
+      </c>
+      <c r="H170" s="3" t="n">
+        <v>182670000</v>
+      </c>
+      <c r="I170" s="3" t="n">
+        <v>214031000</v>
+      </c>
+      <c r="J170" s="8" t="n">
+        <v>0.090131</v>
+      </c>
+      <c r="K170" s="8" t="n">
+        <v>0.08011699999999999</v>
+      </c>
+      <c r="L170" s="3" t="n"/>
+      <c r="M170" s="3" t="n">
+        <v>993464000</v>
+      </c>
+      <c r="N170" s="3" t="n">
+        <v>6736917000</v>
+      </c>
+      <c r="O170" s="3" t="n">
+        <v>6282599000</v>
+      </c>
+      <c r="P170" s="3" t="n">
+        <v>244596000</v>
+      </c>
+      <c r="Q170" s="3" t="n">
+        <v>200177000</v>
+      </c>
+      <c r="R170" s="3" t="n">
+        <v>5424155000</v>
+      </c>
+      <c r="S170" s="3" t="n">
+        <v>967443000</v>
+      </c>
+      <c r="T170" s="3" t="n"/>
+      <c r="U170" s="3" t="n">
+        <v>310263000</v>
+      </c>
+      <c r="V170" s="3" t="n">
+        <v>-6184000</v>
+      </c>
+      <c r="W170" s="3" t="n">
+        <v>304079000</v>
+      </c>
+      <c r="X170" s="3" t="n">
+        <v>-1390277000</v>
+      </c>
+      <c r="Y170" s="3" t="n">
+        <v>-28897000</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Q2 2025</t>
+        </is>
+      </c>
+      <c r="C171" s="10" t="n">
+        <v>45838</v>
+      </c>
+      <c r="D171" s="3" t="n">
+        <v>1003697000</v>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>810763000</v>
+      </c>
+      <c r="F171" s="3" t="n">
+        <v>269317000</v>
+      </c>
+      <c r="G171" s="3" t="n">
+        <v>269317000</v>
+      </c>
+      <c r="H171" s="3" t="n">
+        <v>275847000</v>
+      </c>
+      <c r="I171" s="3" t="n">
+        <v>326727000</v>
+      </c>
+      <c r="J171" s="8" t="n">
+        <v>0.140204</v>
+      </c>
+      <c r="K171" s="8" t="n">
+        <v>0.13019</v>
+      </c>
+      <c r="L171" s="3" t="n"/>
+      <c r="M171" s="3" t="n">
+        <v>929547000</v>
+      </c>
+      <c r="N171" s="3" t="n">
+        <v>7365688000</v>
+      </c>
+      <c r="O171" s="3" t="n">
+        <v>6890393000</v>
+      </c>
+      <c r="P171" s="3" t="n">
+        <v>237812000</v>
+      </c>
+      <c r="Q171" s="3" t="n">
+        <v>192347000</v>
+      </c>
+      <c r="R171" s="3" t="n">
+        <v>5928901000</v>
+      </c>
+      <c r="S171" s="3" t="n">
+        <v>1089640000</v>
+      </c>
+      <c r="T171" s="3" t="n"/>
+      <c r="U171" s="3" t="n">
+        <v>539251000</v>
+      </c>
+      <c r="V171" s="3" t="n">
+        <v>-7634000</v>
+      </c>
+      <c r="W171" s="3" t="n">
+        <v>531617000</v>
+      </c>
+      <c r="X171" s="3" t="n">
+        <v>-617010000</v>
+      </c>
+      <c r="Y171" s="3" t="n">
+        <v>6450000</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Q3 2025</t>
+        </is>
+      </c>
+      <c r="C172" s="10" t="n">
+        <v>45930</v>
+      </c>
+      <c r="D172" s="3" t="n">
+        <v>1181092000</v>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>973785000</v>
+      </c>
+      <c r="F172" s="3" t="n">
+        <v>393256000</v>
+      </c>
+      <c r="G172" s="3" t="n">
+        <v>393256000</v>
+      </c>
+      <c r="H172" s="3" t="n">
+        <v>399231000</v>
+      </c>
+      <c r="I172" s="3" t="n">
+        <v>475599000</v>
+      </c>
+      <c r="J172" s="8" t="n">
+        <v>0.200292</v>
+      </c>
+      <c r="K172" s="8" t="n">
+        <v>0.180263</v>
+      </c>
+      <c r="L172" s="3" t="n"/>
+      <c r="M172" s="3" t="n">
+        <v>1615967000</v>
+      </c>
+      <c r="N172" s="3" t="n">
+        <v>8113960000</v>
+      </c>
+      <c r="O172" s="3" t="n">
+        <v>7586156000</v>
+      </c>
+      <c r="P172" s="3" t="n">
+        <v>235436000</v>
+      </c>
+      <c r="Q172" s="3" t="n">
+        <v>189165000</v>
+      </c>
+      <c r="R172" s="3" t="n">
+        <v>6590457000</v>
+      </c>
+      <c r="S172" s="3" t="n">
+        <v>1180403000</v>
+      </c>
+      <c r="T172" s="3" t="n"/>
+      <c r="U172" s="3" t="n">
+        <v>507664000</v>
+      </c>
+      <c r="V172" s="3" t="n">
+        <v>-6792000</v>
+      </c>
+      <c r="W172" s="3" t="n">
+        <v>500872000</v>
+      </c>
+      <c r="X172" s="3" t="n">
+        <v>181567000</v>
+      </c>
+      <c r="Y172" s="3" t="n">
+        <v>6435000</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
+      <c r="C173" s="10" t="n">
+        <v>46022</v>
+      </c>
+      <c r="D173" s="3" t="n">
+        <v>1406802000</v>
+      </c>
+      <c r="E173" s="3" t="n">
+        <v>1190836000</v>
+      </c>
+      <c r="F173" s="3" t="n">
+        <v>575394000</v>
+      </c>
+      <c r="G173" s="3" t="n">
+        <v>575394000</v>
+      </c>
+      <c r="H173" s="3" t="n">
+        <v>582412000</v>
+      </c>
+      <c r="I173" s="3" t="n">
+        <v>608676000</v>
+      </c>
+      <c r="J173" s="8" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K173" s="8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="L173" s="3" t="n"/>
+      <c r="M173" s="3" t="n">
+        <v>1423796000</v>
+      </c>
+      <c r="N173" s="3" t="n">
+        <v>8900392000</v>
+      </c>
+      <c r="O173" s="3" t="n">
+        <v>8358174000</v>
+      </c>
+      <c r="P173" s="3" t="n">
+        <v>229338000</v>
+      </c>
+      <c r="Q173" s="3" t="n">
+        <v>183474000</v>
+      </c>
+      <c r="R173" s="3" t="n">
+        <v>7387268000</v>
+      </c>
+      <c r="S173" s="3" t="n">
+        <v>1175581000</v>
+      </c>
+      <c r="T173" s="3" t="n"/>
+      <c r="U173" s="3" t="n">
+        <v>777295000</v>
+      </c>
+      <c r="V173" s="3" t="n">
+        <v>-13272000</v>
+      </c>
+      <c r="W173" s="3" t="n">
+        <v>764023000</v>
+      </c>
+      <c r="X173" s="3" t="n">
+        <v>-957831000</v>
+      </c>
+      <c r="Y173" s="3" t="n">
+        <v>-10898000</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Q1 2026</t>
+        </is>
+      </c>
+      <c r="C174" s="10" t="n">
+        <v>46112</v>
+      </c>
+      <c r="D174" s="3" t="n">
+        <v>1632583000</v>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>1416785000</v>
+      </c>
+      <c r="F174" s="3" t="n">
+        <v>753998000</v>
+      </c>
+      <c r="G174" s="3" t="n">
+        <v>753998000</v>
+      </c>
+      <c r="H174" s="3" t="n">
+        <v>760763000</v>
+      </c>
+      <c r="I174" s="3" t="n">
+        <v>870527000</v>
+      </c>
+      <c r="J174" s="8" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K174" s="8" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="L174" s="3" t="n"/>
+      <c r="M174" s="3" t="n">
+        <v>2291631000</v>
+      </c>
+      <c r="N174" s="3" t="n">
+        <v>10199183000</v>
+      </c>
+      <c r="O174" s="3" t="n">
+        <v>9551704000</v>
+      </c>
+      <c r="P174" s="3" t="n">
+        <v>211977000</v>
+      </c>
+      <c r="Q174" s="3" t="n">
+        <v>211977000</v>
+      </c>
+      <c r="R174" s="3" t="n">
+        <v>8449663000</v>
+      </c>
+      <c r="S174" s="3" t="n">
+        <v>1382949000</v>
+      </c>
+      <c r="T174" s="3" t="n"/>
+      <c r="U174" s="3" t="n">
+        <v>899165000</v>
+      </c>
+      <c r="V174" s="3" t="n">
+        <v>-7401000</v>
+      </c>
+      <c r="W174" s="3" t="n">
+        <v>891764000</v>
+      </c>
+      <c r="X174" s="3" t="n">
+        <v>-26724000</v>
+      </c>
+      <c r="Y174" s="3" t="n">
+        <v>3397000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -24807,7 +25650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I249"/>
+  <dimension ref="A1:I259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -36028,6 +36871,456 @@
         </is>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>The New AI Revolution Is Here: Buy These 3 Stocks Before They Surge</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Motley Fool</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/investing/2026/07/07/the-new-ai-revolution-is-here-buy-these-3-stocks-b/</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Positioning PLTR as a beneficiary of AI expansion beyond chips signals broadening software demand, though promotional framing warrants skepticism about durable fundamentals.</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Palantir Expands Mexico Insurance Deal</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>GuruFocus.com</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/technology/ai/articles/palantir-expands-mexico-insurance-deal-185123883.html</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Expanding an existing customer relationship signals product stickiness and land-and-expand success, validating Palantir's commercial growth strategy in international markets.</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Palantir Expands AI Deal With Mexico's GNP Seguros</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>GuruFocus.com</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/technology/ai/articles/palantir-expands-ai-deal-mexicos-184519529.html</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Expanding commercial AI adoption into international insurance signals growing recurring revenue and validates Palantir's platform beyond government contracts.</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Beyond the CIA: Palantir Moves Into Mexico’s Private Sector</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Barrons.com</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>https://www.barrons.com/articles/palantir-stock-price-insurer-deal-0ad3fbbc?siteid=yhoof2&amp;yptr=yahoo</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Expansion into Mexico's commercial market signals diversification beyond government contracts, potentially broadening PLTR's revenue base and reducing dependence on U.S. agencies.</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>QQQ, Meet IQQ. BlackRock Is Launching a Cheaper Nasdaq-100 ETF.</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Barrons.com</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>https://www.barrons.com/advisor/articles/qqq-meet-iqq-blackrock-is-launching-a-cheaper-nasdaq-100-etf-fded526b?siteid=yhoof2&amp;yptr=yahoo</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>This BlackRock ETF launch is unrelated to PLTR fundamentals and unlikely to materially affect long-term investment prospects.</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Palantir Vs. Google: Why Palantir is Surging in July and Should Investors Buy it Over Google</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/07/palantir-vs-google-why-palantir-is-surging-in-july-and-should-investors-buy-it-over-google/</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Palantir's NVIDIA sovereign AI partnership and enterprise momentum signal durable growth drivers that could sustain its premium valuation versus scaled peers.</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Is Palantir Technologies (PLTR) Undervalued After Its Nvidia Partnership And DA Davidson Upgrade?</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Simply Wall St.</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/palantir-technologies-pltr-undervalued-nvidia-171406194.html</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>An expanded Nvidia partnership plus analyst upgrade could strengthen PLTR's AI positioning in government and infrastructure, supporting long-term revenue growth potential.</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Palantir Stock Rises After Major AI Expansion Deal</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>GuruFocus.com</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/technology/ai/articles/palantir-stock-rises-major-ai-171058894.html</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Expanding AI adoption among large enterprise clients like insurers signals growing commercial demand and revenue diversification beyond government contracts.</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Meta Platforms vs. Nebius: Which Is the Better Neocloud Stock?</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/07/meta-platforms-vs-nebius-which-is-the-better-neocloud-stock/</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>The neocloud AI infrastructure trend signals expanding demand for AI compute, an ecosystem where PLTR competes for enterprise AI deployment dollars.</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Palantir Expands AI Deal With Mexico's Largest Insurer</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>GuruFocus.com</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/technology/ai/articles/palantir-expands-ai-deal-mexicos-165856855.html</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Expanding an existing commercial customer signals strong product stickiness and international growth potential in PLTR's non-government AI segment.</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -36042,7 +37335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -37995,6 +39288,80 @@
         <v>48</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Palantir is a dual-market software company selling data-integration and AI-orchestration platforms (Gotham, Foundry, Apollo, AIP) to government/defense and commercial customers. The financial data shows a business inflecting sharply: quarterly revenue grew from ~$884M in Q1 2025 to ~$1.63B in Q1 2026, with year-over-year growth in the most recent quarter of roughly 85%. Simultaneously, profitability has expanded dramatically—operating margin went from ~20% to ~46%, net margin to ~53%, and FCF margin holding above 54%. The balance sheet is pristine: ~$2.3B cash, negligible debt (D/E ~0.025), and a current ratio near 7. ROIC has climbed to ~25% and ROE to ~27% in the latest quarter. The core tension is valuation: at ~$134 the stock trades at ~59x EV/revenue, ~151x trailing P/E, and ~64x forward P/E, pricing in years of continued hypergrowth. Recent news centers on international commercial expansion (Mexico's GNP Seguros) and an expanded Nvidia partnership, both reinforcing the land-and-expand and AI-platform narrative. The fundamental business quality is exceptional; the debate is almost entirely about whether the price already discounts a near-flawless multi-year execution path.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>This is the first writeup, so there is no prior baseline to compare against. The most material items from the evidence: (1) The financial trajectory itself is the biggest development—accelerating revenue growth (QoQ ~13% to ~19% across recent quarters, YoY ~85% in Q1 2026) combined with rapid operating leverage, with operating margin more than doubling from ~20% to ~46% over five quarters. This is a genuine inflection, not incremental. (2) Commercial/international expansion via the expanded GNP Seguros insurance deal in Mexico signals successful land-and-expand outside U.S. government, an important diversification signpost. (3) An expanded Nvidia partnership around sovereign/enterprise AI, which if substantive strengthens PLTR's positioning in AI deployment. The news flow is heavily promotional and single-dated (all July 7, 2026), so I treat the deal headlines as directional confirmation of strategy rather than quantified catalysts—none carry disclosed contract values in the evidence.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Palantir is demonstrating the rare combination of accelerating top-line growth and expanding margins at scale—a signature of a platform with strong operating leverage and high incremental margins (gross margin ~87% and rising). If AIP is becoming the connective tissue for enterprise AI deployment, the addressable market is large and Palantir's early differentiation in operationalizing AI (turning models into actionable, governed workflows) could compound. The government/defense business provides a sticky, high-barrier revenue base with long procurement cycles and switching costs, while commercial and international (e.g., Mexico insurance) open a second growth engine that reduces government dependence. Free cash flow generation is already substantial (~$892M in Q1 2026) and self-funds growth with no debt reliance, so the company controls its own destiny. The Nvidia relationship and sovereign-AI positioning could extend the runway. If growth stays above 40-50% for several years while margins hold in the 40s%, today's multiple can be grown into.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>The valuation embeds near-perfection: ~59x EV/revenue and ~151x trailing earnings leave essentially no margin for a growth deceleration, competitive erosion, or margin reversion. Any quarter that misses the acceleration narrative could compress the multiple violently—the stock is already ~35% below its 52-week high of $207, showing how sensitive the price is. Government revenue concentration exposes the company to budget cycles, political shifts, and lumpy contract timing. The commercial AI platform space is contested by hyperscalers (Microsoft, Google) and a wave of AI-native tooling; PLTR's moat in enterprise AI orchestration is less proven than its government moat, and pricing power there is uncertain. Beta of 1.56 and heavy retail/momentum ownership imply high volatility. The news set is uniformly promotional and lacks quantified deal economics, which raises the risk that sentiment, not fundamentals, is driving near-term price. Stock-based compensation (implied by the eps vs diluted eps gap and historical PLTR patterns) can dilute shareholders even as GAAP profitability improves.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Exceptionally strong. Revenue is high-quality and accelerating: $884M (Q1'25) to $1,633M (Q1'26), with sequential growth of 13-19% and ~85% YoY. Margins have inflected impressively—gross margin ~80% to ~87%, operating margin ~20% to ~46%, net margin ~24% to ~53% (the latest quarter's net margin is flattered by items above operating income, since net income exceeds operating income, likely interest/investment income on the large cash balance and possibly tax effects). FCF is robust and consistent, with FCF margins of 34-54% and Q1'26 FCF of ~$892M against trivial capex (~$7M), reflecting an asset-light model. The balance sheet is fortress-like: ~$2.29B cash, total debt ~$212M (essentially all long-term), D/E ~0.025, current ratio ~6.9. Returns on capital are high and rising (ROIC ~25%, ROE ~27%, ROA ~22% in Q1'26). No dividend. The main watch item is dilution—diluted EPS ($0.34) trails basic EPS ($0.36), consistent with ongoing share-based compensation; no buyback evidence is provided. Overall, capital allocation appears conservative and self-funding, with growth requiring minimal reinvestment.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Overvalued</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>The business quality justifies a large premium, but the current multiples are extreme even for a hypergrowth, high-margin software leader: ~59x EV/revenue, ~154x EV/EBITDA, ~62x price/sales, ~151x trailing P/E, and ~64x forward P/E. A PEG of ~1.86 on the forward figure is not egregious if growth persists, but EV/revenue near 60x historically has been sustainable only for the shortest windows and typically re-rates lower as growth decelerates from hypergrowth toward maturity. The stock trades ~35% below its 52-week high ($207) and above its low ($106), indicating the market has already partly de-rated it. To defend today's price, an investor must underwrite multiple more years of 40%+ growth with margins expanding or holding in the mid-40s%—achievable but demanding. Against the company's own elevated multiple range and the reality that revenue-based multiples of this magnitude leave little downside cushion, I rate it Overvalued for a fundamentals-driven long-term buyer, while acknowledging the business could 'grow into' the multiple if execution stays flawless.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Palantir has a genuine, differentiated moat in its government/defense franchise: Gotham and mission-critical deployments carry high switching costs, security accreditations, deep integration into operational workflows, and long procurement relationships that are extremely hard for competitors to displace. This is reflected in sticky, high-margin recurring revenue. In commercial AI (Foundry/AIP), the moat is emerging but less established—the value proposition of operationalizing and governing AI across enterprise data is compelling, and the land-and-expand pattern (e.g., expanding the Mexico insurer relationship) suggests real stickiness once deployed. However, this arena is contested by hyperscalers (Microsoft, Google—the listed peers) with vast distribution and capital, plus numerous AI-native startups. Pricing power appears strong today given ~87% gross margins, but durability in commercial AI is unproven versus the entrenched government position. Net: a strong, defensible moat in government; a promising but not-yet-proven moat commercially.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>The multi-year growth runway looks substantial if AI deployment demand persists and Palantir remains a preferred platform for turning AI into governed, actionable enterprise workflows. Tailwinds include rising defense/intelligence software budgets, sovereign-AI initiatives (reinforced by the Nvidia partnership), and broad enterprise AI adoption. Diversification into international commercial markets reduces reliance on U.S. government and enlarges the TAM. Key risks over five years: (1) growth deceleration as the law of large numbers sets in, which would compress the premium multiple; (2) intensifying competition from hyperscalers commoditizing AI orchestration; (3) political/budgetary volatility in government contracts; (4) execution risk in scaling commercial sales efficiently; (5) ongoing dilution. The base case is a high-quality business with a strong secular runway, but the outcome distribution for the stock is wide because valuation amplifies both upside and downside.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Palantir is one of the highest-quality growth-software franchises available: accelerating revenue, rapidly expanding margins, prodigious free cash flow, a debt-free fortress balance sheet, and rising returns on capital—an unusually clean fundamental profile. Its government moat is durable and its commercial AI platform is showing credible land-and-expand traction internationally. The fundamentals argue for owning the business; the price argues for caution. At ~59x EV/revenue and ~151x earnings, the market has already priced in years of near-flawless execution, leaving thin downside protection and high sensitivity to any deceleration—as the ~35% drawdown from its 52-week high illustrates. My synthesized view: this is a superb business at a demanding-to-excessive price. For a long-term fundamentals-driven investor, the prudent stance is to admire the quality but wait for a more favorable entry or size positions modestly, as the risk/reward at current multiples skews unfavorably despite the strength of the underlying franchise.</t>
+        </is>
+      </c>
+      <c r="M27" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Confidence is raised by the clarity and consistency of the financial data—the growth acceleration, margin expansion, FCF generation, and balance sheet strength are unambiguous and internally coherent across quarters. It is lowered by: (1) missing Q4 2024 data and absence of prior-year quarters limiting full YoY trend context; (2) news flow that is entirely promotional, single-dated, and lacks quantified deal economics, making it weak evidence; (3) the inherent difficulty of forecasting hypergrowth durability and multiple compression at these valuation levels; and (4) unquantified stock-based-comp dilution. The valuation conclusion is high-conviction on multiples but the ultimate stock outcome depends on execution I cannot fully verify from the data provided.</t>
+        </is>
+      </c>
+      <c r="O27" s="11" t="n">
+        <v>72</v>
+      </c>
+      <c r="P27" s="11" t="n">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/Investment_Research_Dashboard.xlsx
+++ b/Investment_Research_Dashboard.xlsx
@@ -320,7 +320,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="NewsTable" displayName="NewsTable" ref="A1:I259" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="NewsTable" displayName="NewsTable" ref="A1:I305" headerRowCount="1">
   <autoFilter ref="A1:I11"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Date"/>
@@ -338,7 +338,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="NarrativeTable" displayName="NarrativeTable" ref="A1:P27" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="NarrativeTable" displayName="NarrativeTable" ref="A1:P36" headerRowCount="1">
   <autoFilter ref="A1:P2"/>
   <tableColumns count="16">
     <tableColumn id="1" name="Ticker"/>
@@ -652,7 +652,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:R29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -668,7 +668,7 @@
     <col width="21" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="21" customWidth="1" min="18" max="18"/>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="R2" s="10" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="3">
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="R3" s="10" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="4">
@@ -933,16 +933,16 @@
         </is>
       </c>
       <c r="F4" s="8" t="n">
-        <v>196.9</v>
+        <v>196.93</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>4768875413504</v>
+        <v>4769841152000</v>
       </c>
       <c r="H4" s="9" t="n">
-        <v>30.151623</v>
+        <v>30.157732</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>15.424904</v>
+        <v>15.428029</v>
       </c>
       <c r="J4" s="9" t="n">
         <v>0.5996</v>
@@ -969,11 +969,11 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>NVIDIA is a rare combination of hypergrowth and exceptional profitability: ~85% YoY revenue growth, ~75% gross margins, ~77% ROIC, ~$49B quarterly FCF, and a near-debt-free balance sheet. At a forward...</t>
+          <t>NVIDIA is a rare combination of hypergrowth and exceptional profitability: ~85% YoY revenue growth, ~75% gross margins, ~77% ROIC, ~$49B quarterly FCF, and a near-debt-free balance sheet. At forward P...</t>
         </is>
       </c>
       <c r="R4" s="10" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="5">
@@ -1003,16 +1003,16 @@
         </is>
       </c>
       <c r="F5" s="8" t="n">
-        <v>435.605</v>
+        <v>432.57</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>2259253985280</v>
+        <v>2243513024512</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>37.812935</v>
+        <v>37.549477</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>21.469807</v>
+        <v>21.32022</v>
       </c>
       <c r="J5" s="9" t="n">
         <v>1.4213</v>
@@ -1039,11 +1039,11 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>TSMC is a best-in-class business trading at a fair-but-not-cheap valuation. The core thesis: it is the indispensable manufacturer of the leading-edge chips powering the AI buildout, with a moat eviden...</t>
+          <t>TSMC is a best-in-class business at a fair-but-not-cheap valuation, and nothing this week alters that. It is the indispensable manufacturer of leading-edge AI chips, with a moat evidenced by hard numb...</t>
         </is>
       </c>
       <c r="R5" s="10" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="6">
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="F6" s="8" t="n">
-        <v>371.05</v>
+        <v>370.78</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1765300109312</v>
+        <v>1764015603712</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>61.63621</v>
+        <v>61.591362</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>19.13045</v>
+        <v>19.11653</v>
       </c>
       <c r="J6" s="9" t="n">
         <v>0.4052</v>
@@ -1109,11 +1109,11 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Broadcom is a high-quality compounder benefiting from a genuine AI-driven inflection, evidenced by revenue reaccelerating to ~48% YoY, operating margins expanding to ~49%, ~46% FCF margins, and improv...</t>
+          <t>Broadcom is a high-quality compounder benefiting from a genuine AI-driven inflection: revenue reaccelerating to ~48% YoY, operating margins expanding to ~49%, ~46% FCF margins, and improving returns o...</t>
         </is>
       </c>
       <c r="R6" s="10" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="7">
@@ -1143,16 +1143,16 @@
         </is>
       </c>
       <c r="F7" s="8" t="n">
-        <v>337.46</v>
+        <v>339.22</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>904227848192</v>
+        <v>908943818752</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>16.146412</v>
+        <v>16.230623</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>14.146645</v>
+        <v>14.205538</v>
       </c>
       <c r="J7" s="9" t="n">
         <v>1.7686</v>
@@ -1179,11 +1179,11 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>JPMorgan is a best-in-class, diversified megabank that consistently earns mid-teens returns on equity, compounds tangible book value through cycles, and returns substantial capital to shareholders. Th...</t>
+          <t>JPMorgan is a best-in-class, diversified megabank that consistently earns mid-teens ROE, compounds tangible book value through cycles, and returns substantial capital via dividends and buybacks. The l...</t>
         </is>
       </c>
       <c r="R7" s="10" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="8">
@@ -1213,16 +1213,16 @@
         </is>
       </c>
       <c r="F8" s="8" t="n">
-        <v>350.09</v>
+        <v>352.2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>665781469184</v>
+        <v>669794172928</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>30.52223</v>
+        <v>30.70619</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>23.542742</v>
+        <v>23.684635</v>
       </c>
       <c r="J8" s="9" t="n">
         <v>1.5893</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="R8" s="10" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="9">
@@ -1283,19 +1283,19 @@
         </is>
       </c>
       <c r="F9" s="8" t="n">
-        <v>532.5551</v>
+        <v>531.62</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>470557097984</v>
+        <v>469730852864</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>30.837006</v>
+        <v>30.78286</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>23.372032</v>
+        <v>23.332333</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>1.6596</v>
+        <v>1.6403</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>0.006500000000000001</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="R9" s="10" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="10">
@@ -1353,16 +1353,16 @@
         </is>
       </c>
       <c r="F10" s="8" t="n">
-        <v>245.7408</v>
+        <v>245.98</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>2643344490496</v>
+        <v>2646033825792</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>31.83031</v>
+        <v>31.862694</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>24.81492</v>
+        <v>24.840168</v>
       </c>
       <c r="J10" s="9" t="n">
         <v>1.8344</v>
@@ -1387,11 +1387,11 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Amazon is a high-quality, multi-engine compounder whose profitability has structurally improved (operating margins now 11-13% vs low single digits historically) even as it grows revenue ~17% at massiv...</t>
+          <t>Amazon is a high-quality, multi-engine compounder whose profitability has structurally improved (operating margins now 11-13% vs low single digits historically) while still growing revenue ~17% at mas...</t>
         </is>
       </c>
       <c r="R10" s="10" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="11">
@@ -1421,16 +1421,16 @@
         </is>
       </c>
       <c r="F11" s="8" t="n">
-        <v>282.045</v>
+        <v>282.21</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>200394637312</v>
+        <v>200511848448</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>23.251856</v>
+        <v>23.265457</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>19.833845</v>
+        <v>19.845446</v>
       </c>
       <c r="J11" s="9" t="n">
         <v>2.5635</v>
@@ -1457,11 +1457,11 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>McDonald's is a wide-moat, capital-light, cash-generative franchise business trading at a full-but-fair valuation after a ~17% pullback from its high. The Q1 2026 data confirms the business is executi...</t>
+          <t>McDonald's is a wide-moat, capital-light, cash-generative franchise business trading at a full-but-fair valuation after a ~17% pullback. Q1 2026 confirms execution -- ~9.4% revenue growth and ~7% EPS ...</t>
         </is>
       </c>
       <c r="R11" s="10" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="12">
@@ -1491,16 +1491,16 @@
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>43.02</v>
+        <v>43.21</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>63707762688</v>
+        <v>63989129216</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>20.485716</v>
+        <v>20.57619</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>18.10469</v>
+        <v>18.543713</v>
       </c>
       <c r="J12" s="9" t="n">
         <v>1.5389</v>
@@ -1512,8 +1512,18 @@
       <c r="M12" s="5" t="n"/>
       <c r="N12" s="5" t="n"/>
       <c r="O12" s="9" t="n"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fairly Valued</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Nike is a high-quality, dominant brand undergoing a self-inflicted turnaround that appears to be inflecting, trading near multi-year lows at a below-historical valuation. The core thesis is a margin-r...</t>
+        </is>
+      </c>
       <c r="R12" s="10" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="13">
@@ -3014,6 +3024,105 @@
     <cfRule type="cellIs" priority="90" operator="equal" dxfId="2">
       <formula>"Fairly Valued"</formula>
     </cfRule>
+    <cfRule type="cellIs" priority="91" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="92" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="93" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="94" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="95" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="96" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="97" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="98" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="99" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="100" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="101" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="102" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="103" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="104" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="105" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="106" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="107" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="108" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="109" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="110" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="111" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="112" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="113" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="114" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="115" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="116" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="117" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="118" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="119" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="120" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="121" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="122" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="123" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -3029,7 +3138,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -3608,7 +3717,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:R29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
@@ -3845,13 +3954,13 @@
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>196.9</v>
+        <v>196.93</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>4768875413504</v>
+        <v>4769841152000</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>4691951878144</v>
@@ -3860,19 +3969,19 @@
         <v>24221000000</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>30.151623</v>
+        <v>30.157732</v>
       </c>
       <c r="H4" s="9" t="n">
-        <v>15.424904</v>
+        <v>15.428029</v>
       </c>
       <c r="I4" s="9" t="n">
         <v>0.5996</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>18.813742</v>
+        <v>18.816608</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>24.397783</v>
+        <v>24.402725</v>
       </c>
       <c r="L4" s="9" t="n">
         <v>18.509</v>
@@ -3903,13 +4012,13 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>435.605</v>
+        <v>432.57</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2259253985280</v>
+        <v>2243513024512</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>16497778884608</v>
@@ -3918,19 +4027,19 @@
         <v>5186474013</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>37.812935</v>
+        <v>37.549477</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>21.469807</v>
+        <v>21.32022</v>
       </c>
       <c r="I5" s="9" t="n">
         <v>1.4213</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.5505133</v>
+        <v>0.5466777</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>98.05056</v>
+        <v>97.36741000000001</v>
       </c>
       <c r="L5" s="9" t="n">
         <v>4.02</v>
@@ -3961,13 +4070,13 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>371.05</v>
+        <v>370.78</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1765300109312</v>
+        <v>1764015603712</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>1824138199040</v>
@@ -3976,19 +4085,19 @@
         <v>4757580198</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>61.63621</v>
+        <v>61.591362</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>19.13045</v>
+        <v>19.11653</v>
       </c>
       <c r="I6" s="9" t="n">
         <v>0.4052</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>23.392303</v>
+        <v>23.375282</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>20.132935</v>
+        <v>20.118284</v>
       </c>
       <c r="L6" s="9" t="n">
         <v>24.172</v>
@@ -4019,13 +4128,13 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>337.46</v>
+        <v>339.22</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>904227848192</v>
+        <v>908943818752</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>663828627456</v>
@@ -4034,19 +4143,19 @@
         <v>2679511418</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>16.146412</v>
+        <v>16.230623</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>14.146645</v>
+        <v>14.205538</v>
       </c>
       <c r="I7" s="9" t="n">
         <v>1.7686</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>5.209916</v>
+        <v>5.237088</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>2.628623</v>
+        <v>2.6423326</v>
       </c>
       <c r="L7" s="9" t="n">
         <v>3.825</v>
@@ -4075,13 +4184,13 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>350.09</v>
+        <v>352.2</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>665781469184</v>
+        <v>669794172928</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>683806818304</v>
@@ -4090,19 +4199,19 @@
         <v>1659709932</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>30.52223</v>
+        <v>30.70619</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>23.542742</v>
+        <v>23.684635</v>
       </c>
       <c r="I8" s="9" t="n">
         <v>1.5893</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>15.473574</v>
+        <v>15.5668335</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>18.779636</v>
+        <v>18.892822</v>
       </c>
       <c r="L8" s="9" t="n">
         <v>15.893</v>
@@ -4133,13 +4242,13 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>532.5551</v>
+        <v>531.62</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>470557097984</v>
+        <v>469730852864</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>481782562816</v>
@@ -4148,19 +4257,19 @@
         <v>877036230</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>30.837006</v>
+        <v>30.78286</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>23.372032</v>
+        <v>23.332333</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>1.6596</v>
+        <v>1.6403</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>13.86479</v>
+        <v>13.840445</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>70.29501999999999</v>
+        <v>70.17158999999999</v>
       </c>
       <c r="L9" s="9" t="n">
         <v>14.196</v>
@@ -4191,40 +4300,40 @@
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>245.7408</v>
+        <v>245.98</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2643344490496</v>
+        <v>2646033825792</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>2718906712064</v>
+        <v>2738484674560</v>
       </c>
       <c r="F10" s="7" t="n">
         <v>10757109436</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>31.83031</v>
+        <v>31.862694</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>24.81492</v>
+        <v>24.840168</v>
       </c>
       <c r="I10" s="9" t="n">
         <v>1.8344</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>3.5588934</v>
+        <v>3.562358</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>5.979851</v>
+        <v>5.9859343</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>3.66</v>
+        <v>3.687</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>17.444</v>
+        <v>17.57</v>
       </c>
       <c r="N10" s="5" t="n"/>
       <c r="O10" s="9" t="n">
@@ -4247,13 +4356,13 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>282.045</v>
+        <v>282.21</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>200394637312</v>
+        <v>200511848448</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>252311388160</v>
@@ -4262,19 +4371,19 @@
         <v>710505859</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>23.251856</v>
+        <v>23.265457</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>19.833845</v>
+        <v>19.845446</v>
       </c>
       <c r="I11" s="9" t="n">
         <v>2.5635</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>7.301415</v>
+        <v>7.3056855</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>-155.82597</v>
+        <v>-155.91713</v>
       </c>
       <c r="L11" s="9" t="n">
         <v>9.193</v>
@@ -4305,40 +4414,40 @@
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>43.02</v>
+        <v>43.21</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>63707762688</v>
+        <v>63989129216</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>66261884928</v>
+        <v>66069147648</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>1199499281</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>20.485716</v>
+        <v>20.57619</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>18.10469</v>
+        <v>18.543713</v>
       </c>
       <c r="I12" s="9" t="n">
         <v>1.5389</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1.3730713</v>
+        <v>1.3791355</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>4.290844</v>
+        <v>4.3097944</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>1.428</v>
+        <v>1.424</v>
       </c>
       <c r="M12" s="9" t="n">
-        <v>14.609</v>
+        <v>14.567</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>0.0378</v>
@@ -5347,7 +5456,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Q174"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
@@ -5359,7 +5468,7 @@
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
@@ -13141,7 +13250,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Y174"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
@@ -25650,8 +25759,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I259"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I305"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
@@ -37321,6 +37430,2076 @@
         </is>
       </c>
     </row>
+    <row r="260">
+      <c r="A260" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>DeepSeek looks to reduce reliance on Nvidia with own AI chip</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Yahoo Finance Video</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/video/deepseek-looks-to-reduce-reliance-on-nvidia-with-own-ai-chip-203313261.html</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>A major AI customer building its own chips signals rising competitive pressure that could erode Nvidia's dominant market share over time.</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2 Beaten-Down Artificial Intelligence (AI) Stocks That Will Surge at Least 40% Over the Next Year, According to Wall Street</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Motley Fool</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/investing/2026/07/07/beaten-down-artificial-intelligence-ai-stocks/</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Analyst optimism on beaten-down AI names signals potential sector-wide upside, but NVDA may not be among the specific stocks featured.</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>SpaceX Has Joined the Nasdaq-100. Here's What That Means for Index Investors</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Motley Fool</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/investing/2026/07/07/spacex-has-joined-the-nasdaq-100-heres-what-that-means-for-index-investors/</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Nasdaq-100 composition changes have negligible direct impact on NVDA fundamentals, though index reweighting could marginally affect passive fund flows into the stock.</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Why Fiserv Stock Topped the Market Today</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Motley Fool</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/investing/2026/07/07/why-fiserv-stock-topped-the-market-today/</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>This headline concerns Fiserv's business unit sale and has no material relevance to NVDA's fundamentals or outlook.</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Why Sandisk Stock Jumped 34% in June</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Motley Fool</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/investing/2026/07/07/why-sandisk-stock-jumped-34-in-june/</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Strong memory chip demand signals healthy AI infrastructure spending, supporting sustained demand for NVDA's GPUs that rely on high-bandwidth memory.</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Microsoft Looks to Make a Major Reset as It Says This Area of Its Business "Is Not Healthy"</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Motley Fool</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/investing/2026/07/07/microsoft-looks-to-make-a-major-reset-as-it-says-t/</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Microsoft's restructuring is company-specific and only tangentially affects NVDA; unclear if AI spending or GPU demand shifts materially.</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Nervous About the Stock Market? These 7 Words From Warren Buffett Might Change Your Mind.</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Motley Fool</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/investing/2026/07/07/nervous-about-stock-market-7-words-warren-buffett/</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Reinforces a buy-during-fear mindset, suggesting NVDA holders should stay disciplined and view market dips as long-term opportunities.</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Hormuz Tolls Are Just the Beginning: The World’s Busiest Shipping Route Could Be Next</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/07/hormuz-tolls-are-just-the-beginning-the-worlds-busiest-shipping-route-could-be-next/</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Geopolitical shipping disruptions could raise supply chain costs and delay NVDA hardware shipments, though impact on the company is indirect.</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Amazon Stocks Climbs As AI Push Drives $25 Billion Bond Sale</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Investor's Business Daily</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>https://www.investors.com/news/technology/amazon-stock-25-billion-bond-ai-costs-rising/?src=A00220&amp;yptr=yahoo</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Amazon's $25B bond-funded AI infrastructure buildout signals continued hyperscaler capex, sustaining strong demand for NVDA's data center GPUs.</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Robinhood Is Making a Comeback. Should You Buy the Stock?</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Motley Fool</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/investing/2026/07/07/robinhood-is-making-a-comeback-should-you-buy-the/</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>This headline concerns Robinhood, not NVDA, and has no direct relevance to NVDA's fundamentals or long-term investment thesis.</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>DeepSeek looks to reduce reliance on Nvidia with own AI chip</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Yahoo Finance Video</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/video/deepseek-looks-to-reduce-reliance-on-nvidia-with-own-ai-chip-203313261.html</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Taiwan Semiconductor Manufacturing Company</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>DeepSeek's custom AI chip would likely be fabricated by TSMC, expanding its foundry customer base beyond Nvidia as chip design diversifies.</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Samsung saw a record quarter, but it's not enough for investors. Here's why.</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Yahoo Finance Video</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/video/samsung-saw-a-record-quarter-but-its-not-enough-for-investors-heres-why-203148500.html</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Taiwan Semiconductor Manufacturing Company</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Memory sector volatility from Samsung's results signals broader semiconductor demand dynamics that could indirectly affect TSM's foundry outlook.</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>This Semiconductor ETF Is Up 58% This Year and Doesn’t Own TSMC</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/etf/2026/07/07/this-semiconductor-etf-is-up-58-this-year-and-doesnt-own-tsmc/</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Taiwan Semiconductor Manufacturing Company</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>The article highlights TSM's central role fabricating chips for AI designers, reinforcing its indispensability even when excluded from a fabless-focused ETF.</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Up 102% in 2026, This Chip ETF Mysteriously Avoids Taiwan Semiconductor</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/etf/2026/07/07/up-102-in-2026-this-chip-etf-mysteriously-avoids-taiwan-semiconductor/</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Taiwan Semiconductor Manufacturing Company</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>TSM's exclusion from a top-performing chip ETF is a fund-construction quirk, not a reflection of the company's underlying business fundamentals.</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Bank of America Analyst: AI Is Becoming “Deeply Embedded in Enterprise Workflows” as AI Spending Could Reach $1.5 Trillion</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/07/bank-of-america-analyst-ai-is-becoming-deeply-embedded-in-enterprise-workflows-as-ai-spending-could-reach-1-5-trillion/</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Taiwan Semiconductor Manufacturing Company</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Accelerating enterprise AI adoption and massive projected spending signal sustained long-term demand for TSM's advanced chip manufacturing.</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Wall Street tech analyst explains why investors should look past Samsung selloff</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Investing.com</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/wall-street-tech-analyst-explains-163203461.html</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Taiwan Semiconductor Manufacturing Company</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Analyst frames the semiconductor selloff as technical momentum unwind rather than fundamental weakness, suggesting TSM's downside is temporary and buyable.</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>A Circuit Board Problem Just Delayed Nvidia’s Next AI System to 2028 And Chip Stocks Are Already Feeling the Fallout</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/07/a-circuit-board-problem-just-delayed-nvidias-next-ai-system-to-2028-and-chip-stocks-are-already-feeling-the-fallout/</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>A delayed Nvidia AI system could dampen near-term demand for Broadcom's networking and custom chips tied to AI rack deployments.</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Semtech, Power Integrations, Amkor, Entegris, and Kulicke and Soffa Stocks Trade Down, What You Need To Know</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>StockStory</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/semtech-power-integrations-amkor-entegris-194552439.html</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Semiconductor sector weakness and DeepSeek's in-house AI chip development signal competitive pressures that could affect AVGO's AI chip demand outlook.</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>FormFactor, Penguin Solutions, Western Digital, Applied Materials, and KLA Corporation Shares Plummet, What You Need To Know</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>StockStory</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/formfactor-penguin-solutions-western-digital-193752825.html</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>DeepSeek developing its own AI inference chip signals potential competitive threat to Broadcom's custom AI accelerator business over the long term.</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>DeepSeek Reportedly Develops AI Chip as Nvidia Shares Drop 2.2%</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>GuruFocus.com</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/technology/ai/articles/deepseek-reportedly-develops-ai-chip-192001405.html</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Rising custom AI silicon efforts by firms like DeepSeek validate Broadcom's ASIC design business, though it also intensifies competition for AI chip market share.</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Broadcom Stock Drops After Bank Downgrades AI Chip Giant on Valuation</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>GuruFocus.com</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/broadcom-stock-drops-bank-downgrades-184733964.html</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>A valuation-based downgrade signals near-term price concerns but doesn't undermine Broadcom's long-term AI growth fundamentals or business strength.</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Bank of America Analyst: AI Is Becoming “Deeply Embedded in Enterprise Workflows” as AI Spending Could Reach $1.5 Trillion</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/07/bank-of-america-analyst-ai-is-becoming-deeply-embedded-in-enterprise-workflows-as-ai-spending-could-reach-1-5-trillion/</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Sustained AI infrastructure spending growth supports long-term demand for AVGO's custom AI chips and networking products.</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>SpaceX stock drops below IPO opening price despite flood of bullish Wall Street ratings</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/article/spacex-stock-drops-below-ipo-opening-price-despite-flood-of-bullish-wall-street-ratings-153809443.html</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase &amp; Co.</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>This headline concerns SpaceX, not JPM, and has no material relevance to a long-term JPMorgan investor.</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Fiserv Stock Rises on Report Big U.S. Banks Explore Buying Its Debit Card Network</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Barrons.com</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>https://www.barrons.com/articles/fiserv-stock-jpmorgan-wells-fargo-debit-card-73e8fb35?siteid=yhoof2&amp;yptr=yahoo</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase &amp; Co.</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>JPM exploring a joint acquisition of a debit network could reduce reliance on third-party processors and strengthen payments infrastructure control.</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Avaada Seeks $750 Million Refinancing as India Clean-Energy Push Accelerates</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>GuruFocus.com</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/energy/articles/avaada-seeks-750-million-refinancing-191620378.html</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase &amp; Co.</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>This deal signals fee opportunities in emerging-market clean-energy financing, but no direct JPM involvement is indicated, limiting relevance.</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>JPMorgan Cuts Yuan Bets Despite 3% Gain, Eyes New Currency Winners</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>GuruFocus.com</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/currencies/articles/jpmorgan-cuts-yuan-bets-despite-185641555.html</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase &amp; Co.</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>JPM's asset management arm is actively repositioning FX strategies, reflecting tactical currency views rather than material impact on the firm's fundamentals.</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Fiserv Explores Sale of Debit Network</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>GuruFocus.com</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/fiserv-explores-sale-debit-network-182705349.html</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase &amp; Co.</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>A potential STAR Network acquisition could expand JPM's payments infrastructure and merchant reach, but financial impact depends on deal terms.</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Which Small Cap ETF Is the Better Buy in 2026? iShares and JPMorgan Have Compelling Offerings</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Motley Fool</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/coverage/etfs/2026/07/07/which-small-cap-etf-is-the-better-buy-in-2026-ishares-and-jpmorgan-have-compelling-offerings/</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase &amp; Co.</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Highlights JPMorgan's competitive ETF offerings, showing its asset management arm can attract inflows and diversify revenue beyond banking.</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Nvidia-Backed Nscale Secures $900 Million Credit Facility for AI Expansion</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>GuruFocus.com</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/technology/ai/articles/nvidia-backed-nscale-secures-900-170032178.html</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase &amp; Co.</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>This headline concerns Nvidia and Nscale AI financing with no clear connection to JPM's business or investment outlook.</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Major US Banks' Second-Quarter Earnings Poised for Upside, BofA Says</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>MT Newswires</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/major-us-banks-apos-second-165554609.html</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase &amp; Co.</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Strong capital markets recovery could signal sustained revenue diversification, benefiting JPM's earnings resilience beyond traditional lending income.</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Earnings</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Circle's USDC now runs 70% of the stablecoin volume</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Yahoo Finance Video</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/video/circles-usdc-now-runs-70-183000137.html</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Visa Inc.</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Growing stablecoin adoption could disintermediate traditional card networks like Visa, posing a long-term competitive threat to payment volumes.</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>DDSC Brings Regulated Dirham Stablecoin to UAE Exchanges</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>BeInCrypto</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>https://beincrypto.com/uae-dirham-stablecoin-ddsc-exchange-access/</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Visa Inc.</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Regulated dirham stablecoins could bypass card networks for payments, posing a long-term disintermediation risk to Visa's transaction volumes in the region.</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Is Visa (V) Undervalued After Its AI Payments Push And Stablecoin Moves?</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Simply Wall St.</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/visa-v-undervalued-ai-payments-211813162.html</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Visa Inc.</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Visa's expansion into agentic commerce and stablecoin payments signals proactive adaptation to emerging technologies, potentially defending its network dominance and long-term growth.</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Dow Jones Payments Leader Visa Breaks Out; Arista Networks Eyes Buy Point</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Investor's Business Daily</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>https://www.investors.com/stock-lists/stocks-near-a-buy-zone/dow-jones-visa-stock-v-buy-zone-investing-markets/?src=A00220&amp;yptr=yahoo</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Visa Inc.</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Technical breakout signals strong price momentum and investor confidence, though it reflects trading dynamics rather than fundamental business developments for Visa.</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Visa vs Coinbase: Two Different Economic Playbooks But One Winner</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/07/visa-vs-coinbase-two-different-economic-playbooks-but-one-winner/</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Visa Inc.</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Visa's steady payment volumes and 15% revenue growth demonstrate resilience against crypto disruption, reinforcing its durable competitive moat.</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Mastercard (MA) Joins Open USD Stablecoin, Is The Stock Still Cheap?</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Simply Wall St.</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/mastercard-ma-joins-open-usd-171402878.html</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Mastercard Incorporated</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Mastercard's stablecoin adoption and buyback signal proactive positioning in digital payments, potentially defending its network relevance amid crypto disruption.</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>DeepSeek looks to reduce reliance on Nvidia with own AI chip</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Yahoo Finance Video</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/video/deepseek-looks-to-reduce-reliance-on-nvidia-with-own-ai-chip-203313261.html</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>DeepSeek's custom chip signals broader industry shift toward AI hardware independence, indirectly validating Amazon's own Trainium/Inferentia investments amid Nvidia reliance concerns.</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Roku vs. Sirius XM: Which Media Stock Is a Better Buy in 2026?</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Motley Fool</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/coverage/better-buy/2026/07/07/roku-vs-sirius-xm-which-media-stock-is-a-better-buy-in-2026/</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>This headline compares Roku and Sirius XM, with no direct relevance to Amazon's business or investment thesis.</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Nasdaq Slides Nearly 2% As Higher Treasury Yields, Soaring Oil Prices Pressure Tech And Chip Stocks — META, AMZN, SPCX, MSFT In Focus</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Stocktwits</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>https://stocktwits.com/news-articles/markets/equity/nasdaq-slides-nearly-2-as-higher-treasury-yields-soaring-oil-prices-pressure-tech-and-chip-stocks-meta-amzn-spcx-msft-in-focus/cZmlDzSR7ZV</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Broad macro pressures like rising yields and oil prices weigh on tech valuations, but AMZN's long-term fundamentals remain unaffected by short-term sentiment.</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Amazon's Stock Is Historically Cheap. Now Is Your Perfect Buying Opportunity</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Motley Fool</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/investing/2026/07/07/amazons-stock-is-historically-cheap-now-is-your-pe/</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Anticipated AWS growth combined with a relatively low valuation could offer long-term investors an attractive entry point with upside potential.</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Top Analyst Reports for Amazon.com, Walmart &amp; American Express</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/top-analyst-reports-amazon-com-211500537.html</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Amazon's AI investments and global diversification drive long-term growth, though elevated spending and competition may pressure near-term margins.</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Trump's $1.4 Billion Crypto Haul Draws Fresh Investor Scrutiny</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>GuruFocus.com</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/politics/articles/trumps-1-4-billion-crypto-195905371.html</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>This headline concerns Trump's personal crypto ventures and has no material connection to Amazon's business or fundamentals.</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Amazon Plans $25 Billion Bond Sale</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>GuruFocus.com</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/amazon-plans-25-billion-bond-192227995.html</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Debt-funded AI and data-center investment signals aggressive capacity expansion, though rising leverage adds interest costs and execution risk to future returns.</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Amazon's AI Spending Push Hits Bond Market</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>GuruFocus.com</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/amazons-ai-spending-push-hits-191559609.html</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Debt-funded AI capex signals aggressive investment that could pressure near-term free cash flow while betting on long-term cloud and AI growth.</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>The Dividend Growth Snowball: How Modest Income Today Can Become Serious Income Later</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/personal-finance/2026/07/07/the-dividend-growth-snowball-how-modest-income-today-can-become-serious-income-later/</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>McDonald's Corporation</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>MCD</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>MCD's consistent dividend growth history makes it a candidate for compounding income that outpaces high-yield alternatives over long holding periods.</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>McDonald's Franchise Owners Make A Surprising Amount Of Money</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Money Digest</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>https://www.moneydigest.com/1788834/how-much-money-does-mcdonalds-franchise-owners-make/</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>McDonald's Corporation</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>MCD</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Franchisee profitability affects franchise system health, expansion appetite, and MCD's royalty-based revenue stream stability over the long term.</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -37335,8 +39514,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:P36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
@@ -39362,6 +41541,672 @@
         <v>78</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NVIDIA remains an exceptional business at the center of the AI data center buildout, with financials essentially unchanged from the prior day's analysis. The latest reported quarter (period ending 2026-04-30) showed ~$81.6B in revenue (~85% YoY growth), ~75% gross margin, mid-60s% operating margin, ~$48.6B free cash flow, and a near-debt-free balance sheet (D/E ~0.06). Returns on capital are among the highest of any large-cap (ROIC ~77%, ROE ~82% per prior derivation). The stock at $196.93 trades at ~30x trailing and ~15.4x forward earnings with a PEG below 0.6 -- undemanding for the growth trajectory, though price-to-sales ~19 and EV/EBITDA ~28 are rich in absolute terms and depend on demand durability. The central debate is unchanged: not whether NVIDIA is a great business (the data confirms it is), but whether the hyperscaler capex supercycle is durable and how fast custom silicon and AMD erode its position. Today's news adds one incrementally negative competitive data point (DeepSeek building its own chip) balanced against fresh positive signals on hyperscaler capex (Amazon's $25B AI bond, strong memory demand). None of this materially changes the thesis.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Only one calendar day has elapsed since the prior writeup and no new financial data was released, so there is no material change to fundamentals. The one incrementally meaningful news item is a report that DeepSeek -- a significant AI customer -- is developing its own AI chip to reduce Nvidia reliance. This is thematically consistent with the previously noted customer-diversification trend (Turing/AMD, TPUs) rather than a new category of risk; it adds another data point to the 'largest customers are motivated to build alternatives' bear narrative but is too small and too early to quantify. Offsetting this, two news items reinforce the bull side of demand durability: Amazon's $25B bond-funded AI infrastructure buildout signals continued hyperscaler capex, and strong memory-chip (Sandisk) demand corroborates healthy AI infrastructure spending that underpins GPU sales. The remaining headlines (SpaceX Nasdaq-100 addition, Fiserv, Robinhood, Microsoft restructuring, Buffett commentary, Hormuz shipping) are not material to NVDA's fundamentals. Net: no material change; the competitive-diversification theme continues to build slowly while demand signals stay firm.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>NVIDIA sits at the center of arguably the largest infrastructure buildout in tech history, nearly doubling revenue YoY while expanding margins -- a signature of demand exceeding supply and genuine pricing power. FCF generation is enormous (~$48.6B in a single quarter) with capex intensity under $2B/quarter, so growth converts to cash without heavy reinvestment. The CUDA software ecosystem creates switching costs that competitors must overcome across the full developer stack, not just raw hardware. Continued hyperscaler capex commitment -- reinforced today by Amazon's $25B AI-directed bond sale and robust high-bandwidth memory demand -- suggests the demand cycle has runway. At forward P/E ~15.4 and PEG ~0.6, the market implicitly prices meaningful deceleration; if the buildout persists even at a moderating pace, the stock is inexpensive relative to its own earnings trajectory. The fortress balance sheet (D/E ~0.06) and aggressive buybacks (financing outflows ~$21.3B latest quarter) provide downside cushion and shareholder-friendly capital return.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>The thesis rests entirely on the durability of hyperscaler AI capex, which is cyclical and concentrated among a few customers who are simultaneously NVIDIA's largest buyers and most motivated competitors. The steady drumbeat of customer diversification -- now including DeepSeek's own-chip effort alongside Turing/AMD shifts and growing TPU adoption -- is early but directionally real evidence that buyers want to reduce dependence and pricing leverage. Peak gross margins near 75% are difficult to defend indefinitely and naturally attract competition. Inventory more than doubled over the trailing period (from ~$11.3B to ~$25.8B), a risk of writedowns and margin compression if demand softens. A demand air pocket would hit NVIDIA disproportionately given the ~20% sequential growth now embedded in expectations. Beta of 2.2 means the stock amplifies any market drawdown, and a sentiment-driven repricing off a rich P/S (~19) and EV/EBITDA (~28) could be sharp. China export-control exposure remains an ongoing regulatory overhang. Finally, the latest quarter's 70%+ net margin exceeds the 65.6% operating margin, implying non-operating gains that may not recur and argue for normalizing earnings expectations down.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Financial health is exceptional on nearly every dimension and unchanged from the prior analysis. Revenue is high-quality and re-accelerating, with roughly three consecutive quarters of ~20% QoQ growth. Margins are best-in-class and trending up (gross ~75%, operating ~66%). Cash generation is outstanding: operating cash flow ~$50.3B and FCF ~$48.6B in the latest quarter (FCF margin ~60%). The balance sheet is fortress-like -- total debt ~$12.3B against ~$195.5B equity (D/E ~0.06), with immaterial leverage and very high interest coverage; current ratio ~3.4. Capital allocation favors shareholder returns via large buybacks and a token 0.5% dividend. Two items warrant monitoring rather than concern: inventory growth to ~$25.8B (a bet on future demand that becomes a markdown risk if demand softens) and elevated investing outflows (~$26-31B recent quarters, likely securities and strategic investments). ROIC ~77% and ROE ~82% remain among the highest of any large-cap.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Fairly Valued</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>The valuation picture is unchanged. On absolute multiples NVIDIA looks reasonable to cheap: forward P/E ~15.4 and PEG ~0.6 are undemanding for a business growing earnings at triple-digit YoY rates. Trailing P/E ~30 sits well below levels seen in prior enthusiasm phases, reflecting that earnings have caught up to the price. However, price-to-sales ~19 and EV/EBITDA ~28 are rich in absolute terms and only justified if current growth and margin structure persist. The crux: the attractive forward multiple embeds a large forward earnings estimate that itself depends on continued AI capex; if growth normalizes to a still-strong but decelerating pace, the forward multiple proves appropriate rather than a bargain. The stock trades at $196.93, roughly midway between its 52-week range ($158.39-$236.54), consistent with a market weighing quality against durability uncertainty. Given the exceptional business quality alongside genuine (if incremental) competitive and cyclical risks, 'Fairly Valued' remains the honest rating.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>NVIDIA holds one of the strongest moats in technology, anchored by CUDA's software ecosystem and full-stack integration (GPUs, post-Mellanox networking, software), producing system-level lock-in and deep switching costs. Dominant AI-accelerator share sustains pricing power evident in ~75% gross margins. That moat is under measurable but still incremental pressure: AMD is gaining early credibility, hyperscalers' custom silicon (Google TPUs and others) represents structurally motivated in-house competition, and today's DeepSeek own-chip report adds another customer to the diversification list. The sheer profitability NVIDIA extracts is itself the strongest incentive for customers to develop alternatives. Switching costs are high but not absolute. The moat remains dominant today and is more likely to erode gradually than to break abruptly, but the accumulating list of customers pursuing in-house silicon is a trend worth tracking closely.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>The multi-year growth runway remains strong: continued AI infrastructure buildout, scaling inference workloads as models reach production deployment, and expanding use cases (enterprise AI, sovereign AI, automotive/autonomy). Today's demand signals (Amazon capex, memory demand) support the near-term durability of the cycle. Ecosystem lock-in positions NVIDIA to capture the majority of accelerated-computing spend for the foreseeable future. The principal five-year risks are unchanged: (1) a cyclical demand correction if AI monetization lags capex, amplified by customer concentration; (2) gradual margin compression as AMD, TPUs, and now customers like DeepSeek building bespoke silicon capture share and gain pricing leverage; (3) regulatory/export constraints, particularly China. Base case is continued growth at a decelerating rate with some margin give-back from peak -- still an excellent outcome. Bear scenario is a demand air pocket plus faster competitive erosion. The outlook is robustly positive with wider-than-normal uncertainty bands.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NVIDIA is a rare combination of hypergrowth and exceptional profitability: ~85% YoY revenue growth, ~75% gross margins, ~77% ROIC, ~$49B quarterly FCF, and a near-debt-free balance sheet. At forward P/E ~15.4 and PEG ~0.6, the market prices meaningful deceleration, creating favorable asymmetry if the AI buildout persists even at a moderating pace. The core risks -- customer concentration, hyperscaler custom silicon, early AMD share gains, an expanding roster of customers (now including DeepSeek) building their own chips, peak margins, and cyclicality -- are real but continue to show incremental erosion, not structural breakdown. The CUDA ecosystem moat remains the decisive defensive asset, and today's news left the fundamental picture unchanged while adding balanced signals (one competitive negative, two demand positives). Net assessment: a high-quality, dominant franchise trading at a reasonable multiple for its growth, warranting a constructive but risk-aware stance. Valuation is fair rather than a bargain because the attractive forward multiple depends entirely on the durability of a demand cycle carrying genuine cyclical and competitive uncertainty. Position sizing should respect the high beta (2.2) and the risk of a sharp sentiment-driven repricing.</t>
+        </is>
+      </c>
+      <c r="M28" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Confidence is essentially unchanged from the prior writeup because no material new information arrived -- financials are identical and the news is incremental. It is supported by the clarity and strength of the financial data: growth, margins, cash generation, and returns on capital are unambiguous and exceptional, with no solvency concern. It is tempered by: the absence of Q4 2024/Q1 2025 financials limiting full trend analysis; the anomalous 70%+ net margin versus 65.6% operating margin, suggesting non-recurring items that cloud normalized earnings; and the biggest thesis variable -- the durability of AI capex and the pace of competitive erosion -- being inherently unforecastable. The DeepSeek own-chip news reinforces the diversification theme but is too small to quantify. The forward P/E's attractiveness depends on estimates I cannot independently verify from the data provided.</t>
+        </is>
+      </c>
+      <c r="O28" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="P28" s="11" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TSMC remains the world's dominant leading-edge foundry, and the financial data continues to show an exceptionally strong business. Q1 2026 revenue reached ~NT$1,134B, up ~35% year-over-year and ~8% sequentially, with diluted EPS of NT$110.4 (up ~58% YoY). Profitability sits at a series high: gross margin ~66.2%, operating margin ~58.1%, net margin ~50.5%, with ROIC ~46% and ROE ~32%. The balance sheet is fortress-like (debt/equity ~0.19 and declining, current ratio ~2.5, cash ~NT$3.0T) and the company self-funds ~NT$350B/quarter of capex while still generating ~NT$347B of free cash flow. This week's news flow is almost entirely thematic reinforcement of the AI demand narrative rather than any material fundamental change. At ~38x trailing and ~21x forward earnings, the stock is fairly priced for its growth-and-returns profile, with the primary un-hedgeable risk being geographic concentration in Taiwan. The investment case is essentially unchanged from the prior analysis.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Nothing materially changed since the prior writeup one day earlier. There are no new financial disclosures, and the fundamentals (margin inflection to ~66% gross / ~50% net, ~35% YoY revenue growth, ~46% ROIC) remain exactly as previously analyzed. The recent news is thematic and largely confirmatory: multiple items reiterate AI-driven demand durability (BofA's $1.5T enterprise AI spending framing, several 'AI beneficiary' pieces), and a couple note that customer diversification could broaden (a potential DeepSeek custom chip that would likely be fabricated by TSMC). A Samsung-driven semiconductor selloff is characterized as technical/momentum-driven rather than fundamental, and two ETF-construction articles simply underscore TSMC's centrality even when excluded from fabless-focused funds. None of these represent a change to the earnings power, competitive standing, or risk profile. The single most important fact remains the prior quarter's margin step-change, which is not new information here.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>TSMC is the structural chokepoint of the AI hardware buildout: essentially every leading fabless AI designer depends on its leading-edge nodes and CoWoS advanced packaging. The financials validate genuine pricing power — margins expanded to record levels even while capex stayed enormous, contradicting the 'capex crushes margins' fear. The combination of ~66% gross margin, ~50% net margin, ~46% ROIC and 30%+ revenue growth is rare at this scale. The moat is compounding: leading-edge fabs cost tens of billions and take years to ramp, and TSMC's process/yield lead deepens through multi-year customer co-design and high switching costs. Broadening demand (e.g., custom AI silicon from new entrants like DeepSeek, plus Marvell/Credo/Broadcom-type designers) means TSMC wins regardless of which chip designer prevails. The balance sheet funds all of this internally while still growing FCF, and a low-20s forward multiple is undemanding for this growth quality.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>The dominant risk is geopolitical concentration — the bulk of leading-edge capacity sits in Taiwan, and any cross-strait disruption would be catastrophic and cannot be hedged. Customer concentration is high, so an AI capex digestion phase or overbuild would hit TSMC disproportionately given semiconductor cyclicality; the ~35% YoY growth and record margins plausibly represent a cyclical high-water mark rather than a durable baseline. Rising structural capital intensity (~NT$350B/quarter capex) and lower-margin overseas fabs (US, Japan, Germany) could dilute the exceptional profitability shown here. Competitively, Intel Foundry and Samsung are deploying heavy capital and government subsidies; even partial success would pressure leading-edge pricing. The Samsung selloff this week is a reminder that memory/semiconductor sentiment can turn quickly. Finally, the stock trades near its 52-week high after a large rerating, so much good news is already priced and there is little cushion for disappointment.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Financial health is excellent and improving. Revenue has grown sequentially every quarter across the series, from ~NT$839B (Q1 2025) to ~NT$1,134B (Q1 2026), culminating in ~35% YoY growth. Margins expanded across every line (gross ~58.8% to ~66.2%, operating ~48.5% to ~58.1%, net ~43% to ~50.5%), signaling mix improvement and pricing power rather than one-off effects. Cash generation is robust: Q1 2026 operating cash flow of ~NT$699B against ~NT$352B capex yields ~NT$347B FCF, with cash rising to ~NT$3.0T. The balance sheet is conservative — debt/equity ~0.19 and steadily declining, current ratio ~2.5, quick ratio ~2.3. Returns on capital are outstanding (ROIC ~46%, ROE ~32%, ROA ~22%). Capital allocation is dominated by high-return reinvestment, which is appropriate; the dividend yield is modest (~0.8%) and there is no evident dilution. Note the valuation snapshot mixes NT$ financials with USD price data, making EV/EBITDA (~5.8) and price-to-book (~97x) unreliable as cross-currency figures; these should be treated cautiously.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Fairly Valued</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Trailing P/E of ~38x compresses to ~21x forward with a PEG of ~1.4, which must be judged against ~35% revenue growth, ~58% EPS growth, expanding margins, and ~46% ROIC. A low-20s forward multiple is not demanding for a business of this quality and growth — it is roughly in line with or below what the fundamentals justify, and the trailing-to-forward compression reflects expected continued earnings growth. The stock trades near the upper end of its 52-week range ($432.57 vs high $479, low $224), meaning much of the rerating has already occurred and a substantial amount of good news is priced in. Price-to-book (~97x) is not a useful bear signal given the accounting understates the earnings power of these assets and the currency mismatch distorts the figure. Balancing genuine fundamental acceleration against a full price and a likely cyclical peak in margins, 'Fairly Valued' remains the appropriate call — not a bargain, not an obvious short, with valuation risk concentrated in whether AI demand and record margins hold.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>TSMC holds one of the widest moats in global manufacturing. It dominates leading-edge logic production and the advanced packaging (CoWoS) essential to AI accelerators. The moat rests on a compounding process/yield lead, enormous capital barriers to entry (leading-edge fabs cost tens of billions and years to ramp), deep multi-year co-engineering relationships with the largest fabless designers, and high switching costs once a design is tuned to a specific process. Pricing power is directly evidenced by margin expansion despite heavy capex. Industry structure at the leading edge is effectively an oligopoly narrowing toward a near-monopoly, with Samsung a distant second and Intel Foundry attempting re-entry with government backing. The potential broadening of the customer base (new custom-silicon designers such as DeepSeek routing to TSMC) reinforces its indispensability. The competitive threat from Intel/Samsung is real over a five-year horizon but unproven; TSMC's execution consistency remains a durable edge. The core structural vulnerability is geographic concentration in Taiwan, not competition.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>The five-year outlook is strong on fundamentals with elevated tail risk. Growth drivers are secular: AI compute, high-performance computing, advanced packaging, and continued node migration all funnel through TSMC, and demand-side signals (enterprise AI adoption, sustained hyperscaler/fabless capex, broadening custom-silicon designs) point to a multi-year cycle rather than a short spike. Headwinds include inevitable semiconductor cyclicality (a demand digestion phase will come at some point), rising capital intensity, and margin drag from geographically diversified overseas fabs, plus intensifying competition from subsidized rivals. The overarching constraint is geopolitical concentration, which caps the multiple the market will pay regardless of operational excellence. Absent a geopolitical shock, TSMC should keep compounding revenue and earnings at attractive rates, though the record ~35% growth and ~66% gross margin of the latest quarter likely represent a high-water mark that normalizes over the cycle.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>TSMC is a best-in-class business at a fair-but-not-cheap valuation, and nothing this week alters that. It is the indispensable manufacturer of leading-edge AI chips, with a moat evidenced by hard numbers rather than narrative — ~66% gross margin, &gt;50% net margin, ~46% ROIC, and 30%+ revenue growth, all while self-funding massive capex and de-levering a fortress balance sheet. At ~21x forward earnings with a PEG near 1.4, the market pays a reasonable price for durable, high-quality growth. The bull case is that AI demand proves structurally durable and TSMC's leading-edge monopoly sustains premium returns; the bear case is a geopolitical shock or a cyclical AI-capex digestion that reverses peak margins. This remains a high-conviction quality holding whose primary risk is exogenous (Taiwan) rather than operational or competitive. Appropriate posture is constructive ownership with position sizing that respects the un-hedgeable geopolitical tail risk, mindful that the stock trades near its 52-week high with much upside already priced.</t>
+        </is>
+      </c>
+      <c r="M29" s="11" t="n">
+        <v>76</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Confidence is supported by six quarters of consistent, mutually reinforcing financial data — accelerating revenue, margin expansion across every line, exceptional and stable returns on capital, and a de-leveraging balance sheet. These are hard facts, not sentiment, and the recent news is confirmatory rather than contradictory, so the thesis is stable. Confidence is limited by: (1) apparent currency/unit inconsistencies in the valuation snapshot (NT$ financials vs USD price) producing implausible EV and P/B figures, reducing precision on cross-currency multiples; (2) absence of ROE/ROIC for earlier quarters, limiting long-trend confirmation; (3) unquantifiable geopolitical tail risk that no financial analysis can price; and (4) the stock trading near its highs after a large rally, raising odds that near-term returns lag even if the business performs. Since this is only one day after the prior analysis with no material change, I hold the confidence level constant.</t>
+        </is>
+      </c>
+      <c r="O29" s="11" t="n">
+        <v>92</v>
+      </c>
+      <c r="P29" s="11" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Broadcom is a diversified semiconductor and infrastructure-software company riding a powerful AI-driven inflection. Across the five reported quarters, revenue accelerated from ~$15.0B (Q2 2025) to $22.2B (Q2 2026), with the latest quarter delivering ~48% YoY and ~15% sequential growth. Margins are exceptional and expanding: gross margins near 69%, operating margins climbing from ~39% to ~49%, and FCF margin of ~46% ($10.3B FCF on $22.2B revenue, on trivial ~$231M capex). The company generates enormous cash and continues deleveraging, with debt/equity falling from ~0.97 to ~0.74 and interest coverage rising to ~10.7x. ROE (~33%) and ROIC (~20%) confirm high-quality economics, though inflated by VMware's goodwill-heavy balance sheet. At ~$371 the stock trades at ~62x trailing and ~19x forward earnings, ~25% below its 52-week high of $495. This week's price action is a sentiment-driven pullback from a valuation downgrade, a broad chip selloff (Samsung guidance), and competitive-threat headlines (DeepSeek in-house chip), none of which alter the fundamentals in the data provided. The central tension remains a genuinely strong business against a valuation that leaves little room for disappointment.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Nothing in the underlying financials has changed since the prior analysis one day earlier; the reported quarterly data and ratios are identical. The material new items are all sentiment- and news-driven: (1) A valuation-based bank downgrade pushed shares down ~3% and reinforced the view that the stock is priced ahead of fundamentals rather than deteriorating. (2) A broad semiconductor selloff triggered by weak Samsung guidance and general risk-off macro pressure, again a sentiment reset rather than a company-specific event. (3) Reports that DeepSeek is developing its own AI inference chip, and that an Nvidia AI system slipped to 2028, which introduce two conflicting signals for AVGO's custom-ASIC franchise: on one hand, rising in-house/custom silicon efforts validate the ASIC/XPU merchant model Broadcom serves; on the other, a delayed Nvidia rack cycle could soften near-term demand for Broadcom's AI networking content and hyperscalers in-sourcing could pressure long-term share. These are incremental narrative developments, not a demonstrated change in Broadcom's order book or financials. My assessment and ratings are therefore essentially unchanged from the prior writeup.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Broadcom sits at the intersection of two secular franchises: custom AI accelerators (XPUs/ASICs) plus high-speed networking silicon, and a sticky infrastructure-software portfolio anchored by VMware, mainframe, and security. The financials show the thesis materializing: near-50% operating margins, ~46% FCF margins, and revenue reaccelerating to ~48% YoY reflect real operating leverage on a differentiated product set. Hyperscaler custom-silicon demand delivers high-margin, design-win-locked revenue with multi-year visibility, reinforced by the Apple extension through 2031. The software segment adds recurring, high-margin cash flow largely insulated from semiconductor cyclicality. Cash generation is prodigious and rising, funding continued deleveraging, dividends, and buybacks. A forward P/E of ~19x with a PEG near 0.4 implies that even partial persistence of growth makes the current price undemanding relative to the earnings trajectory. Notably, the proliferation of custom-silicon programs (including efforts like DeepSeek's) can validate rather than undermine Broadcom's merchant ASIC design model, since many such players still need Broadcom's IP, SerDes, and networking. ROIC ~20% and ROE ~33% mark a genuine compounder, not a commodity chipmaker.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>The valuation embeds continued hypergrowth: at ~62x trailing earnings, ~24x EV/revenue, and ~43x EV/EBITDA, any deceleration in AI/custom-silicon orders could compress the multiple sharply, as the ~25% drawdown from the 52-week high already hints. Custom-ASIC revenue is concentrated among a handful of hyperscaler customers whose capex plans can shift quickly; a reported Nvidia system delay to 2028 illustrates how AI infrastructure timelines can slip, potentially deferring Broadcom's networking content. Rising in-house AI chip efforts (DeepSeek and others) cut both ways and could over time reduce reliance on merchant partners for some workloads. The Q2 2026 inventory build (from $2.0B to $4.3B over the period, up sharply sequentially) warrants scrutiny as a possible demand-timing risk. Competition in AI optical interconnects and co-packaged optics is intensifying. The balance sheet still carries ~$65B of VMware-related debt, and book value is heavily goodwill/intangibles, so reported ROE/ROIC overstate tangible-capital returns. Quarterly net income is noisy (e.g., the tax/one-off-driven $8.5B in Q4 2025), making the trailing P/E an unreliable gauge.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Financial health is strong and improving. Revenue quality is high, blending design-win-locked semiconductor content with recurring software. Gross margin is stable near 68-69%; operating margin expanded from ~39% (Q2 2025) to ~49% (Q2 2026); FCF margin reached ~46% with $10.3B FCF on ~$231M capex, reflecting an asset-light, IP-driven model. Cash rose to ~$19.6B. The balance sheet carries ~$64.9B total debt against ~$87.7B equity (debt/equity ~0.74, down from ~0.97), with interest coverage improving to ~10.7x, clearly sustainable given cash generation. Financing outflows ($10.1B in Q1 2026, $4.8B in Q2 2026) are consistent with dividends, buybacks, and debt repayment; dividend yield is modest (~0.7%). Caveats: a large intangible/goodwill base from VMware inflates book-based returns, and the notable inventory increase in the latest quarter merits monitoring. Overall, this is a cash machine with a de-risking balance sheet.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Fairly Valued</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>The headline ~62x trailing P/E looks demanding but is distorted by uneven quarterly net income (including the large Q4 2025 figure). More informative are the ~19x forward P/E and PEG near 0.4, alongside ~43x EV/EBITDA and ~24x EV/revenue. For a business compounding revenue ~48% YoY with ~49% operating margins and ~46% FCF margins, a high-teens/low-20s forward multiple is not obviously excessive versus its own history for a franchise of this quality. This week's ~3% decline on a valuation downgrade and broad chip selloff is a sentiment reset, not a fundamental change; shares remain ~25% below the 52-week high. That said, the elevated EV/revenue and EV/EBITDA leave little margin for error if AI-driven growth decelerates or hyperscaler capex enters a digestion phase. Balancing exceptional cash economics and growth against a price that already discounts continued strong execution, Fairly Valued remains the most defensible rating.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Broadcom holds a wide, durable moat across several niches. In custom silicon/ASICs, it is a leading merchant partner for hyperscalers building bespoke AI accelerators, a business with high switching costs because designs are co-engineered and multi-year (the Apple extension to 2031 exemplifies the stickiness). In high-speed networking (switching/routing, SerDes, optical), Broadcom is a share leader with deep IP and process advantages. The Infrastructure Software segment (VMware, mainframe, security) provides mission-critical, embedded products with strong renewal economics and pricing power, evident in ~69% gross margins and expanding operating margins. Threats include intensifying competition in AI optical interconnects/co-packaged optics and the concentration risk of serving a small set of hyperscalers who could in-source; the emergence of players developing their own inference chips (e.g., DeepSeek) is a reminder that in-sourcing is a live long-term risk even as it can also expand the merchant-ASIC market. On balance, IP moats, switching costs, and scale support a strong competitive position.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Over five years, the primary growth driver is AI infrastructure: custom accelerators and the networking backbone that connects them, where Broadcom's content per system is high and rising. Secondary drivers are the recurring, high-margin software franchise and steady non-AI demand across broadband, wireless, and enterprise. Industry tailwinds favor sustained data-center and AI capex, but this spending is cyclical and prone to digestion phases; the reported Nvidia system slip to 2028 is a concrete example of how deployment timelines can shift and introduce lumpiness. Key challenges include hyperscaler customer concentration, in-sourcing risk, rising competition in optical/networking, and execution/retention risk in the software business post-VMware. Given demonstrated margin expansion, cash generation, and deleveraging, the multi-year runway looks strong, but investors should expect volatility rather than smooth linear growth, with the outlook hinging on the durability of AI-driven demand.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Broadcom is a high-quality compounder benefiting from a genuine AI-driven inflection: revenue reaccelerating to ~48% YoY, operating margins expanding to ~49%, ~46% FCF margins, and improving returns on capital (ROIC ~20%). Its moat rests on co-engineered custom silicon with multi-year design-win lock-in (reinforced by the Apple extension to 2031), leadership in high-speed networking, and a sticky software franchise generating recurring cash. The balance sheet is de-risking rapidly, with debt/equity down to ~0.74 and interest coverage above 10x. The offset is valuation: at ~19x forward earnings and ~24x EV/revenue, the market already prices in continued strong execution, leaving the stock vulnerable to AI-capex digestion or in-sourcing/competitive pressure, risks underscored by the inventory build, this week's sector selloff, an Nvidia timeline slip, and DeepSeek's in-house chip reports. The most reasonable stance is that this is a franchise worth owning at a fair (not cheap) price; long-term holders are compensated by quality and cash generation but should size positions with concentration and cyclicality risks in mind. Fairly Valued with a favorable long-term bias.</t>
+        </is>
+      </c>
+      <c r="M30" s="11" t="n">
+        <v>72</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Confidence rests on clear, consistent financial evidence: accelerating revenue, expanding margins, strong FCF, and a de-leveraging balance sheet, corroborated by the Apple extension and durable AI demand narrative. It is tempered by data gaps (Q4 2024/Q1 2025 are NaN, limiting multi-year trend analysis), a trailing P/E distorted by uneven quarterly net income, a goodwill-heavy balance sheet that inflates return ratios, and the absence of segment-level detail to isolate AI/custom-silicon economics from software. This week's news is directionally mixed (valuation downgrade and competitive threats versus AI-spend validation) and did not change the reported financials, so I hold confidence steady rather than raising or lowering it.</t>
+        </is>
+      </c>
+      <c r="O30" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="P30" s="11" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>JPMorgan remains the largest and most diversified U.S. money-center bank, spanning Consumer &amp; Community Banking, an integrated Commercial &amp; Investment Bank, and Asset &amp; Wealth Management. The latest reported quarter (Q1 2026) showed genuine reacceleration: revenue of $49.8B (+~8.8% QoQ, +~9.9% YoY), net income of $16.5B, diluted EPS of $5.94 (+~17% YoY), net margin recovering to ~33% from the Q4 2025 trough of ~28%, and ROE in the healthy mid-teens (~16%). Shareholder equity has compounded steadily from $351B (Q1 2025) to $364B (Q1 2026) despite active buybacks, evidencing real internal capital generation. At ~16x trailing and ~14x forward earnings, ~2.6x book, and near its 52-week high ($339 vs. $343), the market already recognizes the franchise's quality. Recent news is largely non-material to fundamentals, with the notable exception of a possible consortium acquisition of a debit-card network (Fiserv's STAR) that could deepen JPM's payments infrastructure control. The core investment question is unchanged: whether current mid-teens ROE and ~33% margins are a durable run-rate or reflect a favorable point in the credit and capital-markets cycle. The provided data still lacks credit-provision, net-charge-off, CET1, and NIM detail — the key swing variables for a bank. Net, this is a premium franchise fairly priced for its quality.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Nothing in this cycle materially changes the thesis relative to the prior analysis; the financial data is identical (Q1 2026 remains the latest quarter), so the fundamental picture is unchanged. The most notable incremental item in the news flow is a report that JPMorgan and other large U.S. banks are exploring a joint acquisition of Fiserv's STAR debit network. This is worth flagging as a potential (not yet consummated) strategic move that would reduce JPM's reliance on third-party processors and strengthen its control over payments rails — economically sensible given its scale, though financial impact depends entirely on deal terms that are not disclosed. Other items (a BofA note anticipating strong Q2 bank earnings, robust IPO/listing demand such as SK Hynix, JPM's asset-management FX repositioning, and competitive ETF offerings) are directionally supportive of a favorable capital-markets and fee backdrop but are macro/non-specific and do not alter fundamentals. In short: no material change to the underlying thesis, one strategic optionality item to monitor.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>JPMorgan's scale, funding-cost advantage, and diversified earnings streams allow it to compound tangible book value through cycles while earning mid-teens ROE — a level most banks cannot sustainably reach. The integrated CIB captures advisory, underwriting, and trading revenue that is benefiting from a strong issuance and markets environment (evidenced by heavy listing demand and a supportive backdrop for Q2 bank earnings). Consumer banking supplies a low-cost, sticky deposit base and a large payments franchise generating durable net interest income, while AWM adds capital-light, fee-based earnings with high switching costs. Q1 2026's ~17% EPS growth and margin recovery to ~33% demonstrate operating leverage. The fortress balance sheet lets JPM take share opportunistically during stress. Consistent capital return — a ~10% dividend hike plus buybacks executed at a reasonable ~2.6x book — steadily supports per-share compounding. Potential vertical integration into payments infrastructure (the debit-network exploration) is a further margin/optionality lever. If capital-markets activity and rate normalization persist, earnings power looks resilient rather than peaking.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Bank earnings are inherently cyclical, and current ~33% net margins and mid-teens ROE may reflect a benign credit environment plus elevated capital-markets fees rather than a durable run-rate. The provided data gives no visibility into loan-loss reserves, provisions, or net charge-offs — a genuine analytical blind spot; a recession or credit normalization would raise provisions and compress earnings meaningfully. Net interest income is sensitive to the rate path; falling rates or deposit repricing could pressure margins. The Q4 2025 dip to ~28% net margin and $4.63 EPS shows quarterly volatility is real. Debt-to-equity has drifted up from ~1.34x (Q1 2025) to ~1.42x (Q1 2026), and operating cash flow swings violently ($120B in Q4 2025 to -$212B in Q1 2026), reflecting balance-sheet-driven flows that resist conventional analysis. At ~2.6x book and within ~1% of its 52-week high, much of the good news appears priced in, leaving limited margin of safety if the cycle turns. Regulatory capital requirements and perennial litigation/compliance costs remain overhangs.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Financial health is strong. Revenue has trended upward — roughly $45B/quarter through 2025 rising to $49.8B in Q1 2026 — and Q1 2026 net income of $16.5B is the highest in the observed window. Net margin of ~33% and ROE of ~16% indicate high-quality, profitable operations, though margin volatility is evident (28% in Q4 2025 vs. 33% in Q1 2026). Shareholder equity grew steadily from $351B to $364B across five quarters despite active buybacks, confirming genuine internal capital generation. Debt-to-equity of ~1.42x is normal for a large diversified bank though it has crept up modestly. Standard operating/free cash-flow metrics are not meaningful here — the large negative swings reflect changes in trading assets, loans, and deposits, not distress. Capital allocation is shareholder-friendly: a ~10% dividend increase (yield ~1.8%) plus ongoing buybacks near a reasonable book multiple. Key data gaps persist: no credit provisions, net charge-offs, CET1 ratio, NIM, or deposit trends, all central to fully assessing cycle resilience.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Fairly Valued</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>At ~16x trailing and ~14x forward earnings with price-to-book of ~2.6x on mid-teens ROE, JPM trades at the upper end of where large-cap banks historically clear. A 2.6x book multiple is defensible only if ROE stays sustainably in the mid-teens — which JPM has demonstrated but which is cyclically dependent. The forward P/E of ~14x embeds continued earnings growth consistent with the ~17% YoY EPS growth just posted, so the multiple is not stretched relative to demonstrated growth. However, the stock sits within ~1% of its 52-week high, so the market is already rewarding quality and momentum, offering little discount for cycle risk. This is a premium franchise fairly priced for its quality — not an obvious bargain but not expensive given proven returns on equity. I characterize it as fairly valued, leaning toward the high end of fair; the risk/reward is more attractive on cyclical weakness than at current levels.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>JPMorgan has one of the widest moats in banking, rooted in scale, funding-cost advantage, diversification, technology investment, and brand. Its low-cost, sticky deposit base underpins a structural funding advantage, and the integrated CIB is a global leader in trading, underwriting, and advisory where scale and balance sheet directly drive share. High regulatory capital and compliance requirements act as barriers to entry favoring the largest, best-capitalized incumbents. Switching costs are meaningful in institutional/treasury services, custody, and wealth management. Pricing power is moderate — lending is largely commoditized — but breadth enables cross-selling and wallet-share capture. Potential vertical integration into payments infrastructure (the debit-network exploration) would further entrench its payments position. Relative to listed peers Visa and Mastercard (capital-light, higher-margin pure networks), JPM's moat is durable but its returns are structurally lower and more cyclical because it is a balance-sheet-intensive business.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Over five years, JPMorgan's growth drivers include continued share gains from scale and technology investment, expansion in higher-margin, capital-light payments and asset/wealth management, and the ability to deploy its fortress balance sheet during stress. Industry tailwinds include ongoing digitalization and consolidation favoring the largest players. Headwinds include the inherent cyclicality of credit and capital markets, rate-path sensitivity, rising regulatory capital demands that cap returns, and fintech/non-bank competition in payments and lending. The demonstrated ability to earn mid-teens ROE and grow book value through varied environments supports a constructive but measured outlook: this is a steady compounder rather than a high-growth story. Earnings will fluctuate with the macro cycle, but franchise durability plus consistent capital return should support mid-single to high-single-digit long-term per-share value compounding.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>JPMorgan is a best-in-class, diversified megabank that consistently earns mid-teens ROE, compounds tangible book value through cycles, and returns substantial capital via dividends and buybacks. The latest reported quarter confirms reaccelerating revenue and ~17% EPS growth with margin recovery, and the capital-markets backdrop remains supportive. The moat — scale, cheap deposits, regulatory barriers, and an integrated CIB — is durable, with optional upside from deeper payments-infrastructure integration. However, at ~2.6x book and ~14x forward earnings essentially at its 52-week high, the stock is fairly rather than attractively valued, and current profitability likely reflects a favorable point in the credit cycle. The provided data lacks credit-provision and capital-ratio visibility, the key swing factors for a bank. Net: a high-quality core financial holding suitable for long-term investors, best accumulated on cyclical weakness rather than at current elevated levels. Risk/reward is balanced, not compelling, today.</t>
+        </is>
+      </c>
+      <c r="M31" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Confidence is supported by clear, consistent financials showing strong and improving profitability (rising revenue, mid-teens ROE, growing equity, shareholder-friendly capital return) and a well-understood, durable business model. It is reduced by material data gaps: no credit-loss provisions, net charge-offs, CET1/capital ratios, or NIM/deposit detail — all essential for assessing cycle resilience. This cycle's news adds little of substance; the one item worth monitoring (the debit-network acquisition exploration) is unconfirmed and its financial impact is undisclosed. The cyclical nature of bank earnings and the stock's proximity to all-time highs continue to inject uncertainty into forward returns despite clear franchise quality. Confidence is unchanged from the prior analysis given no material fundamental change.</t>
+        </is>
+      </c>
+      <c r="O31" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="P31" s="11" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Visa remains a structurally elite payment-network operator with financials that confirm a toll-booth economic model: gross margins above 81%, operating margins in the high-60s%, and net margins around 53-54% in the most recent quarters. Revenue rose from ~$9.6B (Q1 2025) to $11.2B (Q1 2026), with Q1 2026 up ~17% YoY and diluted EPS up ~35% YoY, showing both top-line acceleration and buyback-driven per-share leverage. Returns on capital are outstanding (ROE &gt;60%, ROIC ~45%, ROA ~23%), and interest coverage above 40x confirms low financial risk. The dominant news theme in the last week is competitive/thematic pressure from stablecoins and crypto rails (Circle/USDC volume dominance, regulated dirham stablecoin, Bitcoin ETF inflows) plus Mastercard's multi-rail expansion, set against countervailing pieces arguing Visa's steady volumes demonstrate resilience. None of these threats has yet dented Visa's numbers. At ~30.7x trailing and ~23.7x forward earnings and near the top of its 52-week range ($294-$365) at $352, the stock is priced for continued high-quality compounding with limited margin of safety. The core long-term question is unchanged: whether Visa's network moat withstands a multi-year migration to alternative rails while it keeps compounding volume and earnings.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>There is little materially new since the prior writeup one day earlier; the financial data set is identical, so no fundamental change has occurred. The news flow this week shifted emphasis toward stablecoin disintermediation specifically -- Circle's USDC reportedly running ~70% of stablecoin volume, a regulated dirham stablecoin launching on UAE exchanges, and strong crypto/Bitcoin ETF momentum -- which sharpens (but does not newly introduce) the alternative-rail threat already flagged. Notably, the prior analysis's reference to a potential bank consortium acquiring Fiserv's debit network does not reappear in this news set, so that specific threat is not corroborated here. Countervailing coverage frames Visa's steady ~15% revenue growth as evidence of resilience against crypto, and highlights Visa's own moves into agentic/AI commerce and stablecoin settlement. A technical breakout was noted but is trading-driven and not fundamentally meaningful. Net: no material change to fundamentals; the competitive narrative is more concentrated on stablecoins, which is a sentiment/framing shift rather than a numbers-level development.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Visa runs one of the highest-quality business models available: an asset-light, two-sided network on global electronic payments with ~81% gross, ~67-68% operating margins, and ~45% ROIC. The multi-decade secular shift from cash to digital and mobile payments continues to expand its transaction base without proportional cost growth, and Q1 2026's 17% YoY revenue and 35% YoY EPS growth show the franchise is still accelerating, not maturing. Aggressive buybacks (financing outflows of $6-9B in recent quarters) shrink the share count and amplify per-share economics. Visa is positioning at the center of emerging channels -- Visa Direct money movement, tokenization, AI-agent commerce, and even stablecoin settlement -- suggesting it can monetize new rails rather than only defend old ones; stablecoins can settle over Visa infrastructure rather than purely bypass it. A fortress balance sheet (interest coverage &gt;40x, debt/equity ~0.67) supports continued capital return and investment. Low beta (0.75) and highly predictable cash flows make it a resilient compounder through cycles.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>The concentration of stablecoin and multi-rail headlines is a genuine long-term warning: if account-to-account, real-time payment, and blockchain/stablecoin rails scale, the card-network toll could be disintermediated, compressing the pricing power underpinning 50%+ net margins. Circle/USDC's dominance of stablecoin volume and regulated fiat-backed stablecoins launching in new jurisdictions show the alternative-rail ecosystem is maturing, and Mastercard's multi-rail diversification signals competitors preparing for a post-card world. Interchange regulation remains a persistent structural overhang on the entire card economic model. The stock's premium multiple (30.7x trailing) leaves little room for disappointment; any deceleration in volume or take-rate, or margin compression from competitive/regulatory forces, could de-rate the shares meaningfully given they sit near the 52-week high. The Q1 2026 FCF drop (FCF margin ~23% on $3.0B operating cash flow versus $6-7B typical) is likely timing but remains unexplained and should be confirmed as non-structural.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Financial health is excellent and unchanged. Revenue is high-quality and recurring, driven by transaction volume on a global network, with remarkably stable margins: gross ~81%, operating ~67-68%, net ~53-54% across recent quarters, indicating durable pricing power rather than cyclical strength. Cash generation is normally very strong (FCF margins 45-62%), though Q1 2026 dipped to ~23% on a $3.0B operating cash flow quarter versus the $6-7B norm -- this stands out and appears to be working-capital/timing rather than a deterioration in economics, but warrants monitoring. The balance sheet is solid: cash ~$12.4B, total debt ~$24B, debt/equity ~0.67, interest coverage &gt;40x. Capital allocation is shareholder-friendly, with heavy buybacks (financing outflows $6-9B/quarter) driving EPS growth ahead of net income growth, plus a modest dividend (~0.75% yield). Returns on capital are elite: ROE &gt;60%, ROIC ~45%, ROA ~23%.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Fairly Valued</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>At $352, Visa trades at ~30.7x trailing and ~23.7x forward earnings, EV/EBITDA ~22.7x, and PEG ~1.6 -- premium multiples that are consistent with Visa's own historical range for a franchise generating ~45% ROIC, 53%+ net margins, and 17% revenue growth with 35% EPS growth. A simplistic 'high P/E therefore overvalued' view is inappropriate given the durability and returns of the business; the forward P/E of ~23.7x against mid-teens revenue growth and higher EPS growth implies a reasonable growth-adjusted price. The shares sit near the upper end of their 52-week range ($294-$365), so there is limited margin of safety and the stock is not cheap. Weighing the strength and durability of the model against emerging (but unquantified) rail-competition risk, the valuation is fair -- appropriate compensation for quality, with downside if disintermediation begins to appear in volume or take-rate trends.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Visa's moat is among the widest in financial services: a two-sided network of billions of cards and tens of millions of acceptance points, reinforced by network effects, entrenched brand acceptance, high switching costs for issuers and merchants, and a scaled, low-cost processing infrastructure (VisaNet). This yields exceptional pricing power, visible in 80%+ gross and 67%+ operating margins, within a rational effective duopoly with Mastercard. However, credible long-term erosion vectors are intensifying: stablecoin and crypto rails (USDC dominance, regulated fiat-backed stablecoins), real-time account-to-account systems, and Mastercard's multi-rail push. The offsetting nuance is that Visa can partly co-opt these -- settling stablecoin flows and extending Visa Direct/tokenization -- rather than being purely bypassed. None of these threats has yet materially dented volumes or margins, but they represent the first genuine structural challenges to the card-toll model in years.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>The five-year outlook remains favorable but with wider tail risk than Visa's history implies. Tailwinds: continued global cash-to-digital conversion, cross-border growth, Visa Direct money movement, tokenization, and monetization of new commerce channels including AI-agent purchasing and potentially stablecoin settlement. These support high-single to low-double-digit volume growth with margin stability and buyback-fueled EPS growth. Headwinds: persistent interchange regulation, maturing alternative rails (stablecoins, A2A/RTP) that could gradually compress value captured per transaction, and competitor diversification. The base case over five years is continued compounding, but the distribution of outcomes has widened -- investors should weight the possibility of slower growth and modest multiple compression if disintermediation accelerates faster than Visa's ability to monetize new rails.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Visa is a best-in-class compounder: an asset-light payment network with elite margins (53%+ net), ~45% ROIC, accelerating revenue (17% YoY) and EPS (35% YoY) growth, a fortress balance sheet, and disciplined capital returns. Secular payment digitization continues to expand its transaction base, and it is proactively extending into money movement, tokenization, AI-driven commerce, and even stablecoin settlement. The primary risk is not near-term fundamentals -- which remain excellent -- but the longer-term structural threat of disintermediation from stablecoin/crypto and A2A rails and competitor multi-rail strategies, compounded by interchange regulation. At ~23.7x forward earnings and near its 52-week high, the stock is fairly valued: a full but justified price for quality, with limited margin of safety. The thesis is to own a durable compounder while monitoring whether emerging rail competition shows up in volume or take-rate trends, and to confirm the Q1 2026 FCF dip is timing-related. Net: a high-quality hold / accumulate-on-weakness rather than a bargain.</t>
+        </is>
+      </c>
+      <c r="M32" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Confidence is supported by the clarity and consistency of Visa's financials -- stable elite margins, high ROIC, strong balance sheet, and accelerating growth are unambiguous and grounded in the data. It is tempered by the absence of full ROE/ROIC history for early quarters, the unexplained Q1 2026 FCF drop, and the lack of financial data on peers (MA, JPM) to directly benchmark competitive share. The stablecoin/alternative-rail threats are genuinely material to the long-term moat but remain difficult to quantify from headlines, and this week's news added narrative emphasis without any change in the underlying numbers, so confidence is held steady rather than raised.</t>
+        </is>
+      </c>
+      <c r="O32" s="11" t="n">
+        <v>87</v>
+      </c>
+      <c r="P32" s="11" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Mastercard remains one of the highest-quality business models in financial services, operating as one half of the global card-network duopoly with Visa. Reported financials continue to confirm elite economics: gross margins in the 76-79% range, operating margins around 58-60%, net margins consistently above 45%, and FCF margins that swing seasonally from ~30% in Q1 to over 60% in stronger quarters. The most recent quarter (Q1 2026) shows revenue of $8.40B, up ~15.8% YoY, with diluted EPS of $4.35, up ~21% YoY, alongside the usual Q1 sequential softness (-4.6% QoQ). The balance sheet carries ~$19B of debt against ~$8-11B cash, but interest coverage near 27-28x and ROIC near 90% underscore a capital-light, highly cash-generative model; negative-to-thin book equity and very high ROE/P/B are artifacts of aggressive buybacks, not distress. At ~30.8x trailing and ~23.3x forward earnings, the stock sits roughly in the lower-to-middle of its historical multiple range and ~12% below its 52-week high. The central long-term debate is unchanged: whether emerging payment rails (stablecoins, bank-owned debit networks) erode the card moat over a multi-year horizon. On balance the fundamentals remain exceptionally strong and the valuation is reasonable relative to quality and growth.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Nothing in this period materially changes the thesis; the news flow is largely a re-articulation of themes already identified in the prior analysis. The financial data set is unchanged from the previous writeup (same trailing quarters through Q1 2026), so there is no new fundamental data point to reassess. The most notable items are competitive-narrative developments rather than events: (1) Mastercard's participation in an open USD stablecoin initiative, which is a constructive signal that management is positioning to participate in, rather than be displaced by, stablecoin settlement rails; and (2) continued reporting that banks may pursue acquisition of a Fiserv-owned debit network, a genuine but still-early disintermediation threat. Neither has appeared in the financials. The stablecoin engagement is a modest incremental positive versus the prior analysis because it converts an abstract threat into a concrete strategic hedge, but it is directional messaging, not evidence of a fundamental shift. In short: no material change to the fundamental picture since the last analysis.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Mastercard is a duopoly network with powerful two-sided network effects, deeply embedded switching costs for issuers and merchants, and structural pricing power that is nearly impossible to replicate. It compounds revenue at double digits (Q1 2026 +15.8% YoY) while sustaining ~58-60% operating margins and converting a large share of revenue to free cash flow, with ROIC near 90%. The secular migration from cash to electronic payments, particularly in emerging markets and in commercial/B2B and cross-border flows, provides a multi-year growth runway. The value-added services layer (analytics, cybersecurity, consulting/AI, loyalty) grows faster than the core network, deepens customer entanglement, and diversifies away from pure interchange. Multi-rail expansion (Mastercard Move, virtual cards, and now stablecoin participation) positions the company to earn economics on newer flows rather than merely defend cards. Management's consistent, value-accretive buyback program ($3-5B financing outflows per quarter) amplifies per-share earnings. At ~23x forward earnings against 20%+ EPS growth, the risk/reward for a business of this quality is favorable.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>The most credible long-term risk remains disintermediation of card rails. A bank consortium acquiring a debit network (e.g., Fiserv's) could route volume around Mastercard, pressuring both transaction counts and pricing. Stablecoin/crypto settlement threatens near-zero-cost rails that could compress the disproportionately lucrative cross-border economics where Mastercard earns outsized margins; Mastercard joining a stablecoin initiative is a hedge but could also cannibalize higher-margin flows. Regulatory scrutiny of interchange is a persistent global overhang. The premium valuation (13.8x sales, 14.2x EV/revenue, 22.5x EV/EBITDA) leaves limited room for error, so any growth deceleration or margin erosion could trigger meaningful multiple compression. Revenue is exposed to consumer discretionary spending and is cyclically vulnerable in a downturn. The balance sheet is financially engineered for shareholder returns via buybacks that have produced thin/negative book equity, which works well only so long as cash generation stays robust. Concentration in a single business model raises idiosyncratic disruption risk over a 5-10 year horizon.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Financial health is excellent. Revenue is high-quality, recurring, and increasingly diversified across geographies and services, with consistent double-digit YoY growth (Q1 2026 +15.8%). Margins are elite and stable: gross margin ~76-79%, operating margin ~58-60%, net margin steady above 45% across all reported quarters. Cash generation is exceptional, with operating cash flow of $2.4B-$5.7B per quarter and FCF margins ranging from ~30% in seasonally weak Q1 to over 60% in Q3 2025. The balance sheet shows ~$19B total debt against ~$8-11B cash, but interest coverage near 27-28x makes debt comfortably serviceable. Reported debt-to-equity (~2.5-2.8x), very high ROE (&gt;190%), and P/B (~70x) are artifacts of buybacks that have shrunk book equity rather than signs of stress; ROIC near ~90% reflects an asset-light, capital-efficient model. Capital allocation strongly favors buybacks with a modest dividend (~0.65% yield), evidenced by $3-5B quarterly financing outflows (Q1 2026 financing outflow of ~$5.0B). The primary caution is that the thin/negative equity structure means the capital-return program depends on continued strong cash flows.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Fairly Valued</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>At ~30.8x trailing and ~23.3x forward earnings, Mastercard trades within its long-run historical range and toward the lower-to-middle portion of it; historically the stock has commanded 30-40x earnings given its growth and margin profile. The forward P/E of ~23.3x against 20%+ EPS growth implies a PEG near 1.64, which is not cheap but is justifiable for a duopoly compounder with ROIC near 90%. Price-to-sales of ~13.8x and EV/EBITDA of ~22.5x are high in absolute terms but consistent with the business's exceptional margins and cash conversion. The price sitting ~12% below the 52-week high suggests some multiple compression has already occurred. Given the combination of quality, growth, and a multiple modestly below historical peaks, the stock looks fairly valued with a slight lean toward attractive rather than expensive; it is not a deep-value situation, and the premium reflects genuine business quality rather than speculation. This rating is unchanged from the prior analysis, appropriately, since neither the financials nor the valuation inputs have materially shifted.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Mastercard holds one of the widest and most durable moats available. As one half of the global card-network duopoly, it benefits from strong two-sided network effects, extremely high switching costs embedded in its rails, and structural pricing power. Industry structure is concentrated and rational, and the capital-light model delivers returns on capital that few businesses can match. Value-added services and multi-rail initiatives deepen customer entanglement and expand the addressable market. The principal threats are structural rather than from a single named competitor: bank-owned debit networks that could bypass the network, and stablecoin/crypto settlement rails that could undercut cross-border economics. Mastercard's decision to participate in an open USD stablecoin effort is evidence it intends to embed itself in emerging rails rather than defend cards alone, which modestly strengthens the case that it can participate in disruption. These threats are real but still nascent and have not appeared in the financials; the moat remains formidable while warranting ongoing monitoring.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>The long-term outlook remains strong. Secular tailwinds include the continued global cash-to-digital migration, growth in commercial/B2B and cross-border flows, emerging-market penetration, and expansion of high-margin value-added services. Multi-rail and stablecoin initiatives are deliberate hedges that could turn disruptive settlement technologies into incremental revenue rather than pure threats. The chief headwinds are regulatory pressure on interchange, potential disintermediation from bank-owned networks, and stablecoin/crypto settlement that could compress the most lucrative cross-border economics over a 5-10 year horizon; success in offsetting these is not guaranteed and the landscape is more dynamic than a decade ago. Over the next five years the base case is continued double-digit revenue growth and mid-teens-plus EPS growth, with the pace potentially moderating if disruption accelerates or the consumer weakens cyclically.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Mastercard is a best-in-class compounder: a duopoly network with elite and stable margins (net &gt;45%), extraordinary returns on capital (ROIC ~90%), consistent double-digit revenue growth, and prodigious free cash flow steadily deployed into buybacks. The financials show no deterioration, and the valuation at ~23x forward earnings against 20%+ EPS growth is reasonable relative to the company's own history and quality. The bull case rests on the enduring cash-to-digital shift, services diversification, and pricing power; the bear case rests on multi-year disintermediation risk from bank-owned debit rails and stablecoins alongside a premium multiple with limited margin for error. This period's news adds no material fundamental change—the stablecoin participation is a mild positive that converts an abstract threat into a concrete strategic hedge. On the evidence available, the moat and growth durability outweigh the still-early competitive threats, making Mastercard an attractive long-term holding for investors comfortable paying a quality premium, with disruption of the core rails the key variable to monitor.</t>
+        </is>
+      </c>
+      <c r="M33" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Confidence is high because the financial data is unusually clean and consistent: elite margins, strong cash generation, high interest coverage, and durable growth are directly evidenced across multiple quarters, and the duopoly moat is well established. It is unchanged from the prior analysis because no new financial data was introduced and the news flow reinforced rather than altered the existing thesis. Confidence is tempered by three factors: genuine early-stage structural threats (bank-owned debit networks, stablecoins) whose eventual impact is uncertain; the thin/negative book equity from buybacks that limits some traditional balance-sheet checks; and ratio fields (ROE, P/B) distorted by capital structure that require interpretation. Missing full-year segment detail and Q4 2024 comparability data slightly reduce precision.</t>
+        </is>
+      </c>
+      <c r="O33" s="11" t="n">
+        <v>90</v>
+      </c>
+      <c r="P33" s="11" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Amazon operates three engines -- North America retail, International retail, and AWS -- supplemented by high-margin advertising and Prime subscriptions. The trailing data through Q1 2026 shows a business scaling revenue past $180B/quarter with structurally improved profitability: operating margins now sit in the 11-13% range versus historically thin single-digit retail-era levels. Q1 2026 net income of $30.3B (16.7% net margin) and ~75% YoY EPS growth reflect strong operating leverage, but the headline was flattered by roughly $17B of non-operating items (EBIT of $40.6B vs operating income of $23.9B), so underlying operating momentum is more modest than the EPS print suggests. The defining strategic tension remains capital intensity: capex has ballooned to $39-44B per quarter to build AI/cloud infrastructure, pushing free cash flow negative in Q1 2026 (-$18.2B) despite robust operating cash flow. Amazon is now tapping the bond market for ~$25B to fund this buildout, and total debt has risen from ~$133B to ~$210B over the past year. ROIC of ~16-17% and ROE of ~20% suggest capital is still being deployed productively. Valuation at ~32x trailing and ~25x forward earnings sits within Amazon's historical norm for a franchise of this quality. Nothing in the last week materially changes the thesis established in the prior analysis.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>There is no material change from the previous analysis dated one day earlier. The only concrete news item -- the ~$25B bond sale to fund AI infrastructure -- was already identified and analyzed in the prior writeup, so it is not new. This week's news flow is otherwise repetitive coverage of the same bond-sale story (multiple outlets restating debt-funded AI capex), plus non-material or tangential items (DeepSeek's custom chip, SpaceX's Nasdaq-100 inclusion, Roku vs. Sirius XM, Trump crypto, a broad macro selloff on higher yields/oil). The DeepSeek custom-chip story is a mild, indirect positive that reinforces the industry-wide move toward proprietary AI silicon, validating Amazon's Trainium/Inferentia strategy, but it is directional color rather than a fundamental change. In short: no new quarter of financials, no new guidance, and no change to the balance-sheet or capex trajectory beyond what was already captured. Plainly stated, nothing material changed.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Amazon has transformed from a low-margin retailer into a diversified compound-margin business, with operating margins structurally higher (11-13%) than the sub-5% levels of a few years ago, driven by mix shift toward AWS, advertising, and third-party marketplace services -- high-margin, capital-light revenue layered on the retail base. AWS is the crown jewel: if the current AI infrastructure buildout captures meaningful enterprise AI/cloud workload share, incremental margins are very high and could sustain years of double-digit growth with expanding profitability. The company still generates enormous operating cash flow ($54.5B in Q4 2025, $26B in Q1 2026), so today's negative FCF reflects deliberate investment, not distress. ROIC of ~16-17% shows capital is still being deployed above its cost. The ability to raise $25B of debt cheaply reflects a fortress credit profile, funding growth without equity dilution. Revenue grew ~17% YoY in Q1 2026 -- a remarkable rate at this scale -- and the industry-wide push toward custom AI silicon (echoed by DeepSeek's chip effort) supports Amazon's own vertically integrated Trainium/Inferentia cost advantage.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>The AI capex cycle is the central risk. Capex of $39-44B per quarter has already driven FCF negative (-$18.2B in Q1 2026), and the $25B bond raise signals intensification. If AI/cloud demand disappoints or competitive pricing from Azure and Google Cloud compresses returns, Amazon could be left with a rapidly depreciating asset base, rising interest expense, and years of suppressed free cash flow. Total debt nearly doubled YoY to ~$210B, with long-term debt rising from ~$53B to ~$119B -- a material shift in balance-sheet risk profile, though still manageable. Earnings quality is a caveat: Q1 2026 net income substantially exceeded operating income on ~$17B of non-operating gains, so the ~75% EPS growth overstates operating momentum, and normalized earnings imply a higher effective multiple. Retail remains exposed to consumer-cyclical weakness, and macro pressure (higher yields, oil) can compress high-beta tech multiples (beta 1.46). At ~32x trailing earnings with FCF negative, the stock prices in continued flawless execution; any AWS growth stumble or capex-driven margin disappointment could de-rate the multiple.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Revenue quality is high and diversified, growing ~17% YoY to $181.5B in Q1 2026, with the best-margin revenue (AWS, advertising, subscriptions) carrying the strongest economics. Gross margin is stable at ~48-52%. Operating margin has improved to the 11-13% range -- a genuine structural gain. Operating cash flow is very strong ($26B in Q1 2026; $54.5B in Q4 2025), but free cash flow has turned sharply negative (-$18.2B in Q1 2026) as capex surged to $44B/quarter; this is investment-driven, not operational weakness. The balance sheet has weakened at the margin: total debt rose from ~$133B (Q1 2025) to ~$210B (Q1 2026), with a further ~$25B bond adding more. However, interest coverage remains very comfortable (~46x), debt-to-equity of ~0.47 is moderate against $442B of equity, and ~$102B of cash provides ample liquidity. ROE (~20%) and ROIC (~16-17%) indicate productive capital deployment. No dividend; share count is roughly flat, so dilution is not a concern and there is no evidence of meaningful buybacks. The key watch item remains whether rising capex and debt service continue to suppress free cash flow for an extended period.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Fairly Valued</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>At ~32x trailing and ~25x forward earnings, ~3.7x EV/revenue, and ~17.4x EV/EBITDA, Amazon trades within the range typical of its historically premium multiple for a high-growth franchise. For a business compounding revenue ~17% with expanding operating margins and mid-teens ROIC, a ~25x forward P/E is not demanding relative to its own history, where Amazon frequently commanded far higher multiples during retail-margin-compressed periods. Two factors temper enthusiasm: a PEG of ~1.83, and trailing earnings partly inflated by ~$17B of non-operating gains -- normalized operating earnings would push the effective multiple higher. Negative free cash flow makes FCF-based valuation unattractive today, but that reflects investment intensity rather than deteriorating economics. The stock sits ~12% below its 52-week high of $278.56 and well above its $196 low. Balancing a durable, improving franchise against elevated capex risk and somewhat flattered earnings, fairly valued is the most defensible conclusion -- neither an obvious bargain (despite media framing of 'historically cheap') nor stretched.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Amazon possesses one of the widest moats in the market, spanning multiple businesses. In retail, its scale, logistics/fulfillment network, and Prime ecosystem create switching costs and a self-reinforcing marketplace flywheel that competitors struggle to replicate. AWS is a category leader in cloud infrastructure with deep switching costs (embedded enterprise workloads, data, and tooling), network effects, and pricing power from scale economics; its vertical integration into custom silicon (Trainium/Inferentia) is a structural cost advantage, reinforced by the broader industry shift toward proprietary AI chips. The advertising business benefits from proprietary purchase-intent data. Primary threats are Microsoft Azure and Google Cloud, where all three are spending aggressively on AI infrastructure -- a potential capacity arms race that could pressure returns. In retail, competition from Walmart and lower-cost cross-border platforms persists but has not eroded Amazon's dominance. Overall the moat is durable and multi-dimensional.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>The five-year outlook is anchored on AWS and AI. If Amazon successfully monetizes the AI infrastructure it is building, cloud can drive sustained double-digit growth with high incremental margins, while advertising continues scaling as a high-margin profit center. Retail provides a stable, cash-generative base with modest margin upside from automation and third-party mix. Tailwinds include secular cloud adoption, enterprise AI deployment, and Amazon's structural cost/logistics advantages. Headwinds include the risk that the current AI capex supercycle produces overcapacity or sub-cost-of-capital returns, intensifying cloud price competition, rising interest expense from a larger debt load, regulatory/antitrust scrutiny, and consumer-cyclical retail exposure. The realistic base case is continued mid-teens revenue growth with margins holding or gradually expanding, but with free cash flow suppressed for the next 1-3 years while the AI buildout is digested. Execution on capital allocation is the biggest swing variable.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Amazon is a high-quality, multi-engine compounder whose profitability has structurally improved (operating margins now 11-13% vs low single digits historically) while still growing revenue ~17% at massive scale. The bull thesis rests on AWS and advertising continuing to shift the earnings mix toward high-margin, moaty businesses, with the current AI investment eventually earning strong returns given ~16-17% ROIC. The bear thesis centers on capital intensity: capex has driven FCF negative, debt nearly doubled to ~$210B, and a ~$25B bond raise signals more spending ahead -- if AI/cloud returns disappoint, free cash flow stays depressed and the premium multiple could compress. Earnings quality is a caveat, as Q1 2026 net income was materially boosted by non-operating gains. At ~25x forward earnings the stock is fairly valued for its quality and growth, offering reasonable but not exceptional risk-adjusted upside. This remains a hold/accumulate-on-weakness franchise for patient investors comfortable with a multi-year capex-digestion period, rather than a deep-value opportunity. The past week produced no fundamental change to this view.</t>
+        </is>
+      </c>
+      <c r="M34" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Confidence is supported by six quarters of consistent, high-quality financial data showing durable revenue growth, structurally improved margins, strong operating cash flow, and solid returns on capital, plus a clearly identifiable moat. It is reduced by: (1) missing full-year YoY comparability (several ratio fields are NaN and Q4 2024 data is absent), (2) earnings-quality concerns from large non-operating gains in Q1 2026, (3) genuine uncertainty about whether the aggressive AI capex cycle will earn its cost of capital -- the swing factor for the thesis, and (4) reliance on qualitative, largely repetitive news rather than fresh quantified data. Because nothing material changed this week, confidence is unchanged from the prior analysis.</t>
+        </is>
+      </c>
+      <c r="O34" s="11" t="n">
+        <v>88</v>
+      </c>
+      <c r="P34" s="11" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MCD</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>McDonald's remains a franchise-heavy, capital-light QSR operator with industry-leading and stable margins (operating margin consistently 44-48%, net margin ~30-33%) and strong free cash flow. The most recent reported quarter (Q1 2026) showed revenue of $6.52B, up ~9.4% YoY, net income of $1.98B, and EPS up ~6.9% YoY, confirming continued fundamental progress despite a soft QSR demand backdrop. The business carries a deliberately negative book equity (~-$1.29B) driven by years of debt-funded buybacks and dividends, a feature of its capital-return model rather than a distress signal given ~7.9x interest coverage and reliable operating cash flow. At $282, the stock trades ~17% below its 52-week high of $341.75 and near the low of $264.53, on ~23x trailing and ~20x forward earnings. This analysis covers a one-day increment (prior analysis dated 2026-07-07); the underlying financial data is unchanged, and news flow this week reinforces existing themes rather than introducing anything materially new. The picture remains a high-quality, wide-moat defensive compounder facing cyclical demand and intensifying value competition, priced at a full-but-fair valuation with no clear margin of safety.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Nothing materially changed since the prior analysis one day ago. No new quarterly financials, guidance, or capital-allocation actions were reported. This week's news is thematic reinforcement rather than fresh signal: several pieces frame MCD as a beaten-down dividend aristocrat and dividend-growth compounder (attractive to income investors after the pullback), while competition coverage centers on Wendy's digital/AI momentum and its recent stock rally, and one item favors Chipotle on valuation despite MCD's stronger traffic execution via the value menu. A former MCD HR executive moving to Kroger is operationally immaterial, and options-activity/'big move' speculation offers no fundamental read for long-term holders. Net: the core tension (resilient value-menu-driven traffic recovery versus broadening QSR/convenience competition and soft sector traffic) is unchanged from the prior writeup.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>MCD's franchise/royalty model produces durable, high-margin, capital-light cash flows -- operating margins consistently above 44% and net margins around 30-33% are among the best in the restaurant industry. The value-menu strategy is reviving traffic, evidenced by ~9.4% YoY revenue growth in Q1 2026 during a weak consumer environment, demonstrating brand pull and pricing discipline. Scale, owned real estate, global brand ubiquity, supply-chain purchasing power, and franchisee density create a wide, durable moat and make MCD the price-setter in value QSR. Low beta (0.42) and a dividend-aristocrat track record make it a defensive holding that can outperform in volatile or recessionary markets, aided by the trade-down effect that benefits value-oriented QSR. Free cash flow is robust (~$1.7B in Q1 2026) and supports continued dividend growth and buybacks. If MCD sustains mid-single-digit revenue and EPS growth while returning capital, it can deliver steady, lower-volatility total returns.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Competition is intensifying from multiple directions -- Wendy's digital/AI investment (and its recent ~28% one-month stock rally reflecting renewed momentum), convenience-store entrants into chicken/value, and broad QSR value wars -- which could erode traffic and force margin-dilutive promotions. The value-menu lever that is driving traffic may compress franchisee unit economics if discounting becomes structural rather than temporary. Sector-wide soft U.S. traffic points to cyclical pressure on the cost-conscious consumer base MCD depends on. Negative book equity and ~$54.9B total debt, while manageable at ~7.9x coverage, leave less cushion if cash flows weaken or rates stay elevated, and the current ratio hovering near 1.0 offers limited liquidity buffer. Growth is mature and mostly incremental, so multiple expansion is limited and the stock is sensitive to any deceleration. A PEG near 2.6 against ~7% EPS growth means investors are paying a quality premium with little embedded upside.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Revenue quality is high given the franchise-royalty-heavy model, producing stable recurring cash flows. Margins are excellent and stable across the last five reported quarters: gross margin ~56-58%, operating margin ~44-48%, net margin ~30-33%. Free cash flow is consistent ($1.25B-$2.42B quarterly; $1.73B in Q1 2026, FCF margin ~27%). The balance sheet shows negative shareholder equity (-$1.29B in Q1 2026), a deliberate result of cumulative buybacks and debt-funded distributions rather than operating losses. Total debt (~$54.9B) is substantial but supported by ~7.9x interest coverage and reliable operating cash flow (~$2.4B in Q1 2026). ROIC ~19% and ROA ~14% indicate efficient capital deployment; ROE is not meaningful given negative equity. Capital allocation prioritizes a growing dividend (~2.66% yield, aristocrat status) and buybacks. Watch items: current ratio near 1.0 and steadily widening negative equity (debt/equity moving from ~-15x to ~-43x over five quarters), which reduce financial flexibility.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Fairly Valued</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>At ~23x trailing and ~20x forward earnings, MCD trades within the range typical for a high-quality, wide-moat defensive compounder and ~17% below its 52-week high. EV/EBITDA of ~17x and price/sales of ~7.3x reflect a premium justified by best-in-class margins and cash conversion rather than an obvious excess. The forward P/E of ~20x against mid-single-digit EPS growth (~7% YoY) yields a PEG near 2.6, which is elevated and caps upside -- you are paying for quality and durability, not growth. Book-value metrics are not meaningful given negative equity. The pullback has brought the multiple to a reasonable level relative to MCD's own historical premium and business quality, but there is no clear margin of safety. A defensible entry for income/quality investors, but not a bargain.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>McDonald's has one of the strongest moats in the restaurant industry, built on global scale, brand ubiquity, an extensive franchised real-estate footprint, supply-chain purchasing power, and cost leadership that confers pricing power and traffic resilience. The value-menu-driven traffic recovery in a weak consumer environment shows brand pull and price positioning remain intact. Switching costs are inherently low in QSR, so the moat rests on convenience density, marketing scale, and cost advantage rather than lock-in. Threats are real and broadening -- Wendy's digital/AI push, convenience-store entrants into value/chicken, and soft sector-wide traffic -- but few competitors can match MCD's cost structure, unit density, or global reach, keeping it the price-setter. The moat is wide and durable but not immune to margin pressure from persistent value competition.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Over five years, growth drivers are international unit expansion, digital/loyalty and delivery monetization, and franchisee royalty growth on a mature but resilient base. The trade-down effect during economic softness structurally favors value-oriented QSR, benefiting MCD's positioning. Headwinds include intensifying competition across QSR and convenience channels, wage/input inflation for franchisees, and current sector-wide traffic softness. Expected growth is mid-single-digit at the revenue and EPS level, supplemented by dividends and buybacks to reach total returns. The central five-year challenge is defending traffic and value perception without permanently eroding franchise-level unit economics through discounting. The outlook is solid and defensive but not high-growth -- a compounder, not a breakout.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>McDonald's is a wide-moat, capital-light, cash-generative franchise business trading at a full-but-fair valuation after a ~17% pullback. Q1 2026 confirms execution -- ~9.4% revenue growth and ~7% EPS growth in a soft consumer backdrop -- alongside industry-leading margins (~44% operating) and strong ROIC (~19%). The intentional negative-equity capital structure and ~$54.9B debt are supported by reliable free cash flow and ~7.9x interest coverage, funding a dividend-aristocrat payout and buybacks. The core risk is intensifying value competition (Wendy's digital momentum, convenience-store entrants, sector-wide traffic softness) that could pressure traffic and force margin-dilutive discounting. With a PEG near 2.6 and no meaningful margin of safety, this is best owned as a defensive quality holding for total return and downside protection (beta 0.42) rather than an aggressive alpha idea. The thesis: own a durable compounder at a reasonable price and collect a growing dividend, accepting mid-single-digit growth and limited multiple expansion. This one-day-later reassessment does not change that view.</t>
+        </is>
+      </c>
+      <c r="M35" s="11" t="n">
+        <v>72</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Confidence is supported by consistent financial evidence: stable high margins, strong FCF, solid ~19% ROIC, and manageable debt coverage across multiple quarters, plus a well-established moat and defensive characteristics. It is reduced by data gaps -- Q4 2024 financials are entirely NaN, YoY revenue/EPS growth is computable only for the most recent quarter, and comparable-store metrics and management guidance are absent. The competitive/demand picture is genuinely mixed (value-driven traffic recovery versus intensifying peer competition and sector-wide softness), and valuation offers no clear margin of safety. Because this increment covers only one additional day with no new fundamental data, confidence is unchanged from the prior analysis.</t>
+        </is>
+      </c>
+      <c r="O35" s="11" t="n">
+        <v>85</v>
+      </c>
+      <c r="P35" s="11" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>NIKE is the dominant global athletic footwear and apparel brand, currently working through a self-inflicted turnaround after a period of over-reliance on direct-to-consumer channels and weak product cadence. The stock trades at $43.21, near its 52-week low of $40 and roughly 46% below its 52-week high of $80.17, indicating the market has heavily de-rated the shares. Recent quarterly data show a business under margin pressure: gross margins have slipped from the low-42% range to about 40%, and operating margins have been volatile (2.9% to 8.1% across recent quarters). Revenue is essentially flat year-over-year (Q1 2026 up just 0.1% YoY), consistent with a stabilizing but not yet re-accelerating top line. The most recent reported diluted EPS of $0.72 (Q2 2026) suggests a meaningful sequential earnings recovery and represents strong YoY growth off a depressed prior-year base. Management has signaled a channel strategy reset—rebuilding wholesale relationships and cleaning inventory—which is the classic playbook for restoring healthy growth. The balance sheet remains solid with a current ratio above 2.0 and declining debt-to-equity (~0.79). The core question for a long-term holder is whether the brand's enduring pricing power and distribution reach can restore double-digit operating margins and mid-single-digit growth, which would make the current valuation attractive.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>This is the first writeup, so the following are the most material recent items. First, earnings appear to be inflecting: reported Q2 2026 diluted EPS of $0.72 is well above the $0.35 in Q1 2026 and prior quarters, and the earnings-beat coverage points to operational resilience. Second, management transition—a new CFO—introduces some uncertainty but is framed as continuity rather than disruption. Third, the strategic pivot back toward wholesale distribution and cleaner inventory is the most fundamentally important development: it directly addresses the primary cause of Nike's revenue and margin deterioration over the prior two years. Fourth, a 7-Eleven trademark lawsuit over shoe design is a minor legal item unlikely to be financially material for a company of this scale. Net: the operational data and strategy reset suggest the trough may be forming, though margins remain well below Nike's historical peak levels.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Nike remains arguably the strongest brand in its category globally, with unmatched scale, athlete/marketing budgets, and distribution. The turnaround thesis is credible: rebuilding wholesale partnerships and clearing excess inventory typically restores full-price sell-through and gross margins over 4-6 quarters. Gross margin is depressed at ~40% versus a historical range closer to 44-46%; even partial mean-reversion drives substantial EPS leverage. The stock has been cut nearly in half from its 52-week high, so if the company merely restores mid-single-digit revenue growth and recovers 200-400bps of operating margin, earnings power could expand meaningfully from the trough, and the forward P/E of ~18.5 would look cheap against restored earnings. The dividend yield of ~3.8% is well-supported and unusually high for Nike, offering downside cushion and signaling management confidence. Balance sheet strength (current ratio &gt;2, declining leverage) gives ample runway to fund the turnaround and continue buybacks/dividends. Q2 2026's EPS jump is early tangible evidence the recovery is underway.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>The bear case, supported by the 'multi-year earnings deceleration' framing, is that Nike's problems are structural, not merely self-inflicted. Revenue is essentially flat YoY and margins have not durably recovered—Q1 2026 gross margin (40.2%) and operating margin (4.9%) both deteriorated sequentially from Q4 2025, showing the recovery is uneven. Competitive intensity in athletic footwear has risen materially, with newer performance and lifestyle brands taking share, particularly among younger and running-focused consumers, eroding Nike's pricing power. Greater China remains a chronic risk zone with weak consumer demand and local-brand competition. If the wholesale reset compresses margins (wholesale is structurally lower-margin than DTC), the margin recovery thesis could stall. The stock trading near 52-week lows may reflect a legitimate reassessment of Nike's terminal growth rate rather than temporary pessimism. A trailing P/E of ~20.6 on depressed earnings is not obviously cheap if earnings power has permanently reset lower.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Nike's balance sheet is healthy. Cash of ~$6.7B, current ratio consistently above 2.0, and quick ratio around 1.4 indicate strong liquidity. Total debt (~$11.2B) against ~$14.1B equity gives debt-to-equity of ~0.79, which has trended down over the observed quarters—a positive deleveraging signal. Inventory has declined from ~$8.1B (Q3 2025) to ~$7.5B (Q1 2026), consistent with the stated cleanup effort. Profitability metrics are the concern: gross margin has slipped to ~40% from low-42%, and operating margin has been erratic (2.9%-8.1%), reflecting a business in transition. ROE of ~16-18% and ROIC of ~12-13% (per the two quarters reported) remain respectable for a consumer brand but are below Nike's historical premium levels. Net margins in the 4.6-6.4% range are subdued. Free cash flow data was not provided, limiting assessment of cash conversion, but the maintained ~3.8% dividend yield and prior buyback history suggest capital return remains active. Overall: strong balance sheet, weak-but-stabilizing profitability.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Fairly Valued</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>At $43.21, Nike trades at a trailing P/E of ~20.6 and forward P/E of ~18.5, with EV/EBITDA of ~14.6 and price-to-sales of ~1.38. These multiples sit below Nike's historical premium range (the stock historically commanded high-20s to 30s P/E during its growth heyday). However, the trailing earnings base is depressed by the turnaround, so the trailing P/E overstates cheapness on normalized earnings and understates it if margins recover. On a normalized-earnings view—assuming gross margin recovers toward 44% and operating margin toward 12%—the shares would look meaningfully undervalued. On a bear view where margins stay near current trough levels, the current multiple is roughly fair. Given genuine uncertainty about whether the margin reset is cyclical or structural, and price-to-sales of 1.38 being below the company's historical average, I rate it Fairly Valued with an upside skew. The ~3.8% dividend provides a valuation floor. This is not a bare 'P/E is high' assessment—it reflects the wide range of plausible normalized earnings.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Nike possesses one of the strongest brand moats in consumer cyclicals, built on decades of marketing investment, athlete endorsements, iconic sub-brands (Jordan/Jumpman, Converse), and global distribution scale. Its pricing power historically supported gross margins in the mid-40s. However, the moat has narrowed: competitors have captured share in performance running and lifestyle categories, and Nike's DTC over-pivot damaged wholesale relationships that are now being rebuilt. Switching costs for consumers are essentially zero in footwear/apparel, so the moat rests entirely on brand equity and product innovation, both of which require constant reinvestment. The brand remains dominant but is no longer unassailable. The provided peer (GME) is not a meaningful competitive comparison. Overall, Nike still holds a wide but somewhat eroded moat—the key open question is whether recent share losses are temporary or reflect a durable shift in consumer preference.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Over a five-year horizon, Nike's growth drivers include restored wholesale distribution, product innovation cadence, expanding campus/collegiate partnerships, international growth, and the structural tailwind of global athleisure and health/wellness trends. If management executes the reset, mid-single-digit revenue growth with margin recovery is achievable, producing solid EPS growth off the current trough. The primary risks are intensifying competition, chronic softness and local-brand encroachment in Greater China, and the possibility that DTC/wholesale mix shifts permanently cap margins below historical peaks. Macro discretionary spending sensitivity (beta 1.13) adds cyclicality. The most likely outcome is a gradual, multi-quarter recovery rather than a sharp snap-back, with meaningful execution risk. Nike is not structurally declining, but its era of premium growth-multiple expansion is likely behind it; the next five years are more about margin normalization and steady compounding than hypergrowth.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Nike is a high-quality, dominant brand undergoing a self-inflicted turnaround that appears to be inflecting, trading near multi-year lows at a below-historical valuation. The core thesis is a margin-recovery and channel-reset story: gross margins are depressed at ~40% versus a historical mid-40s, and even partial normalization would drive substantial EPS leverage from a stabilized, flat revenue base. Early evidence (Q2 2026 EPS of $0.72, declining inventory, deleveraging balance sheet, wholesale rebuild) supports the turnaround, while a strong balance sheet and ~3.8% dividend limit downside. The bear risk is that competitive share losses and China weakness are structural rather than cyclical, in which case current earnings power is the new normal and the stock is only fairly valued. Given the balance of a stabilizing operational picture, a supportive valuation with upside optionality, and a defended dividend against genuine but not thesis-breaking competitive risks, this is an attractive risk/reward for a patient holder—but conviction is tempered by the unresolved question of margin durability. A moderate long position or accumulation on weakness is warranted, sized to reflect execution uncertainty.</t>
+        </is>
+      </c>
+      <c r="M36" s="11" t="n">
+        <v>58</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Confidence is moderate. It is increased by clear balance-sheet strength, tangible early turnaround signals (EPS inflection, inventory reduction, deleveraging), and a valuation that offers downside protection via the dividend. It is decreased by incomplete data (missing FCF, several NaN quarters, no historical multiple ranges provided), the erratic and still-depressed margin profile, flat revenue that has not yet demonstrated durable re-acceleration, and genuine ambiguity over whether competitive share losses are cyclical or structural. The mixed news signal (both 'turnaround ahead' and 'bear of the day/earnings deceleration') reflects the real disagreement in the evidence.</t>
+        </is>
+      </c>
+      <c r="O36" s="11" t="n">
+        <v>72</v>
+      </c>
+      <c r="P36" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/Investment_Research_Dashboard.xlsx
+++ b/Investment_Research_Dashboard.xlsx
@@ -320,7 +320,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="NewsTable" displayName="NewsTable" ref="A1:I305" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="NewsTable" displayName="NewsTable" ref="A1:I441" headerRowCount="1">
   <autoFilter ref="A1:I11"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Date"/>
@@ -338,7 +338,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="NarrativeTable" displayName="NarrativeTable" ref="A1:P36" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="NarrativeTable" displayName="NarrativeTable" ref="A1:P48" headerRowCount="1">
   <autoFilter ref="A1:P2"/>
   <tableColumns count="16">
     <tableColumn id="1" name="Ticker"/>
@@ -659,16 +659,16 @@
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="21" customWidth="1" min="18" max="18"/>
@@ -1553,16 +1553,16 @@
         </is>
       </c>
       <c r="F13" s="8" t="n">
-        <v>949.46</v>
+        <v>947.5</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>421065392128</v>
+        <v>420196188160</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>47.80765</v>
+        <v>47.70896</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>42.005726</v>
+        <v>41.881027</v>
       </c>
       <c r="J13" s="9" t="n">
         <v>4.6407</v>
@@ -1589,11 +1589,11 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Costco is a best-in-class defensive compounder: a wide-moat, capital-efficient retailer (ROIC ~40%, ROE ~26%) with a recurring, high-margin membership fee stream, a fortress balance sheet (net cash, 8...</t>
+          <t>Costco is a best-in-class defensive compounder: a wide-moat, capital-efficient retailer (ROIC ~41%, ROE ~26%) with a recurring, high-margin membership fee stream, a net-cash fortress balance sheet (80...</t>
         </is>
       </c>
       <c r="R13" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="14">
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="F14" s="8" t="n">
-        <v>84.05</v>
+        <v>82.63</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>361623650304</v>
+        <v>355514122240</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>26.430819</v>
+        <v>26.231745</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>24.128172</v>
+        <v>23.71774</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>4.3016</v>
+        <v>4.2638</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.0256</v>
+        <v>0.0257</v>
       </c>
       <c r="L14" s="5" t="n">
         <v>0.1206757121035133</v>
@@ -1659,11 +1659,11 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Coca-Cola is a best-in-class defensive compounder with an exceptional moat, ~60% gross margins, ~30% net margins, ~21% ROIC, improving leverage, and strong recurring cash generation—confirmed by solid...</t>
+          <t>Coca-Cola is a best-in-class defensive compounder with an exceptional moat, ~60% gross margins, ~30% net margins, ~21% ROIC, improving leverage, and strong recurring cash generation—reconfirmed by sol...</t>
         </is>
       </c>
       <c r="R14" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="15">
@@ -1693,22 +1693,22 @@
         </is>
       </c>
       <c r="F15" s="8" t="n">
-        <v>151.145</v>
+        <v>146.85</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>351956107264</v>
+        <v>341954789376</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>22.097223</v>
+        <v>21.691286</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>21.382473</v>
+        <v>20.772392</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>4.1941</v>
+        <v>4.1685</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.0285</v>
+        <v>0.0287</v>
       </c>
       <c r="L15" s="5" t="n">
         <v>0.07377629449838188</v>
@@ -1729,11 +1729,11 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>PG is a best-in-class defensive compounder: a wide-moat portfolio of daily-consumption brands generating ~50% gross margins, 20%+ ROIC, and abundant recurring free cash flow, funding a reliable and gr...</t>
+          <t>PG is a best-in-class defensive compounder: a wide-moat portfolio of daily-consumption brands generating ~50% gross margins, ~22% ROIC, and abundant recurring free cash flow that funds a reliable, gro...</t>
         </is>
       </c>
       <c r="R15" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="16">
@@ -1763,22 +1763,22 @@
         </is>
       </c>
       <c r="F16" s="8" t="n">
-        <v>1230.2921</v>
+        <v>1216.95</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1097102393344</v>
+        <v>1085204594688</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>43.62738</v>
+        <v>43.108395</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>27.642206</v>
+        <v>27.161745</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1.57</v>
+        <v>1.5725</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.0058</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="L16" s="5" t="n">
         <v>0.5554246209443005</v>
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="R16" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="17">
@@ -1833,22 +1833,22 @@
         </is>
       </c>
       <c r="F17" s="8" t="n">
-        <v>425.93</v>
+        <v>431.68</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>386805923840</v>
+        <v>392027766784</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>32.04891</v>
+        <v>32.45714</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>20.349699</v>
+        <v>20.572365</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1.4484</v>
+        <v>1.4748</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.0222</v>
+        <v>0.0215</v>
       </c>
       <c r="L17" s="5" t="n">
         <v>0.01958475929728496</v>
@@ -1869,11 +1869,11 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>UNH is a dominant, vertically integrated managed-care leader whose earnings suffered a severe, likely-transitory medical-cost shock through 2025 before rebounding sharply in Q1 2026. The core debate i...</t>
+          <t>UNH is a dominant, vertically integrated managed-care leader whose earnings suffered a severe, likely-transitory medical-cost shock through 2025 before rebounding sharply in Q1 2026. The core debate —...</t>
         </is>
       </c>
       <c r="R17" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="18">
@@ -1903,22 +1903,22 @@
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>919.605</v>
+        <v>938.39</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>423562674176</v>
+        <v>432214900736</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>45.797062</v>
+        <v>47.178986</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>30.430405</v>
+        <v>30.858398</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>2.2855</v>
+        <v>2.2489</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.0067</v>
+        <v>0.0069</v>
       </c>
       <c r="L18" s="5" t="n">
         <v>0.2221910309495403</v>
@@ -1939,11 +1939,11 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>CAT is a high-quality, wide-moat cyclical industrial firing on all cylinders: record EPS, ~17% ROIC, strong and diversified cash flows, disciplined pricing, and genuine secular tailwinds from AI-drive...</t>
+          <t>CAT is a high-quality, wide-moat cyclical industrial operating near peak performance: record EPS, ~17% ROIC, strong diversified cash flows, disciplined pricing, an 8% dividend hike plus buybacks, and ...</t>
         </is>
       </c>
       <c r="R18" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="19">
@@ -1973,22 +1973,22 @@
         </is>
       </c>
       <c r="F19" s="8" t="n">
-        <v>223.955</v>
+        <v>223.42</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>70954893312</v>
+        <v>70785392640</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>17.873505</v>
+        <v>17.60599</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>22.777431</v>
+        <v>23.231173</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>8.582000000000001</v>
+        <v>8.2273</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>0.0412</v>
+        <v>0.0426</v>
       </c>
       <c r="L19" s="5" t="n">
         <v>0.02442577030812325</v>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="R19" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="20">
@@ -2043,22 +2043,22 @@
         </is>
       </c>
       <c r="F20" s="8" t="n">
-        <v>139.98</v>
+        <v>137.67</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>580209672192</v>
+        <v>570676281344</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>23.565655</v>
+        <v>23.17845</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>12.907913</v>
+        <v>12.932058</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1.1318</v>
+        <v>1.1409</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0.0302</v>
+        <v>0.03</v>
       </c>
       <c r="L20" s="5" t="n">
         <v>0.02594438550173949</v>
@@ -2079,11 +2079,11 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>ExxonMobil is a financially fortified integrated major currently in a cyclical earnings trough, with margins, EPS, and free cash flow all deteriorating meaningfully over the last six quarters due to w...</t>
+          <t>ExxonMobil is a financially fortified integrated major in a cyclical earnings/FCF trough driven by weak commodity price realizations rather than lost volume. The provided cash-flow data confirms the s...</t>
         </is>
       </c>
       <c r="R20" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="21">
@@ -2113,22 +2113,22 @@
         </is>
       </c>
       <c r="F21" s="8" t="n">
-        <v>88.705</v>
+        <v>87.23</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>185003622400</v>
+        <v>181927362560</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>22.51396</v>
+        <v>22.139595</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>20.157433</v>
+        <v>19.82027</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1.947</v>
+        <v>1.9101</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>0.0285</v>
+        <v>0.0286</v>
       </c>
       <c r="L21" s="5" t="n">
         <v>0.07267488394429326</v>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="R21" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="22">
@@ -2183,22 +2183,22 @@
         </is>
       </c>
       <c r="F22" s="8" t="n">
-        <v>369.47</v>
+        <v>355.01</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>4508484632576</v>
+        <v>4332035506176</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>28.160824</v>
+        <v>27.1</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>25.379679</v>
+        <v>24.36164</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1.4171</v>
+        <v>1.4131</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0025</v>
       </c>
       <c r="L22" s="5" t="n">
         <v>0.2179001263381874</v>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="R22" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="23">
@@ -2253,22 +2253,22 @@
         </is>
       </c>
       <c r="F23" s="8" t="n">
-        <v>605.29</v>
+        <v>664.375</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1536482213888</v>
+        <v>1686465019904</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>22.01855</v>
+        <v>24.185476</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>16.435736</v>
+        <v>17.980846</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0033</v>
       </c>
       <c r="L23" s="5" t="n">
         <v>0.3307888642057003</v>
@@ -2289,11 +2289,11 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Meta is a dominant, exceptionally profitable advertising franchise trading at a reasonable ~16x forward earnings while reaccelerating revenue to ~30%+ YoY growth with 40% operating margins and ~25% RO...</t>
+          <t>Meta is a dominant, exceptionally profitable advertising franchise trading at a reasonable ~18x forward earnings while reaccelerating revenue to ~30%+ YoY growth with 40% operating margins and ~25% RO...</t>
         </is>
       </c>
       <c r="R23" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="24">
@@ -2323,22 +2323,22 @@
         </is>
       </c>
       <c r="F24" s="8" t="n">
-        <v>142.085</v>
+        <v>139.43</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>135562739712</v>
+        <v>133029601280</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>35.69975</v>
+        <v>34.94486</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>41.91298</v>
+        <v>41.12979</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>108.4636</v>
+        <v>109.965</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0.0305</v>
+        <v>0.0303</v>
       </c>
       <c r="L24" s="5" t="n">
         <v>0.07387044233559927</v>
@@ -2359,11 +2359,11 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Prologis is a best-in-class, wide-moat logistics REIT with stable high margins, strong free cash flow, and a manageable balance sheet, now layering in a strategically attractive but capital-intensive ...</t>
+          <t>Prologis is a best-in-class, wide-moat logistics REIT with stable ~74% gross margins, strong FCF conversion, and a manageable investment-grade balance sheet, now actively pursuing a strategically attr...</t>
         </is>
       </c>
       <c r="R24" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="25">
@@ -2393,22 +2393,22 @@
         </is>
       </c>
       <c r="F25" s="8" t="n">
-        <v>343.565</v>
+        <v>336.26</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>84735369216</v>
+        <v>82933694464</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>33.0351</v>
+        <v>32.239693</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>25.934347</v>
+        <v>25.347143</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>2.6978</v>
+        <v>2.5656</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>0.0092</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="L25" s="5" t="n">
         <v>0.0680777277267844</v>
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="R25" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="26">
@@ -2463,16 +2463,16 @@
         </is>
       </c>
       <c r="F26" s="8" t="n">
-        <v>21.995</v>
+        <v>21.725</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>9868964864</v>
+        <v>9747817472</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>16.414179</v>
+        <v>16.212687</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>18.177687</v>
+        <v>17.954546</v>
       </c>
       <c r="J26" s="9" t="n">
         <v>0.31</v>
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="R26" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="27">
@@ -2597,22 +2597,22 @@
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>97.56</v>
+        <v>95.88</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>169414049792</v>
+        <v>166496714752</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>15.6096</v>
+        <v>15.340799</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>13.028934</v>
+        <v>12.810269</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>2.2618</v>
+        <v>2.236</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>0.0154</v>
+        <v>0.0156</v>
       </c>
       <c r="L28" s="5" t="n">
         <v>0.0654925701706109</v>
@@ -2626,8 +2626,18 @@
       <c r="O28" s="9" t="n">
         <v>0.4356441108290098</v>
       </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Fairly Valued</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Disney is a high-quality, IP-rich franchise trading below its historical multiple after a period of earnings volatility and heavy investment. The bull thesis is that irreplaceable IP and Experiences a...</t>
+        </is>
+      </c>
       <c r="R28" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="29">
@@ -2657,19 +2667,19 @@
         </is>
       </c>
       <c r="F29" s="8" t="n">
-        <v>134.37</v>
+        <v>126.18</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>322126807040</v>
+        <v>302492844032</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>150.97752</v>
+        <v>141.77528</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>64.15434</v>
+        <v>60.24407</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>1.8605</v>
+        <v>1.9026</v>
       </c>
       <c r="K29" s="5" t="n"/>
       <c r="L29" s="5" t="n">
@@ -2695,7 +2705,7 @@
         </is>
       </c>
       <c r="R29" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
     </row>
   </sheetData>
@@ -3123,6 +3133,150 @@
     <cfRule type="cellIs" priority="123" operator="equal" dxfId="2">
       <formula>"Fairly Valued"</formula>
     </cfRule>
+    <cfRule type="cellIs" priority="124" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="125" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="126" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="127" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="128" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="129" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="130" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="131" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="132" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="133" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="134" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="135" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="136" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="137" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="138" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="139" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="140" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="141" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="142" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="143" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="144" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="145" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="146" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="147" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="148" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="149" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="150" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="151" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="152" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="153" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="154" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="155" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="156" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="157" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="158" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="159" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="160" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="161" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="162" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="163" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="164" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="165" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="166" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="167" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="168" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="169" operator="equal" dxfId="0">
+      <formula>"Undervalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="170" operator="equal" dxfId="1">
+      <formula>"Overvalued"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="171" operator="equal" dxfId="2">
+      <formula>"Fairly Valued"</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -3721,7 +3875,7 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -4472,40 +4626,40 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>949.46</v>
+        <v>947.5</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>421065392128</v>
+        <v>420196188160</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>419738484736</v>
+        <v>418522595328</v>
       </c>
       <c r="F13" s="7" t="n">
         <v>443478804</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>47.80765</v>
+        <v>47.70896</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>42.005726</v>
+        <v>41.881027</v>
       </c>
       <c r="I13" s="9" t="n">
         <v>4.6407</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1.43421</v>
+        <v>1.4312494</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>25.469715</v>
+        <v>25.417137</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1.43</v>
+        <v>1.426</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>30.438</v>
+        <v>30.35</v>
       </c>
       <c r="N13" s="5" t="n">
         <v>0.0062</v>
@@ -4530,43 +4684,43 @@
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>84.05</v>
+        <v>82.63</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>361623650304</v>
+        <v>355514122240</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>389861933056</v>
+        <v>388442128384</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>4302482418</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>26.430819</v>
+        <v>26.231745</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>24.128172</v>
+        <v>23.71774</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>4.3016</v>
+        <v>4.2638</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>7.3375463</v>
+        <v>7.2135806</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>10.753583</v>
+        <v>10.571903</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>7.911</v>
+        <v>7.882</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>23.324</v>
+        <v>23.239</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>0.0256</v>
+        <v>0.0257</v>
       </c>
       <c r="O14" s="9" t="n">
         <v>0.349</v>
@@ -4578,7 +4732,7 @@
         <v>65.34999999999999</v>
       </c>
       <c r="R14" s="7" t="n">
-        <v>16742185</v>
+        <v>16813025</v>
       </c>
     </row>
     <row r="15">
@@ -4588,43 +4742,43 @@
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>151.145</v>
+        <v>146.85</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>351956107264</v>
+        <v>341954789376</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>373388115968</v>
+        <v>367659745280</v>
       </c>
       <c r="F15" s="7" t="n">
         <v>2328598978</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>22.097223</v>
+        <v>21.691286</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>21.382473</v>
+        <v>20.772392</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>4.1941</v>
+        <v>4.1685</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>4.058675</v>
+        <v>3.9433422</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>6.54846</v>
+        <v>6.362376</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>4.306</v>
+        <v>4.24</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>14.91</v>
+        <v>14.682</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>0.0285</v>
+        <v>0.0287</v>
       </c>
       <c r="O15" s="9" t="n">
         <v>0.38</v>
@@ -4636,7 +4790,7 @@
         <v>137.62</v>
       </c>
       <c r="R15" s="7" t="n">
-        <v>8971840</v>
+        <v>9027725</v>
       </c>
     </row>
     <row r="16">
@@ -4646,43 +4800,43 @@
         </is>
       </c>
       <c r="B16" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>1230.2921</v>
+        <v>1216.95</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1097102393344</v>
+        <v>1085204594688</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1108231192576</v>
+        <v>1123292676096</v>
       </c>
       <c r="F16" s="7" t="n">
         <v>891741406</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>43.62738</v>
+        <v>43.108395</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>27.642206</v>
+        <v>27.161745</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>1.57</v>
+        <v>1.5725</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>15.185019</v>
+        <v>15.020341</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>35.23476</v>
+        <v>34.85265</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>15.339</v>
+        <v>15.548</v>
       </c>
       <c r="M16" s="9" t="n">
-        <v>30.601</v>
+        <v>31.017</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>0.0058</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="O16" s="9" t="n">
         <v>0.506</v>
@@ -4694,7 +4848,7 @@
         <v>623.78</v>
       </c>
       <c r="R16" s="7" t="n">
-        <v>3277000</v>
+        <v>3278837</v>
       </c>
     </row>
     <row r="17">
@@ -4704,55 +4858,55 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>425.93</v>
+        <v>431.68</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>386805923840</v>
+        <v>392027766784</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>433721278464</v>
+        <v>446153785344</v>
       </c>
       <c r="F17" s="7" t="n">
         <v>908144404</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>32.04891</v>
+        <v>32.45714</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>20.349699</v>
+        <v>20.572365</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>1.4484</v>
+        <v>1.4748</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.86011726</v>
+        <v>0.8717288</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>3.9511867</v>
+        <v>4.004527</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.964</v>
+        <v>0.992</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>20.207</v>
+        <v>20.786</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>0.0222</v>
+        <v>0.0215</v>
       </c>
       <c r="O17" s="9" t="n">
         <v>0.633</v>
       </c>
       <c r="P17" s="8" t="n">
-        <v>430.2</v>
+        <v>434.3</v>
       </c>
       <c r="Q17" s="8" t="n">
         <v>234.6</v>
       </c>
       <c r="R17" s="7" t="n">
-        <v>7360857</v>
+        <v>7239543</v>
       </c>
     </row>
     <row r="18">
@@ -4762,43 +4916,43 @@
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>919.605</v>
+        <v>938.39</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>423562674176</v>
+        <v>432214900736</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>486530056192</v>
+        <v>472006164480</v>
       </c>
       <c r="F18" s="7" t="n">
         <v>460591983</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>45.797062</v>
+        <v>47.178986</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>30.430405</v>
+        <v>30.858398</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>2.2855</v>
+        <v>2.2489</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>5.9863286</v>
+        <v>6.108613</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>22.700129</v>
+        <v>23.163832</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>6.876</v>
+        <v>6.671</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>33.422</v>
+        <v>32.425</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>0.0067</v>
+        <v>0.0069</v>
       </c>
       <c r="O18" s="9" t="n">
         <v>1.565</v>
@@ -4807,10 +4961,10 @@
         <v>1073.46</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>391.52</v>
+        <v>401.7</v>
       </c>
       <c r="R18" s="7" t="n">
-        <v>3000924</v>
+        <v>3021185</v>
       </c>
     </row>
     <row r="19">
@@ -4820,43 +4974,43 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>223.955</v>
+        <v>223.42</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>70954893312</v>
+        <v>70785392640</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>99681968128</v>
+        <v>97223393280</v>
       </c>
       <c r="F19" s="7" t="n">
         <v>316826559</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>17.873505</v>
+        <v>17.60599</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>22.777431</v>
+        <v>23.231173</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>8.582000000000001</v>
+        <v>8.2273</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1.8840917</v>
+        <v>1.8795909</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>5.2211266</v>
+        <v>5.208654</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>2.647</v>
+        <v>2.582</v>
       </c>
       <c r="M19" s="9" t="n">
-        <v>11.692</v>
+        <v>11.403</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0.0412</v>
+        <v>0.0426</v>
       </c>
       <c r="O19" s="9" t="n">
         <v>0.93</v>
@@ -4868,7 +5022,7 @@
         <v>195.86786</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>4714244</v>
+        <v>4721082</v>
       </c>
     </row>
     <row r="20">
@@ -4878,43 +5032,43 @@
         </is>
       </c>
       <c r="B20" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>139.98</v>
+        <v>137.67</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>580209672192</v>
+        <v>570676281344</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>611377610752</v>
+        <v>615605469184</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>4144947162</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>23.565655</v>
+        <v>23.17845</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>12.907913</v>
+        <v>12.932058</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>1.1318</v>
+        <v>1.1409</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1.7797406</v>
+        <v>1.7503706</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>2.255232</v>
+        <v>2.2181764</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>1.875</v>
+        <v>1.888</v>
       </c>
       <c r="M20" s="9" t="n">
-        <v>10.916</v>
+        <v>10.992</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0.0302</v>
+        <v>0.03</v>
       </c>
       <c r="O20" s="9" t="n">
         <v>0.162</v>
@@ -4926,7 +5080,7 @@
         <v>105.53</v>
       </c>
       <c r="R20" s="7" t="n">
-        <v>17855252</v>
+        <v>17344139</v>
       </c>
     </row>
     <row r="21">
@@ -4936,43 +5090,43 @@
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>88.705</v>
+        <v>87.23</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>185003622400</v>
+        <v>181927362560</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>296157249536</v>
+        <v>295448248320</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>2085605358</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>22.51396</v>
+        <v>22.139595</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>20.157433</v>
+        <v>19.82027</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>1.947</v>
+        <v>1.9101</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>6.639045</v>
+        <v>6.5286503</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>3.34976</v>
+        <v>3.29406</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>10.628</v>
+        <v>10.602</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>20.917</v>
+        <v>20.866</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>0.0285</v>
+        <v>0.0286</v>
       </c>
       <c r="O21" s="9" t="n">
         <v>0.667</v>
@@ -4984,7 +5138,7 @@
         <v>69.23999999999999</v>
       </c>
       <c r="R21" s="7" t="n">
-        <v>11320196</v>
+        <v>11590167</v>
       </c>
     </row>
     <row r="22">
@@ -4994,43 +5148,43 @@
         </is>
       </c>
       <c r="B22" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>369.47</v>
+        <v>355.01</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>4508484632576</v>
+        <v>4332035506176</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>4409065472000</v>
+        <v>4317347315712</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>5867155790</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>28.160824</v>
+        <v>27.1</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>25.379679</v>
+        <v>24.36164</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>1.4171</v>
+        <v>1.4131</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>10.67102</v>
+        <v>10.2533865</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>9.350357000000001</v>
+        <v>8.984411</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>10.436</v>
+        <v>10.219</v>
       </c>
       <c r="M22" s="9" t="n">
-        <v>27.332</v>
+        <v>26.763</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0025</v>
       </c>
       <c r="O22" s="9" t="n">
         <v>1.247</v>
@@ -5039,10 +5193,10 @@
         <v>408.61</v>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>172.77</v>
+        <v>176.48</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>31796745</v>
+        <v>31709442</v>
       </c>
     </row>
     <row r="23">
@@ -5052,43 +5206,43 @@
         </is>
       </c>
       <c r="B23" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>605.29</v>
+        <v>664.375</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1536482213888</v>
+        <v>1686465019904</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1529379160064</v>
+        <v>1608552546304</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>2196045588</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>22.01855</v>
+        <v>24.185476</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>16.435736</v>
+        <v>17.980846</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>7.1476593</v>
+        <v>7.8453736</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>6.3042502</v>
+        <v>6.919636</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>7.115</v>
+        <v>7.483</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>13.991</v>
+        <v>14.716</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0033</v>
       </c>
       <c r="O23" s="9" t="n">
         <v>1.246</v>
@@ -5100,7 +5254,7 @@
         <v>520.26</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>17467213</v>
+        <v>17370160</v>
       </c>
     </row>
     <row r="24">
@@ -5110,43 +5264,43 @@
         </is>
       </c>
       <c r="B24" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>142.085</v>
+        <v>139.43</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>135562739712</v>
+        <v>133029601280</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>169661808640</v>
+        <v>170743316480</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>932338000</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>35.69975</v>
+        <v>34.94486</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>41.91298</v>
+        <v>41.12979</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>108.4636</v>
+        <v>109.965</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>14.458309</v>
+        <v>14.18814</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>2.47876</v>
+        <v>2.4324417</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>18.095</v>
+        <v>18.21</v>
       </c>
       <c r="M24" s="9" t="n">
-        <v>25.861</v>
+        <v>26.026</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>0.0305</v>
+        <v>0.0303</v>
       </c>
       <c r="O24" s="9" t="n">
         <v>1.34</v>
@@ -5158,7 +5312,7 @@
         <v>103.41</v>
       </c>
       <c r="R24" s="7" t="n">
-        <v>3705840</v>
+        <v>3699121</v>
       </c>
     </row>
     <row r="25">
@@ -5168,43 +5322,43 @@
         </is>
       </c>
       <c r="B25" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>343.565</v>
+        <v>336.26</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>84735369216</v>
+        <v>82933694464</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>99994230784</v>
+        <v>95801155584</v>
       </c>
       <c r="F25" s="7" t="n">
         <v>246635621</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>33.0351</v>
+        <v>32.239693</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>25.934347</v>
+        <v>25.347143</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>2.6978</v>
+        <v>2.5656</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>3.5401545</v>
+        <v>3.4648824</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>19.011953</v>
+        <v>18.607716</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>4.178</v>
+        <v>4.002</v>
       </c>
       <c r="M25" s="9" t="n">
-        <v>21.941</v>
+        <v>21.021</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>0.0092</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="O25" s="9" t="n">
         <v>1.1</v>
@@ -5216,7 +5370,7 @@
         <v>289.86</v>
       </c>
       <c r="R25" s="7" t="n">
-        <v>2279755</v>
+        <v>2299688</v>
       </c>
     </row>
     <row r="26">
@@ -5226,40 +5380,40 @@
         </is>
       </c>
       <c r="B26" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="C26" s="8" t="n">
-        <v>21.995</v>
+        <v>21.725</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>9868964864</v>
+        <v>9747817472</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>6183213056</v>
+        <v>5819772928</v>
       </c>
       <c r="F26" s="7" t="n">
         <v>448691257</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>16.414179</v>
+        <v>16.212687</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>18.177687</v>
+        <v>17.954546</v>
       </c>
       <c r="I26" s="9" t="n">
         <v>0.31</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>2.6438503</v>
+        <v>2.6113956</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>1.6893241</v>
+        <v>1.6685867</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>1.656</v>
+        <v>1.559</v>
       </c>
       <c r="M26" s="9" t="n">
-        <v>14.997</v>
+        <v>14.115</v>
       </c>
       <c r="N26" s="5" t="n"/>
       <c r="O26" s="9" t="n">
@@ -5272,7 +5426,7 @@
         <v>19.93</v>
       </c>
       <c r="R26" s="7" t="n">
-        <v>7510416</v>
+        <v>7432563</v>
       </c>
     </row>
     <row r="27">
@@ -5334,55 +5488,55 @@
         </is>
       </c>
       <c r="B28" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="C28" s="8" t="n">
-        <v>97.56</v>
+        <v>95.88</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>169414049792</v>
+        <v>166496714752</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>217433571328</v>
+        <v>215280304128</v>
       </c>
       <c r="F28" s="7" t="n">
         <v>1736511424</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>15.6096</v>
+        <v>15.340799</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>13.028934</v>
+        <v>12.810269</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>2.2618</v>
+        <v>2.236</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>1.7418139</v>
+        <v>1.7118196</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>1.5660465</v>
+        <v>1.5390788</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>2.236</v>
+        <v>2.213</v>
       </c>
       <c r="M28" s="9" t="n">
-        <v>11.026</v>
+        <v>10.917</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>0.0154</v>
+        <v>0.0156</v>
       </c>
       <c r="O28" s="9" t="n">
         <v>1.398</v>
       </c>
       <c r="P28" s="8" t="n">
-        <v>123.71</v>
+        <v>123.4</v>
       </c>
       <c r="Q28" s="8" t="n">
         <v>92.19</v>
       </c>
       <c r="R28" s="7" t="n">
-        <v>9560960</v>
+        <v>9626734</v>
       </c>
     </row>
     <row r="29">
@@ -5392,40 +5546,40 @@
         </is>
       </c>
       <c r="B29" s="10" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="C29" s="8" t="n">
-        <v>134.37</v>
+        <v>126.18</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>322126807040</v>
+        <v>302492844032</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>310031908864</v>
+        <v>301641334784</v>
       </c>
       <c r="F29" s="7" t="n">
         <v>2296071334</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>150.97752</v>
+        <v>141.77528</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>64.15434</v>
+        <v>60.24407</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>1.8605</v>
+        <v>1.9026</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>61.66081</v>
+        <v>57.90252</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>38.11915</v>
+        <v>35.795742</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>59.346</v>
+        <v>57.74</v>
       </c>
       <c r="M29" s="9" t="n">
-        <v>153.614</v>
+        <v>149.457</v>
       </c>
       <c r="N29" s="5" t="n"/>
       <c r="O29" s="9" t="n">
@@ -5438,7 +5592,7 @@
         <v>106.37</v>
       </c>
       <c r="R29" s="7" t="n">
-        <v>46368559</v>
+        <v>43984711</v>
       </c>
     </row>
   </sheetData>
@@ -25759,7 +25913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I305"/>
+  <dimension ref="A1:I441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -39500,6 +39654,6126 @@
         </is>
       </c>
     </row>
+    <row r="306">
+      <c r="A306" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Costco Wholesale (COST) Posts Strong Results, Is It Fully Priced?</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Simply Wall St.</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/costco-wholesale-cost-posts-strong-192053402.html</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Costco Wholesale Corporation</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Strong fundamentals and high membership renewals support Costco's durability, but a premium valuation may limit upside for new long-term investors.</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>Earnings</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Walmart Cuts Food Prices, but Shoppers Are Fed Up</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Barrons.com</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>https://www.barrons.com/articles/iwalmart-stock-food-prices-1f58357f?siteid=yhoof2&amp;yptr=yahoo</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Costco Wholesale Corporation</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Intensifying grocery price competition and stretched consumer patience could pressure margins and pricing power across warehouse and discount retailers like Costco.</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Top Dividend King Down 12% and Worth Loading Up On Now</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Motley Fool</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/investing/2026/07/09/top-dividend-king-down-12-and-worth-loading-up-on/</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>A 12% price decline offers long-term investors an attractive entry point into a reliable dividend-growing stock with strong income potential.</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>How Coke Finally Beat Pepsi</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Barrons.com</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>https://www.barrons.com/articles/coca-cola-vs-pepsi-stock-ko-pep-earnings-0c7ce517?siteid=yhoof2&amp;yptr=yahoo</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>KO is gaining favor over PepsiCo among investors, signaling a perceived superior business model that could support sustained outperformance.</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Coca-Cola (KO) Stock Drops Despite Market Gains: Important Facts to Note</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/coca-cola-ko-stock-drops-214502134.html</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>A single day's minor price decline reflects short-term market noise rather than any fundamental change to KO's long-term investment thesis.</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Marriott’s Global Beverage Deal Could Be A Game Changer For Coca-Cola (KO)</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Simply Wall St.</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/marriott-global-beverage-deal-could-211547719.html</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>A global hospitality partnership expands KO's distribution footprint and long-term revenue potential across its broader beverage portfolio, strengthening recurring institutional demand.</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Marriott International (MAR), Coca-Cola Company (KO) Announce Global Beverage Partnership</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Insider Monkey</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/marriott-international-mar-coca-cola-183651151.html</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>Securing Marriott as an exclusive global beverage partner expands KO's distribution footprint across hospitality, locking in recurring institutional demand across multiple product categories.</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>PepsiCo Reports 2% Food Sales Decline as Consumer Spending Softens</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>GuruFocus.com</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/pepsico-reports-2-food-sales-174142524.html</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Weakness at rival PepsiCo signals broad consumer softness that could similarly pressure KO's North America volumes and pricing power.</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>New Price Prediction For this Popular Blue-Chip Dividend Stock</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/09/new-price-prediction-for-this-popular-blue-chip-dividend-stock/</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>The bullish analysis targets rival PepsiCo, not KO, offering limited direct relevance beyond peer valuation context for Coca-Cola investors.</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>PepsiCo Q2 Earnings Beat on Volume Gains &amp; International Strength</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/pepsico-q2-earnings-beat-volume-142300214.html</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Rival PepsiCo's strong volumes and international growth signal healthy beverage demand but intensify competitive pressure on Coca-Cola's market share.</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>3 Reasons to Buy This 4.2%-Yielding Dividend King Stock in July</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Motley Fool</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/investing/2026/07/09/3-reasons-to-buy-this-42-yielding-dividend-king-st/</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>KO's Dividend King status with a rare 4%+ yield underscores its reliability as a durable income holding for long-term investors.</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>How a $1 Million Dividend Portfolio Can Generate $100,000 Annually</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/09/a-1-million-dividend-portfolio-generating-100000-annually-what-happens-when-your-highest-yielder-cuts-the-payout/</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>This generic dividend-strategy piece isn't KO-specific and offers little actionable insight for a long-term Coca-Cola shareholder.</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Top Dividend King Down 12% and Worth Loading Up On Now</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Motley Fool</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/investing/2026/07/09/top-dividend-king-down-12-and-worth-loading-up-on/</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>The Procter &amp; Gamble Company</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>A 12% pullback in a reliable dividend payer may offer long-term investors a rare entry point at a discounted valuation.</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Procter &amp; Gamble (PG) Stock Sinks As Market Gains: What You Should Know</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/procter-gamble-pg-stock-sinks-215005443.html</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>The Procter &amp; Gamble Company</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>A single day's minor price dip against market gains is routine noise and carries little significance for long-term PG holders.</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Micron Gives Stocks a $250 Billion AI Boost: Stock Market Today</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Kiplinger</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>https://www.kiplinger.com/investing/stocks/micron-gives-stocks-a-usd250-billion-ai-boost-stock-market-today</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>The Procter &amp; Gamble Company</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Broad market rally driven by AI optimism has little direct bearing on PG, a consumer staples company insulated from tech cycles.</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>How Large Does Your Portfolio Need to Be to Generate $12,000 a Month?</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/personal-finance/2026/07/09/how-large-does-your-portfolio-need-to-be-to-generate-12000-a-month/</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>The Procter &amp; Gamble Company</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>This generic income-planning article offers no PG-specific insight, providing minimal relevance to investors evaluating Procter &amp; Gamble's fundamentals or prospects.</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Why the Best Retirement Paycheck May Start Smaller Than You Expect</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/personal-finance/2026/07/09/why-the-best-retirement-paycheck-may-start-smaller-than-you-expect/</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>The Procter &amp; Gamble Company</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>This generic retirement-income article has no bearing on Procter &amp; Gamble's fundamentals or investment thesis, offering no actionable insight for PG holders.</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>The Retirement Portfolio That Pays You Without Demanding Constant Attention</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/personal-finance/2026/07/09/the-retirement-portfolio-that-pays-you-without-demanding-constant-attention/</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>The Procter &amp; Gamble Company</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>This generic income-investing article doesn't discuss PG specifically, offering no actionable insight for a long-term holder of the stock.</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Kleenex owner Arbex targets global market share gains with Suzano, Kimberly-Clark backing</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>https://uk.finance.yahoo.com/news/kleenex-owner-arbex-targets-global-060928287.html</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>The Procter &amp; Gamble Company</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>A rebranded Kimberly-Clark tissue unit backed by Suzano signals intensifying competition in tissue and personal care categories where PG competes.</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>The Case For Buying Smaller Dividends That Grow Faster</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/personal-finance/2026/07/09/the-case-for-buying-smaller-dividends-that-grow-faster/</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>The Procter &amp; Gamble Company</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Reinforces the dividend-growth investing thesis, though it may prompt investors to weigh PG's slower-growing yield against faster-compounding alternatives.</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Procter &amp; Gamble (PG) Suffers a Larger Drop Than the General Market: Key Insights</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/procter-gamble-pg-suffers-larger-220005571.html</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>The Procter &amp; Gamble Company</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>A single day's underperformance versus the market is short-term noise and rarely alters the long-term thesis for a stable consumer staple.</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Procter &amp; Gamble (PG) Extends Its Dividend Appeal, Is The Stock Already Fully Valued?</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Simply Wall St.</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/procter-gamble-pg-extends-dividend-182058674.html</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>The Procter &amp; Gamble Company</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>PG's durable 70-year dividend growth and steady product innovation signal reliability, though valuation concerns suggest limited near-term upside for new buyers.</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Zacks Investment Ideas feature highlights: XLV, XBI, LLY, EXEL, PTCT, FTRE and ILMN</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/healthcare/articles/zacks-investment-ideas-feature-highlights-063700181.html</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Eli Lilly and Company</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>LLY featured among healthcare and biotech leaders signals sector strength and improving earnings momentum, reinforcing long-term positioning.</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Record Numbers of Americans Are on GLP-1 Drugs. That's Great News for This Stock.</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Motley Fool</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/investing/2026/07/09/record-numbers-of-americans-on-glp-1-drugs-thats/</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Eli Lilly and Company</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Growing GLP-1 adoption expands Eli Lilly's addressable market, supporting durable revenue growth and reinforcing its leadership in a lucrative therapeutic category.</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Eli Lilly’s $400 Billion Surge Is Reshaping Big Pharma</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/09/eli-lillys-400-billion-surge-is-reshaping-big-pharma/</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Eli Lilly and Company</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>LLY's trillion-dollar valuation and sustained outperformance signal strong market confidence, though elevated levels may compress future upside for new investors.</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Stocks Look Shaky, But This Sector is Booming (Biotech)</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/healthcare/articles/stocks-look-shaky-sector-booming-170400242.html</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Eli Lilly and Company</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>LLY's inclusion among biotech sector leaders signals strong relative momentum, though sector-wide rotation matters less than company-specific fundamentals for long-term holders.</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Two Drugmakers Own 90% of the Obesity Boom. One Fund Owns Both for 0.59%</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/09/two-drugmakers-own-90-of-the-obesity-boom-one-fund-owns-both-for-0-59/</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Eli Lilly and Company</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>LLY's dominant obesity-drug position underpins strong healthcare fund returns, signaling its central role in a major growth market for long-term holders.</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Jim Cramer Says Biotech is The Hottest Group in The Market Right Now</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/09/jim-cramer-says-biotech-is-the-hottest-group-in-the-market-right-now/</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Eli Lilly and Company</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Broad biotech sector momentum and a friendlier FDA environment could lift sentiment and valuations across large-cap pharma names like LLY.</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Buyout Buzz Around VKTX Is Back: What's Fueling the Speculation?</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/healthcare/articles/buyout-buzz-around-vktx-back-135600482.html</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Eli Lilly and Company</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Rising M&amp;A interest in obesity player VKTX signals intensifying competition and potential acquirers vying for share in Lilly's key growth market.</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>ABBV Leads Its Peer Group. You Pay For That</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Trefis</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>https://www.trefis.com/articles/606394/abbv-leads-its-peer-group-you-pay-for-that/2026-07-09</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Eli Lilly and Company</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>AbbVie's premium valuation highlights how strong-performing pharma peers can command rich multiples, offering a valuation benchmark for LLY investors.</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Eli Lilly Stock Gets a Lift After Canada Backs Eczema Drug</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>GuruFocus.com</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/healthcare/articles/eli-lilly-stock-gets-lift-124412596.html</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Eli Lilly and Company</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>Regulatory backing in Canada expands the addressable market for Lilly's eczema treatment, supporting long-term revenue diversification beyond its core franchises.</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>Regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Lilly Gets Canada Boost</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>GuruFocus.com</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/healthcare/articles/lilly-gets-canada-boost-122512001.html</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Eli Lilly and Company</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Expanded Canadian reimbursement for Ebglyss could broaden the drug's addressable market and incrementally support Lilly's long-term dermatology revenue growth.</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>Regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Is UnitedHealth Group (UNH) Fully Valued On Raised Guidance Ahead Of Q2?</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Simply Wall St.</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/unitedhealth-group-unh-fully-valued-071156269.html</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>UnitedHealth Group Incorporated</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>Raised guidance and cost discipline signal operational strength, but strong recent gains raise questions about whether the stock is now fully valued.</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Why Did CSX, PENG, UNH Stocks Ascend To 52-Week Highs Today?</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Stocktwits</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>https://stocktwits.com/news-articles/markets/equity/why-did-csx-peng-unh-stocks-ascend-to-52-week-highs-today/cZmAF0cR7F4</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>UnitedHealth Group Incorporated</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>UNH reaching a 52-week high signals renewed investor confidence and healthcare sector momentum, though price milestones alone don't confirm long-term fundamentals.</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Jim Cramer: “The Real Bull Market” Is Happening in Health Insurance. CVS Is One of the Biggest Winners as Walgreens “Basically Disappears”</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/09/jim-cramer-the-real-bull-market-is-happening-in-health-insurance-cvs-is-one-of-the-biggest-winners-as-walgreens-basically-disappears/</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>UnitedHealth Group Incorporated</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>A bullish thesis on managed care insurers getting properly paid for underwritten risk supports UNH's pricing power and margin recovery outlook.</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>The Real Price Of UnitedHealth Stock Isn't On Today's Label</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Trefis</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>https://www.trefis.com/articles/606413/the-real-price-of-unitedhealth-stock-isnt-on-todays-label/2026-07-09</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>UnitedHealth Group Incorporated</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Current valuation metrics may overstate UNH's expensiveness, suggesting long-term investors could be acquiring future earnings at an attractive effective discount.</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>UnitedHealth Is Emerging From Its Worst Crisis in Decades. Here's What History Says Is Coming Next.</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Motley Fool</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/investing/2026/07/09/unitedhealth-emerging-worst-crisis-history-unh/</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>UnitedHealth Group Incorporated</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>A recovery from crisis lows may signal renewed investor confidence, but historical patterns suggest examining whether the rebound is sustainable.</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Don't Buy UnitedHealth Group (UNH) Stock Before Reading This</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Motley Fool</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/investing/2026/07/08/dont-buy-unitedhealth-group-unh-stock-before-readi/</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>UnitedHealth Group Incorporated</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>Suggests better-value healthcare alternatives exist, prompting long-term holders to reassess UNH's relative positioning and competitive standing in the sector.</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>UNH's $1.5B AI Push: Can It Deliver More Than Cost Savings?</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/healthcare/articles/unhs-1-5b-ai-push-152500066.html</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>UnitedHealth Group Incorporated</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>A $1.5B AI investment signals UNH's commitment to operational efficiency and new revenue streams, potentially strengthening long-term competitive positioning and margins.</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Dollar Tree upgraded, PayPal initiated: Wall Street's top analyst calls</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>The Fly</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/broadcom-downgraded-unitedhealth-upgraded-wall-135834606.html</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>UnitedHealth Group Incorporated</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>This headline concerns Dollar Tree and PayPal analyst actions, with no relevance to UNH's business or investment outlook.</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>This Stock Stumbled Last Year. Now It's the First Half's Best Performing Mega-Cap Healthcare Stock. Is It Too Late to Buy?</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Motley Fool</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/investing/2026/07/07/this-stock-stumbled-last-year-now-its-the-first-ha/</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>UnitedHealth Group Incorporated</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>A strong rebound signals UNH's turnaround is gaining traction, suggesting improving fundamentals and renewed investor confidence in its long-term prospects.</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Dow Jones Stocks Could Be the Perfect Portfolio for 2026 Now That Google’s in the Mix. Here’s 3 Ways to Profit.</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Barchart</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>https://www.barchart.com/story/news/3162711/dow-jones-stocks-could-be-the-perfect-portfolio-for-2026-now-that-googles-in-the-mix-heres-3-ways-to-profit</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>UnitedHealth Group Incorporated</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>This headline focuses on Dow Jones index composition broadly and offers no UNH-specific catalyst, so it carries minimal direct relevance for long-term holders.</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>AI could cause a huge electricity shortfall in the US, Bank of America says: A closer look</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Yahoo Finance Video</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/video/ai-could-cause-huge-electricity-201410692.html</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Caterpillar Inc.</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>Rising power demand could boost demand for Caterpillar's generators and power infrastructure equipment as utilities and data centers expand capacity.</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Caterpillar (CAT) Stock Dips While Market Gains: Key Facts</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/caterpillar-cat-stock-dips-while-214505307.html</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Caterpillar Inc.</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>A single-day 1% dip against a rising market reflects short-term noise rather than any fundamental change in CAT's long-term outlook.</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>These Dividend Paying Stocks Offer Strong Exposure to AI Trends</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/dividend-paying-stocks-offer-strong-211900130.html</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Caterpillar Inc.</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>CAT is positioned as a beneficiary of AI-driven infrastructure demand while offering reliable dividends, appealing to income-focused long-term investors.</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Is Caterpillar (CAT) Still A Bargain Or Already Fully Priced?</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Simply Wall St.</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/caterpillar-cat-still-bargain-already-111423923.html</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Caterpillar Inc.</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>Conflicting valuation signals suggest CAT's strong run may have priced in growth, warranting caution on entry timing for long-term investors.</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>CAT Stock Heads For Second Weekly Loss: Is Caterpillar's AI Rally Fading?</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Stocktwits</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>https://stocktwits.com/news-articles/markets/equity/cat-stock-heads-for-second-weekly-loss-is-caterpillar-ai-rally-fading/cZmosRuR7Vu</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Caterpillar Inc.</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Recent momentum loss signals that CAT's valuation may have outrun fundamentals, raising the risk of a pullback amid tariff and execution concerns.</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>3 Mega-Cap Stocks with Competitive Advantages</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>StockStory</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/3-mega-cap-stocks-competitive-083700085.html</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Caterpillar Inc.</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>Being cited as a mega-cap with a competitive moat reinforces CAT's durable market position but signals limited growth headroom ahead.</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>'Big Short' Michael Burry Bets Against Nvidia and Tesla Again</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>GuruFocus.com</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/big-short-michael-burry-bets-183357587.html</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Caterpillar Inc.</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>This headline concerns Nvidia and Tesla, not Caterpillar, so it has no direct relevance to CAT investors.</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Can Caterpillar's Skycatch Deal Boost Its Mining Tech Edge?</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/technology/articles/caterpillars-skycatch-deal-boost-mining-160200975.html</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Caterpillar Inc.</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>The acquisition strengthens CAT's high-margin technology and autonomous mining capabilities, supporting recurring revenue and long-term competitive differentiation.</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Why Caterpillar’s (CAT) Dividend Hike and Buybacks Make Capital-Return Mix Central to Its Tax Profile</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Insider Monkey</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/why-caterpillar-cat-dividend-hike-124814177.html</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Caterpillar Inc.</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>An 8% dividend increase alongside buybacks signals management confidence and a shareholder-friendly capital-return strategy supporting long-term total returns.</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Memory chip stocks fall into a bear market amid latest tech sell-off</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Yahoo Finance Video</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/video/memory-chip-stocks-fall-bear-191922938.html</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Caterpillar Inc.</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>This headline concerns memory chipmakers and has no direct relevance to Caterpillar's construction and mining equipment business fundamentals.</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>New Strong Sell Stocks for July 10th</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/strong-sell-stocks-july-10th-090200770.html</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Honeywell International Inc.</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>A Strong Sell rating signals near-term earnings estimate downgrades, suggesting potential headwinds that long-term investors should investigate before adding to positions.</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Honeywell International Inc. (HON) Laps the Stock Market: Here's Why</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/honeywell-international-inc-hon-laps-221503770.html</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Honeywell International Inc.</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>A single day's stock outperformance offers little insight into HON's fundamentals or long-term investment thesis.</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Why Honeywell’s New Earnings Guidance Isn’t as Good as It Looks</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Barrons.com</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>https://www.barrons.com/articles/honeywell-stock-earnings-guidance-9bbf75b8?siteid=yhoof2&amp;yptr=yahoo</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Honeywell International Inc.</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>The doubled EPS guidance appears inflated by accounting or one-time factors, so investors should scrutinize underlying operational performance before assuming genuine growth.</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Honeywell Technologies Revises 2026 Guidance Post Reverse Stock Split</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/honeywell-technologies-revises-2026-guidance-160600010.html</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Honeywell International Inc.</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>The EPS guidance change reflects only a mechanical share-count adjustment from the reverse split, not any real change in underlying business fundamentals.</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>GE Keeps Climbing. Should You Climb On?</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Trefis</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>https://www.trefis.com/articles/606398/ge-keeps-climbing-should-you-climb-on/2026-07-09</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Honeywell International Inc.</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>GE's aerospace momentum signals strong sector demand that could benefit Honeywell's aerospace segment, though rich valuations warn against chasing peers.</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Jim Cramer on Solstice: “This Pullback May Be Giving You a Terrific Buying Opportunity”</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Insider Monkey</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/jim-cramer-solstice-pullback-may-121854537.html</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Honeywell International Inc.</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>The favorable coverage of Solstice, a recent Honeywell spinoff, reflects positively on HON's portfolio restructuring strategy and unlocking of shareholder value.</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Wall Street Remains Bullish On Honeywell (HON) Post Spinoff</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Insider Monkey</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/wall-street-remains-bullish-honeywell-115834660.html</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Honeywell International Inc.</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>Analyst confidence and a $253 price target suggest continued upside potential and validate Honeywell's strategy following its business spinoff.</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>HON Stock Gains Overnight: Will The Updated Outlook Revive Interest In The Automation Giant?</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Stocktwits</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>https://stocktwits.com/news-articles/markets/equity/hon-stock-gains-overnight-will-the-updated-outlook-revive-interest-in-the-automation-giant/cZmoFtPR7Vn</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Honeywell International Inc.</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>Updated guidance and stock split signal management's confidence, potentially reshaping investor perception of Honeywell's automation-focused strategy going forward.</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Honeywell Technologies raises profit guidance after one-for-two reverse stock split</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/honeywell-technologies-raises-profit-guidance-210627717.html</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Honeywell International Inc.</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>The doubled EPS guidance largely reflects the reverse split's mechanical share-count reduction, so investors should assess whether underlying operating performance genuinely improved post-spinoff.</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Should You Buy, Sell or Hold Honeywell Stock Post Aerospace Spin-Off?</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/buy-sell-hold-honeywell-stock-160800166.html</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Honeywell International Inc.</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>The aerospace spin-off reshapes HON into an automation-focused business, changing its long-term growth profile and valuation for investors.</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Can Chevron's Microsoft Partnership Power the Next Leg of Growth?</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/energy/articles/chevrons-microsoft-partnership-power-next-132800261.html</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Exxon Mobil Corporation</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>Chevron's move into AI-driven power supply signals a competitive diversification trend that XOM investors should watch for parallel opportunities or lagging positioning.</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>‘Staggering’: Goldman Sachs Says China’s Oil Demand May Never Fully Recover</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/10/staggering-goldman-sachs-says-chinas-oil-demand-may-never-fully-recover/</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Exxon Mobil Corporation</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>Structurally weaker Chinese oil demand could pressure long-term crude prices and cap XOM's upstream revenue growth prospects.</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>ExxonMobil (XOM) Stock Looks Reasonable On Earnings But Stretched After 180% Run</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Simply Wall St.</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/exxonmobil-xom-stock-looks-reasonable-081408471.html</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Exxon Mobil Corporation</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>Valuation appears fair on earnings metrics but the large multi-year gain suggests limited near-term upside and heightened downside risk if oil weakens.</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>Earnings</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>The Real Risk Inside ExxonMobil Stock</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Trefis</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>https://www.trefis.com/articles/606402/the-real-risk-inside-exxonmobil-stock/2026-07-09</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Exxon Mobil Corporation</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>Investors should assess XOM's exposure to long-term structural threats, like energy transition, that could undermine its core profit engine despite operational strength.</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Exxon Mobil Holdings (XOM) Stock Falls Amid Market Uptick: What Investors Need to Know</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/exxon-mobil-holdings-xom-stock-214502284.html</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Exxon Mobil Corporation</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>A single-day 2.6% dip against a rising market is short-term noise and unlikely to affect XOM's long-term investment thesis.</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>CVX Stock Has A New Bull Case — Why Bank Of America Favors Chevron Over Exxon As Hormuz Risks Push Oil Prices Higher</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Stocktwits</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>https://stocktwits.com/news-articles/markets/equity/cvx-stock-bull-case-why-bank-of-america-favors-chevron-over-exxon-as-hormuz-risks-lift-oil-prices/cZmY4UyR7nv</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Exxon Mobil Corporation</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>Analyst preference for Chevron over Exxon signals relative competitive weakness, potentially pressuring XOM's investor appeal despite favorable oil price tailwinds.</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Exxon Mobil signals massive profit spike but Wall Street is divided</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>TheStreet</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>https://www.thestreet.com/investing/stocks/exxon-mobil-xom-q2-earnings-signals</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Exxon Mobil Corporation</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>Exxon's profit outlook hinges on volatile oil prices, and mixed analyst views signal uncertainty about near-term earnings sustainability for shareholders.</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Strong Commodity Tailwinds Poised to Boost XOM's Q2 Results</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/commodities/articles/strong-commodity-tailwinds-poised-boost-161400086.html</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Exxon Mobil Corporation</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>ExxonMobil's earnings remain heavily tied to volatile commodity prices, highlighting cyclical exposure rather than fundamental operational improvements for long-term holders.</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>Earnings</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>ExxonMobil CFO backs semiannual reporting option: 5 takeaways</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>CFO Dive</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>https://www.cfodive.com/news/exxonmobil-cfo-backs-sec-semiannual-reporting-option-5-takeaways/824854/</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Exxon Mobil Corporation</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>Reduced reporting frequency could lower compliance costs but may decrease transparency and timely visibility into XOM's financial performance for shareholders.</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Why Is Exxon Mobil (XOM) Taking Cuba To Court Again?</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Insider Monkey</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/energy/articles/why-exxon-mobil-xom-taking-121500296.html</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Exxon Mobil Corporation</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>Ongoing legal action against Cuba signals asset-recovery efforts but reflects continued geopolitical and legacy expropriation risks affecting Exxon's long-term positioning.</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>NextEra Energy vs. Duke Energy: A $67 Billion Deal Could Change the Revenue Script</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Motley Fool</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/coverage/charts/2026/07/10/nextera-energy-vs-duke-energy-the-usd67-billion-deal-could-change-the-revenue-script/</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>NextEra Energy, Inc.</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>NEE's seasonal revenue volatility versus Duke's steadier sales highlights earnings predictability concerns relevant when comparing utility investments for stable long-term returns.</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Don’t Let Your Kids’ Braces Chew Up Your Retirement</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/personal-finance/2026/07/09/dont-let-your-kids-braces-take-a-bite-out-of-your-retirement/</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>NextEra Energy, Inc.</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>This personal-finance article about orthodontics costs is unrelated to NextEra Energy and carries no relevance for investors.</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>NextEra Energy (NEE) Stock Looks Stretched Despite Its 32% Five Year Run</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Simply Wall St.</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/energy/articles/nextera-energy-nee-stock-looks-161055071.html</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>NextEra Energy, Inc.</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>Valuation models signal NEE may be overvalued, suggesting limited upside and reduced margin of safety for investors buying at current prices.</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Can ES' Portfolio Transformation Create Long-Term Shareholder Value?</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/es-portfolio-transformation-create-long-160100259.html</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>NextEra Energy, Inc.</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>This headline concerns Eversource (ES), not NextEra (NEE), so it has minimal direct relevance to NEE investors beyond broad utility-sector read-through.</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Why the Best Retirement Paycheck May Start Smaller Than You Expect</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/personal-finance/2026/07/09/why-the-best-retirement-paycheck-may-start-smaller-than-you-expect/</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>NextEra Energy, Inc.</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>This is a generic retirement planning article with no NEE-specific content, offering no material insight for investors in the stock.</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Can Vistra's Long-Term PPAs Act as a Catalyst for Its Growth?</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/vistras-long-term-ppas-act-124500120.html</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>NextEra Energy, Inc.</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>Vistra's data-center PPAs highlight strong utility demand from hyperscalers, signaling a similar growth avenue NEE can pursue with its clean-energy assets.</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>AI Stocks Look Expensive. These 3 ETFs Could Help Investors Stay in the Game.</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Barchart</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>https://www.barchart.com/story/news/3201847/ai-stocks-look-expensive-these-3-etfs-could-help-investors-stay-in-the-game</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>NextEra Energy, Inc.</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>This general ETF piece barely touches NEE and offers little direct insight for long-term utility investors focused on renewable energy fundamentals.</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>XLU vs. VPU: Which Utilities ETF Best Powers the AI Data-Center Boom?</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/etf/2026/07/08/xlu-vs-vpu-which-utilities-etf-best-powers-the-ai-data-center-boom/</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>NextEra Energy, Inc.</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>NEE benefits from the AI-driven utilities growth narrative, and its weighting in these popular ETFs affects passive inflows and demand.</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>CEG Stock Trails Industry in the Past Year: Time to Buy, Hold or Sell?</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/ceg-stock-trails-industry-past-160600944.html</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>NextEra Energy, Inc.</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>This headline concerns Constellation Energy (CEG), a peer utility, not NEE directly, offering limited relevance beyond competitive context.</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Why the AI Boom Is About to Break the U.S. Power Grid</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Oilprice.com</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/energy/articles/why-ai-boom-break-u-000000959.html</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>NextEra Energy, Inc.</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>Surging AI-driven power demand supports long-term growth for utilities and generators like NEE, though grid constraints may pressure capacity investment.</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>What to expect this earnings season amid lingering Hindenburg Omens</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Yahoo Finance Video</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/video/expect-earnings-season-amid-lingering-151000741.html</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>Broad market commentary on earnings season and technical warning signals offers little GOOGL-specific insight for long-term investors.</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Alphabet Is the Dow's Newest Member. This One Has Been Raising Its Dividend Since Before Google Existed.</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Motley Fool</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/investing/2026/07/10/alphabet-is-the-dows-newest-member-this-one-has-be/</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>Alphabet's inclusion in the Dow signals blue-chip status, but the article contrasts it with a longtime dividend grower, offering little direct GOOGL impact.</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>AI’s $15 Trillion Opportunity Is Just Getting Started</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/10/ais-15-trillion-opportunity-is-just-getting-started/</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>A rapidly expanding AI market signals strong tailwinds for Google's cloud and AI investments, supporting long-term revenue growth potential.</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>AI’s $182 Billion Borrowing Spree Could Become Its Biggest Risk Yet</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/10/ais-182-billion-borrowing-spree-could-become-its-biggest-risk-yet/</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>Massive AI capex funded by debt raises questions about whether returns will justify the spending, pressuring GOOGL's future free cash flow.</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>AppLovin gains e-commerce ad share as advertisers expand platform use, Jefferies survey finds</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Proactive</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>https://www.proactiveinvestors.com/companies/news/1095274/applovin-gains-e-commerce-ad-share-as-advertisers-expand-platform-use-jefferies-survey-finds-1095274.html</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>AppLovin's growing e-commerce ad share signals rising competition for digital ad budgets that could pressure Google's core advertising revenue over time.</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Is It Time To Buy The Dip On Microsoft Stock?</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Trefis</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>https://www.trefis.com/articles/606599/is-it-time-to-buy-the-dip-on-microsoft-stock/2026-07-10</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>Microsoft's premium valuation and strong growth highlight competitive dynamics that could pressure GOOGL's positioning in cloud and AI markets.</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Why I Can’t Stop Buying Microsoft Even As Fears Of An AI Bubble Resurface</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/10/why-i-cant-stop-buying-microsoft-even-as-fears-of-an-ai-bubble-resurface/</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>AI bubble fears and cloud investment thesis apply broadly, signaling potential valuation pressure and opportunity across major AI players including Google.</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>How OpenAI’s New GPT 5.6 Measures Up to SpaceX, Google, Anthropic</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Barrons.com</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>https://www.barrons.com/articles/openai-gpt-5-6-spacex-google-anthropic-7a511e79?siteid=yhoof2&amp;yptr=yahoo</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>Competitive AI benchmarks show Google trailing OpenAI, raising concerns about Alphabet's positioning in the high-stakes race for AI leadership.</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Intel’s $200 Billion Turnaround Plan Is Under the Microscope</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/10/intels-200-billion-turnaround-plan-is-under-the-microscope/</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>Intel's chip resurgence could diversify semiconductor supply, affecting Google's TPU and data center hardware sourcing and competitive dynamics.</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Stock Of A Great Dividend King Jumps 24%</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/10/stock-of-a-great-dividend-king-jumps-24/</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>This headline concerns a tobacco dividend stock, not GOOGL, offering no material insight for Alphabet investors beyond a passing AI-spending mention.</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Jim Cramer Says NVIDIA Is the Most Proprietary Chip Company in History, and the Market Is Getting Its Valuation Wrong</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/10/jim-cramer-says-nvidia-is-the-most-proprietary-chip-company-in-history-and-the-market-is-getting-its-valuation-wrong/</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>This headline centers on NVIDIA's valuation, not META, offering no direct relevance to META's business or long-term investment thesis.</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Bank of America's new META stock outlook cuts to the chase</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>TheStreet</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>https://www.thestreet.com/investing/stocks/bank-of-america-meta-stock-investors-buy</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>Heavy AI infrastructure spending is pressuring META's stock, testing investor patience on whether the capital outlays will yield sufficient long-term returns.</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Meta Vs. Coreweave: How Meta is Looking to Bury Coreweave With ‘Meta Compute’ Sovereign Scale</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/10/meta-vs-coreweave-how-meta-is-looking-to-bury-coreweave-with-meta-compute-sovereign-scale/</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>Meta's push toward self-built AI compute infrastructure could reduce reliance on costly external providers, improving long-term margins and strategic control.</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>AI’s $182 Billion Borrowing Spree Could Become Its Biggest Risk Yet</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/10/ais-182-billion-borrowing-spree-could-become-its-biggest-risk-yet/</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>Massive AI-driven debt across tech giants raises the risk that META's heavy AI spending may not generate proportional returns, pressuring future cash flows.</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>AppLovin gains e-commerce ad share as advertisers expand platform use, Jefferies survey finds</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Proactive</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>https://www.proactiveinvestors.com/companies/news/1095274/applovin-gains-e-commerce-ad-share-as-advertisers-expand-platform-use-jefferies-survey-finds-1095274.html</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>AppLovin's growing e-commerce ad share signals rising competition for META's advertising dollars, potentially pressuring its core revenue growth.</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Analysts Think AI Demand Has No Ceiling And Raised AMD’s Price Target Again</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/10/analysts-think-ai-demand-has-no-ceiling-and-raised-amds-price-target-again/</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>Bullish AI demand signals support Meta's heavy AI infrastructure spending thesis, though rising chip costs could pressure margins.</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Meta Is a Buy at $630 Despite 2026 Chop and Here’s Why</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/10/meta-is-a-buy-at-630-despite-2026-chop-and-heres-why/</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>Strong operational fundamentals diverging from a depressed share price may signal a buying opportunity for patient long-term investors.</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Top Midday Stories: SK Hynix Marks Record-Setting Debut in US Market; Meta Faces $2 Billion Manus Deal Rollback</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>MT Newswires</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/top-midday-stories-sk-hynix-155216910.html</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>A potential $2 billion deal rollback signals setbacks in Meta's AI expansion strategy, raising concerns about capital allocation and growth execution.</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Why AI spending is beginning to hit a 'speed bump'</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Yahoo Finance Video</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/video/why-ai-spending-beginning-hit-200500299.html</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>A pullback in AI spending could pressure META's heavy AI capex narrative, though cost discipline may improve margins and returns over time.</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="10" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Tech stocks live: SK Hynix begins trading on Nasdaq, SpaceX stock tumbles</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/technology/live/tech-stocks-live-sk-hynix-begins-trading-on-nasdaq-spacex-stock-tumbles-131003284.html</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>Broad tech and hardware momentum signals healthy sector sentiment, but this headline has no direct bearing on META's fundamentals.</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>SEGRO Slams Prologis Proposal, Touts £4.1B Pipeline Upside</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>MarketBeat</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>https://www.marketbeat.com/instant-alerts/segro-slams-prologis-proposal-touts-41b-pipeline-upside-2026-07-09/?utm_source=yahoofinance&amp;utm_medium=yahoofinance</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Prologis, Inc.</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>PLD</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>SEGRO's public rejection signals potential resistance or higher costs for Prologis's expansion ambitions in the European logistics market.</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Prologis Pushes for Talks on $16.9 Billion Segro Bid</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>The Wall Street Journal</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>https://www.wsj.com/business/deals/prologis-pushes-for-talks-on-16-9-billion-segro-bid-c1eb3172?siteid=yhoof2&amp;yptr=yahoo</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Prologis, Inc.</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>PLD</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>A $16.9B Segro acquisition would significantly expand Prologis's European logistics footprint, but raises questions about deal price and integration risk.</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Prologis Seeks SEGRO Shareholders' Support to Spring an Offer for Merger</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>MT Newswires</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/prologis-seeks-segro-shareholders-apos-091221233.html</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Prologis, Inc.</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>PLD</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>A SEGRO merger would significantly expand Prologis's European logistics footprint, but pursuing an unsolicited deal raises integration and overpayment risks.</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Prologis (PLD) Stock Looks Fully Valued With Growth Already Priced In</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Simply Wall St.</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/prologis-pld-stock-looks-fully-081453525.html</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Prologis, Inc.</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>PLD</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>Valuation analysis suggests limited near-term upside despite strong logistics fundamentals, signaling investors may find better entry points after any price pullback.</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Is Prologis (PLD) Fairly Valued Following Its Board Appointment?</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Simply Wall St.</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/prologis-pld-fairly-valued-following-061051144.html</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Prologis, Inc.</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>PLD</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Adding a seasoned executive to the board strengthens governance oversight, potentially improving strategic decisions as Prologis navigates M&amp;A and valuation questions.</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>NVIDIA Was the Darling Of The AI Boom, Now It’s Cheaper Than The King Of House Paint</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/09/nvidia-was-the-darling-of-the-ai-boom-now-its-cheaper-than-the-king-of-house-paint/</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>The Sherwin-Williams Company</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>SHW</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>SHW's premium valuation versus NVIDIA highlights that its high P/E multiple may leave limited upside if growth disappoints long-term.</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>UFP Industries, Sherwin-Williams, and Vulcan Materials Stocks Trade Down, What You Need To Know</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>StockStory</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/ufp-industries-sherwin-williams-vulcan-072500792.html</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>The Sherwin-Williams Company</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>SHW</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>SHW's decline stems from broad macro fears rather than company-specific issues, suggesting limited long-term impact on fundamentals.</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Sherwin Williams (SHW) In Focus As Cost Cutting Narrative Meets Valuation Questions</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Simply Wall St.</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/sherwin-williams-shw-focus-cost-021400574.html</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>The Sherwin-Williams Company</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>SHW</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>Cost-cutting efforts and a new payment partnership signal operational focus, but valuation concerns and index removal warrant caution on future returns.</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Nasdaq Nearly Flat in Afternoon Trading, Gets Boost From Chip Bounce</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Barrons.com</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>https://www.barrons.com/livecoverage/stock-market-news-today-070826/card/nasdaq-nearly-flat-in-afternoon-trading-gets-boost-from-chip-bounce-NyG9nhzsGedDMthd55Wa?siteid=yhoof2&amp;yptr=yahoo</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>The Sherwin-Williams Company</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>SHW</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>This broad market movement is driven by chip stocks and has no direct relevance to Sherwin-Williams' coatings business fundamentals.</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="10" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Dow Drops 800 Points. These Stocks Are a Big Drag.</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Barrons.com</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>https://www.barrons.com/livecoverage/stock-market-news-today-070826/card/dow-drops-600-points-these-stocks-are-the-biggest-drags--rsHThW3BINNz8dHU9Gmz?siteid=yhoof2&amp;yptr=yahoo</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>The Sherwin-Williams Company</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>SHW</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>Broad market sell-offs pressure SHW's stock short-term, but long-term investors should focus on company fundamentals rather than macro-driven volatility.</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Take-Two 'GTA VI' Pre-Order Data Indicate 'Robust' Demand, B. Riley Says</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>MT Newswires</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/two-apos-gta-vi-apos-165328884.html</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>GameStop Corp.</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Strong GTA VI demand could drive foot traffic and software sales at GameStop, benefiting its core retail business during the launch window.</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>GameStop just cleared a hurdle nobody was watching</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>TheStreet</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>https://www.thestreet.com/investing/gme-gamestop-share-increase-ebay-acquisition</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>GameStop Corp.</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>Expanded share authorization gives GameStop flexibility for capital raises or acquisitions, but signals potential dilution as its core physical-media business faces obsolescence.</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Sony Is Going All-Digital—But Investors Should Watch This Instead</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>MarketBeat</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>https://www.marketbeat.com/articles/sony-is-going-all-digitalbut-investors-should-watch-this-instead/?utm_source=yahoofinance&amp;utm_medium=yahoofinance</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>GameStop Corp.</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>Sony's shift away from physical discs signals accelerating decline in the physical game media market central to GameStop's retail business.</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="10" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>GME Stock Rises After Hours — GameStop Shareholders Back Bigger Share Count To Support Proposed eBay Acquisition</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Stocktwits</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>https://stocktwits.com/news-articles/markets/equity/gamestop-stock-rises-after-shareholders-approve-bigger-share-count-for-proposed-ebay-acquisition/cZmlDx0R7ZN</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>GameStop Corp.</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>Expanded share authorization signals dilution risk but enables strategic pivots like a potential eBay deal, reshaping GameStop's long-term business trajectory.</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Disney+ is considering a free streaming tier, report says</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>TechCrunch</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/media-advertising/articles/disney-considering-free-streaming-tier-162905974.html</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>A free ad-supported tier could expand Disney+'s reach and boost advertising revenue, though it risks cannibalizing higher-margin subscription income.</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Disney (DIS) Upgraded to Buy: Here's What You Should Know</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/disney-dis-upgraded-buy-heres-160003523.html</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>Rising earnings estimates signal improving fundamentals, suggesting Disney's core businesses may be recovering and supporting stronger long-term value creation.</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>Earnings</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Why WD-40 Is Crushing the Hottest AI Stocks</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Barrons.com</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>https://www.barrons.com/articles/wd-40-earnings-stock-price-ai-ea2f8b96?siteid=yhoof2&amp;yptr=yahoo</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>This headline concerns WD-40, not Disney, and has no bearing on a long-term DIS investor's thesis.</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Why Netflix’s Pivot to Live TV Is a Big Risk</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Barrons.com</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>https://www.barrons.com/articles/netflix-stock-price-live-tv-6a3deb6d?siteid=yhoof2&amp;yptr=yahoo</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>Netflix moving into live TV intensifies competition for Disney's streaming and traditional TV businesses, potentially pressuring engagement and ad revenue.</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Can Strategic Partnerships Strengthen Crocs' Market Position?</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/strategic-partnerships-strengthen-crocs-market-134600865.html</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>Disney's brand licensing partnerships, like with Crocs, generate incremental royalty revenue and reinforce the enduring commercial value of its IP portfolio.</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>3 Consumer Stocks with Questionable Fundamentals</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>StockStory</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/3-consumer-stocks-questionable-fundamentals-134320556.html</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>Weakening consumer discretionary demand could pressure DIS's theme parks, streaming, and merchandise revenue if the broader economy slows further.</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Here Is the Main Reason to Buy Netflix Before July 16</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>https://247wallst.com/investing/2026/07/10/here-is-the-main-reason-to-buy-netflix-before-july-16/</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>Netflix's strong operating momentum and streaming dominance intensify competitive pressure on Disney's own streaming business and content strategy.</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Disney Explores Free Disney+ Option to Strengthen Streaming Growth (DIS)</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>InvestorsHub</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>https://investorshub.advfn.com/market-news/article/31629/disney-explores-free-disney-option-to-strengthen-streaming-growth-dis</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>A free ad-supported tier could expand Disney+ reach and advertising revenue, though it risks cannibalizing paid subscriptions and margins.</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>VZ, T, TMUS: SpaceX Starlink’s Rise Tests Telecom Giants, But This Analyst Sees Opportunity Ahead</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Stocktwits</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>https://stocktwits.com/news-articles/markets/equity/vz-t-tmus-space-x-starlink-rise-tests-telecom-giants-analyst-sees-opportunity-ahead/cZmAs9lR7Fg</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>This headline concerns telecom carriers and satellite competition, with no meaningful relevance to Disney's business or long-term investment thesis.</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Disney (DIS) Stock Looks Cheap On Earnings And Cash Flow</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Simply Wall St.</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/disney-dis-stock-looks-cheap-001803786.html</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>Valuation models suggesting DIS trades below intrinsic value may signal a buying opportunity for patient investors despite recent underperformance.</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>Earnings</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Defense AI Heats Up: BigBear.ai Lands First European Validation for AI-Powered Airport Screening</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>IPO-Edge.com</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/technology/ai/articles/defense-ai-heats-bigbear-ai-162529616.html</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>A competitor's traction in defense AI screening signals a growing, competitive market that could pressure PLTR's positioning in government AI contracts.</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>Competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>PAYC vs. PLTR: Which Stock Should Value Investors Buy Now?</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/payc-vs-pltr-stock-value-154003916.html</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>A comparative value screen may flag PLTR's high valuation, potentially deterring value-focused investors and signaling limited near-term margin of safety.</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Rackspace Technology's Enterprise AI Buildout Could Generate Up to $600 Million in Annual Revenue, RBC Says</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>MT Newswires</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/technology/ai/articles/rackspace-technology-apos-enterprise-ai-142632211.html</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>Enterprise AI monetization by peers signals a growing addressable market, validating demand tailwinds that could benefit Palantir's AIP platform.</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Palantir (PLTR) Lands First Latin America Commercial Customer With GNP And Rackspace</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Simply Wall St.</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/palantir-pltr-lands-first-latin-121431834.html</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>Latin America market entry and Rackspace partnership expand Palantir's commercial reach into regulated sectors, signaling durable international growth potential.</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>PLTR Is Back At A Level It Has Defended Before</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Trefis</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>https://www.trefis.com/articles/606600/pltr-is-back-at-a-level-it-has-defended-before/2026-07-10</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>A repeatedly tested support level suggests a critical technical juncture where buyers historically step in, signaling potential entry or downside risk.</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>5 Cloud Computing Stocks to Buy for 2H 2026 as Digital Demand Soars</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Zacks</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/technology/articles/5-cloud-computing-stocks-buy-115400804.html</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>Inclusion in a curated cloud/AI growth list signals analyst confidence in PLTR's positioning to capture rising data center and AI demand.</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Bernie Sanders Asks Who Do You Trust: The Pope or Peter Thiel, After Billionaire Palantir Founder Calls the Pontiff a 'Chinese Communist Agent</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Benzinga</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>https://www.yahoo.com/news/politics/articles/bernie-sanders-asks-trust-pope-113107485.html</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>Political controversy involving Palantir's co-founder could pose reputational risk but has minimal direct impact on the company's fundamentals or contracts.</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Palantir Stock Is Down 36% From Its All-Time High. Time to Buy?</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Motley Fool</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/investing/2026/07/10/palantir-stock-is-down-36-from-its-all-time-high-t/</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>A 36% pullback tests whether PLTR's strong business fundamentals justify buying despite persistently high valuation concerns for long-term holders.</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>1 Cash-Heavy Stock with Impressive Fundamentals and 2 Facing Challenges</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>StockStory</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/1-cash-heavy-stock-impressive-090316087.html</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>A cash-heavy screening piece may highlight PLTR's balance sheet strength or flag valuation concerns, warranting a check on which category PLTR falls into.</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="10" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Stocks to Watch: PepsiCo, Salesforce, AstraZeneca</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>The Wall Street Journal</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>https://www.wsj.com/livecoverage/stock-market-today-dow-sp-500-nasdaq-07-09-2026/card/stocks-to-watch-levi-strauss-pepsico-astrazeneca-ZzQtATlnpm26Cd3dKfnN?siteid=yhoof2&amp;yptr=yahoo</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>This headline covers PepsiCo, Salesforce, and AstraZeneca with no mention of Palantir, offering no direct relevance to PLTR investors.</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -39514,7 +45788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:P48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -42207,6 +48481,894 @@
         <v>60</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Costco remains a best-in-class membership warehouse retailer combining a low-margin, high-volume merchandise business with a recurring, high-margin membership fee stream. The most recent quarter (Q2 2026) shows revenue up ~11.6% YoY and EPS up ~15% YoY to $4.93, with gross margins stable around 12.7-13% and operating margins near 4%. Returns on capital are exceptional for a retailer: ROIC ~41% and ROE ~26% in the latest quarters, reflecting the capital-light economics of the fee stream. The balance sheet is a fortress net-cash position (cash ~$18.9B vs. total debt ~$8.1B), with interest coverage above 80x and debt-to-equity continuing to decline to ~0.24. Free cash flow remains positive every quarter despite ongoing warehouse expansion capex. The core concern is unchanged: at ~48x trailing and ~42x forward earnings with a PEG above 4, the stock embeds years of continued flawless execution. Recent news is almost entirely non-fundamental, with the only substantive recurring theme being Walmart's expanding high-margin advertising/retail-media business as a competitive and strategic watch item. This is an unimpeachable business trading at a demanding price.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Nothing material has changed since the prior analysis one day earlier. The financial data is identical, and the news flow (spanning July 6-7, 2026) is largely commentary rather than fundamental disclosure: articles on the enduring hot-dog loss-leader, long-term compounding retrospectives, and analyst optimism, none of which introduce new information. The only recurring substantive theme, already flagged previously, is Walmart's ~$6B high-margin advertising business and intensifying grocery price competition, which highlights both a competitive threat and an unexploited monetization avenue for Costco. In short, this update reinforces rather than changes the established thesis; there is no discontinuity from Costco's long-term trajectory.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Costco's moat is a self-reinforcing flywheel: high-renewal membership fees fund rock-bottom pricing, which drives volume, which strengthens supplier leverage, which enables further price leadership and sustains renewals. The data quantifies exceptional quality: ROIC ~41%, ROE ~26%, interest coverage above 80x, and rising cash generation. Revenue growth remains double-digit (~11.6% YoY) despite Costco's massive scale, driven by new warehouse openings (the referenced ~$250B expansion strategy) plus traffic and ticket growth, with the annualized run-rate now above $275B. Free cash flow is consistently positive and growing even while funding expansion. Defensive positioning (beta 0.87, consumables-heavy mix) provides recession resilience. International expansion, particularly in Asia, offers a multi-year runway, and periodic membership fee increases add embedded, low-friction pricing power. If Costco eventually monetizes retail media/advertising as Walmart is doing, it could layer a high-margin profit stream not currently reflected in results.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>The dominant risk is valuation rather than business quality. At ~48x trailing and ~42x forward earnings with a PEG above 4.6, the stock requires sustained mid-teens earnings growth just to hold its price; any deceleration in membership growth or comps could trigger meaningful multiple compression given the thin margin of safety. Operating margins are structurally ~4%, so equity value is disproportionately sensitive to the membership fee stream and continued top-line growth. Competitive pressure is building: Walmart's high-margin advertising business and aggressive food-price cuts intensify the battle for value-conscious households, and Costco has not matched this monetization model. As warehouse count grows, domestic saturation and lower incremental new-store returns could slow the growth the valuation depends on. FX exposure across many international markets adds volatility, and the negligible 0.62% dividend yield means total return hinges almost entirely on earnings growth and multiple maintenance. Reversion toward the middle of Costco's historical multiple range would offset much of even solid operating performance.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Financial health is excellent. Revenue quality is high given the recurring membership fee component and defensive consumables mix, and margins are stable across the trailing quarters (gross ~12.7-13%, operating ~3.7-4%, net ~3%) with no erosion. Cash generation is strong: Q2 2026 operating cash flow of ~$3.4B and FCF of ~$2.0B, positive every quarter despite $1.3-2.0B of quarterly expansion capex. The balance sheet is a net-cash position (cash ~$18.9B vs. total debt ~$8.1B), with debt-to-equity declining to ~0.24 and interest coverage above 80x, indicating essentially no solvency risk. The current ratio (~1.07) is modest but typical for a fast-turning retailer with efficient working capital. Returns on capital are outstanding: ROIC ~41%, ROE ~26%, ROA ~10%. Capital allocation favors reinvestment in warehouses, a small regular dividend, and periodic special dividends; share count appears stable with no evidence of dilution.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Overvalued</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Costco consistently trades at a premium to the market and to retail peers, justified by its superior returns on capital and recurring membership economics, so a high absolute multiple is warranted. But at ~48x trailing and ~42x forward earnings with a PEG above 4.6 against roughly mid-teens earnings growth, the multiple sits at or near the upper end of the range this business has historically commanded. Price-to-book of 25x and EV/EBITDA above 30x reinforce how richly the equity is priced relative to fundamentals. At $947.50 the stock is below its 52-week high ($1,096) but well above the low ($844), offering no discount. For the multiple to hold, Costco must keep compounding earnings at mid-teens rates indefinitely; the more probable 3-5 year path is partial multiple compression toward the middle of its historical range, offsetting a meaningful share of earnings growth. A great business at a demanding price, hence Overvalued rather than Fairly Valued.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Costco has a wide, durable moat rooted in scale-driven cost advantage combined with the membership model. Its purchasing scale and deliberately limited SKU count deliver exceptional supplier leverage and inventory efficiency, enabling price leadership that conventional merchandise retailers cannot match. Switching costs are behavioral and financial: the annual fee creates a sunk-cost commitment that supports high renewal rates and predictable, high-margin fee income. Pricing power manifests as periodic membership fee increases that members have historically accepted with minimal churn. The principal competitive threat is Walmart (including Sam's Club and Walmart+), which has comparable scale and is monetizing high-margin retail media faster than Costco, alongside Amazon competing for share of wallet. Despite this, Costco's value proposition and member loyalty remain distinctive, placing its moat among the strongest in retail.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>The long-term outlook is favorable but tempered by the demanding starting valuation. Growth drivers include continued domestic and, more importantly, international warehouse expansion (notably Asia), steady membership growth with periodic fee increases, and gradual e-commerce and ancillary-services buildout. Industry tailwinds include the defensive nature of consumables demand and the value orientation that benefits Costco in inflationary and recessionary environments. Over five years the challenges include potential domestic saturation slowing the new-unit growth rate, intensifying competition from Walmart's high-margin advertising model, FX volatility across many markets, and structurally thin operating margins that limit earnings leverage. An underexploited retail-media/advertising opportunity could become a meaningful profit lever if pursued. On balance, this is a durable, above-average compounder likely to keep growing, though the pace should moderate as scale increases.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Costco is a best-in-class defensive compounder: a wide-moat, capital-efficient retailer (ROIC ~41%, ROE ~26%) with a recurring, high-margin membership fee stream, a net-cash fortress balance sheet (80x+ interest coverage), and consistent double-digit revenue and mid-teens EPS growth. The business quality is essentially unimpeachable and merits a premium multiple. The constraint is that the current price (~48x trailing, ~42x forward, PEG &gt;4.6) already prices in years of flawless execution with little margin of safety; the most probable 3-5 year outcome is that solid operating growth is partially offset by multiple compression toward the middle of Costco's historical range, capping total returns. Competitive pressure from Walmart's high-margin advertising monetization is a watch item but not yet a fundamental threat. The rational stance for new capital is to admire the business and wait for a better entry point; existing holders are justified in patience given the quality. Nothing in the latest data or news alters this conclusion.</t>
+        </is>
+      </c>
+      <c r="M37" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Confidence is supported by the clarity and consistency of the fundamentals: stable margins across multiple quarters, exceptional and quantified returns on capital, a strong net-cash balance sheet, and a well-understood, durable business model. The valuation conclusion is corroborated by multiple metrics (P/E, PEG, EV/EBITDA, P/B) all pointing to a premium. Confidence is reduced by missing data (the two oldest quarters are NaN, no explicit historical multiple range or membership renewal figures were provided, and no peer financials were given), forcing reliance on general knowledge of Costco's characteristics. The latest news flow is almost entirely non-fundamental, adding no incremental analytical value beyond the recurring Walmart competitive theme.</t>
+        </is>
+      </c>
+      <c r="O37" s="11" t="n">
+        <v>88</v>
+      </c>
+      <c r="P37" s="11" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Coca-Cola remains a high-quality consumer defensive franchise built on an asset-light concentrate-and-brands model with an unmatched global bottler network. The financial profile is unchanged from the prior analysis: ~60-63% gross margins, low-to-mid 30% operating margins in normal quarters, ~30% net margins, ROIC ~21%, and ROE ~41%. Q1 2026 confirmed healthy momentum with ~12% YoY revenue growth to $12.47B and ~18% EPS growth, while continued deleveraging (D/E down to 1.30x from 1.87x a year prior) improves financial flexibility. The stock at $82.63 sits ~3.5% below its 52-week high ($85.68) and has declined modestly since the prior writeup ($84.05), trading at ~26x trailing and ~24x forward earnings. Recent news is dominated by a Marriott global beverage partnership and competitive read-throughs from PepsiCo's Q2 results, rather than new fundamental data. The valuation debate is unchanged: business quality is not in question, but the multiple embeds fairly aggressive growth expectations against a low-to-mid single-digit organic growth reality. The core question remains margin of safety at a full price rather than any deterioration in the franchise.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Little has materially changed since the July 7 analysis three days ago. The most notable new item is a global beverage partnership with Marriott, which (if it is genuinely exclusive across Marriott's hospitality footprint) modestly expands institutional distribution and locks in recurring on-premise demand across KO's broader portfolio—incrementally positive but not thesis-altering in magnitude. The Walmart retail price-cut narrative that dominated the prior analysis has receded from the current news flow, replaced by PepsiCo-focused coverage: Pepsi reported a Q2 earnings beat driven by volume gains and international strength, alongside a ~2% decline in its food (snacks) sales. This is a two-sided read for KO—healthy beverage demand internationally supports the category, but Pepsi's volume strength and softening consumer spending in North America hint at both competitive pressure and potential demand softness. The stock has drifted down ~1.7% since the prior writeup, which is noise. On fundamentals, no new quarter has been reported; the Q4 2025 margin dip and Q1 2026 rebound remain the key data points. Net: no material change to the thesis—this is a maintenance update.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Coca-Cola owns one of the world's most valuable brand portfolios paired with a global distribution moat that is effectively impossible to replicate. The concentrate model generates exceptional and durable economics—~60% gross margins, ~30% net margins, ROIC north of 20%—enabling high-return capital compounding while funding a reliable, growing dividend. Deleveraging continues (LT debt down to $39.1B, D/E to 1.30x), improving flexibility and reducing rate sensitivity. Q1 2026's double-digit revenue and ~18% EPS growth show the franchise still has organic pricing/mix power and international runway, with optionality in still beverages (fairlife, BODYARMOR, Costa, smartwater, Powerade). The Marriott partnership illustrates KO's ability to win large institutional channels that entrench distribution. The stock's low beta (~0.35) offers portfolio ballast, and Pepsi's international volume strength confirms the beverage category itself is healthy, not in secular decline. For income-oriented, risk-averse capital, KO is a rare combination of defensiveness, quality, and dependable cash return.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>The central issue remains valuation versus growth: ~24x forward earnings and a PEG above 4 for a business whose realistic long-term organic growth is low-to-mid single digits leaves thin margin of safety and real risk of multiple compression if growth or margins disappoint. The stock trades near its 52-week high, so much good news appears priced in. PepsiCo's report is a warning shot—softening North American consumer spending could pressure KO volumes and pricing, and Pepsi's volume gains hint at intensifying competition. Structurally, sugary sparkling drinks face persistent health-and-wellness headwinds and regulatory/sugar-tax risk that cap flagship volume growth. Debt remains substantial in absolute terms (~$44B total), and this is a currency-exposed, internationally weighted business subject to FX swings. The Q4 2025 margin drop (operating 24.2%, net 19.2%), while it rebounded, is a reminder quarterly results can be lumpy and the cause is not fully explained in the data. If retailer pricing pressure re-emerges (as the prior Walmart narrative suggested), realized pricing could erode.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Financial health is strong and unchanged. Revenue is high-quality, recurring, and globally diversified, with margins stable in normal quarters (gross ~60-63%, operating ~32-35%, net ~30%); Q4 2025 was the notable exception (operating 24.2%, net 19.2%) that fully rebounded to 35.1%/31.5% in Q1 2026, supporting the view it was seasonal or contained one-off charges. Cash generation is robust but seasonal—Q2 and Q3 2025 produced FCF of $3.4B and $4.6B, while Q1 quarters are weak on working capital (Q1 2025 OCF was -$5.2B; Q1 2026 a softer $2.0B OCF, $1.76B FCF). The balance sheet is solid: total debt ~$43.9B against ~$33.6B equity (D/E 1.30x and trending down favorably), interest coverage ~11x, and improving liquidity (current ratio 1.36, quick 1.15). Returns on capital are excellent (ROIC ~21%, ROE ~41%, ROA ~13%). Capex is consistently low ($266M-$882M/quarter), consistent with the asset-light model. Share count is stable (~4.3B), so no dilution concern; capital allocation prioritizes dividends (~2.6% yield, well covered). This is the profile of a durable, cash-generative compounder with manageable leverage.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Overvalued</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>At ~26x trailing and ~24x forward earnings, ~7.9x EV/revenue, ~23x EV/EBITDA, and ~10.6x book, KO trades at a premium sitting toward the upper end of what a mature low-to-mid single-digit organic grower warrants, and within ~3.5% of its 52-week high. A premium multiple is justified by the franchise's ~60% gross margins, 20%+ ROIC, and defensive stability—so a naive 'P/E is high' dismissal is inappropriate. However, the PEG of ~4.3 signals the price embeds aggressive growth expectations the underlying volume/pricing trajectory may struggle to sustain, particularly with PepsiCo's report flagging North American consumer softness. The forward multiple is not extreme by KO's own historical band, but with the stock near a valuation high and competitive/demand questions surfacing, the risk/reward skews toward compression rather than expansion. I maintain Overvalued, but this is a modest overvaluation of a high-quality asset near the Fairly Valued boundary—not a broken thesis. The ~1.7% pullback since the prior analysis does not change the rating.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Coca-Cola's moat is among the widest in consumer staples—an iconic global brand portfolio, unrivaled distribution scale via its bottler network, and deep retailer/shelf-space relationships. Pricing power has historically been strong, evidenced by consistently ~60% gross and ~30% net margins across cycles. The Marriott global partnership reinforces the company's ability to lock up large institutional/on-premise channels, extending distribution advantages that competitors cannot easily match. PepsiCo's international volume strength is a reminder that the category is competitive and that Pepsi is a formidable, well-resourced rival, but it also confirms robust category demand rather than share collapse for KO. Consumer switching costs are individually low but brand habit and loyalty are powerful in aggregate, and portfolio breadth (sparkling, water, sports, coffee, tea, juice, dairy, plant-based) diversifies the moat beyond core cola. The principal threats remain PepsiCo, private label/regional players, and the secular shift toward healthier options, which KO is actively addressing via still-beverage acquisitions and reformulation. On balance, the moat is intact and best-in-class.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Over 3-5 years, KO's growth drivers are pricing/mix optimization, emerging-market volume expansion, and continued diversification into faster-growing still beverages (water, sports, coffee, dairy), supplemented by institutional channel wins like the Marriott deal. These support durable low-to-mid single-digit organic revenue growth and, with disciplined margins and stable capital allocation, high-single-digit EPS growth. Headwinds are unchanged: secular health-and-wellness pressure on sugary sparkling drinks, potential sugar taxes/regulation, currency volatility for an internationally weighted business, and retailer-driven pricing/promotional pressure in concentrated channels. PepsiCo's flag on softening North American consumer spending adds near-term demand uncertainty. Deleveraging enhances flexibility, and defensive demand provides recession downside protection. The net picture is a stable, moderate-growth compounder—unlikely to deliver explosive growth but well-positioned to grow steadily with limited existential risk, contingent on continued portfolio reallocation toward healthier and still-beverage categories.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Coca-Cola is a best-in-class defensive compounder with an exceptional moat, ~60% gross margins, ~30% net margins, ~21% ROIC, improving leverage, and strong recurring cash generation—reconfirmed by solid Q1 2026 results and now incrementally supported by the Marriott institutional partnership. Business quality is not the issue; price is. The stock trades near its 52-week high at ~24x forward earnings with a PEG above 4, leaving thin margin of safety for a business whose realistic long-term growth is low-to-mid single digits, and PepsiCo's report raises fresh questions about North American consumer softness and competitive intensity. Nothing material has changed since the prior analysis to alter the posture: admire the franchise, but new capital deployed at current levels faces asymmetric downside from potential multiple compression rather than upside from multiple expansion. Existing long-term holders with low cost basis have little reason to sell a durable, cash-generative asset. Fundamentals support a hold / quality-at-a-full-price stance rather than a fresh buy.</t>
+        </is>
+      </c>
+      <c r="M38" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Confidence is elevated by the clarity and consistency of the financial data—stable high margins, strong ROIC, improving leverage, and a predictable, durable business model. It is tempered by the lack of full-year historical multiple ranges to precisely benchmark today's valuation, the unexplained Q4 2025 margin anomaly, the absence of peer financials, and the ambiguity of the current news flow: the PepsiCo read-through is genuinely two-sided (healthy international category demand vs. North American consumer softness and competitive pressure), and the Marriott deal's financial magnitude and exclusivity terms are not quantified. The valuation call carries the most uncertainty since it sits near the Fairly Valued/Overvalued boundary. Confidence is unchanged from the prior analysis because no new quarter or material fundamental data has arrived.</t>
+        </is>
+      </c>
+      <c r="O38" s="11" t="n">
+        <v>88</v>
+      </c>
+      <c r="P38" s="11" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Procter &amp; Gamble remains a large-cap consumer staples franchise with category-leading brands across fabric/home care, baby/feminine/family care, grooming, health, and beauty. The financial profile is unchanged from the prior analysis and continues to reflect a durable, high-quality business: gross margins around 49-51%, operating margins in the low-to-mid 20s, net margins ~18-21%, ROIC ~21-22%, and interest coverage above 25x. Free cash flow remains recurring at roughly $3-4B per quarter, funding a reliable and growing dividend (yield ~2.87%). The most recent quarter (Q1 2026) showed ~7.4% YoY revenue growth and ~5.8% YoY EPS growth, with a sequential revenue decline (~4.4%) and a modest sequential margin dip (gross margin ~49.5% vs ~51% prior quarter). Since the last writeup, the stock has drifted lower (from ~$151 to $146.85), now sitting near the low end of its 52-week range ($137.62-$167.25). The forward P/E has moved to ~20.8x from ~21.4x, incrementally improving the entry point. The dominant new theme in the evidence is a competitor development in tissue/personal care (Kimberly-Clark's Arbex spinoff backed by Suzano). Overall this remains a defensive compounder priced close to fair value, with the recent price weakness marginally improving the risk/reward for long-term holders.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Little of fundamental substance has changed since the July 7 analysis. The most notable financial shift is the continued modest decline in share price to $146.85 (from ~$151), pushing the stock toward its 52-week low and nudging the forward multiple down to ~20.8x — a marginally more attractive entry point but not a material change to the thesis. The one genuinely new competitive datapoint is the rebranding/spinoff of Kimberly-Clark's international tissue unit as Arbex, backed by pulp producer Suzano, explicitly targeting global share gains in tissue and personal care — categories where PG's Bounty, Charmin, and Puffs compete. This signals potential intensification of competition and vertical integration (Suzano's pulp backing could pressure input-cost economics) in a specific product line, though it is not yet quantifiable in PG's financials. The remaining news flow is generic retirement/dividend-income commentary and routine single-day price-move coverage that carries no fundamental significance. No change in strategy, capital structure, margin trajectory, or capital allocation is evident. In short: no material fundamental change; the developments are a slightly better valuation entry and one credible new competitive threat in tissue.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PG's core strength is the durability and profitability of its franchise — gross margins near 50% and ROIC consistently above 20% demonstrate pricing power and efficient capital deployment that few consumer businesses match. Its portfolio holds leading positions in daily-consumption, low-ticket categories with habitual repeat purchase, producing demand that is largely insensitive to economic cycles (beta 0.38 confirms defensiveness). Investment-led innovation rather than pure cost-cutting supports steady low-single-digit organic volume growth plus pricing, compounding at high returns on capital. Recurring free cash flow of $3-4B per quarter funds a dependable, growing dividend plus buybacks, delivering mid-single-digit-plus total returns with low volatility. The recent pullback to near the 52-week low modestly improves the entry point and the margin of safety for patient capital. In uncertain macro conditions, this defensive quality profile can outperform on a risk-adjusted basis over 3-5 years.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>The thesis is primarily valuation- and growth-constrained: at ~22x trailing and ~21x forward earnings for a business growing high-single-digits at best (and structurally mid-single-digits over time), the multiple leaves thin room for error and could compress if growth stalls or if rate dynamics make bond-like equities less attractive. Organic growth is structurally slow — PG competes in mature, penetrated categories where volume gains are hard-won and increasingly reliant on price, which faces limits as consumers trade down to private label. The new Arbex/Suzano competitive push in tissue is a concrete reminder that well-capitalized, vertically integrated challengers can pressure share and margins in specific categories. The sequential margin dip in Q1 2026 (gross margin ~49.5% vs ~51%) bears watching for signs of input-cost, FX, or promotional pressure. The business offers little optionality for upside surprise — the thesis is steady compounding, so any secular acceleration in downtrading or channel disruption (e-commerce, DTC challengers) directly threatens the core. The current ratio below 1.0 (~0.73), while structurally normal, reflects reliance on continuous cash generation.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Financial health is strong and consistent. Revenue quality is high — recurring branded-staples consumption produces a predictable top line, with Q1 2026 revenue of ~$21.2B up ~7.4% YoY. Margins are elevated and stable: gross margin ~49-51%, operating margin low-to-mid 20s, net margin ~18-21%, though the latest quarter shows a mild sequential softening (gross margin ~49.5%, operating margin ~21.6%) worth monitoring. Cash generation is a standout: quarterly operating cash flow ~$4-5B and free cash flow ~$3B in the latest quarter, with FCF margins in the mid-teens. The balance sheet is conservative — total debt ~$37B against ~$54.5B equity (D/E ~0.68), interest coverage &gt;25x, and cash of ~$12.3B. Capital efficiency is excellent: ROE ~30%, ROA ~13%, ROIC ~21.8% (ROE flattered somewhat by buyback-driven equity reduction). Capital allocation remains shareholder-friendly, with financing outflows reflecting dividends and repurchases and no signs of dilution; the ~2.87% dividend is well-covered by FCF. Mild flags are the sub-1.0 current ratio (structurally normal) and slowly rising total debt.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Fairly Valued</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>PG trades at ~21.7x trailing and ~20.8x forward earnings, EV/EBITDA ~14.7x, and price-to-sales ~3.9x. The PEG of ~4.2 looks rich in isolation, but that metric unfairly penalizes low-growth, high-quality compounders and overstates the concern. The more relevant frame is PG's own historical range: a low-to-mid-20s P/E is broadly consistent with where this high-ROIC, low-beta staple has traded through recent cycles, so the current multiple is neither a clear discount nor an obvious excess. Since the prior analysis, the stock has fallen to $146.85 — near the 52-week low ($137.62) and well below the high ($167.25) — trimming the forward multiple to ~20.8x and modestly improving the margin of safety. Given durable ~20%+ ROIC, reliable FCF, and a well-covered dividend, the premium is justified by quality, but the ~21x forward multiple still prices in continued execution. On balance, Fairly Valued — reasonable for long-term holders and slightly more attractive after the pullback, but not yet a compelling bargain demanding aggressive new capital.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>PG possesses one of the widest moats in consumer staples, built on scale, brand equity, distribution reach, and R&amp;D/marketing spend that smaller rivals cannot match. Its brands hold leading or top-tier share in categories defined by habitual repeat purchase and modest ticket size, creating soft switching costs rooted in brand trust and habit. Sustained ~50% gross margins and 20%+ ROIC are direct evidence of durable pricing power. The new Arbex/Suzano development is a reminder that the moat is not impervious at the category level: a well-funded, vertically integrated tissue competitor could pressure PG's Bounty/Charmin/Puffs share and economics, particularly given Suzano's pulp cost advantage. That said, this is a threat in one product line rather than a challenge to the diversified portfolio's overall moat. Ongoing risks include private-label encroachment during downtrading, retailer bargaining power (mass merchandisers, club stores), and channel shifts toward e-commerce/DTC where challenger brands gain footholds cheaply. Net, the moat remains wide and durable but faces gradual, category-specific erosion pressures.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Over five years, PG's growth is likely steady but unspectacular — low-single-digit organic volume growth supplemented by pricing and mix, aggregating to mid-single-digit revenue growth in favorable conditions. Tailwinds include emerging-market penetration, premiumization in beauty and grooming, and a consistent innovation cadence. Headwinds include developed-market category maturity, persistent private-label competition, FX volatility from global exposure, the ceiling on price-led growth as affordability pressures rise, and now intensifying competition in tissue from vertically integrated players like Arbex/Suzano. Margin expansion opportunities exist through productivity and mix but are incremental, and the recent sequential margin softening warrants monitoring. The dividend-growth and buyback engine should continue converting modest operating growth into respectable per-share returns. The trajectory is that of a resilient compounder rather than a high-growth story; the principal risk to the outlook is a structural acceleration of downtrading or channel/competitive disruption rather than any near-term operational deterioration.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>PG is a best-in-class defensive compounder: a wide-moat portfolio of daily-consumption brands generating ~50% gross margins, ~22% ROIC, and abundant recurring free cash flow that funds a reliable, growing dividend and buybacks. The financials confirm consistency and balance-sheet strength (D/E ~0.68, interest coverage &gt;25x). The case is not about outsized growth — organic growth is structurally modest — but about durable, low-volatility total return (dividend plus buybacks plus mid-single-digit earnings growth) with strong downside protection (beta 0.38). Since the last analysis, the stock's drift to near its 52-week low has trimmed the forward multiple to ~20.8x, marginally improving the entry point without changing the fundamental picture. The one new watch item is intensifying tissue-category competition (Arbex/Suzano), which is worth tracking but not yet thesis-altering. This suits long-term, income-oriented capital seeking stability and compounding rather than capital-appreciation upside. Key risks — multiple compression and gradual private-label/competitive share erosion — are real but slow-moving. A hold/accumulate-on-weakness stance remains warranted, with the current pullback making incremental accumulation more reasonable.</t>
+        </is>
+      </c>
+      <c r="M39" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Confidence is elevated by the clarity and consistency of the financial evidence: stable high margins, recurring FCF, high ROIC, a conservative balance sheet, and a well-covered dividend all point to a predictable, durable business, reinforced by the low beta. Confidence is tempered by the absence of full trailing-twelve-month organic-growth detail (Q4 2024 is NaN and YoY growth is available for only one quarter), no peer financials to benchmark competitive dynamics, and largely generic news flow. The new Arbex/Suzano competitive item introduces a modest, unquantified risk to the tissue category. Valuation judgment carries moderate uncertainty because the historical multiple range is inferred rather than provided. Net, nothing in the latest evidence materially changed the thesis, so confidence remains steady.</t>
+        </is>
+      </c>
+      <c r="O39" s="11" t="n">
+        <v>87</v>
+      </c>
+      <c r="P39" s="11" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>UnitedHealth is the largest integrated US managed-care and health-services company, combining insurance (UnitedHealthcare) with health services (Optum Health, Insight, Rx). The trailing data show a severe 2025 earnings shock — operating margin collapsed from 8.3% (Q1 2025) to 0.3% (Q4 2025) with net income falling to essentially zero ($10M) in December — followed by a sharp Q1 2026 rebound to 8.0% operating margin, $6.28B net income, and $8.1B free cash flow. This pattern is most consistent with a transitory medical-cost/MLR spike and likely reserve strengthening rather than structural revenue loss, since revenue held flat around $110-113B per quarter throughout. The stock now trades at $431.68, at its 52-week high ($434.30) and roughly double the $234.60 low, so the market has largely priced in a normalization of earnings. Forward P/E of ~20.6x versus a distorted trailing P/E of 32x reflects that trough earnings understate normalized earning power. The central unresolved question remains whether the 2025 cost spike is behind them (as one quarter of Q1 2026 suggests) or a signal of durable government-plan cost-trend pressure. Nothing in this update materially changes that debate; it largely confirms the recovery narrative already established.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Little has materially changed since the July 7 analysis three days ago — this is essentially a continuation of the same recovery story with slightly more positive framing in the news flow. (1) The stock has ticked up modestly (from $425.93 to $431.68) and set a fresh 52-week high, but this is price action, not a fundamental change. (2) News now references raised guidance ahead of Q2, which — if confirmed by actual results — would be the first management-level corroboration that the Q1 2026 rebound is sustainable rather than a one-quarter artifact; but guidance is not yet reported financials, so I treat it as an unverified signal. (3) A $1.5B AI investment aimed at operational efficiency and new revenue streams is disclosed; this is incremental and directionally supportive of margin discipline but not thesis-changing at this scale relative to a &gt;$450B revenue base. (4) Industry commentary continues to point to managed-care insurers repricing to be 'properly paid' for underwritten risk, which supports the transitory-cost/margin-recovery reading. No new financial data has arrived since the prior writeup, so the core financial picture is unchanged.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>UNH is the scale leader in US managed care with a vertically integrated Optum model that few can replicate, providing structural cost, data, and cross-segment pricing advantages. The Q1 2026 snapback to 8% operating margin and $8.1B quarterly FCF (7.3% FCF margin) demonstrates intact earnings power once cost trends normalize; if 2025 was a transitory MLR/reserve event, current normalized earnings are understated and the ~20.6x forward P/E is reasonable rather than rich. Reported guidance raises and industry-wide repricing to recover underwritten risk suggest the sector is regaining pricing power, directly benefiting the scale leader. Optum Health, Insight, and Rx add diversified, recurring, higher-return, less MLR-exposed revenue. The $1.5B AI push, if it delivers efficiency, supports the margin-discipline pivot. Beta of 0.63 and a 2.2% dividend plus a stable-to-declining share count provide defensive total-return characteristics, and multi-decade Medicare demographic tailwinds underpin long-run enrollment growth.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>The 2025 margin collapse is a genuine warning that the model can see a single quarter's earnings wiped out by medical-cost trends, whether from Medicare Advantage utilization, Medicaid redeterminations concentrating sicker enrollees, or coding/reimbursement pressure. Revenue is flat (+2% YoY in Q1 2026), signaling a growth plateau for a stock priced for continued compounding and sitting at its 52-week high. Government reimbursement risk is structural and political — MA rate pressure and DOJ/regulatory scrutiny of the integrated payer-provider model could compress margins durably. ROIC ~10% and ROE ~12% are solid but not exceptional, and the trailing 32x P/E reflects trough earnings, not cheapness. Current ratio below 0.8 and D/E ~0.8 with interest coverage ~4.7x are normal for the model but offer limited cushion if cost trends re-accelerate. Critically, the market has already priced in the recovery: with the stock near all-time highs, a second cost-trend disappointment would carry material downside and the entry point offers thin margin of safety.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Revenue is high-quality and recurring but stagnant at ~$110-113B/quarter (+2% YoY in Q1 2026). The defining feature remains extreme 2025 margin volatility: gross margin fell 21.7%→16.3% and operating margin 8.3%→0.3% across four quarters before rebounding to 22.7%/8.0% in Q1 2026 — a signature of medical-cost inflation and likely reserve strengthening rather than revenue erosion. Cash generation is robust in normal periods (Q1 2026: $8.9B operating cash flow, $8.1B FCF) but cratered to $160M FCF alongside the Q4 2025 earnings trough, underscoring cyclicality. Balance sheet: total debt ~$78B against ~$98B equity (D/E ~0.80, improving slightly QoQ), interest coverage ~4.7x — adequate, not fortress-like. Current ratio ~0.80 is typical for an insurer carrying float. Capital allocation includes a 2.2% dividend and a roughly stable-to-declining share count (~908M shares) with no meaningful dilution. Returns on a recovering basis: ROE ~12%, ROIC ~10% — decent for the scale but depressed by the 2025 shock. Overall financially durable, with demonstrated sensitivity to cost trends.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Fairly Valued</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>The trailing P/E of 32x is distorted upward by the near-zero Q4 2025 earnings and overstates expensiveness. The ~20.6x forward P/E is the more informative figure and, for a scale leader with demonstrated normalized ~8% operating margins, sits within a reasonable range but is not clearly cheap given flat revenue and unresolved government-reimbursement risk. EV/EBITDA of ~20.8x is elevated for a business at a growth plateau, while price-to-sales of 0.87x and EV/revenue of 0.99x are low in absolute terms but appropriate for a low-margin, insurance-heavy revenue base. With the stock at its 52-week high after roughly doubling off the $234 trough, the market has largely priced in earnings normalization. If Q1 2026 profitability and the raised guidance prove sustainable, modest upside remains; if cost trends re-emerge, downside is material. Risk/reward is roughly balanced — Fairly Valued.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>UNH holds one of the strongest moats in US healthcare: unmatched medical-membership scale combined with Optum's vertically integrated care delivery, PBM, and health-data analytics. This integration produces cost advantages, data network effects, and cross-segment pricing leverage that standalone insurers and PBMs cannot easily match, while employer and government contract switching costs plus broad provider networks reinforce stickiness. The $1.5B AI investment, if effective, could further widen the operational-efficiency gap. However, the moat is not absolute — pricing power is capped by government reimbursement schedules (Medicare/Medicaid), and vertically integrated competitors like CVS/Aetna and government-program-focused Centene compete directly. The 2025 cost shock proved scale does not fully insulate the company from industry-wide medical-trend pressures, and regulatory/antitrust scrutiny is a persistent structural threat to the integrated payer-provider model.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Aging-population-driven Medicare enrollment growth remains the primary multi-year driver, complemented by Optum's expansion into higher-margin, less capital-intensive health services and potential AI-driven efficiency gains. The strategic pivot toward margin discipline over volume should improve earnings quality but implies slower top-line growth than the company's historical norm — consistent with the current ~2% YoY revenue trajectory. Key five-year risks: (1) durable MA rate and cost-trend pressure; (2) Medicaid margin compression amid redeterminations and utilization/fraud scrutiny; (3) intensifying vertically integrated competition; and (4) regulatory/antitrust risk to the integrated model. The 2025 episode demonstrated the earnings base is more fragile than historically assumed. Net assessment: a mature, defensive compounder with real demographic tailwinds but capped upside from cost-trend and regulatory headwinds — no longer a high-double-digit grower.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>UNH is a dominant, vertically integrated managed-care leader whose earnings suffered a severe, likely-transitory medical-cost shock through 2025 before rebounding sharply in Q1 2026. The core debate — transitory versus structural cost pressure — is unchanged from the prior analysis; Q1 2026's return to 8% operating margin and $8.1B FCF plus the newly referenced guidance raise support the transitory view, but this remains one reported quarter plus an unverified guidance signal against a backdrop of flat revenue and demonstrated margin fragility. At ~20.6x forward earnings and a 52-week high, the market has largely priced in normalization, leaving balanced risk/reward and limited margin of safety. This is a defensible hold for investors comfortable with the moat and demographic tailwinds, but adding conviction requires seeing the medical loss ratio and margin trajectory hold up over the next two to three actual reported quarters — with Q2 2026 results (against which guidance can be tested) as the next key checkpoint.</t>
+        </is>
+      </c>
+      <c r="M40" s="11" t="n">
+        <v>59</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Confidence is essentially unchanged from the prior 58 — marginally higher because the raised-guidance news and continued industry repricing commentary lend modest additional support to the transitory-cost interpretation, but no new hard financials have arrived to verify it. The extreme, incompletely explained 2025 margin volatility (a single-quarter collapse to near-zero net income) remains the dominant uncertainty; its precise root cause (MLR, reserves, or structural trend) is not fully clarified by the data. The Q1 2026 rebound is only one quarter. Missing data (no revenue segment detail, no full YoY history, NaN Q4 2024 figures, no peer financials for LLY) limits cross-referencing. Confidence is supported by a clear balance sheet, strong normalized cash generation, and a durable scale/integration moat well-grounded in the data.</t>
+        </is>
+      </c>
+      <c r="O40" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="P40" s="11" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Caterpillar remains a globally diversified heavy-equipment manufacturer (Construction, Resource/mining, Energy &amp; Transportation, and Financial Products) operating at what appears to be a strong point in its cycle. The trailing six quarters show revenue rising from ~$14.2B in Q1 2025 to a $17-19B range, with net income growing steadily to $2.55B in Q1 2026 and diluted EPS of $5.47, up ~30% YoY. Operating margins have generally held in the 17-18% band (with a notable Q4 2025 dip to ~13.9% that recovered to ~17.7% in Q1 2026), while ROIC sits around 17% and ROE is elevated at 42-51% partly due to a leveraged, low-equity capital structure. Free cash flow is healthy but lumpy, swinging with working capital and heavy capital returns. The balance sheet carries debt/equity of ~2.3x, much of it in the captive Financial Products arm, with interest coverage near 24x indicating comfortable serviceability. Recent news continues to revolve around the AI/data-center power-demand tailwind for Energy &amp; Transportation, a mining-tech acquisition (Skycatch), and an 8% dividend hike alongside buybacks. At ~47x trailing and ~31x forward earnings near the upper end of a wide 52-week range ($402-$1,073), the stock prices in substantial optimism against likely peak-cycle earnings. Nothing in the past few days materially alters the prior thesis.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Little has materially changed since the July 7 analysis. The one genuine incremental fact is confirmation of an 8% dividend increase paired with ongoing buybacks, consistent with the large financing outflows seen in the data (~$5.95B in Q1 2026) and reinforcing a shareholder-friendly capital-return posture and management confidence. The Skycatch mining-tech acquisition remains the same event flagged previously; news now frames it more constructively as strengthening high-margin autonomous/analytics capabilities, but there is no new financial evidence to change my 'sound but unproven' view. The remaining news flow is largely noise: single-day price dips, restatements of the AI power-demand thesis, and unrelated headlines about memory chips, Nvidia and Tesla. Several items also flag valuation/momentum fatigue (second weekly loss, 'fully priced' framing), which is sentiment-driven and directionally consistent with my existing overvaluation call rather than a new fundamental development. Net: no material change to fundamentals; the valuation-versus-quality tension from the prior writeup stands.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>CAT is the scale leader in construction and mining equipment, with a global dealer/service network and a large installed base that generate high-margin, recurring aftermarket parts and service revenue that stabilizes earnings across equipment cycles. The Energy &amp; Transportation segment is a structural beneficiary of AI/data-center power demand, grid electrification, and reshoring-driven industrial construction, potentially sustaining elevated demand for generator sets, backup power, and turbines for years. Margins have proven resilient (operating ~17-18%, ROIC ~17%), demonstrating pricing discipline and operating leverage. Capital allocation is strong: an 8% dividend hike plus sizable buybacks shrink the share count and compound per-share value. The Skycatch acquisition, if integrated well, deepens the moat in autonomous/analytics fleet management where switching costs are high. If the current strength reflects a durable secular uptrend (infrastructure, energy-transition metals mining, data centers) rather than a classic cyclical peak, the premium multiple could be validated by a longer-than-typical earnings growth runway.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>The core risk is that current financials look like a cyclical peak: record EPS, ~22% YoY revenue growth, and high margins are precisely the conditions that precede mean reversion, and paying ~47x trailing / ~31x forward on peak earnings offers little margin of safety. A downturn in construction or mining capex could compress earnings and the multiple simultaneously. The Q4 2025 operating-margin drop to ~13.9% shows margins are not perfectly stable, and gross margin fell as low as ~28.6% that quarter. The AI/data-center power tailwind, while real, is exposed to a spending pullback, and recent momentum loss and 'fully priced' commentary signal how quickly sentiment can turn. Financial leverage (debt/equity ~2.3x) sits atop operating leverage, amplifying downside in a recession, and a beta of 1.57 implies the stock likely falls harder than the market. The elevated ROE flatters returns via the leveraged, thin-equity structure. Absent a new margin of safety, the risk/reward at these levels is unattractive.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Financial health is solid but cyclical. Revenue is diversified across four segments and has trended up over the trailing six quarters, though Q1 2026 showed a normal seasonal QoQ decline (-9%) while still up ~22% YoY. Margins are healthy for the industry: gross margin ~29-33% (dipping to ~28.6% in Q4 2025), operating margin generally 17-18% (with the Q4 2025 outlier at ~13.9%), and net margin ~13-15%. Cash generation is strong but lumpy, with operating cash flow ranging from ~$1.3B to ~$3.7B and FCF swinging from ~$0.37B to ~$2.67B depending on working capital and capex (~$0.9-1.3B/quarter). Cash built to ~$10B by Q4 2025 then fell to ~$4.1B in Q1 2026 alongside a ~$5.95B financing outflow, reflecting heavy buybacks and dividends. Debt/equity is ~2.3x and total debt ~$43B, inflated by the captive Financial Products arm; interest coverage near 24x confirms comfortable serviceability. ROIC (~17%) is a cleaner efficiency measure than the leveraged ROE (~42-51%). Capital allocation clearly favors shareholder returns—an 8% dividend hike plus buybacks—while the dividend yield remains modest at ~0.69%. Leverage is the main caveat in a downturn.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Overvalued</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>At ~47x trailing and ~31x forward earnings, EV/EBITDA of ~32x, and price/sales of ~6x, CAT trades well above the mid-teens P/E and single-digit EV/EBITDA ranges that have historically characterized much of its cycle. The central concern is that these premium multiples are applied to what looks like peak-cycle earnings (record EPS, ~22% YoY growth, elevated margins). For a cyclical industrial, paying a premium on peak earnings is the classic value trap; normalized earnings would imply a materially higher effective multiple. A PEG of ~2.2 signals growth is not cheaply priced. The AI power-demand secular story and genuine business quality (ROIC ~17%, strong FCF, wide moat) justify some premium above historical norms, but not the full extent of the current re-rating given the peak-cycle backdrop. Trading near the upper part of a wide 52-week range ($402-$1,073) underscores how much optimism is embedded, leaving little margin of safety.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>CAT has a genuine, durable moat: (1) an unmatched global dealer and service network that is very difficult to replicate; (2) a large installed base generating high-margin recurring aftermarket parts/service revenue and real switching costs (operators standardize on CAT for parts availability, uptime, and resale value); (3) brand strength and scale economies in manufacturing and R&amp;D; and (4) growing technology differentiation in autonomous mining, fleet analytics, and telematics, deepened by the Skycatch acquisition. It holds leading share in construction and mining equipment and has demonstrated pricing power through sustained high margins across volume fluctuations. The industry structure is oligopolistic with high entry barriers (capital intensity, dealer networks, emissions/regulatory expertise). Competitive threats include Komatsu and Deere in equipment and GE Vernova, Cummins, and Honeywell-adjacent players in power/energy. This is a wide but not impregnable moat; cyclicality, not competition, is the dominant risk.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Multi-year growth drivers include AI/data-center power demand (generators, backup power, turbines), grid electrification, infrastructure spending, reshoring of manufacturing, and mining capex tied to energy-transition metals plus autonomous mining technology—secular tailwinds layered on the traditional equipment replacement cycle. The primary long-term risk is the cyclicality of end markets: construction and mining capex can contract sharply in a recession or commodity downturn, and current results appear near a cyclical high. A pullback in AI infrastructure spending would remove a key growth pillar and pressure the part of the story supporting the premium multiple. Over five years, expect strong but volatile earnings, aftermarket-driven margin resilience, and continued shareholder returns, but with meaningful risk of an earnings and multiple correction if the cycle rolls over. The moat and diversification should allow CAT to compound through cycles, though entry point matters greatly given cyclicality and leverage.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>CAT is a high-quality, wide-moat cyclical industrial operating near peak performance: record EPS, ~17% ROIC, strong diversified cash flows, disciplined pricing, an 8% dividend hike plus buybacks, and legitimate secular tailwinds from AI-driven power demand and mining technology. Business quality is not the question—price and timing are. The market applies a premium multiple (~31x forward, ~32x EV/EBITDA) to what look like peak-cycle earnings, leaving little margin of safety and creating double-risk of earnings mean reversion plus multiple compression in any downturn, amplified by ~2.3x leverage and a 1.57 beta. The recent dividend increase and Skycatch deal are supportive but do not change the thesis; the momentum fatigue and 'fully priced' commentary in the news are consistent with the overvaluation view. I want to own this franchise over a full cycle, but not at this valuation near cyclical and price highs. The prudent stance remains to admire the business while waiting for a more attractive entry during a cyclical pullback.</t>
+        </is>
+      </c>
+      <c r="M41" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Confidence is supported by six quarters of consistent, high-quality financial data showing clear margin, cash flow, and return-on-capital trends, plus a well-understood business model and durable moat. It is reduced by the absence of full-year historical multiples to precisely benchmark current valuation against CAT's own long-term range, lack of segment-level detail to gauge how much earnings depend on the potentially fragile AI/data-center tailwind, missing Q4 2024 data, and the inherent difficulty of timing a cyclical near what appears to be a peak. The valuation conclusion is fairly firm; the precise magnitude of downside is less certain. Recent news added confirmation (dividend hike) but no thesis-altering information.</t>
+        </is>
+      </c>
+      <c r="O41" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="P41" s="11" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ExxonMobil remains a financially fortified integrated oil and gas major in a cyclical earnings trough. The financial data extends through Q1 2026 and shows continued strain: free cash flow fell to $2.2B in Q1 2026 (from $7.1B a year earlier) against roughly $6.5B of quarterly capex, cash declined to $8.4B, total debt rose to $47.7B, and the current ratio slipped to ~1.04. Note the ratios table now reports no margin/ROE/ROIC figures for any quarter, so the specific profitability trend detail cited in the prior writeup is no longer directly grounded in the provided data and must be treated more cautiously. Debt-to-equity ticked up again to ~0.19, consistent with gradual balance-sheet tightening while the business absorbs weaker cash generation. The stock trades at $137.67, roughly flat versus the prior $139.96, at ~23.2x trailing and ~12.9x forward earnings—the wide gap again implying the market expects an earnings recovery. Recent news centers on Q2 earnings anticipation (with commodity-price tailwinds cited), competitive positioning versus Chevron, and structural energy-transition/China-demand concerns. Fundamentally this remains a commodity-exposed cash cow whose near-term earnings power hinges on price realizations it cannot control. Nothing in the current data set materially alters the prior 'defensive income hold' framing.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Little has materially changed since the July 7 analysis three days ago. The price is essentially flat ($137.67 vs $139.96), the balance-sheet trends (rising debt to $47.7B, falling cash to $8.4B, current ratio ~1.04, D/E ~0.19) are unchanged from the same Q1 2026 data. The main change is presentational rather than fundamental: the current ratios table no longer contains the gross/operating/net margin, ROE, ROIC and interest-coverage figures that the prior writeup relied on, so I can no longer independently verify the '~46% net income decline' and 'margin halving' claims from the provided data alone—I flag this as a data-quality caveat, not a business improvement. On the news side, the notable items are directional signals rather than facts: forthcoming Q2 results are expected to benefit from firmer commodity prices (Hormuz-related supply risk), while Goldman's structurally-weaker-China-demand thesis reinforces the long-term demand headwind. A Bank of America relative preference for Chevron over Exxon is analyst opinion and, per my mandate, I do not weight it. Net: no material fundamental change; this is a maintenance update.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Exxon retains one of the strongest balance sheets among integrated majors—D/E of only ~0.19 and equity of ~$254B—giving it staying power through downcycles and the capacity to keep funding its ~3% dividend and counter-cyclical investment. The current earnings/FCF trough appears largely price-driven rather than volume- or cost-driven; with meaningful operating leverage, a recovery in crude and refining spreads—plausibly amplified by geopolitical supply shocks such as a Strait of Hormuz disruption—could drive a sharp rebound in upstream cash flow. The forward P/E of ~12.9x versus ~23.2x trailing signals the market is pricing exactly this recovery; if Q2 results confirm the commodity tailwind narrative, there is re-rating potential toward the $176 52-week high. Advantaged low-cost assets (Guyana, Permian, expanding deepwater), vertical integration that smooths cyclicality, and low beta (0.16) make it a defensive holding with embedded upside optionality. Lower-carbon bets (CCS, hydrogen, lithium, Proxxima) provide long-dated optionality that is not priced in.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>This is fundamentally a price-taking commodity business with no durable pricing power, and the cash-generation trend is the core concern: FCF of just $2.2B in Q1 2026 against ~$6.5B quarterly capex means the dividend and any buybacks are increasingly funded from a thinning cushion or incremental debt. Total debt has climbed to $47.7B while cash fell to $8.4B and the current ratio slipped to ~1.04—a clear, if gradual, balance-sheet tightening. Operating cash flow dropped to $8.7B in Q1 2026 from $13.0B a year earlier, showing the strain is real and persistent, not a single soft quarter. Structural demand risk is intensifying: a credible view that Chinese oil demand may never fully recover threatens long-run crude prices and terminal value, compounding energy-transition and carbon-policy risk. If the earnings recovery implied by the ~12.9x forward multiple fails to materialize, the stock is not cheap on trailing earnings (~23.2x) or on EV/EBITDA (~11x, toward the high end of major-peer ranges). Heavy long-cycle capex carries execution and commodity-price risk if prices stay soft.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Top-line revenue quality has been stable historically (implied ~$80-83B/quarter in the prior analysis), but the provided ratios table now lacks margin, ROE, and ROIC data, so I cannot independently re-verify the profitability trend this cycle; I rely on the cash-flow statements, which tell a clear deterioration story. Operating cash flow fell to $8.7B in Q1 2026 from $13.0B in Q1 2025, and free cash flow collapsed to $2.2B (fcf margin roughly 2-3%) as capex stayed near $6.5B. Cash declined steadily across six quarters ($17.0B → $8.4B) while total debt rose ($37.6B → $47.7B) and the current ratio slipped from ~1.24 to ~1.04—a coherent picture of a balance sheet absorbing weaker cash generation. That said, absolute leverage remains conservative (D/E ~0.19) and the equity base is large (~$254B), so this is tightening from a fortress starting point, not distress. Financing outflows have moderated, consistent with dividends/buybacks being trimmed to preserve cash. The key sustainability question is FCF-to-dividend coverage if the trough persists—currently thin and worth monitoring.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Fairly Valued</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>At $137.67 the stock trades at ~23.2x trailing and ~12.9x forward earnings, ~2.22x book, ~1.75x sales, and ~11.0x EV/EBITDA. The elevated trailing P/E reflects a cyclical earnings trough rather than premium business quality, so it overstates apparent expensiveness; conversely the ~12.9x forward multiple is only attractive if the embedded earnings recovery arrives. EV/EBITDA near 11x sits toward the higher end of typical integrated-major ranges, arguing against calling it cheap. The ~3% dividend yield is supportive but unexceptional for the sector, and thinning FCF coverage tempers its reliability at the margin. Balancing trough earnings (which counter an 'overvalued' call) against a full EV/EBITDA multiple and weak current cash generation (which counter an 'undervalued' call), the stock is Fairly Valued—priced for a recovery that is plausible but not assured. This is unchanged from the prior assessment, appropriately, given essentially flat price and unchanged underlying data.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Exxon competes in a commodity industry where crude, gas, refined fuels, and petrochemicals are price-taking products with minimal pricing power, structurally capping any moat. Its genuine advantages are scale, vertical integration across upstream/downstream/chemicals that smooths cyclicality, a low-cost advantaged resource base (Guyana, Permian, expanding deepwater), strong operational/technical execution, and a fortress balance sheet enabling counter-cyclical investment. Switching costs for its core commodities are effectively nil; the Exxon/Esso/Mobil brands and the lubricants/specialty franchise offer only modest differentiation. Emerging lower-carbon initiatives (CCS, hydrogen, lithium, Proxxima) represent optionality, not yet durable moats. Relative to Chevron, Exxon's scale and cost-curve position are advantages, but the recent Bank of America relative preference for Chevron (analyst opinion I do not weight) is a reminder that peer positioning is contested. Overall this is a cost/scale advantage within a cyclical commodity, not a structural monopoly.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>The five-year outlook embodies the classic integrated-major tension: near-term cash-generative dominance against long-term demand risk. Growth drivers include advantaged upstream assets, deepwater expansion, chemicals/specialty products, and price-recovery/geopolitical optionality. Headwinds have arguably firmed since the last review: the structural view that Chinese oil demand may never fully recover adds weight to the secular-demand concern, layered atop carbon/regulatory policy risk, political pressure on fuel margins, and capital intensity. The recent FCF and cash-flow deterioration underscores how exposed the franchise is to price cycles. Deregulation could offer near-term cost relief, and low-carbon bets could eventually matter, but they are unproven at scale and do not resolve the terminal-value question around oil demand. Expect continued cyclicality, dividends backed by a strong (if gradually tightening) balance sheet, and modest structural growth constrained by transition risk—a durable but not high-growth franchise.</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>ExxonMobil is a financially fortified integrated major in a cyclical earnings/FCF trough driven by weak commodity price realizations rather than lost volume. The provided cash-flow data confirms the strain—FCF of $2.2B in Q1 2026 against ~$6.5B capex, OCF down to $8.7B from $13.0B a year prior, cash falling and debt rising—while the balance sheet remains conservative in absolute terms (D/E ~0.19). The bull case rests on operating leverage to a price recovery (which the ~12.9x forward multiple implies the market expects) plus dividend durability and geopolitical/deregulation optionality; the bear case rests on the absence of pricing power, thinning dividend coverage, and firming secular-demand headwinds. Valuation is Fairly Valued—not cheap on EV/EBITDA (~11x), not expensive if earnings recover. Since the prior analysis only three days ago, nothing fundamental has changed; the price is flat and the balance-sheet data is identical, with the only notable difference being the disappearance of margin/return ratios from the data, which I flag as a caveat. The appropriate stance remains a defensive, income-oriented hold: suitable for low-beta dividend exposure with recovery optionality, but not a high-conviction growth or deep-value position.</t>
+        </is>
+      </c>
+      <c r="M42" s="11" t="n">
+        <v>58</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Confidence is supported by six quarters of consistent balance-sheet and cash-flow data showing an unambiguous cash-generation deterioration alongside a verifiably strong balance sheet. It is reduced relative to the prior writeup because the current ratios table lacks margin, ROE, ROIC, and interest-coverage figures, so I can no longer independently verify the profitability-trend claims from the data provided—forcing partial reliance on the prior analysis. Confidence is further tempered by the absence of peer financial data for direct benchmarking, no visibility into the forward commodity-price assumptions driving the low forward P/E, and genuinely conflicting news signals (near-term commodity tailwinds and Hormuz optionality versus structural China-demand weakness and transition risk). The central uncertainty remains whether the earnings recovery priced into the forward multiple actually materializes.</t>
+        </is>
+      </c>
+      <c r="O42" s="11" t="n">
+        <v>55</v>
+      </c>
+      <c r="P42" s="11" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>NextEra Energy is a large-cap regulated utility pairing a monopoly Florida distribution business (FPL, ~12 million people served) with the largest renewable/storage development platform in North America (NEER). The financial profile is classic utility: high gross margins (57-64%), heavy capital intensity, substantial leverage, and recurring cash flows, but with more growth optionality than a typical peer. Trailing net income across the last four quarters is roughly $8.2B, supporting a diluted EPS run-rate near $3.90 and the ~22x trailing P/E. Operating cash flow remains robust (~$2.5-4.0B per quarter) but free cash flow is thin to negative because capex is running at record levels and is debt-funded. Total debt has climbed from ~$90B in Q1 2025 to ~$104B by Q1 2026, debt-to-equity sits near 1.9x, and interest coverage is uncomfortably low at ~2-2.4x. The dominant narrative remains AI/data-center-driven electricity demand supporting a multi-year rate-base and generation capex cycle where NEE is unusually well positioned. At $87.23 the stock trades in the upper-middle of its 52-week range ($69.24-$98.75) at a premium to a typical regulated utility, justified only if the renewable/data-center growth optionality plays out. Since the prior analysis three days ago, nothing material has changed in the fundamentals; the price has drifted marginally lower (from ~$88.70 to $87.23).</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Nothing material has changed since the July 7 analysis. The financial data is unchanged (Q1 2026 remains the latest reported quarter), and the only difference in the valuation snapshot is a modest price decline from ~$88.70 to $87.23, which is noise rather than a fundamental shift. The recent news flow is thin and largely non-fundamental: several articles concern peers (Eversource, Vistra, Constellation, Duke) or generic retirement/ETF/AI themes with no NEE-specific content. The recurring substantive theme continues to be AI/data-center power demand as a structural tailwind for utilities including NEE, and one piece flags that NEE's ETF weighting affects passive flows. There is a mildly negative valuation-model note suggesting the stock looks stretched, but per our rules I discount third-party valuation opinions and reach my own conclusion from the data. In short, this is a maintenance update: the balance-sheet leverage build, thin coverage, and negative peak-capex free cash flow described previously remain the defining fundamental features, with no new catalyst to reprice the thesis.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>NextEra owns the best-positioned renewable and storage development pipeline in North America precisely as US electricity demand inflects upward after two decades of flat load growth, driven by data centers, electrification, and reshoring. FPL provides a durable, low-risk regulated earnings base in a constructive Florida jurisdiction with a growing customer count. The dual model recycles regulated cash flow into higher-return renewable development while capturing scale advantages in procurement, interconnection queues, tax-equity financing, and development expertise that smaller players cannot match. If load growth sustains the capex cycle, rate base and earnings can compound at high-single-digit rates for years, with a ~2.86% dividend yield and a long growth track record adding to total return. Low beta (0.67) makes it a defensive way to play the secular electricity-demand theme. Structurally high, stable gross margins and a low-marginal-cost nuclear/wind/solar fleet reinforce a durable cost position versus fossil-exposed peers.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>The balance sheet is the central risk. Total debt has grown to ~$104B, debt-to-equity is ~1.9x, and interest coverage of ~2-2.4x is thin for a capital-intensive utility, leaving little cushion if rates stay elevated or regulators tighten allowed returns. Free cash flow turned negative (-$580M in Q1 2026) as capex peaked at $3.19B, meaning growth is debt- and equity-funded and exposed to financing-cost and refinancing risk. Project economics depend on an accretive spread between borrowing cost and allowed returns; persistently high rates compress that spread. Clean-energy tax-credit policy is a material swing factor for NEER's return profile. Reported quarterly earnings are lumpy and inflated by NEER mark-to-market items (net margins swinging from 13% to 33%), making underlying earnings quality hard to isolate. At ~22x trailing earnings the stock prices in continued premium growth, so any disappointment in the load-growth thesis or a rate-base slowdown could compress the multiple toward the regulated-utility average.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Revenue quality is high and recurring, anchored by regulated Florida operations, with quarterly revenue of $6.2-8.0B and ~7% YoY growth in Q1 2026. Gross margins are strong (57-64%) and operating margins healthy (23-36%), but both fluctuate with NEER's contribution and mark-to-market items; the swing in net margin from 13% to 33% across recent quarters signals earnings lumpiness rather than a clean trend. Operating cash flow is solid (~$2.5-4.0B per quarter) but free cash flow is minimal to negative because capex runs $2.2-3.2B quarterly and is climbing. The balance sheet is heavily levered: ~$104B total debt against ~$55B equity (D/E ~1.9x), with a weak current ratio (~0.54) typical of utilities but notable given the debt load. Interest coverage of ~2-2.4x is the clearest weak spot. Reported ROE has improved to ~15% and ROIC sits near 5%, consistent with a regulated utility earning close to its allowed return. There is no evidence of buybacks; growth is debt-funded (financing inflows of $7.7B in Q1 2026) alongside a ~2.86% dividend. Debt appears manageable in a stable-rate environment but is a genuine vulnerability if rates rise or cash flows disappoint.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Fairly Valued</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>At $87.23 the stock trades at ~22.1x trailing and ~19.8x forward earnings, ~3.3x book, and ~20.9x EV/EBITDA. These are premium multiples versus a typical regulated electric utility, which the market justifies by NEE's renewable growth platform and data-center demand exposure. Relative to its own 52-week range ($69-$99), the stock sits in the upper-middle, off its highs but not cheap. The premium is defensible given the dual business model and growth optionality, but it is not a bargain: a PEG near 1.9x and thin/negative free cash flow mean investors are paying up for growth contingent on sustained load growth and favorable financing conditions. Balance-sheet leverage and thin interest coverage offset the growth premium, leaving risk/reward balanced rather than mispriced in either direction, which supports a Fairly Valued rating. The modest price decline since the prior analysis does not change this conclusion.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>NextEra has one of the strongest competitive positions in the sector. FPL is a regulated monopoly with effectively no direct competition, high switching costs (customers cannot choose their utility), and regulated pricing power via the rate-setting process. NEER is the largest renewable and storage developer in North America, providing scale advantages in equipment procurement, interconnection queues, tax-equity financing, and development expertise that smaller players struggle to replicate. Its combined nuclear, wind, solar, and storage fleet offers a low marginal-cost, low-carbon position. The moat's main constraints are that allowed regulated returns are set by regulators (capping upside and exposing NEE to political/regulatory shifts) and renewable returns depend on policy support such as tax credits. Overall the moat is wide and durable within the regulated segment and scale-driven in renewables, though not immune to regulatory and policy risk.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>The structural setup is favorable: US electricity demand is inflecting higher after decades of stagnation, driven by AI/data centers, electrification, and reshoring, supporting a sustained rate-base and generation-capex cycle where NEE is best positioned. Over five years the base case is high-single-digit earnings and dividend growth if load growth and capex plans proceed. The primary headwinds are interest rates (the model depends on an accretive spread over allowed returns), clean-energy tax-credit policy risk, and sector-wide regulatory pressure on allowed returns. Execution risk on a massive, debt-funded capex program is real. On balance the growth runway is strong and multi-year but capital- and policy-dependent, which tempers the outlook from exceptional to strong-but-conditional.</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NextEra is a high-quality regulated utility with a best-in-class renewable growth engine, positioned to benefit from a genuine secular increase in electricity demand. The bull thesis rests on sustained load growth fueling a long rate-base and renewable-development cycle, compounding earnings and dividends at attractive rates with defensive, low-beta characteristics. The counterweight is a heavily leveraged balance sheet (D/E ~1.9x, interest coverage ~2x, negative free cash flow at peak capex) that makes the growth story sensitive to interest rates, financing access, and tax-credit policy. Valuation is a fair-value premium to peers, so the market already pays for the growth optionality and the stock is neither a clear bargain nor obviously overpriced. This is best viewed as a core defensive holding for investors who believe in the electricity-demand supercycle and can tolerate financing/policy sensitivity, rather than a deep-value or high-conviction outperformance idea at current levels.</t>
+        </is>
+      </c>
+      <c r="M43" s="11" t="n">
+        <v>62</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Confidence is supported by clear, consistent financial data showing a durable regulated business, strong margins, and a credible structural demand tailwind, and it is unchanged from the prior analysis because nothing material has shifted. It is reduced by several factors: reported earnings are lumpy and inflated by NEER mark-to-market items, making underlying earnings quality hard to isolate; the news flow this week is largely generic, peer-focused, or non-fundamental; and the thesis hinges on external variables (interest rates, tax-credit policy) outside the data provided. Thin interest coverage and negative free cash flow add genuine, quantifiable risk that caps confidence.</t>
+        </is>
+      </c>
+      <c r="O43" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="P43" s="11" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Meta remains an exceptionally profitable advertising franchise with a reaccelerated revenue trajectory (Q1 2026 revenue up ~33% YoY) and stable operating margins in the 40-41% range. The core Family of Apps continues to throw off enormous operating cash flow (~$32B in Q1 2026), but that cash is increasingly consumed by an AI infrastructure buildout, with capex running ~$18-21B per quarter and free cash flow margins settling into the low-20s%. The stock trades at ~24x trailing and ~18x forward earnings, and now sits ~17% below its 52-week high of $796 (price $664 vs prior $630 reference), reflecting continued investor skepticism about AI capex payback rather than any deterioration in the underlying numbers. Since the prior analysis one week ago, nothing has changed in the fundamentals; the news flow simply intensifies the same debate — AI capex return-on-investment versus franchise quality. A reported ~$2B AI deal rollback and third-party survey data on ad-share competition (AppLovin) are new but small-magnitude items. Debt has continued climbing (~$87B), extending the notable 2025 shift from self-funding to debt-financed capex. On balance, this is still one of the highest-return, most cash-generative businesses available, but the central uncertainty — whether escalating capital intensity permanently resets its return profile — is unchanged and unresolved.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Little material has changed versus the July 7 analysis; the intervening week is dominated by narrative and sentiment rather than new fundamental data. The genuinely new, but individually modest, items: (1) A reported ~$2B 'Manus' AI deal rollback, which if accurate signals execution friction in Meta's external AI/compute ambitions and is a minor negative on capital-allocation discipline, though the dollar magnitude is small relative to Meta's ~$80B annualized capex. (2) Third-party survey evidence (Jefferies via AppLovin) suggesting AppLovin is gaining e-commerce ad share — worth monitoring as an incremental competitive datapoint, but not yet visible in Meta's own reaccelerating revenue. (3) Continued framing of 'Meta Compute' as a potential sovereign-scale, self-built infrastructure play that could reduce reliance on external providers and improve long-term unit economics — this remains speculative optionality, not realized. (4) Broader macro/industry commentary flagging an AI-spending 'speed bump' and a large tech-sector AI borrowing wave, reinforcing (not newly introducing) the debt/return risk already identified. Importantly, no new financial results, guidance, or regulatory rulings appeared, so the thesis baseline is intact.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Meta owns a portfolio of dominant social and messaging platforms serving billions of users, generating durable network effects and substantial pricing power in digital advertising. Revenue reaccelerated to ~33% YoY in Q1 2026 while gross margins held above 81% and operating margins near 40%, demonstrating that AI-driven targeting and engagement gains are converting into real, monetizable growth rather than just cost. Returns on capital remain elite (ROE ~29%, ROIC ~23-26%), evidence of historically high-quality capital deployment. If the current AI capex improves ad relevance, expands new surfaces (Reels, business messaging, Meta AI assistant), and matures into internally-built 'Meta Compute' that lowers infrastructure cost per unit, the growth runway and moat both widen. At ~18x forward earnings with a PEG below 1, the valuation is undemanding for a franchise compounding earnings at double-digit-to-30%+ rates. Optionality in wearables (Ray-Ban/Oakley Meta glasses, neural band) and potential external compute monetization provides additional upside not embedded in current estimates.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>The AI capex cycle is the dominant, unresolved risk: capex has escalated to ~$18-21B per quarter, free cash flow margins have compressed into the low-20s%, and total debt has nearly doubled to ~$87B, marking a structural departure from Meta's historically self-funded model. If these investments fail to earn adequate returns, ROIC erodes and the free-cash-flow profile underpinning the multiple deteriorates — the recent reported ~$2B deal rollback is a small but real reminder that execution can slip. Industry-wide signs of an AI-spending 'speed bump' and a broad tech borrowing wave raise the possibility of an arms race with uncertain payback. Reality Labs remains a persistent large loss center. Revenue is heavily concentrated in advertising, exposing Meta to ad-market cyclicality, privacy/platform changes, and emerging share competition (e.g., AppLovin in e-commerce ads). Regulatory and legal overhangs (youth-safety litigation, India and EU scrutiny) remain material and unquantifiable. The Q3 2025 net-income collapse to $2.7B against $20.5B operating income is a reminder that large non-operating charges can surface unpredictably.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Financial health is strong but the capital-intensity trend continues to be the key watch item. Revenue quality is high and growing, dominated by recurring advertising demand across billions of users; Q1 2026 revenue of ~$56B was up ~33% YoY (the sequential -6% QoQ reflects normal Q4-to-Q1 seasonality, not weakness). Margins are exceptional and stable: gross margin ~82%, operating margin ~40-41% across quarters. Operating cash flow is very strong (~$32B in Q1 2026), but capex consumes the bulk of it, leaving FCF margins in the low-20s%. The balance sheet remains solid — current ratio ~2.3, interest coverage above 60x — but total debt has climbed to ~$87B (debt-to-equity ~0.36, up from ~0.27 a year prior) as Meta taps debt markets to fund infrastructure. Return on capital remains high (ROIC ~23-26%, ROE ~28-29%). Net income shows quarter-to-quarter volatility from apparent one-time items (Q3 2025 anomaly; Q1 2026 net margin of ~47.5% appears elevated by a favorable non-operating/tax item and should not be extrapolated). Capital allocation historically favored buybacks and a token dividend (~0.33% yield); the debt-funded capex pivot is the defining recent change and, while manageable given cash flow, warrants monitoring.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Fairly Valued</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>At ~24x trailing and ~18x forward earnings with a PEG near 0.87, Meta screens as reasonably priced for a business growing revenue ~30% YoY with 40% operating margins and mid-20s% ROIC. The forward multiple is modest relative to the earnings growth trajectory and below where a franchise of this quality has often traded. EV/EBITDA of ~14.7x is not demanding for the quality. Two caveats temper the case for outright cheapness: reported net income is distorted by one-time items in both directions (Q3 2025 depressed, Q1 2026 elevated), so trailing multiples should be read with care; and forward estimates embed continued strong ad growth and margin stability that rising capex, a possible AI-spend slowdown, and regulatory risk could challenge. The price at ~$664 is ~17% below the 52-week high, removing some froth but not offering a deep margin of safety. Net: fairly valued — the multiple is defensible and arguably attractive if AI capex earns adequate returns and margins hold, but not cheap enough to be a clear bargain given rising capital intensity and legal overhangs.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Meta possesses one of the strongest moats in technology: network effects across a family of apps used by billions, high switching costs embedded in social graphs and messaging, and a data/scale advantage powering superior ad targeting. The sustained ~82% gross margins and ~40% operating margins are direct financial evidence of that moat's strength and pricing power. It competes primarily against Alphabet in a duopoly-like structure for online ad budgets, with TikTok as the principal disruptor for attention and short-form video, and now incremental niche pressure from performance-ad platforms like AppLovin in e-commerce — worth watching but not yet material to Meta's reaccelerating revenue. Emerging AI capabilities could deepen the moat by improving engagement and ad ROI, and internally-built compute could reinforce cost advantages. Threats remain shifting user attention (younger demographics), platform regulation, and privacy restrictions on targeting. The competitive position is dominant and durable in its core, though not immune to attention competition and regulatory constraint.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Over five years, growth drivers include continued ad share gains via AI-improved targeting and recommendation, new ad surfaces (Reels, business messaging, Meta AI), international monetization, and optionality in wearables and potential compute monetization. Industry tailwinds favor the ongoing shift of ad dollars to digital, AI-enhanced performance advertising. The principal headwinds: the sustainability of returns on the massive AI capex (now amplified by industry signs of a spending 'speed bump' and rising debt across the sector), mounting regulatory and legal pressure (youth-safety litigation, India/EU scrutiny), persistent Reality Labs losses, and competition for user attention. The central long-term uncertainty is unchanged — whether Meta's elevated capital intensity is a temporary investment phase that expands the moat and TAM, or a structural reset that lowers incremental returns on capital. Given the strength of the core franchise and its cash generation, the outlook remains favorable but with wider dispersion of outcomes than in prior years.</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Meta is a dominant, exceptionally profitable advertising franchise trading at a reasonable ~18x forward earnings while reaccelerating revenue to ~30%+ YoY growth with 40% operating margins and ~25% ROIC. The core thesis is that the durable moat and pricing power continue to compound earnings, and that current AI capex — while depressing free cash flow and driving new debt issuance — ultimately reinforces the ad engine and opens new surfaces. The primary risk is that the capital-intensity ramp fails to earn adequate returns, permanently converting a high-return, asset-light compounder into a capital-heavy business with a compressed FCF profile, compounded by escalating regulatory and legal liabilities. Nothing in the past week materially altered this balance: the news is incrementally negative on capex/competition sentiment but small in magnitude, and the fundamentals are unchanged. The balance sheet and cash generation provide ample cushion, and valuation offers a reasonable entry point but not a large margin of safety. This is a high-quality holding whose multi-year returns hinge on capex discipline and regulatory outcomes; position sizing should reflect elevated but well-compensated risk.</t>
+        </is>
+      </c>
+      <c r="M44" s="11" t="n">
+        <v>72</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Confidence is supported by clear, consistent financial evidence of a dominant franchise: high stable margins, strong ROIC/ROE, reaccelerating revenue, and a defensible valuation. It is held down by the same unresolved unknowns as before, none of which the past week clarified: the payback and trajectory of AI capex are genuinely uncertain; debt is rising quickly; net income is distorted by one-time items in multiple quarters (Q3 2025 downward, Q1 2026 upward), limiting precision on true earnings power; and legal/regulatory exposure remains unquantifiable. New items this week (the ~$2B deal rollback, AppLovin ad-share survey, AI-spend 'speed bump' commentary) are individually small and do not change the thesis, so I am holding confidence steady rather than revising. The absence of Reality Labs segment detail and forward capex guidance continues to constrain precision.</t>
+        </is>
+      </c>
+      <c r="O44" s="11" t="n">
+        <v>88</v>
+      </c>
+      <c r="P44" s="11" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PLD</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Prologis remains the dominant global industrial/logistics REIT with a highly cash-generative model: gross margins near 74%, operating margins in the 36-40% range, and free cash flow conversion consistently above 50% of revenue. Revenue grew steadily to ~$2.30B in Q1 2026, up ~7.4% year-over-year. GAAP net income remains volatile and inflated by non-operating gains and promote/fair-value income (Q4 2025 net margin of 62%, Q1 2026 of 43%), so recurring operating margins are the better guide to underlying earnings power. The balance sheet carries ~$34.7B total debt against ~$53.5B equity (D/E ~0.65) with interest coverage around 5x, adequate for an investment-grade REIT. The most consequential change since the prior analysis is that the reported acquisition has crystallized into a concrete, contested situation: PLD is publicly pursuing a ~$16.9B (~£12.6-13B) bid for SEGRO, which SEGRO's board has now rejected. The stock trades near its 52-week high ($139 vs. $150 high) on rich headline multiples. Fundamentals are healthy and the franchise is durable, but the valuation continues to leave a thin margin of safety, now compounded by a live, potentially hostile M&amp;A process with attendant financing and overpayment risk.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>The material change is the escalation and public contestation of the SEGRO acquisition. In the prior analysis this was a reported ~£12.6B pursuit; it has now become an active, disclosed situation in which Prologis is soliciting SEGRO shareholder support to force talks, while SEGRO's board has publicly rejected the proposal and is defending its standalone value (touting a ~£4.1B development pipeline). The bid is now sized at roughly $16.9B. This matters for three reasons: (1) a rejected/unsolicited posture raises the odds of a higher price or a protracted, distracting fight, increasing overpayment and integration risk; (2) it confirms management's strategic intent to expand European logistics scale and data-center exposure, a real capital-allocation pivot rather than rumor; (3) a debt-funded deal of this size would meaningfully alter leverage against an already ~$34.7B debt load and ~5x interest coverage. A board appointment adding governance experience was also disclosed but is minor. Operationally nothing changed materially: Q1 2026 continued the same steady sequential revenue growth and ~$1.29B operating cash flow trend. The stock has drifted modestly lower (from ~$142 to ~$139) but remains near highs.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Prologis owns an irreplaceable, globally diversified portfolio of logistics assets concentrated in supply-constrained infill markets, conferring durable pricing power as leases mark to higher market rents. Gross margins near 74% and FCF margins above 50% evidence a capital-efficient, highly cash-generative model that funds both the dividend and reinvestment. Steady ~7.4% YoY revenue growth suggests continued rent escalation and portfolio expansion despite a mature cycle. The owned-and-managed platform and co-investment ventures generate recurring fee and promote income while limiting balance-sheet capital intensity, supporting returns. The SEGRO pursuit, if disciplined, would add European scale, geographic diversification, and — importantly — data-center optionality tied to AI/cloud demand, an adjacency the market rewards with higher multiples; PLD's land bank and power-access positioning is a genuine differentiator. If the deal is abandoned rather than overpaid for, PLD retains a strong standalone franchise; if consummated accretively, it could re-rate toward infrastructure-like multiples.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>The stock trades at demanding multiples (P/B ~2.4x, EV/EBITDA ~26x) with the price near its 52-week high, leaving little margin of safety if industrial rent growth decelerates from post-pandemic peaks or new supply lifts vacancies. Recurring returns on capital are modest (ROIC ~4.7%, ROE ~7%), so the premium rests heavily on continued rent growth and cap-rate stability rather than current returns. GAAP net income is flattered by non-operating gains and promote/fair-value income, risking overstatement of the earnings power investors are paying for. The now-public, rejected SEGRO bid is a specific new risk: an unsolicited/contested process can force a higher price, incur substantial deal costs, distract management, and — if debt-funded at ~$16.9B — pressure leverage against ~$34.7B existing debt and only ~5x interest coverage. Beta of 1.34 signals above-average sensitivity to rate and macro shocks, a key swing factor for REIT valuations. The data-center ambition is capital-intensive, power-constrained, and increasingly competitive, so execution is far from guaranteed.</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Revenue quality is high and recurring, anchored by long-duration logistics leases; revenue rose steadily from $2.14B (Q1 2025) to $2.30B (Q1 2026). Gross margins are stable at ~74% and operating margins in the 36-40% band. Cash generation is a standout: operating cash flow of $1.16-1.45B per quarter with FCF conversion above 50%. Net income margins in Q4 2025 (62%) and Q1 2026 (43%) are inflated by non-operating gains and should not be extrapolated; recurring operating margins are the cleaner guide. The balance sheet holds ~$34.7B total debt against ~$53.5B equity (D/E ~0.65) with interest coverage around 5x — adequate for a large investment-grade REIT but not conservative. Financing outflows (-$1.16B in Q1 2026, -$1.22B in Q4 2025) reflect dividends and debt activity; the ~3.05% dividend yield is consistent with a mature REIT. Share count is stable (~932M), with no evidence of meaningful dilution or buybacks. ROIC (~4.7%) and ROE (~7%) are typical for the asset class but unremarkable relative to valuation. A large debt-funded SEGRO deal is the key forward risk to leverage and coverage and warrants close monitoring.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Overvalued</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>For a REIT, FFO/AFFO and NAV matter more than GAAP P/E, and the provided forward P/E (~41x) and PEG (~110) are distorted by REIT accounting and lumpy gains, so they should not be read literally. Even adjusting for that, the framing multiples — EV/EBITDA ~26x, P/B ~2.4x, price near the 52-week high — indicate a premium valuation that prices in continued healthy rent growth plus successful expansion, including the data-center narrative. Given modest recurring returns (ROIC ~4.7%, ROE ~7%), that premium reflects franchise quality and growth optionality rather than current cash returns on capital. The stock has pulled back only marginally from ~$142 to ~$139 and sits well above its 52-week low ($103), so the bullish narrative and the strategic pivot are already substantially credited. With a contested, potentially value-destructive M&amp;A situation now live and no FFO/NAV data provided to independently confirm intrinsic value, the balance of evidence points to a full-to-rich valuation with limited downside protection. Rating held at Overvalued.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Prologis has one of the strongest moats in real estate: irreplaceable scale in supply-constrained, high-demand logistics locations near major consumption centers. Its owned-and-managed platform and co-investment ventures create scale advantages, superior capital-raising capacity, and recurring fee income that smaller peers cannot match. Switching costs are meaningful for large logistics tenants given location-critical distribution networks, supporting renewal pricing power. The land bank and development capability provide a pipeline advantage, and power/energy positioning is a credible differentiator for data-center expansion. Competitive threats include new industrial supply in select markets, rising cap rates, and well-capitalized data-center competitors. The SEGRO episode is a reminder that scaling in Europe is contested — the target's board is resisting and touting its own pipeline — which underscores that PLD's advantages, while durable, do not guarantee frictionless expansion.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Structural tailwinds — e-commerce penetration, supply-chain reconfiguration/nearshoring, and inventory resilience — support long-term logistics demand, while constrained infill supply underpins rent growth. The data-center avenue offers a credible secondary growth engine tied to AI/cloud demand and could lift growth and returns if executed with capital discipline. Over five years the main challenges are interest-rate sensitivity (the dominant driver of REIT valuations and cap rates), cyclical moderation in industrial rent growth from peak levels, and the capital intensity and competition of data centers. The SEGRO pursuit adds a nearer-term fork: an accretive deal adds diversification and optionality, but a contested/overpriced deal or a costly failed bid would impair returns and management focus. On balance the growth runway is above the REIT average, but recurring returns on capital are modest and much of the optimism is already reflected in price.</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Prologis is a best-in-class, wide-moat logistics REIT with stable ~74% gross margins, strong FCF conversion, and a manageable investment-grade balance sheet, now actively pursuing a strategically attractive but capital-intensive European/data-center expansion via SEGRO. The fundamentals remain sound and the franchise durable, but the valuation is demanding on the provided metrics while recurring returns on capital are only modest (ROIC ~4.7%, ROE ~7%), and GAAP net income is inflated by non-operating gains. The key change since the last review is that the SEGRO situation has turned public and contested — SEGRO's board has rejected the ~$16.9B bid — which raises the odds of a higher price, deal costs, distraction, or added leverage, all against a backdrop where the stock still trades near its 52-week high. The risk/reward continues to favor watchful patience over aggressive accumulation: long-term holders own a high-quality compounder, but at current prices with a live M&amp;A overhang, the margin of safety is thin. A more attractive entry point, clearer accretion evidence, or an abandoned bid would each strengthen the case.</t>
+        </is>
+      </c>
+      <c r="M45" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Confidence is supported by clear, consistent operating data (stable gross/operating margins, steady revenue growth, strong cash flow) and a well-understood, high-quality business model, and is modestly increased by the SEGRO situation now being concrete and disclosed rather than rumored. It is reduced by the absence of REIT-specific metrics (FFO/AFFO, NAV, same-store NOI, occupancy, lease mark-to-market) essential for precise REIT valuation, by GAAP net income being distorted by non-recurring gains, and by the SEGRO deal outcome being genuinely uncertain — a contested bid could end in overpayment, a failed costly process, or abandonment, each with different implications. Missing peer financials also limit direct competitive benchmarking.</t>
+        </is>
+      </c>
+      <c r="O45" s="11" t="n">
+        <v>85</v>
+      </c>
+      <c r="P45" s="11" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SHW</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Sherwin-Williams remains a high-quality, moaty paint and coatings franchise anchored by its company-owned Paint Stores Group distribution network. The financial data are unchanged from the prior writeup: the business generates ~$23B annualized revenue with stable gross margins around 48-49%, mid-teens full-year operating margins (seasonally peaking near 18% in Q2/Q3), and excellent capital returns (ROIC ~17%, ROE ~56-59% inflated by a thin equity base). Q1 2026 confirmed a slow-growth but resilient posture, with ~6.8% YoY revenue growth and ~7.5% EPS growth against a soft housing/coatings backdrop. Cash generation is strong and seasonal, with a near-breakeven Q1 FCF that is normal, not a red flag. The balance sheet carries meaningful leverage (debt/equity ~3x, total debt ~$13.8B) but interest coverage near 8x keeps debt sustainable. The stock now trades at ~$336, down modestly from the ~$344 in the prior analysis, at ~32x trailing and ~25x forward earnings. Recent news is entirely macro-driven noise (broad market sell-offs) with no company-specific fundamental change. The debate continues to center on valuation rather than business quality.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Nothing material has changed since the July 7 analysis. The price has drifted down slightly (~$344 to ~$336), pulling forward P/E from ~26x to ~25x, but this is a modest move within the existing 52-week range ($290-$380) and does not alter the thesis. The recent news flow is dominated by macro sell-off coverage (Dow dropping, Nasdaq flat, SHW trading down alongside UFP and Vulcan) that news summaries themselves attribute to broad market fears rather than company-specific issues. Two items merit a passing note without being material: commentary referencing a cost-cutting narrative and a new payment partnership (operational focus but unquantified), and a possible index removal mention (which could pressure passive flows short-term but is not a fundamental event). No new earnings, guidance, or segment data has been provided, so the underlying financials remain the Q1 2026 set already analyzed. In short, this is a continuation, not an inflection.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>SHW owns and controls its Paint Stores distribution, a structural advantage peers reliant on third-party retail lack, generating direct professional-contractor relationships, pricing power, and high switching costs for pros dependent on consistent availability, color-matching, and service. Gross margins have held firmly at 48-49% through a soft demand period, evidencing durable pricing power and disciplined input-cost management. ROIC near 17% on a low-capital-intensity model shows efficient capital compounding, and strong seasonal free cash flow funds a modest dividend plus ongoing buybacks (financing outflows and thin equity are consistent with continued repurchases). Much of the architectural repaint/maintenance business is non-discretionary and recurring, providing a defensive revenue base. If housing turnover and remodel activity recover from cyclically depressed levels, incremental volume would flow through with high operating leverage. Over 3-5 years, contractor share gains, store-count expansion, pricing, and buyback-driven EPS accretion should support mid-single-digit revenue growth plus high-single-digit EPS growth even before any cyclical upturn.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Valuation is the central risk: ~32x trailing and ~25x forward earnings for a company growing revenue mid-single digits and EPS high-single digits (PEG ~2.6) offers minimal margin of safety, so any growth or margin disappointment could drive a meaningful de-rating. Demand is tied to housing turnover, new construction, and remodeling, all soft, and a prolonged weak housing cycle could keep volumes stagnant. Leverage is elevated (debt/equity ~3x, ~$13.8B total debt) and interest expense has crept up to ~$132M/quarter, pressuring net income; coverage of ~7.8-8.2x is adequate but not comfortable if EBITDA softens. The Consumer Brands segment depends on retail partners such as Lowe's, exposing it to shelf/channel shifts. Raw-material (petrochemical/pigment) cost inflation could compress the currently strong gross margins. The headline ROE of ~56-59% is partly an artifact of a leveraged, buyback-thinned equity base, which magnifies downside if earnings decline. A possible index removal could add short-term passive-flow pressure.</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Revenue quality is high and recurring, anchored by architectural repaint and professional demand, with normal seasonality (Q1 weakest, Q2/Q3 strongest). Gross margins are stable and strong (48-49%), and operating margins run mid-teens on a full-year basis, reaching ~18% in peak quarters. Cash generation is robust: FY2025 quarterly operating cash flow was strongly positive with FCF of ~$1.1B in Q3 2025, while Q1 2026 FCF was near-breakeven (~$0.8M) which is seasonally typical and not alarming. The balance sheet is leveraged: total debt ~$13.8B against thin equity (~$4.4B) yields debt/equity ~3.1x and price-to-book ~19x. Interest coverage of ~7.8-8.2x and consistent cash flow keep debt sustainable but leave limited cushion. Capital allocation favors buybacks and a modest ~0.9% dividend; financing outflows and the shrinking equity base indicate ongoing repurchases (share count near 246.6M). ROIC of ~17% is excellent and should be read as the true measure of quality, with the elevated ROE understood as leverage-and-buyback-magnified rather than a clean profitability signal.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Overvalued</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>SHW trades at ~32x trailing and ~25x forward earnings, EV/EBITDA ~21x, and price-to-sales ~3.5x. For a franchise of this quality these are not historically unusual multiples, as SHW has long commanded a premium for its owned-distribution moat and ~17% ROIC, but the multiple is being paid against decelerating mid-single-digit revenue growth and a soft demand backdrop, producing a PEG near 2.6. The recent price decline to ~$336 marginally improved the entry point versus the prior ~$344, nudging forward P/E from ~26x to ~25x, but this is not enough to change the assessment. The stock sits roughly in the middle-to-lower half of its $290-$380 range. The premium is justified by the moat and returns on capital, but insufficiently by near-term growth, leaving little embedded margin of safety and asymmetric downside risk if a cyclical recovery is delayed or margins slip. On balance this remains full-to-slightly-rich, warranting an Overvalued rating with the caveat that quality could support the multiple if growth reaccelerates.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>SHW holds one of the stronger moats in specialty materials, primarily through its vertically integrated, company-owned Paint Stores network that gives direct control of distribution to professional painters, a channel advantage peers largely lack. This creates real switching costs and stickiness with contractors who prioritize consistent color-matching, availability, and service, and supports demonstrable pricing power reflected in stable ~48-49% gross margins through soft demand. The Sherwin-Williams brand carries strong recognition in both professional and DIY channels. The industry is a consolidated oligopoly with generally rational pricing behavior. Threats include reliance on third-party retail (e.g., Lowe's) for the Consumer Brands segment, exposing it to shelf/channel risk, and input-cost cyclicality, but the core professional franchise remains well-insulated. Overall a wide, durable moat.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Over five years, SHW should grow modestly above GDP driven by recurring repaint/maintenance demand, professional contractor share gains, store-count expansion, and pricing power, with EPS growth augmented by buybacks. Tailwinds include the non-discretionary nature of much of its architectural business, an aging housing stock requiring repainting, and continued industry consolidation. Headwinds include sensitivity to housing turnover and new-construction cycles, raw-material cost volatility, elevated leverage that limits flexibility in a downturn, and rising interest costs. The near term is likely to remain soft given the housing environment, but the structural franchise is intact and positioned to benefit disproportionately when the remodel/housing cycle turns. Expect steady, unspectacular compounding rather than rapid growth.</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>SHW is a best-in-class, moaty compounder whose owned-distribution model, pricing power, and ~17% ROIC make it a high-quality long-term holding. The fundamentals are sound: stable gross margins, strong seasonal cash generation, sustainable if elevated leverage, and shareholder-friendly capital return. The constraint remains price: at ~25x forward earnings against mid-single-digit revenue growth in a soft demand environment, the valuation prices in a recovery that has not yet materialized and offers minimal downside protection. The recent macro-driven pullback to ~$336 has marginally improved the entry point but not enough to shift the posture. The most sensible stance is to admire the business but wait for a more attractive entry, a further pullback toward the lower end of the range or evidence of housing/coatings demand reacceleration. The thesis remains 'great company, full price,' favoring patience over immediate action.</t>
+        </is>
+      </c>
+      <c r="M46" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Confidence is supported by six quarters of consistent, high-quality financial data showing stable margins, strong returns on capital, and sustainable debt service, plus a well-understood competitive model that has not changed. It is reduced by the absence of full-year historical multiple ranges, missing Q4 2024 data and YoY comparators for several quarters, no peer financials for direct competitive benchmarking, unquantified references to cost-cutting and a possible index removal in the news, and the inherent uncertainty of the housing/coatings demand cycle. The valuation judgment carries more subjectivity than the financial-health assessment, and nothing this period materially reduced or increased the uncertainty.</t>
+        </is>
+      </c>
+      <c r="O46" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="P46" s="11" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Disney trades at $95.88, near its 52-week low of $92.19 and well below its high of $123.40, at a trailing P/E of ~15.3 and forward P/E of ~12.8. The company operates three segments -- Entertainment (studios and streaming), Sports (ESPN), and Experiences (parks, resorts, cruises) -- underpinned by one of the most valuable IP libraries in media. Recent quarterly data show revenue in the $22-26B range with operating margins holding in the 11.6%-15.4% band, indicating a fundamentally profitable business despite cyclical noise. Net income is volatile quarter to quarter (a $5.26B spike in Q2 2025, likely one-off items, versus $1.3B in Q3 2025), and free cash flow swings sharply, including a negative FCF quarter in Q4 2025 driven by elevated capex. The balance sheet is moderate with debt-to-equity around 0.44 and interest coverage near 8x. Key strategic questions center on the streaming business model (a potential free ad-supported tier), continued heavy investment in Experiences, and intensifying competition from well-capitalized platform rivals. Returns on capital are modest (ROIC ~7.4%, ROE ~10%), suggesting the business earns above its cost of debt but has not yet demonstrated the high-return profile of its best historical years. Overall this is a high-quality franchise trading at a below-average multiple, with the debate being whether streaming economics and parks demand can lift returns back toward historical levels.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>No previous analysis exists, so this is a baseline writeup. The most material recent item is the reported consideration of a free ad-supported Disney+ tier, which represents a genuine strategic pivot: it could materially expand reach and advertising monetization but risks cannibalizing higher-margin subscription revenue -- the outcome depends on execution that cannot yet be judged from the data. Competitively, evidence points to Netflix pushing into live TV, which directly encroaches on both Disney's streaming and its ESPN/traditional-TV franchises. On fundamentals, the most notable data point is the sharp EPS deterioration year-over-year in Q1 2026 (-29.8%) alongside modest revenue growth (+6.5% YoY), showing that top-line recovery is not yet translating into earnings leverage. FCF also whipsawed from -$2.28B in Q4 2025 (capex of $3.0B) back to +$4.94B in Q1 2026, underscoring lumpy cash generation tied to the parks investment cycle.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Disney owns arguably the deepest portfolio of durable, monetizable IP in entertainment (Marvel, Pixar, Lucasfilm, Disney animation, National Geographic, ESPN), which supports multiple reinforcing revenue streams -- theatrical, streaming, licensing/merchandise, and physical Experiences. The Experiences segment provides a structurally advantaged, hard-to-replicate asset base (parks, cruises, resorts) with real pricing power and recurring demand tied to brand affinity. If the streaming business reaches sustainable profitability and a free ad-tier successfully expands the funnel and advertising revenue without heavily cannibalizing subscriptions, margin and returns could re-rate meaningfully. The forward P/E near 12.8 versus a trailing 15.3 implies the market expects earnings growth, and rising earnings estimates plus the stock trading near 52-week lows create asymmetric upside if operational execution improves. Interest coverage near 8x and moderate leverage give the company room to keep investing while returning cash. Licensing partnerships (e.g., branded consumer products) continue to generate high-margin royalty income off the existing IP with minimal incremental capital.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Returns on capital are unremarkable (ROIC ~7.4%, ROE ~10%), suggesting the business is not currently a high-compounder and that heavy Experiences capex may be diluting returns. Earnings are volatile and the -29.8% YoY EPS decline in Q1 2026 shows recovery is fragile. Streaming remains a competitive battleground against far larger platform players; a free ad-tier is an admission that subscriber growth and pricing may be maturing, and it risks cannibalizing the most profitable subscription base. The Sports/ESPN franchise faces secular cord-cutting pressure and rising rights costs, while Netflix's move into live TV threatens a formerly protected niche. Experiences and merchandise revenue are exposed to consumer discretionary weakness, which would hit the segment carrying the best margins. FCF is lumpy and turned negative in one recent quarter, and the multi-front investment across streaming and parks limits financial flexibility. Current ratio below 0.7 indicates thin near-term liquidity coverage, though this is normal for the business model.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Revenue is sizable and relatively stable in the $22-26B/quarter range, with Q1 2026 up 6.5% YoY. Gross margins are consistent around 36-38%, and operating margins have held roughly 11.6%-15.4%, indicating a durably profitable operating model despite quarter-to-quarter swings. Net margins are noisier (5.8% to 22.2%), reflecting one-off items and mix. Cash generation is real but lumpy: FCF ranged from +$4.94B (Q1 2026) to -$2.28B (Q4 2025) driven by a capex peak of $3.0B, consistent with the Experiences build cycle. The balance sheet is moderate: total debt ~$47.4B against ~$108.7B equity (D/E ~0.44), interest coverage ~8x, and cash ~$5.7B. Leverage is manageable and coverage is comfortable. Financing outflows in most quarters (e.g., -$4.1B in Q1 2026) suggest debt paydown and/or shareholder returns; the dividend yield is modest at ~1.56%. Returns on capital are the weakest link: ROIC ~7.4% and ROE ~10% are adequate but below what the brand quality might imply, indicating capital intensity is weighing on efficiency. Overall financial health is solid and sustainable, but not exceptional on a returns basis.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Fairly Valued</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>At a trailing P/E of ~15.3, forward P/E ~12.8, EV/EBITDA of ~10.9, and price-to-book of ~1.54, Disney trades at a discount to the premium multiples it commanded in prior years, reflecting compressed growth expectations and modest returns on capital. The forward multiple below the trailing multiple signals the market prices in earnings growth. On EV/EBITDA of ~10.9, the valuation is reasonable for a diversified media/experiences business with irreplaceable assets. However, with ROIC only ~7.4% and lumpy FCF, the discount is arguably justified rather than a clear mispricing -- the stock is cheap relative to its own history but not obviously cheap relative to current fundamentals. A re-rating requires demonstrated margin and returns improvement, particularly in streaming. Balancing the below-historical multiple against unproven returns recovery, Fairly Valued is the appropriate rating, with genuine upside optionality if execution improves.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Disney's moat rests on its IP library and brand, which are extremely difficult to replicate and drive cross-monetization across film, streaming, licensing, and physical Experiences. The Experiences segment (parks, cruises, resorts) is a particularly strong moat -- capital-intensive, geographically anchored, and tied to emotional brand loyalty, giving real pricing power. Licensing generates high-margin royalties with low incremental capital. However, the competitive picture is bifurcated: in streaming, Disney faces scaled, well-funded rivals and is now reportedly contemplating a free tier, signaling pricing/growth maturation. In sports, ESPN faces secular cord-cutting and escalating rights costs, and Netflix's push into live TV erodes a historically defensible position. Compared with the listed peers (GOOGL, META), Disney lacks the platform network effects and data advantages of those firms, but it owns durable content and physical assets they cannot easily replicate. Net moat is strong in Experiences and IP, but contested and narrowing in streaming and linear/sports distribution.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Over five years, growth drivers include continued Experiences expansion (cruises, park investment), streaming monetization via advertising and potentially a free tier, and ongoing IP licensing. The Experiences build-out should support revenue and, if capex normalizes, improve FCF and returns. Streaming is the swing factor: reaching sustained profitability at scale would be the biggest lever for margins and re-rating. Headwinds are significant: secular decline in linear TV and cord-cutting pressuring the Sports/legacy Entertainment cash flows, rising sports rights costs, intensifying streaming competition, and cyclical exposure of the discretionary Experiences and merchandise businesses to consumer spending. The most probable path is steady mid-single-digit revenue growth with gradual margin recovery, but execution risk in streaming and content hit-rate variability make the trajectory uncertain. The business is not structurally declining, but neither is it positioned for exceptional growth; it is a mature franchise navigating a distribution-model transition.</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Disney is a high-quality, IP-rich franchise trading below its historical multiple after a period of earnings volatility and heavy investment. The bull thesis is that irreplaceable IP and Experiences assets, combined with improving streaming economics (including a possible advertising-led free tier), lift returns on capital from today's modest ~7% ROIC back toward levels that justify a premium multiple, generating asymmetric upside from a stock near 52-week lows with a forward P/E under 13. The bear thesis is that structural decline in linear/sports distribution, intensifying streaming competition, and consumer-discretionary exposure keep returns depressed and earnings lumpy, meaning the current discount is deserved. Given solid but unexceptional fundamentals, a fair (not cheap) valuation on current returns, and real optionality tied to streaming execution, this is a reasonable long-term holding for patient investors who believe in the durability of the IP and Experiences moat, but not a high-conviction bargain. The key monitorable is whether streaming profitability and normalized capex translate into rising ROIC and consistent FCF.</t>
+        </is>
+      </c>
+      <c r="M47" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Confidence is supported by the durability and clarity of Disney's IP/Experiences moat, a moderate and sustainable balance sheet, and a valuation cushion below historical multiples. It is tempered by significant data gaps and noise: Q4 2024 financials are entirely missing, YoY comparisons are limited, net income and FCF are highly volatile quarter to quarter, and returns on capital are modest. The streaming strategy is in flux (free-tier is only a report), and competitive pressures from scaled rivals are real but hard to quantify from the provided evidence. These uncertainties keep conviction moderate rather than high.</t>
+        </is>
+      </c>
+      <c r="O47" s="11" t="n">
+        <v>72</v>
+      </c>
+      <c r="P47" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Palantir remains a dual-market (government/defense and commercial) platform software company whose financials continue to show a rare combination of accelerating growth and rapid margin expansion. Over the trailing quarters, revenue grew from ~$884M (Q1'25) to ~$1.63B (Q1'26), with ~85% YoY growth and sequential growth of 13-19%. Profitability has inflected sharply: operating margin from ~20% to ~46%, net margin to ~53%, and FCF margin holding above 54%, with ~$892M FCF in the latest quarter against trivial capex. The balance sheet is fortress-like: ~$2.3B cash, ~$212M debt (D/E ~0.025), current ratio ~6.9, and ROIC/ROE rising to ~25%/~27%. The unchanged core tension is valuation: at ~$126 the stock trades at ~58x EV/revenue, ~142x trailing P/E, and ~60x forward P/E, pricing in years of near-flawless execution. Recent news adds a Latin America commercial win (GNP via Rackspace) but is otherwise light on quantified catalysts and includes some reputational noise around a co-founder. The stock is now ~39% below its 52-week high of $207 and near its 52-week low of $106, indicating meaningful de-rating already underway. The debate is essentially unchanged from the prior analysis: exceptional business quality against a demanding-to-excessive price.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Little has materially changed since the July 7 analysis three days prior; the financial data set is identical, so the fundamental picture is unchanged. The only incremental item is confirmation of the first Latin America commercial customer (GNP Seguros in Mexico) landed through a Rackspace partnership, which extends the prior GNP narrative into a channel-partner distribution model and reinforces the international land-and-expand story—directionally positive but with no disclosed contract economics. The stock has drifted lower (from ~$134 to ~$126, now ~39% off its high versus ~35% previously), tightening the observed de-rating but not changing the thesis. News on competitors (BigBear.ai, Rackspace/enterprise AI) signals a growing but increasingly contested defense/enterprise AI market. A political controversy involving co-founder Peter Thiel is reputational noise with no evident impact on contracts or fundamentals. Net: no material fundamental change; this is a continuation, not an inflection, of the prior view.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Palantir is exhibiting the rare pairing of accelerating revenue and expanding margins at scale—the hallmark of a high-incremental-margin platform with strong operating leverage (gross margin ~87% and climbing, operating margin ~46%). If AIP is becoming the connective layer for operationalizing and governing enterprise AI, the TAM is large and Palantir's differentiation in turning models into actionable, permissioned workflows could compound. The government/defense franchise is sticky, accreditation-gated, and deeply embedded in operational workflows, providing a durable high-margin base. Commercial and international expansion—now including a partner-led Latin America entry via Rackspace—opens a second growth engine that reduces government dependence and could scale distribution faster. FCF of ~$892M in a single quarter self-funds all growth with no debt reliance, giving the company full control of its destiny. If growth stays above 40% for several years while margins hold in the mid-40s%, the current multiple can be grown into, and continued acceleration would validate the premium.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>The valuation embeds near-perfection: ~58x EV/revenue and ~142x trailing earnings leave essentially no cushion for growth deceleration, competitive erosion, or margin reversion. The ~39% drawdown from the 52-week high—now trading near the 52-week low—demonstrates how violently the multiple can compress on any sentiment shift, and the stock's proximity to a repeatedly tested support level highlights fragility. Government revenue concentration exposes the company to budget cycles, procurement lumpiness, and political shifts. The commercial AI orchestration space is increasingly contested by hyperscalers (Microsoft, Google) with vast distribution and capital, plus AI-native tooling and emerging defense-AI competitors—PLTR's commercial moat is less proven than its government one. The net margin of ~53% exceeds operating margin, meaning reported profitability is flattered by non-operating items (interest income on cash, tax effects) that are less durable than core operating profit. Ongoing stock-based compensation dilution (diluted EPS $0.34 vs basic $0.36) persists with no buyback evidence. Beta ~1.56 and momentum-heavy ownership amplify volatility, and news flow remains promotional and unquantified.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Exceptionally strong and, if anything, still improving. Revenue is high-quality and accelerating: $884M (Q1'25) to $1,633M (Q1'26), ~85% YoY with 13-19% sequential growth. Margins have inflected across the board—gross ~80%→~87%, operating ~20%→~46%, net ~24%→~53%. Note that net income exceeds operating income, so the headline net margin is flattered by non-operating income (interest/investment income on the large cash balance and tax effects); the more durable operating margin trend near mid-40s% is the better gauge. FCF is robust and consistent (34-54% margins; ~$892M in Q1'26 against ~$7M capex), reflecting an asset-light model. Balance sheet is a fortress: ~$2.29B cash, ~$212M total debt, D/E ~0.025, current ratio ~6.9. Returns on capital are high and rising (ROIC ~25%, ROE ~27%, ROA ~22%). No dividend; capital allocation is conservative and self-funding. The key watch item remains dilution from share-based compensation, with no offsetting buyback evidence provided.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Overvalued</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Business quality justifies a substantial premium, but the multiples remain extreme even for a hypergrowth, high-margin software leader: ~58x EV/revenue, ~149x EV/EBITDA, ~58x price/sales, ~142x trailing P/E, and ~60x forward P/E. The modest slide since the prior writeup (price ~$134 to ~$126) has trimmed multiples slightly but not enough to change the conclusion. A forward PEG near 1.9 is not egregious if growth persists, but EV/revenue near 58x has historically been sustainable only for brief windows and typically re-rates lower as growth decelerates from hypergrowth toward maturity. The stock now sits near its 52-week low ($106) and ~39% below its high ($207), showing the market has already partly de-rated it—yet the remaining multiple still requires underwriting multiple more years of 40%+ growth with margins holding in the mid-40s%. Against the company's own elevated range and the thin downside cushion inherent in revenue multiples of this magnitude, the rating stays Overvalued for a fundamentals-driven long-term buyer, while acknowledging the business could grow into the multiple with flawless execution.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Palantir has a genuine, differentiated moat in its government/defense franchise: Gotham and mission-critical deployments carry high switching costs, security accreditations, deep operational integration, and long procurement relationships that are hard to displace—reflected in sticky, high-margin recurring revenue. In commercial AI (Foundry/AIP), the moat is emerging but less established; the value proposition of operationalizing and governing enterprise AI is compelling, and the land-and-expand pattern (now extended to Latin America via a Rackspace channel) suggests real stickiness once deployed. However, this arena is contested by hyperscalers (Microsoft, Google) with vast distribution and capital, AI-native startups, and defense-AI challengers (e.g., BigBear.ai gaining validation in adjacent screening use cases). Pricing power looks strong today given ~87% gross margins, but its durability in commercial AI is unproven versus the entrenched government position. Net: a strong, defensible moat in government; a promising but not-yet-proven moat commercially.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>The multi-year runway looks substantial if enterprise and sovereign AI deployment demand persists and Palantir remains a preferred platform for turning AI into governed, actionable workflows. Tailwinds include rising defense/intelligence software budgets, sovereign-AI initiatives, and broad enterprise AI adoption, with international/commercial diversification enlarging the TAM and reducing U.S.-government reliance. The Rackspace partnership hints at a potentially scalable channel/distribution model for commercial expansion. Key five-year risks: (1) growth deceleration as the law of large numbers sets in, compressing the premium multiple; (2) hyperscaler competition commoditizing AI orchestration; (3) political/budgetary volatility in government contracts; (4) execution risk scaling commercial sales efficiently; (5) ongoing dilution. Base case is a high-quality business with a strong secular runway, but the stock-outcome distribution is wide because valuation amplifies both upside and downside.</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Palantir is one of the highest-quality growth-software franchises available: accelerating revenue, rapidly expanding margins, prodigious free cash flow, a debt-free fortress balance sheet, and rising returns on capital—an unusually clean fundamental profile. Its government moat is durable, and its commercial AI platform is showing credible international land-and-expand traction, now with a channel-partner distribution angle via Rackspace. The fundamentals argue for owning the business; the price argues for caution. At ~58x EV/revenue and ~142x earnings, the market has already priced in years of near-flawless execution, leaving thin downside protection and high sensitivity to deceleration—as the ~39% drawdown from the 52-week high and proximity to the 52-week low illustrate. My synthesized view is unchanged from the prior analysis: a superb business at a demanding-to-excessive price. For a long-term fundamentals-driven investor, the prudent stance is to admire the quality but wait for a more favorable entry or size positions modestly, as risk/reward at current multiples still skews unfavorably despite the franchise's strength.</t>
+        </is>
+      </c>
+      <c r="M48" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Confidence is supported by the clarity and internal consistency of the financial data—growth acceleration, margin expansion, FCF generation, and balance-sheet strength are unambiguous and coherent across quarters. It is tempered by: (1) missing Q4 2024 data and limited multi-year prior-quarter context; (2) news flow that is largely promotional, single-dated, and lacks quantified deal economics; (3) the inherent difficulty of forecasting hypergrowth durability and multiple compression at these valuation levels; (4) unquantified SBC dilution and reliance on non-operating income to lift net margin; and (5) the fact that essentially nothing material changed since the prior writeup three days earlier, so this is a continuation of an existing view rather than fresh conviction. The valuation conclusion is high-conviction on multiples, but the ultimate stock outcome depends on execution I cannot fully verify from the data.</t>
+        </is>
+      </c>
+      <c r="O48" s="11" t="n">
+        <v>72</v>
+      </c>
+      <c r="P48" s="11" t="n">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
